--- a/input/ES/reg_education.xlsx
+++ b/input/ES/reg_education.xlsx
@@ -70,7 +70,7 @@
     <t>Raw generalized ordered logit regression estimates of education attainment - individuals aged 16+ exiting education. Useful for the 'Gologit predictor' file.</t>
   </si>
   <si>
-    <t>Regions: ES1 =  Noroeste , ES2 = Noreste , ES3 = Madrid , ES4 =  Centro , ES5 = Este , ES5 =  Sur , ES5 = ,  Canarias.</t>
+    <t>Regions: ES1 =  Noroeste , ES2 = Noreste , ES3 = Madrid , ES4 =  Centro , ES5 = Este , ES6=  Sur , ES7 = ,  Canarias.</t>
   </si>
   <si>
     <t>Goodnessoffit</t>
@@ -121,7 +121,7 @@
     <t>Dag</t>
   </si>
   <si>
-    <t>Dag_knot17</t>
+    <t>Dag16</t>
   </si>
   <si>
     <t>Dag_knot23</t>
@@ -199,10 +199,10 @@
     <t>Les_c3_NotEmployed_L1</t>
   </si>
   <si>
-    <t>Dnc_L1</t>
-  </si>
-  <si>
-    <t>Dnc02_L1</t>
+    <t>Dnc1_plus_L1</t>
+  </si>
+  <si>
+    <t>Dnc02_yes_L1</t>
   </si>
   <si>
     <t>Year_transformed_sq</t>
@@ -430,7 +430,7 @@
         <v>20</v>
       </c>
       <c r="B5">
-        <v>0.12245658060838782</v>
+        <v>0.12245687569794139</v>
       </c>
       <c r="C5"/>
       <c r="D5"/>
@@ -438,7 +438,7 @@
         <v>28</v>
       </c>
       <c r="F5">
-        <v>1758.7069157973515</v>
+        <v>1758.7106271074354</v>
       </c>
     </row>
     <row r="6">
@@ -454,7 +454,7 @@
         <v>29</v>
       </c>
       <c r="F6">
-        <v>-16413868.351592593</v>
+        <v>-16413827.602108937</v>
       </c>
     </row>
     <row r="7">
@@ -483,7 +483,7 @@
         <v>20</v>
       </c>
       <c r="B10">
-        <v>0.57198790870397231</v>
+        <v>0.57370596602107504</v>
       </c>
       <c r="C10"/>
       <c r="D10"/>
@@ -491,7 +491,7 @@
         <v>28</v>
       </c>
       <c r="F10">
-        <v>4414.8508217536273</v>
+        <v>4603.6455857170358</v>
       </c>
     </row>
     <row r="11">
@@ -507,7 +507,7 @@
         <v>29</v>
       </c>
       <c r="F11">
-        <v>-10741309.37955562</v>
+        <v>-10698186.240769662</v>
       </c>
     </row>
     <row r="12">
@@ -536,7 +536,7 @@
         <v>20</v>
       </c>
       <c r="B15">
-        <v>0.18881923759007713</v>
+        <v>0.18881926192104559</v>
       </c>
       <c r="C15"/>
       <c r="D15"/>
@@ -641,73 +641,73 @@
         <v>32</v>
       </c>
       <c r="B2">
-        <v>-0.11662549415848325</v>
+        <v>-0.11662447696316315</v>
       </c>
       <c r="C2">
-        <v>0.00059812895559139493</v>
+        <v>0.00059812867888842374</v>
       </c>
       <c r="D2">
-        <v>5.3193649979360526e-05</v>
+        <v>1.7651026892560023e-06</v>
       </c>
       <c r="E2">
-        <v>-5.1428598898282878e-05</v>
+        <v>-5.1429849423037284e-05</v>
       </c>
       <c r="F2">
-        <v>-7.0558560923431831e-06</v>
+        <v>-7.0556998576366222e-06</v>
       </c>
       <c r="G2">
-        <v>1.0886774099703148e-05</v>
+        <v>1.0886439448035665e-05</v>
       </c>
       <c r="H2">
-        <v>1.2529968570254973e-05</v>
+        <v>1.2530577705779919e-05</v>
       </c>
       <c r="I2">
-        <v>-1.0829178140764063e-05</v>
+        <v>-1.0829388282259129e-05</v>
       </c>
       <c r="J2">
-        <v>-8.9295702880047762e-07</v>
+        <v>-8.9154141434915328e-07</v>
       </c>
       <c r="K2">
-        <v>2.4508499888608335e-05</v>
+        <v>2.4510385167041444e-05</v>
       </c>
       <c r="L2">
-        <v>-2.3998532418859173e-05</v>
+        <v>-2.3997063754733366e-05</v>
       </c>
       <c r="M2">
-        <v>-2.8194944869930041e-05</v>
+        <v>-2.8196457508709166e-05</v>
       </c>
       <c r="N2">
-        <v>-4.522595549044485e-05</v>
+        <v>-4.5227974366673126e-05</v>
       </c>
       <c r="O2">
-        <v>-2.5840480169790163e-05</v>
+        <v>-2.5841294697318413e-05</v>
       </c>
       <c r="P2">
-        <v>-3.1950497087190546e-05</v>
+        <v>-3.19522070572313e-05</v>
       </c>
       <c r="Q2">
-        <v>-5.5034652584934606e-05</v>
+        <v>-5.5036374184787003e-05</v>
       </c>
       <c r="R2">
-        <v>-5.4892795347689844e-05</v>
+        <v>-5.4894143815320052e-05</v>
       </c>
       <c r="S2">
-        <v>-1.4008448127536329e-06</v>
+        <v>-1.4008057441146856e-06</v>
       </c>
       <c r="T2">
-        <v>7.6597438813352488e-06</v>
+        <v>7.6602284271958237e-06</v>
       </c>
       <c r="U2">
-        <v>-1.6929726171922863e-05</v>
+        <v>-1.6930302265998695e-05</v>
       </c>
       <c r="V2">
-        <v>-1.6729840998895316e-05</v>
+        <v>-1.6729711706180123e-05</v>
       </c>
       <c r="W2">
-        <v>2.9216649903653991e-05</v>
+        <v>2.9216267533437298e-05</v>
       </c>
       <c r="X2">
-        <v>-0.0011421058980991157</v>
+        <v>-0.00026782037041550523</v>
       </c>
     </row>
     <row r="3">
@@ -715,73 +715,73 @@
         <v>33</v>
       </c>
       <c r="B3">
-        <v>1.3916811932985813</v>
+        <v>-0.14559711954200455</v>
       </c>
       <c r="C3">
-        <v>5.3193649979360526e-05</v>
+        <v>1.7651026892560023e-06</v>
       </c>
       <c r="D3">
-        <v>0.002030146897168887</v>
+        <v>8.7674227140811044e-05</v>
       </c>
       <c r="E3">
-        <v>-0.0022397170447150784</v>
+        <v>0.00029724376059475058</v>
       </c>
       <c r="F3">
-        <v>0.00037085548082979369</v>
+        <v>-0.00018019225085596068</v>
       </c>
       <c r="G3">
-        <v>-9.0037511151221724e-05</v>
+        <v>0.00011002334803386221</v>
       </c>
       <c r="H3">
-        <v>0.000461875688277367</v>
+        <v>-4.4521885406181616e-05</v>
       </c>
       <c r="I3">
-        <v>5.094259051608048e-06</v>
+        <v>-2.1589168437395894e-06</v>
       </c>
       <c r="J3">
-        <v>0.00022690310448790117</v>
+        <v>8.6514903466760977e-05</v>
       </c>
       <c r="K3">
-        <v>0.00041132774121925651</v>
+        <v>0.00017205609895866247</v>
       </c>
       <c r="L3">
-        <v>0.0003754954909824821</v>
+        <v>0.00018131654951066521</v>
       </c>
       <c r="M3">
-        <v>6.6515231849917367e-05</v>
+        <v>-2.0444164833006507e-05</v>
       </c>
       <c r="N3">
-        <v>9.2740681412253889e-06</v>
+        <v>-2.9149268702997368e-05</v>
       </c>
       <c r="O3">
-        <v>2.6736941195512447e-05</v>
+        <v>-2.9131533922440117e-05</v>
       </c>
       <c r="P3">
-        <v>3.2053495963847017e-05</v>
+        <v>-1.6142784236935397e-05</v>
       </c>
       <c r="Q3">
-        <v>2.1261853803977482e-05</v>
+        <v>-1.6520012026069276e-05</v>
       </c>
       <c r="R3">
-        <v>-1.8969461165578572e-07</v>
+        <v>-7.2687491563628388e-06</v>
       </c>
       <c r="S3">
-        <v>-1.0587506193577559e-06</v>
+        <v>1.5913813405596874e-06</v>
       </c>
       <c r="T3">
-        <v>-7.5011823935464822e-05</v>
+        <v>-2.9280593706172784e-06</v>
       </c>
       <c r="U3">
-        <v>0.00016871663592922417</v>
+        <v>-2.1535077201024439e-05</v>
       </c>
       <c r="V3">
-        <v>0.00011882050598569643</v>
+        <v>-1.5924522668357439e-05</v>
       </c>
       <c r="W3">
-        <v>0.00011560415401382952</v>
+        <v>-7.9848367730172469e-06</v>
       </c>
       <c r="X3">
-        <v>-0.034068304683519832</v>
+        <v>-0.0017924371667468965</v>
       </c>
     </row>
     <row r="4">
@@ -789,73 +789,73 @@
         <v>34</v>
       </c>
       <c r="B4">
-        <v>-1.5372788892215477</v>
+        <v>-1.5372786640638925</v>
       </c>
       <c r="C4">
-        <v>-5.1428598898282878e-05</v>
+        <v>-5.1429849423037284e-05</v>
       </c>
       <c r="D4">
-        <v>-0.0022397170447150784</v>
+        <v>0.00029724376059475058</v>
       </c>
       <c r="E4">
-        <v>0.0025369615157825121</v>
+        <v>0.0025369555023489346</v>
       </c>
       <c r="F4">
-        <v>-0.00055104790373587188</v>
+        <v>-0.0005510471422363022</v>
       </c>
       <c r="G4">
-        <v>0.00020006098598102903</v>
+        <v>0.00020006144129067752</v>
       </c>
       <c r="H4">
-        <v>-0.00050639744265073075</v>
+        <v>-0.00050639727639288483</v>
       </c>
       <c r="I4">
-        <v>-7.2533360795856358e-06</v>
+        <v>-7.2530235086693288e-06</v>
       </c>
       <c r="J4">
-        <v>-0.00014038868855446006</v>
+        <v>-0.00014038751107323859</v>
       </c>
       <c r="K4">
-        <v>-0.00023927173883689021</v>
+        <v>-0.00023927141411159061</v>
       </c>
       <c r="L4">
-        <v>-0.00019417914259680855</v>
+        <v>-0.00019417807775790291</v>
       </c>
       <c r="M4">
-        <v>-8.6959488674868968e-05</v>
+        <v>-8.6955610511307412e-05</v>
       </c>
       <c r="N4">
-        <v>-3.8423567687042443e-05</v>
+        <v>-3.8418787722349721e-05</v>
       </c>
       <c r="O4">
-        <v>-5.5867962324224023e-05</v>
+        <v>-5.5868557601869342e-05</v>
       </c>
       <c r="P4">
-        <v>-4.8196213021198253e-05</v>
+        <v>-4.8192904526197285e-05</v>
       </c>
       <c r="Q4">
-        <v>-3.7782244525188385e-05</v>
+        <v>-3.7776783440613177e-05</v>
       </c>
       <c r="R4">
-        <v>-7.0790705166464546e-06</v>
+        <v>-7.0752729348080509e-06</v>
       </c>
       <c r="S4">
-        <v>2.6501764231130808e-06</v>
+        <v>2.6499221390003936e-06</v>
       </c>
       <c r="T4">
-        <v>7.2083364144905765e-05</v>
+        <v>7.2082010005209557e-05</v>
       </c>
       <c r="U4">
-        <v>-0.00019025226127189249</v>
+        <v>-0.00019024964748715122</v>
       </c>
       <c r="V4">
-        <v>-0.00013474512706184404</v>
+        <v>-0.00013474371578078349</v>
       </c>
       <c r="W4">
-        <v>-0.00012358938128425971</v>
+        <v>-0.00012358751192967344</v>
       </c>
       <c r="X4">
-        <v>0.037329020849452166</v>
+        <v>-0.0057993087758113574</v>
       </c>
     </row>
     <row r="5">
@@ -863,73 +863,73 @@
         <v>35</v>
       </c>
       <c r="B5">
-        <v>-0.045831179907822879</v>
+        <v>-0.045832274175645074</v>
       </c>
       <c r="C5">
-        <v>-7.0558560923431831e-06</v>
+        <v>-7.0556998576366222e-06</v>
       </c>
       <c r="D5">
-        <v>0.00037085548082979369</v>
+        <v>-0.00018019225085596068</v>
       </c>
       <c r="E5">
-        <v>-0.00055104790373587188</v>
+        <v>-0.0005510471422363022</v>
       </c>
       <c r="F5">
-        <v>0.00064988377966434066</v>
+        <v>0.00064988441010083858</v>
       </c>
       <c r="G5">
-        <v>-0.00086476528277704687</v>
+        <v>-0.00086476740349140544</v>
       </c>
       <c r="H5">
-        <v>9.2192316042434249e-05</v>
+        <v>9.2192680585024157e-05</v>
       </c>
       <c r="I5">
-        <v>-1.2780930870135636e-05</v>
+        <v>-1.278108997361608e-05</v>
       </c>
       <c r="J5">
-        <v>-0.00015615001659738777</v>
+        <v>-0.00015614960831265709</v>
       </c>
       <c r="K5">
-        <v>-0.00027663839782530683</v>
+        <v>-0.000276637659283532</v>
       </c>
       <c r="L5">
-        <v>-0.00029534385251739565</v>
+        <v>-0.00029534326502125055</v>
       </c>
       <c r="M5">
-        <v>2.7965907548179857e-05</v>
+        <v>2.7962621392732707e-05</v>
       </c>
       <c r="N5">
-        <v>5.0107183411360941e-05</v>
+        <v>5.0104063907688637e-05</v>
       </c>
       <c r="O5">
-        <v>4.511243552299737e-05</v>
+        <v>4.5110121240774913e-05</v>
       </c>
       <c r="P5">
-        <v>3.2550970032155842e-05</v>
+        <v>3.2548177969952442e-05</v>
       </c>
       <c r="Q5">
-        <v>2.8870010482474772e-05</v>
+        <v>2.8866317913841348e-05</v>
       </c>
       <c r="R5">
-        <v>2.9251057269304311e-05</v>
+        <v>2.9248414192957928e-05</v>
       </c>
       <c r="S5">
-        <v>-2.892868432953979e-06</v>
+        <v>-2.8927603308168332e-06</v>
       </c>
       <c r="T5">
-        <v>3.5537068623255064e-05</v>
+        <v>3.553832431412449e-05</v>
       </c>
       <c r="U5">
-        <v>3.7498118066576629e-05</v>
+        <v>3.7496946559498488e-05</v>
       </c>
       <c r="V5">
-        <v>2.9926161694933048e-05</v>
+        <v>2.9925794256317707e-05</v>
       </c>
       <c r="W5">
-        <v>2.567965025156117e-06</v>
+        <v>2.5668704388639605e-06</v>
       </c>
       <c r="X5">
-        <v>-0.0057985832469997951</v>
+        <v>0.0035692276467660811</v>
       </c>
     </row>
     <row r="6">
@@ -937,73 +937,73 @@
         <v>36</v>
       </c>
       <c r="B6">
-        <v>0.26606742302774322</v>
+        <v>0.26606349634549448</v>
       </c>
       <c r="C6">
-        <v>1.0886774099703148e-05</v>
+        <v>1.0886439448035665e-05</v>
       </c>
       <c r="D6">
-        <v>-9.0037511151221724e-05</v>
+        <v>0.00011002334803386221</v>
       </c>
       <c r="E6">
-        <v>0.00020006098598102903</v>
+        <v>0.00020006144129067752</v>
       </c>
       <c r="F6">
-        <v>-0.00086476528277704687</v>
+        <v>-0.00086476740349140544</v>
       </c>
       <c r="G6">
-        <v>0.0026981147126885719</v>
+        <v>0.0026981185158032025</v>
       </c>
       <c r="H6">
-        <v>0.00032842104698869892</v>
+        <v>0.00032841930053446877</v>
       </c>
       <c r="I6">
-        <v>4.6637004269431658e-05</v>
+        <v>4.6636211371820348e-05</v>
       </c>
       <c r="J6">
-        <v>0.00011295617033839677</v>
+        <v>0.00011295289957566473</v>
       </c>
       <c r="K6">
-        <v>0.00013673933195652551</v>
+        <v>0.00013673657893888759</v>
       </c>
       <c r="L6">
-        <v>0.0001551658951200366</v>
+        <v>0.00015516340464972388</v>
       </c>
       <c r="M6">
-        <v>-9.4531997023219322e-08</v>
+        <v>-8.6605854461921372e-08</v>
       </c>
       <c r="N6">
-        <v>-3.3601347419204156e-06</v>
+        <v>-3.3534860002313715e-06</v>
       </c>
       <c r="O6">
-        <v>4.1241467339216066e-06</v>
+        <v>4.1301294243326092e-06</v>
       </c>
       <c r="P6">
-        <v>7.1090382189545201e-06</v>
+        <v>7.1158286582024156e-06</v>
       </c>
       <c r="Q6">
-        <v>1.7492770235083858e-05</v>
+        <v>1.7500937488835574e-05</v>
       </c>
       <c r="R6">
-        <v>-3.4991076690749458e-05</v>
+        <v>-3.4985097604349588e-05</v>
       </c>
       <c r="S6">
-        <v>2.1732153148047034e-06</v>
+        <v>2.1730594511169837e-06</v>
       </c>
       <c r="T6">
-        <v>-1.3186859635059634e-05</v>
+        <v>-1.3190440475201832e-05</v>
       </c>
       <c r="U6">
-        <v>1.1618301981157768e-05</v>
+        <v>1.1618287407189176e-05</v>
       </c>
       <c r="V6">
-        <v>3.8741605864164733e-05</v>
+        <v>3.8741080464001795e-05</v>
       </c>
       <c r="W6">
-        <v>4.4605492709096529e-05</v>
+        <v>4.4606115886502962e-05</v>
       </c>
       <c r="X6">
-        <v>0.00094012714511956157</v>
+        <v>-0.00246090698286843</v>
       </c>
     </row>
     <row r="7">
@@ -1011,73 +1011,73 @@
         <v>37</v>
       </c>
       <c r="B7">
-        <v>0.18378990882031238</v>
+        <v>0.1837903568861094</v>
       </c>
       <c r="C7">
-        <v>1.2529968570254973e-05</v>
+        <v>1.2530577705779919e-05</v>
       </c>
       <c r="D7">
-        <v>0.000461875688277367</v>
+        <v>-4.4521885406181616e-05</v>
       </c>
       <c r="E7">
-        <v>-0.00050639744265073075</v>
+        <v>-0.00050639727639288483</v>
       </c>
       <c r="F7">
-        <v>9.2192316042434249e-05</v>
+        <v>9.2192680585024157e-05</v>
       </c>
       <c r="G7">
-        <v>0.00032842104698869892</v>
+        <v>0.00032841930053446877</v>
       </c>
       <c r="H7">
-        <v>0.001266779385634536</v>
+        <v>0.0012667759019090829</v>
       </c>
       <c r="I7">
-        <v>1.7292440640060054e-05</v>
+        <v>1.7293387898520228e-05</v>
       </c>
       <c r="J7">
-        <v>5.5391659836240672e-05</v>
+        <v>5.5390732907903214e-05</v>
       </c>
       <c r="K7">
-        <v>0.00011280522818479604</v>
+        <v>0.00011280351142830191</v>
       </c>
       <c r="L7">
-        <v>0.00010553343649324703</v>
+        <v>0.00010553261768774734</v>
       </c>
       <c r="M7">
-        <v>-1.6289375362371454e-05</v>
+        <v>-1.6292918739662228e-05</v>
       </c>
       <c r="N7">
-        <v>-8.1337514177894608e-05</v>
+        <v>-8.1340843056609824e-05</v>
       </c>
       <c r="O7">
-        <v>-6.5610573065993331e-05</v>
+        <v>-6.5614278631255125e-05</v>
       </c>
       <c r="P7">
-        <v>-5.6169650351423767e-05</v>
+        <v>-5.6172970668571213e-05</v>
       </c>
       <c r="Q7">
-        <v>-7.9393822986723289e-05</v>
+        <v>-7.9396741760532917e-05</v>
       </c>
       <c r="R7">
-        <v>-9.2730461256786633e-05</v>
+        <v>-9.2733346618528999e-05</v>
       </c>
       <c r="S7">
-        <v>-3.2415906310007234e-07</v>
+        <v>-3.2418698911375941e-07</v>
       </c>
       <c r="T7">
-        <v>-2.5310924149370487e-05</v>
+        <v>-2.5305530055338125e-05</v>
       </c>
       <c r="U7">
-        <v>6.1629529262797436e-05</v>
+        <v>6.1628758911100887e-05</v>
       </c>
       <c r="V7">
-        <v>0.0002620207638744116</v>
+        <v>0.0002620191602555103</v>
       </c>
       <c r="W7">
-        <v>0.0001472398772038822</v>
+        <v>0.0001472388666721383</v>
       </c>
       <c r="X7">
-        <v>-0.0087091976760404581</v>
+        <v>-0.00010043214947687935</v>
       </c>
     </row>
     <row r="8">
@@ -1085,73 +1085,73 @@
         <v>38</v>
       </c>
       <c r="B8">
-        <v>0.17524687296317709</v>
+        <v>0.17524740922346632</v>
       </c>
       <c r="C8">
-        <v>-1.0829178140764063e-05</v>
+        <v>-1.0829388282259129e-05</v>
       </c>
       <c r="D8">
-        <v>5.094259051608048e-06</v>
+        <v>-2.1589168437395894e-06</v>
       </c>
       <c r="E8">
-        <v>-7.2533360795856358e-06</v>
+        <v>-7.2530235086693288e-06</v>
       </c>
       <c r="F8">
-        <v>-1.2780930870135636e-05</v>
+        <v>-1.278108997361608e-05</v>
       </c>
       <c r="G8">
-        <v>4.6637004269431658e-05</v>
+        <v>4.6636211371820348e-05</v>
       </c>
       <c r="H8">
-        <v>1.7292440640060054e-05</v>
+        <v>1.7293387898520228e-05</v>
       </c>
       <c r="I8">
-        <v>0.0009542190544955388</v>
+        <v>0.00095421900206692873</v>
       </c>
       <c r="J8">
-        <v>0.00054290751350707706</v>
+        <v>0.00054290811050876516</v>
       </c>
       <c r="K8">
-        <v>0.00053922671623172287</v>
+        <v>0.0005392274558404538</v>
       </c>
       <c r="L8">
-        <v>0.00054685433343747061</v>
+        <v>0.0005468550263626194</v>
       </c>
       <c r="M8">
-        <v>-9.0388214320876533e-05</v>
+        <v>-9.0388836317207465e-05</v>
       </c>
       <c r="N8">
-        <v>-9.6410016835903609e-05</v>
+        <v>-9.6410998299437575e-05</v>
       </c>
       <c r="O8">
-        <v>-0.0001295255367519522</v>
+        <v>-0.00012952807267497285</v>
       </c>
       <c r="P8">
-        <v>-8.2870078476063455e-05</v>
+        <v>-8.2871565907973965e-05</v>
       </c>
       <c r="Q8">
-        <v>-0.00011042575338982546</v>
+        <v>-0.00011042738596135537</v>
       </c>
       <c r="R8">
-        <v>-5.9123860069565056e-05</v>
+        <v>-5.9125238864812872e-05</v>
       </c>
       <c r="S8">
-        <v>5.5969320279936984e-06</v>
+        <v>5.5968767735519801e-06</v>
       </c>
       <c r="T8">
-        <v>-6.4440812233982898e-05</v>
+        <v>-6.4442836347353749e-05</v>
       </c>
       <c r="U8">
-        <v>-1.1317385367941544e-05</v>
+        <v>-1.1316703399615107e-05</v>
       </c>
       <c r="V8">
-        <v>1.8157987464934808e-05</v>
+        <v>1.8159333328198641e-05</v>
       </c>
       <c r="W8">
-        <v>-3.2135624532412009e-05</v>
+        <v>-3.2134967341227819e-05</v>
       </c>
       <c r="X8">
-        <v>-0.00063166482585753697</v>
+        <v>-0.00050835998413518773</v>
       </c>
     </row>
     <row r="9">
@@ -1159,73 +1159,73 @@
         <v>39</v>
       </c>
       <c r="B9">
-        <v>0.2319060809798166</v>
+        <v>0.23190674790880267</v>
       </c>
       <c r="C9">
-        <v>-8.9295702880047762e-07</v>
+        <v>-8.9154141434915328e-07</v>
       </c>
       <c r="D9">
-        <v>0.00022690310448790117</v>
+        <v>8.6514903466760977e-05</v>
       </c>
       <c r="E9">
-        <v>-0.00014038868855446006</v>
+        <v>-0.00014038751107323859</v>
       </c>
       <c r="F9">
-        <v>-0.00015615001659738777</v>
+        <v>-0.00015614960831265709</v>
       </c>
       <c r="G9">
-        <v>0.00011295617033839677</v>
+        <v>0.00011295289957566473</v>
       </c>
       <c r="H9">
-        <v>5.5391659836240672e-05</v>
+        <v>5.5390732907903214e-05</v>
       </c>
       <c r="I9">
-        <v>0.00054290751350707706</v>
+        <v>0.00054290811050876516</v>
       </c>
       <c r="J9">
-        <v>0.0016613152337981636</v>
+        <v>0.0016613185852550078</v>
       </c>
       <c r="K9">
-        <v>0.00096394065614741607</v>
+        <v>0.00096394314566897827</v>
       </c>
       <c r="L9">
-        <v>0.00097833907314359009</v>
+        <v>0.00097834125852321085</v>
       </c>
       <c r="M9">
-        <v>-9.602916571895383e-05</v>
+        <v>-9.6037099052273317e-05</v>
       </c>
       <c r="N9">
-        <v>-0.00010236043911532582</v>
+        <v>-0.0001023684546753497</v>
       </c>
       <c r="O9">
-        <v>-0.00010509280849465381</v>
+        <v>-0.00010509838355078426</v>
       </c>
       <c r="P9">
-        <v>-6.7271735399217474e-05</v>
+        <v>-6.727988575313008e-05</v>
       </c>
       <c r="Q9">
-        <v>-5.7381072824868679e-05</v>
+        <v>-5.7388991244186518e-05</v>
       </c>
       <c r="R9">
-        <v>-4.892447248826563e-05</v>
+        <v>-4.8932099875027477e-05</v>
       </c>
       <c r="S9">
-        <v>1.0675743650283322e-05</v>
+        <v>1.0675856802272877e-05</v>
       </c>
       <c r="T9">
-        <v>-2.0762785150680273e-05</v>
+        <v>-2.0756253359436108e-05</v>
       </c>
       <c r="U9">
-        <v>-8.4348473741263896e-05</v>
+        <v>-8.4348409378344103e-05</v>
       </c>
       <c r="V9">
-        <v>-3.8108735429636049e-05</v>
+        <v>-3.8109229291328475e-05</v>
       </c>
       <c r="W9">
-        <v>-7.7107325670070209e-06</v>
+        <v>-7.7111327278098435e-06</v>
       </c>
       <c r="X9">
-        <v>-0.004887594910949926</v>
+        <v>-0.0025009936575565114</v>
       </c>
     </row>
     <row r="10">
@@ -1233,73 +1233,73 @@
         <v>40</v>
       </c>
       <c r="B10">
-        <v>0.27766935331692755</v>
+        <v>0.27766658031748337</v>
       </c>
       <c r="C10">
-        <v>2.4508499888608335e-05</v>
+        <v>2.4510385167041444e-05</v>
       </c>
       <c r="D10">
-        <v>0.00041132774121925651</v>
+        <v>0.00017205609895866247</v>
       </c>
       <c r="E10">
-        <v>-0.00023927173883689021</v>
+        <v>-0.00023927141411159061</v>
       </c>
       <c r="F10">
-        <v>-0.00027663839782530683</v>
+        <v>-0.000276637659283532</v>
       </c>
       <c r="G10">
-        <v>0.00013673933195652551</v>
+        <v>0.00013673657893888759</v>
       </c>
       <c r="H10">
-        <v>0.00011280522818479604</v>
+        <v>0.00011280351142830191</v>
       </c>
       <c r="I10">
-        <v>0.00053922671623172287</v>
+        <v>0.0005392274558404538</v>
       </c>
       <c r="J10">
-        <v>0.00096394065614741607</v>
+        <v>0.00096394314566897827</v>
       </c>
       <c r="K10">
-        <v>0.0026691769481156638</v>
+        <v>0.0026691732283158362</v>
       </c>
       <c r="L10">
-        <v>0.0014023855920340088</v>
+        <v>0.0014023872457685569</v>
       </c>
       <c r="M10">
-        <v>-9.8264610459967983e-05</v>
+        <v>-9.8268229473548983e-05</v>
       </c>
       <c r="N10">
-        <v>-0.00021447481293727661</v>
+        <v>-0.00021447845653637917</v>
       </c>
       <c r="O10">
-        <v>-0.00021541532721094155</v>
+        <v>-0.0002154225704627782</v>
       </c>
       <c r="P10">
-        <v>-0.00010796268269526801</v>
+        <v>-0.00010796767401879048</v>
       </c>
       <c r="Q10">
-        <v>-0.00017125762063220643</v>
+        <v>-0.00017126113878212942</v>
       </c>
       <c r="R10">
-        <v>-4.9031188382731017e-05</v>
+        <v>-4.9034975211005583e-05</v>
       </c>
       <c r="S10">
-        <v>8.7829495122087253e-06</v>
+        <v>8.783004711298111e-06</v>
       </c>
       <c r="T10">
-        <v>-0.00011357970325363322</v>
+        <v>-0.00011358015980964279</v>
       </c>
       <c r="U10">
-        <v>-6.7102283309917283e-05</v>
+        <v>-6.7102564024877891e-05</v>
       </c>
       <c r="V10">
-        <v>-1.5478070372863979e-05</v>
+        <v>-1.547961679484967e-05</v>
       </c>
       <c r="W10">
-        <v>3.1541556483074846e-05</v>
+        <v>3.1540406941475783e-05</v>
       </c>
       <c r="X10">
-        <v>-0.0083148960405415445</v>
+        <v>-0.0042472755154065941</v>
       </c>
     </row>
     <row r="11">
@@ -1307,73 +1307,73 @@
         <v>41</v>
       </c>
       <c r="B11">
-        <v>0.47490623086040473</v>
+        <v>0.47490578906085984</v>
       </c>
       <c r="C11">
-        <v>-2.3998532418859173e-05</v>
+        <v>-2.3997063754733366e-05</v>
       </c>
       <c r="D11">
-        <v>0.0003754954909824821</v>
+        <v>0.00018131654951066521</v>
       </c>
       <c r="E11">
-        <v>-0.00019417914259680855</v>
+        <v>-0.00019417807775790291</v>
       </c>
       <c r="F11">
-        <v>-0.00029534385251739565</v>
+        <v>-0.00029534326502125055</v>
       </c>
       <c r="G11">
-        <v>0.0001551658951200366</v>
+        <v>0.00015516340464972388</v>
       </c>
       <c r="H11">
-        <v>0.00010553343649324703</v>
+        <v>0.00010553261768774734</v>
       </c>
       <c r="I11">
-        <v>0.00054685433343747061</v>
+        <v>0.0005468550263626194</v>
       </c>
       <c r="J11">
-        <v>0.00097833907314359009</v>
+        <v>0.00097834125852321085</v>
       </c>
       <c r="K11">
-        <v>0.0014023855920340088</v>
+        <v>0.0014023872457685569</v>
       </c>
       <c r="L11">
-        <v>0.0032711063078087821</v>
+        <v>0.0032711015761770364</v>
       </c>
       <c r="M11">
-        <v>-7.0487437067535096e-05</v>
+        <v>-7.0491929602225709e-05</v>
       </c>
       <c r="N11">
-        <v>-0.00025104275626890507</v>
+        <v>-0.00025104600977592399</v>
       </c>
       <c r="O11">
-        <v>-0.00026612762067304931</v>
+        <v>-0.00026613082485046143</v>
       </c>
       <c r="P11">
-        <v>-3.7048506380579424e-05</v>
+        <v>-3.7054164029303067e-05</v>
       </c>
       <c r="Q11">
-        <v>-0.00016676477625602701</v>
+        <v>-0.00016676909247221195</v>
       </c>
       <c r="R11">
-        <v>6.8469102283529124e-05</v>
+        <v>6.8463871906335161e-05</v>
       </c>
       <c r="S11">
-        <v>1.4560200974086083e-05</v>
+        <v>1.4560298566931645e-05</v>
       </c>
       <c r="T11">
-        <v>-0.00015028335220506652</v>
+        <v>-0.00015028077791048042</v>
       </c>
       <c r="U11">
-        <v>-0.0001627536439591375</v>
+        <v>-0.00016275318016031369</v>
       </c>
       <c r="V11">
-        <v>-6.4630217792316716e-05</v>
+        <v>-6.4631717847807996e-05</v>
       </c>
       <c r="W11">
-        <v>-3.5149684232688248e-05</v>
+        <v>-3.5151370033865829e-05</v>
       </c>
       <c r="X11">
-        <v>-0.0078344464290013675</v>
+        <v>-0.0045334035957148369</v>
       </c>
     </row>
     <row r="12">
@@ -1381,73 +1381,73 @@
         <v>42</v>
       </c>
       <c r="B12">
-        <v>-0.036469755115334922</v>
+        <v>-0.036474548956195722</v>
       </c>
       <c r="C12">
-        <v>-2.8194944869930041e-05</v>
+        <v>-2.8196457508709166e-05</v>
       </c>
       <c r="D12">
-        <v>6.6515231849917367e-05</v>
+        <v>-2.0444164833006507e-05</v>
       </c>
       <c r="E12">
-        <v>-8.6959488674868968e-05</v>
+        <v>-8.6955610511307412e-05</v>
       </c>
       <c r="F12">
-        <v>2.7965907548179857e-05</v>
+        <v>2.7962621392732707e-05</v>
       </c>
       <c r="G12">
-        <v>-9.4531997023219322e-08</v>
+        <v>-8.6605854461921372e-08</v>
       </c>
       <c r="H12">
-        <v>-1.6289375362371454e-05</v>
+        <v>-1.6292918739662228e-05</v>
       </c>
       <c r="I12">
-        <v>-9.0388214320876533e-05</v>
+        <v>-9.0388836317207465e-05</v>
       </c>
       <c r="J12">
-        <v>-9.602916571895383e-05</v>
+        <v>-9.6037099052273317e-05</v>
       </c>
       <c r="K12">
-        <v>-9.8264610459967983e-05</v>
+        <v>-9.8268229473548983e-05</v>
       </c>
       <c r="L12">
-        <v>-7.0487437067535096e-05</v>
+        <v>-7.0491929602225709e-05</v>
       </c>
       <c r="M12">
-        <v>0.0050663617973414048</v>
+        <v>0.0050663860419252948</v>
       </c>
       <c r="N12">
-        <v>0.0038804826940876639</v>
+        <v>0.0038805056949495274</v>
       </c>
       <c r="O12">
-        <v>0.0038837541176409865</v>
+        <v>0.0038837774293781001</v>
       </c>
       <c r="P12">
-        <v>0.0038771904397917</v>
+        <v>0.0038772135642165103</v>
       </c>
       <c r="Q12">
-        <v>0.0038853715250227274</v>
+        <v>0.0038853946959927386</v>
       </c>
       <c r="R12">
-        <v>0.003875929909630997</v>
+        <v>0.0038759532011701861</v>
       </c>
       <c r="S12">
-        <v>2.6894911541993705e-06</v>
+        <v>2.6895318857309418e-06</v>
       </c>
       <c r="T12">
-        <v>2.2851032876457581e-05</v>
+        <v>2.2843894055343036e-05</v>
       </c>
       <c r="U12">
-        <v>-3.0056860886744282e-05</v>
+        <v>-3.0058754792146336e-05</v>
       </c>
       <c r="V12">
-        <v>-3.520523061372946e-05</v>
+        <v>-3.5206270989632292e-05</v>
       </c>
       <c r="W12">
-        <v>-5.5574613304413515e-05</v>
+        <v>-5.5574648317858457e-05</v>
       </c>
       <c r="X12">
-        <v>-0.0048819682986149891</v>
+        <v>-0.0034036755612217328</v>
       </c>
     </row>
     <row r="13">
@@ -1455,73 +1455,73 @@
         <v>43</v>
       </c>
       <c r="B13">
-        <v>0.028707420107739381</v>
+        <v>0.028700698626239644</v>
       </c>
       <c r="C13">
-        <v>-4.522595549044485e-05</v>
+        <v>-4.5227974366673126e-05</v>
       </c>
       <c r="D13">
-        <v>9.2740681412253889e-06</v>
+        <v>-2.9149268702997368e-05</v>
       </c>
       <c r="E13">
-        <v>-3.8423567687042443e-05</v>
+        <v>-3.8418787722349721e-05</v>
       </c>
       <c r="F13">
-        <v>5.0107183411360941e-05</v>
+        <v>5.0104063907688637e-05</v>
       </c>
       <c r="G13">
-        <v>-3.3601347419204156e-06</v>
+        <v>-3.3534860002313715e-06</v>
       </c>
       <c r="H13">
-        <v>-8.1337514177894608e-05</v>
+        <v>-8.1340843056609824e-05</v>
       </c>
       <c r="I13">
-        <v>-9.6410016835903609e-05</v>
+        <v>-9.6410998299437575e-05</v>
       </c>
       <c r="J13">
-        <v>-0.00010236043911532582</v>
+        <v>-0.0001023684546753497</v>
       </c>
       <c r="K13">
-        <v>-0.00021447481293727661</v>
+        <v>-0.00021447845653637917</v>
       </c>
       <c r="L13">
-        <v>-0.00025104275626890507</v>
+        <v>-0.00025104600977592399</v>
       </c>
       <c r="M13">
-        <v>0.0038804826940876639</v>
+        <v>0.0038805056949495274</v>
       </c>
       <c r="N13">
-        <v>0.0049098931726962508</v>
+        <v>0.0049099138110512185</v>
       </c>
       <c r="O13">
-        <v>0.0039019477856904326</v>
+        <v>0.0039019710887432555</v>
       </c>
       <c r="P13">
-        <v>0.0038824463182896623</v>
+        <v>0.0038824694256181574</v>
       </c>
       <c r="Q13">
-        <v>0.0039014695594394885</v>
+        <v>0.0039014927038091749</v>
       </c>
       <c r="R13">
-        <v>0.0038757397072861702</v>
+        <v>0.0038757630256736494</v>
       </c>
       <c r="S13">
-        <v>-6.7320030585571537e-07</v>
+        <v>-6.7311660324824815e-07</v>
       </c>
       <c r="T13">
-        <v>4.9306879152243889e-05</v>
+        <v>4.9300053457845741e-05</v>
       </c>
       <c r="U13">
-        <v>-2.8353646572706025e-06</v>
+        <v>-2.8369510054613358e-06</v>
       </c>
       <c r="V13">
-        <v>-2.9510309237540692e-05</v>
+        <v>-2.9512044145471659e-05</v>
       </c>
       <c r="W13">
-        <v>-4.7447764792684635e-05</v>
+        <v>-4.7447769892382643e-05</v>
       </c>
       <c r="X13">
-        <v>-0.0037597706085894063</v>
+        <v>-0.003106592029700316</v>
       </c>
     </row>
     <row r="14">
@@ -1529,73 +1529,73 @@
         <v>44</v>
       </c>
       <c r="B14">
-        <v>-0.052635246843647031</v>
+        <v>-0.052637815371653775</v>
       </c>
       <c r="C14">
-        <v>-2.5840480169790163e-05</v>
+        <v>-2.5841294697318413e-05</v>
       </c>
       <c r="D14">
-        <v>2.6736941195512447e-05</v>
+        <v>-2.9131533922440117e-05</v>
       </c>
       <c r="E14">
-        <v>-5.5867962324224023e-05</v>
+        <v>-5.5868557601869342e-05</v>
       </c>
       <c r="F14">
-        <v>4.511243552299737e-05</v>
+        <v>4.5110121240774913e-05</v>
       </c>
       <c r="G14">
-        <v>4.1241467339216066e-06</v>
+        <v>4.1301294243326092e-06</v>
       </c>
       <c r="H14">
-        <v>-6.5610573065993331e-05</v>
+        <v>-6.5614278631255125e-05</v>
       </c>
       <c r="I14">
-        <v>-0.0001295255367519522</v>
+        <v>-0.00012952807267497285</v>
       </c>
       <c r="J14">
-        <v>-0.00010509280849465381</v>
+        <v>-0.00010509838355078426</v>
       </c>
       <c r="K14">
-        <v>-0.00021541532721094155</v>
+        <v>-0.0002154225704627782</v>
       </c>
       <c r="L14">
-        <v>-0.00026612762067304931</v>
+        <v>-0.00026613082485046143</v>
       </c>
       <c r="M14">
-        <v>0.0038837541176409865</v>
+        <v>0.0038837774293781001</v>
       </c>
       <c r="N14">
-        <v>0.0039019477856904326</v>
+        <v>0.0039019710887432555</v>
       </c>
       <c r="O14">
-        <v>0.0049614810184243274</v>
+        <v>0.004961502865514192</v>
       </c>
       <c r="P14">
-        <v>0.0038831519799170759</v>
+        <v>0.0038831754775257954</v>
       </c>
       <c r="Q14">
-        <v>0.0038987188486178164</v>
+        <v>0.0038987426195524703</v>
       </c>
       <c r="R14">
-        <v>0.0038740793498985293</v>
+        <v>0.0038741029270415216</v>
       </c>
       <c r="S14">
-        <v>-4.086143453624645e-06</v>
+        <v>-4.0864270777853218e-06</v>
       </c>
       <c r="T14">
-        <v>4.2640386112416818e-05</v>
+        <v>4.2631616529122682e-05</v>
       </c>
       <c r="U14">
-        <v>-3.08183736132756e-05</v>
+        <v>-3.0817792982529426e-05</v>
       </c>
       <c r="V14">
-        <v>-4.8977232810807161e-05</v>
+        <v>-4.8975607964531621e-05</v>
       </c>
       <c r="W14">
-        <v>-2.6944114635863619e-05</v>
+        <v>-2.694158706709692e-05</v>
       </c>
       <c r="X14">
-        <v>-0.0039998827815752895</v>
+        <v>-0.003050127409013211</v>
       </c>
     </row>
     <row r="15">
@@ -1603,73 +1603,73 @@
         <v>45</v>
       </c>
       <c r="B15">
-        <v>-0.049905577185413323</v>
+        <v>-0.049909564482433964</v>
       </c>
       <c r="C15">
-        <v>-3.1950497087190546e-05</v>
+        <v>-3.19522070572313e-05</v>
       </c>
       <c r="D15">
-        <v>3.2053495963847017e-05</v>
+        <v>-1.6142784236935397e-05</v>
       </c>
       <c r="E15">
-        <v>-4.8196213021198253e-05</v>
+        <v>-4.8192904526197285e-05</v>
       </c>
       <c r="F15">
-        <v>3.2550970032155842e-05</v>
+        <v>3.2548177969952442e-05</v>
       </c>
       <c r="G15">
-        <v>7.1090382189545201e-06</v>
+        <v>7.1158286582024156e-06</v>
       </c>
       <c r="H15">
-        <v>-5.6169650351423767e-05</v>
+        <v>-5.6172970668571213e-05</v>
       </c>
       <c r="I15">
-        <v>-8.2870078476063455e-05</v>
+        <v>-8.2871565907973965e-05</v>
       </c>
       <c r="J15">
-        <v>-6.7271735399217474e-05</v>
+        <v>-6.727988575313008e-05</v>
       </c>
       <c r="K15">
-        <v>-0.00010796268269526801</v>
+        <v>-0.00010796767401879048</v>
       </c>
       <c r="L15">
-        <v>-3.7048506380579424e-05</v>
+        <v>-3.7054164029303067e-05</v>
       </c>
       <c r="M15">
-        <v>0.0038771904397917</v>
+        <v>0.0038772135642165103</v>
       </c>
       <c r="N15">
-        <v>0.0038824463182896623</v>
+        <v>0.0038824694256181574</v>
       </c>
       <c r="O15">
-        <v>0.0038831519799170759</v>
+        <v>0.0038831754775257954</v>
       </c>
       <c r="P15">
-        <v>0.0046989229914850932</v>
+        <v>0.0046989448140561125</v>
       </c>
       <c r="Q15">
-        <v>0.0038871063559766457</v>
+        <v>0.0038871296090359189</v>
       </c>
       <c r="R15">
-        <v>0.0038792938481784453</v>
+        <v>0.0038793170582723997</v>
       </c>
       <c r="S15">
-        <v>2.9128547413869845e-06</v>
+        <v>2.9128911858045434e-06</v>
       </c>
       <c r="T15">
-        <v>2.8901852155131195e-05</v>
+        <v>2.8892822648469074e-05</v>
       </c>
       <c r="U15">
-        <v>-3.2072151975284449e-05</v>
+        <v>-3.207345260224613e-05</v>
       </c>
       <c r="V15">
-        <v>-3.5883572139240941e-05</v>
+        <v>-3.5885215201416081e-05</v>
       </c>
       <c r="W15">
-        <v>-4.8243239997314345e-05</v>
+        <v>-4.8243077861052897e-05</v>
       </c>
       <c r="X15">
-        <v>-0.0043026246343775849</v>
+        <v>-0.0034833036844281588</v>
       </c>
     </row>
     <row r="16">
@@ -1677,73 +1677,73 @@
         <v>46</v>
       </c>
       <c r="B16">
-        <v>-0.056201557200878285</v>
+        <v>-0.056202180904038987</v>
       </c>
       <c r="C16">
-        <v>-5.5034652584934606e-05</v>
+        <v>-5.5036374184787003e-05</v>
       </c>
       <c r="D16">
-        <v>2.1261853803977482e-05</v>
+        <v>-1.6520012026069276e-05</v>
       </c>
       <c r="E16">
-        <v>-3.7782244525188385e-05</v>
+        <v>-3.7776783440613177e-05</v>
       </c>
       <c r="F16">
-        <v>2.8870010482474772e-05</v>
+        <v>2.8866317913841348e-05</v>
       </c>
       <c r="G16">
-        <v>1.7492770235083858e-05</v>
+        <v>1.7500937488835574e-05</v>
       </c>
       <c r="H16">
-        <v>-7.9393822986723289e-05</v>
+        <v>-7.9396741760532917e-05</v>
       </c>
       <c r="I16">
-        <v>-0.00011042575338982546</v>
+        <v>-0.00011042738596135537</v>
       </c>
       <c r="J16">
-        <v>-5.7381072824868679e-05</v>
+        <v>-5.7388991244186518e-05</v>
       </c>
       <c r="K16">
-        <v>-0.00017125762063220643</v>
+        <v>-0.00017126113878212942</v>
       </c>
       <c r="L16">
-        <v>-0.00016676477625602701</v>
+        <v>-0.00016676909247221195</v>
       </c>
       <c r="M16">
-        <v>0.0038853715250227274</v>
+        <v>0.0038853946959927386</v>
       </c>
       <c r="N16">
-        <v>0.0039014695594394885</v>
+        <v>0.0039014927038091749</v>
       </c>
       <c r="O16">
-        <v>0.0038987188486178164</v>
+        <v>0.0038987426195524703</v>
       </c>
       <c r="P16">
-        <v>0.0038871063559766457</v>
+        <v>0.0038871296090359189</v>
       </c>
       <c r="Q16">
-        <v>0.0045811429793194206</v>
+        <v>0.0045811661521422773</v>
       </c>
       <c r="R16">
-        <v>0.003883069565017785</v>
+        <v>0.0038830929992130564</v>
       </c>
       <c r="S16">
-        <v>-2.230626294622599e-06</v>
+        <v>-2.2305747263225335e-06</v>
       </c>
       <c r="T16">
-        <v>0.00015290423224988701</v>
+        <v>0.00015289556543355881</v>
       </c>
       <c r="U16">
-        <v>-1.560351935279614e-05</v>
+        <v>-1.5604999875911947e-05</v>
       </c>
       <c r="V16">
-        <v>-4.9391358686804842e-05</v>
+        <v>-4.9392499122509373e-05</v>
       </c>
       <c r="W16">
-        <v>-8.0543466674808258e-05</v>
+        <v>-8.0542882071318509e-05</v>
       </c>
       <c r="X16">
-        <v>-0.0039917000963350449</v>
+        <v>-0.0033494268064500916</v>
       </c>
     </row>
     <row r="17">
@@ -1751,73 +1751,73 @@
         <v>47</v>
       </c>
       <c r="B17">
-        <v>-0.039447690923021854</v>
+        <v>-0.039452231840961173</v>
       </c>
       <c r="C17">
-        <v>-5.4892795347689844e-05</v>
+        <v>-5.4894143815320052e-05</v>
       </c>
       <c r="D17">
-        <v>-1.8969461165578572e-07</v>
+        <v>-7.2687491563628388e-06</v>
       </c>
       <c r="E17">
-        <v>-7.0790705166464546e-06</v>
+        <v>-7.0752729348080509e-06</v>
       </c>
       <c r="F17">
-        <v>2.9251057269304311e-05</v>
+        <v>2.9248414192957928e-05</v>
       </c>
       <c r="G17">
-        <v>-3.4991076690749458e-05</v>
+        <v>-3.4985097604349588e-05</v>
       </c>
       <c r="H17">
-        <v>-9.2730461256786633e-05</v>
+        <v>-9.2733346618528999e-05</v>
       </c>
       <c r="I17">
-        <v>-5.9123860069565056e-05</v>
+        <v>-5.9125238864812872e-05</v>
       </c>
       <c r="J17">
-        <v>-4.892447248826563e-05</v>
+        <v>-4.8932099875027477e-05</v>
       </c>
       <c r="K17">
-        <v>-4.9031188382731017e-05</v>
+        <v>-4.9034975211005583e-05</v>
       </c>
       <c r="L17">
-        <v>6.8469102283529124e-05</v>
+        <v>6.8463871906335161e-05</v>
       </c>
       <c r="M17">
-        <v>0.003875929909630997</v>
+        <v>0.0038759532011701861</v>
       </c>
       <c r="N17">
-        <v>0.0038757397072861702</v>
+        <v>0.0038757630256736494</v>
       </c>
       <c r="O17">
-        <v>0.0038740793498985293</v>
+        <v>0.0038741029270415216</v>
       </c>
       <c r="P17">
-        <v>0.0038792938481784453</v>
+        <v>0.0038793170582723997</v>
       </c>
       <c r="Q17">
-        <v>0.003883069565017785</v>
+        <v>0.0038830929992130564</v>
       </c>
       <c r="R17">
-        <v>0.0045718907160676335</v>
+        <v>0.0045719145913298131</v>
       </c>
       <c r="S17">
-        <v>7.6943964903274792e-07</v>
+        <v>7.6941130727885705e-07</v>
       </c>
       <c r="T17">
-        <v>6.5610707463617003e-05</v>
+        <v>6.5605083411572184e-05</v>
       </c>
       <c r="U17">
-        <v>-3.9206288543135664e-05</v>
+        <v>-3.9207255258127006e-05</v>
       </c>
       <c r="V17">
-        <v>-7.6601391362328105e-05</v>
+        <v>-7.6603401658696386e-05</v>
       </c>
       <c r="W17">
-        <v>-6.7721794015233199e-05</v>
+        <v>-6.7721247831995673e-05</v>
       </c>
       <c r="X17">
-        <v>-0.00373289604320955</v>
+        <v>-0.0036125684484087962</v>
       </c>
     </row>
     <row r="18">
@@ -1825,73 +1825,73 @@
         <v>48</v>
       </c>
       <c r="B18">
-        <v>0.020278543133396859</v>
+        <v>0.020278810072804784</v>
       </c>
       <c r="C18">
-        <v>-1.4008448127536329e-06</v>
+        <v>-1.4008057441146856e-06</v>
       </c>
       <c r="D18">
-        <v>-1.0587506193577559e-06</v>
+        <v>1.5913813405596874e-06</v>
       </c>
       <c r="E18">
-        <v>2.6501764231130808e-06</v>
+        <v>2.6499221390003936e-06</v>
       </c>
       <c r="F18">
-        <v>-2.892868432953979e-06</v>
+        <v>-2.8927603308168332e-06</v>
       </c>
       <c r="G18">
-        <v>2.1732153148047034e-06</v>
+        <v>2.1730594511169837e-06</v>
       </c>
       <c r="H18">
-        <v>-3.2415906310007234e-07</v>
+        <v>-3.2418698911375941e-07</v>
       </c>
       <c r="I18">
-        <v>5.5969320279936984e-06</v>
+        <v>5.5968767735519801e-06</v>
       </c>
       <c r="J18">
-        <v>1.0675743650283322e-05</v>
+        <v>1.0675856802272877e-05</v>
       </c>
       <c r="K18">
-        <v>8.7829495122087253e-06</v>
+        <v>8.783004711298111e-06</v>
       </c>
       <c r="L18">
-        <v>1.4560200974086083e-05</v>
+        <v>1.4560298566931645e-05</v>
       </c>
       <c r="M18">
-        <v>2.6894911541993705e-06</v>
+        <v>2.6895318857309418e-06</v>
       </c>
       <c r="N18">
-        <v>-6.7320030585571537e-07</v>
+        <v>-6.7311660324824815e-07</v>
       </c>
       <c r="O18">
-        <v>-4.086143453624645e-06</v>
+        <v>-4.0864270777853218e-06</v>
       </c>
       <c r="P18">
-        <v>2.9128547413869845e-06</v>
+        <v>2.9128911858045434e-06</v>
       </c>
       <c r="Q18">
-        <v>-2.230626294622599e-06</v>
+        <v>-2.2305747263225335e-06</v>
       </c>
       <c r="R18">
-        <v>7.6943964903274792e-07</v>
+        <v>7.6941130727885705e-07</v>
       </c>
       <c r="S18">
-        <v>9.8016595576940421e-06</v>
+        <v>9.8016326339319552e-06</v>
       </c>
       <c r="T18">
-        <v>-3.1958357735086801e-05</v>
+        <v>-3.1958200906701467e-05</v>
       </c>
       <c r="U18">
-        <v>-4.2820524119084633e-05</v>
+        <v>-4.2820290373907706e-05</v>
       </c>
       <c r="V18">
-        <v>-5.1902418439418456e-05</v>
+        <v>-5.190217687613927e-05</v>
       </c>
       <c r="W18">
-        <v>-6.1496128085235122e-05</v>
+        <v>-6.1495867770999216e-05</v>
       </c>
       <c r="X18">
-        <v>-0.0001550940309811374</v>
+        <v>-0.00020014573082023952</v>
       </c>
     </row>
     <row r="19">
@@ -1899,73 +1899,73 @@
         <v>49</v>
       </c>
       <c r="B19">
-        <v>-0.26606786959317796</v>
+        <v>-0.26606533252041181</v>
       </c>
       <c r="C19">
-        <v>7.6597438813352488e-06</v>
+        <v>7.6602284271958237e-06</v>
       </c>
       <c r="D19">
-        <v>-7.5011823935464822e-05</v>
+        <v>-2.9280593706172784e-06</v>
       </c>
       <c r="E19">
-        <v>7.2083364144905765e-05</v>
+        <v>7.2082010005209557e-05</v>
       </c>
       <c r="F19">
-        <v>3.5537068623255064e-05</v>
+        <v>3.553832431412449e-05</v>
       </c>
       <c r="G19">
-        <v>-1.3186859635059634e-05</v>
+        <v>-1.3190440475201832e-05</v>
       </c>
       <c r="H19">
-        <v>-2.5310924149370487e-05</v>
+        <v>-2.5305530055338125e-05</v>
       </c>
       <c r="I19">
-        <v>-6.4440812233982898e-05</v>
+        <v>-6.4442836347353749e-05</v>
       </c>
       <c r="J19">
-        <v>-2.0762785150680273e-05</v>
+        <v>-2.0756253359436108e-05</v>
       </c>
       <c r="K19">
-        <v>-0.00011357970325363322</v>
+        <v>-0.00011358015980964279</v>
       </c>
       <c r="L19">
-        <v>-0.00015028335220506652</v>
+        <v>-0.00015028077791048042</v>
       </c>
       <c r="M19">
-        <v>2.2851032876457581e-05</v>
+        <v>2.2843894055343036e-05</v>
       </c>
       <c r="N19">
-        <v>4.9306879152243889e-05</v>
+        <v>4.9300053457845741e-05</v>
       </c>
       <c r="O19">
-        <v>4.2640386112416818e-05</v>
+        <v>4.2631616529122682e-05</v>
       </c>
       <c r="P19">
-        <v>2.8901852155131195e-05</v>
+        <v>2.8892822648469074e-05</v>
       </c>
       <c r="Q19">
-        <v>0.00015290423224988701</v>
+        <v>0.00015289556543355881</v>
       </c>
       <c r="R19">
-        <v>6.5610707463617003e-05</v>
+        <v>6.5605083411572184e-05</v>
       </c>
       <c r="S19">
-        <v>-3.1958357735086801e-05</v>
+        <v>-3.1958200906701467e-05</v>
       </c>
       <c r="T19">
-        <v>0.002806910865253703</v>
+        <v>0.0028069101300403116</v>
       </c>
       <c r="U19">
-        <v>0.00033201217204164478</v>
+        <v>0.00033201114459715755</v>
       </c>
       <c r="V19">
-        <v>0.00035605009461404458</v>
+        <v>0.00035605014978948974</v>
       </c>
       <c r="W19">
-        <v>0.00038489494204674345</v>
+        <v>0.00038489454480272268</v>
       </c>
       <c r="X19">
-        <v>0.0015815161396942694</v>
+        <v>0.00035609015579773614</v>
       </c>
     </row>
     <row r="20">
@@ -1973,73 +1973,73 @@
         <v>50</v>
       </c>
       <c r="B20">
-        <v>0.3401716096331488</v>
+        <v>0.34017059044499881</v>
       </c>
       <c r="C20">
-        <v>-1.6929726171922863e-05</v>
+        <v>-1.6930302265998695e-05</v>
       </c>
       <c r="D20">
-        <v>0.00016871663592922417</v>
+        <v>-2.1535077201024439e-05</v>
       </c>
       <c r="E20">
-        <v>-0.00019025226127189249</v>
+        <v>-0.00019024964748715122</v>
       </c>
       <c r="F20">
-        <v>3.7498118066576629e-05</v>
+        <v>3.7496946559498488e-05</v>
       </c>
       <c r="G20">
-        <v>1.1618301981157768e-05</v>
+        <v>1.1618287407189176e-05</v>
       </c>
       <c r="H20">
-        <v>6.1629529262797436e-05</v>
+        <v>6.1628758911100887e-05</v>
       </c>
       <c r="I20">
-        <v>-1.1317385367941544e-05</v>
+        <v>-1.1316703399615107e-05</v>
       </c>
       <c r="J20">
-        <v>-8.4348473741263896e-05</v>
+        <v>-8.4348409378344103e-05</v>
       </c>
       <c r="K20">
-        <v>-6.7102283309917283e-05</v>
+        <v>-6.7102564024877891e-05</v>
       </c>
       <c r="L20">
-        <v>-0.0001627536439591375</v>
+        <v>-0.00016275318016031369</v>
       </c>
       <c r="M20">
-        <v>-3.0056860886744282e-05</v>
+        <v>-3.0058754792146336e-05</v>
       </c>
       <c r="N20">
-        <v>-2.8353646572706025e-06</v>
+        <v>-2.8369510054613358e-06</v>
       </c>
       <c r="O20">
-        <v>-3.08183736132756e-05</v>
+        <v>-3.0817792982529426e-05</v>
       </c>
       <c r="P20">
-        <v>-3.2072151975284449e-05</v>
+        <v>-3.207345260224613e-05</v>
       </c>
       <c r="Q20">
-        <v>-1.560351935279614e-05</v>
+        <v>-1.5604999875911947e-05</v>
       </c>
       <c r="R20">
-        <v>-3.9206288543135664e-05</v>
+        <v>-3.9207255258127006e-05</v>
       </c>
       <c r="S20">
-        <v>-4.2820524119084633e-05</v>
+        <v>-4.2820290373907706e-05</v>
       </c>
       <c r="T20">
-        <v>0.00033201217204164478</v>
+        <v>0.00033201114459715755</v>
       </c>
       <c r="U20">
-        <v>0.0042466804579488291</v>
+        <v>0.0042466795588720196</v>
       </c>
       <c r="V20">
-        <v>0.00042789070015688738</v>
+        <v>0.00042788862498169522</v>
       </c>
       <c r="W20">
-        <v>0.00046212919002346038</v>
+        <v>0.00046212687161064248</v>
       </c>
       <c r="X20">
-        <v>-0.0022393863416426021</v>
+        <v>0.00099488919988803353</v>
       </c>
     </row>
     <row r="21">
@@ -2047,73 +2047,73 @@
         <v>51</v>
       </c>
       <c r="B21">
-        <v>0.41933273280949823</v>
+        <v>0.41933051322313097</v>
       </c>
       <c r="C21">
-        <v>-1.6729840998895316e-05</v>
+        <v>-1.6729711706180123e-05</v>
       </c>
       <c r="D21">
-        <v>0.00011882050598569643</v>
+        <v>-1.5924522668357439e-05</v>
       </c>
       <c r="E21">
-        <v>-0.00013474512706184404</v>
+        <v>-0.00013474371578078349</v>
       </c>
       <c r="F21">
-        <v>2.9926161694933048e-05</v>
+        <v>2.9925794256317707e-05</v>
       </c>
       <c r="G21">
-        <v>3.8741605864164733e-05</v>
+        <v>3.8741080464001795e-05</v>
       </c>
       <c r="H21">
-        <v>0.0002620207638744116</v>
+        <v>0.0002620191602555103</v>
       </c>
       <c r="I21">
-        <v>1.8157987464934808e-05</v>
+        <v>1.8159333328198641e-05</v>
       </c>
       <c r="J21">
-        <v>-3.8108735429636049e-05</v>
+        <v>-3.8109229291328475e-05</v>
       </c>
       <c r="K21">
-        <v>-1.5478070372863979e-05</v>
+        <v>-1.547961679484967e-05</v>
       </c>
       <c r="L21">
-        <v>-6.4630217792316716e-05</v>
+        <v>-6.4631717847807996e-05</v>
       </c>
       <c r="M21">
-        <v>-3.520523061372946e-05</v>
+        <v>-3.5206270989632292e-05</v>
       </c>
       <c r="N21">
-        <v>-2.9510309237540692e-05</v>
+        <v>-2.9512044145471659e-05</v>
       </c>
       <c r="O21">
-        <v>-4.8977232810807161e-05</v>
+        <v>-4.8975607964531621e-05</v>
       </c>
       <c r="P21">
-        <v>-3.5883572139240941e-05</v>
+        <v>-3.5885215201416081e-05</v>
       </c>
       <c r="Q21">
-        <v>-4.9391358686804842e-05</v>
+        <v>-4.9392499122509373e-05</v>
       </c>
       <c r="R21">
-        <v>-7.6601391362328105e-05</v>
+        <v>-7.6603401658696386e-05</v>
       </c>
       <c r="S21">
-        <v>-5.1902418439418456e-05</v>
+        <v>-5.190217687613927e-05</v>
       </c>
       <c r="T21">
-        <v>0.00035605009461404458</v>
+        <v>0.00035605014978948974</v>
       </c>
       <c r="U21">
-        <v>0.00042789070015688738</v>
+        <v>0.00042788862498169522</v>
       </c>
       <c r="V21">
-        <v>0.0020087159162776335</v>
+        <v>0.0020087136516202019</v>
       </c>
       <c r="W21">
-        <v>0.00054469311235799938</v>
+        <v>0.00054469042251637651</v>
       </c>
       <c r="X21">
-        <v>-0.0014450452046893365</v>
+        <v>0.00084561858084993761</v>
       </c>
     </row>
     <row r="22">
@@ -2121,73 +2121,73 @@
         <v>52</v>
       </c>
       <c r="B22">
-        <v>0.26057031782376838</v>
+        <v>0.26056826108764686</v>
       </c>
       <c r="C22">
-        <v>2.9216649903653991e-05</v>
+        <v>2.9216267533437298e-05</v>
       </c>
       <c r="D22">
-        <v>0.00011560415401382952</v>
+        <v>-7.9848367730172469e-06</v>
       </c>
       <c r="E22">
-        <v>-0.00012358938128425971</v>
+        <v>-0.00012358751192967344</v>
       </c>
       <c r="F22">
-        <v>2.567965025156117e-06</v>
+        <v>2.5668704388639605e-06</v>
       </c>
       <c r="G22">
-        <v>4.4605492709096529e-05</v>
+        <v>4.4606115886502962e-05</v>
       </c>
       <c r="H22">
-        <v>0.0001472398772038822</v>
+        <v>0.0001472388666721383</v>
       </c>
       <c r="I22">
-        <v>-3.2135624532412009e-05</v>
+        <v>-3.2134967341227819e-05</v>
       </c>
       <c r="J22">
-        <v>-7.7107325670070209e-06</v>
+        <v>-7.7111327278098435e-06</v>
       </c>
       <c r="K22">
-        <v>3.1541556483074846e-05</v>
+        <v>3.1540406941475783e-05</v>
       </c>
       <c r="L22">
-        <v>-3.5149684232688248e-05</v>
+        <v>-3.5151370033865829e-05</v>
       </c>
       <c r="M22">
-        <v>-5.5574613304413515e-05</v>
+        <v>-5.5574648317858457e-05</v>
       </c>
       <c r="N22">
-        <v>-4.7447764792684635e-05</v>
+        <v>-4.7447769892382643e-05</v>
       </c>
       <c r="O22">
-        <v>-2.6944114635863619e-05</v>
+        <v>-2.694158706709692e-05</v>
       </c>
       <c r="P22">
-        <v>-4.8243239997314345e-05</v>
+        <v>-4.8243077861052897e-05</v>
       </c>
       <c r="Q22">
-        <v>-8.0543466674808258e-05</v>
+        <v>-8.0542882071318509e-05</v>
       </c>
       <c r="R22">
-        <v>-6.7721794015233199e-05</v>
+        <v>-6.7721247831995673e-05</v>
       </c>
       <c r="S22">
-        <v>-6.1496128085235122e-05</v>
+        <v>-6.1495867770999216e-05</v>
       </c>
       <c r="T22">
-        <v>0.00038489494204674345</v>
+        <v>0.00038489454480272268</v>
       </c>
       <c r="U22">
-        <v>0.00046212919002346038</v>
+        <v>0.00046212687161064248</v>
       </c>
       <c r="V22">
-        <v>0.00054469311235799938</v>
+        <v>0.00054469042251637651</v>
       </c>
       <c r="W22">
-        <v>0.0019701660158234083</v>
+        <v>0.0019701635726684483</v>
       </c>
       <c r="X22">
-        <v>-0.0011619669450318182</v>
+        <v>0.00093904132100188279</v>
       </c>
     </row>
     <row r="23">
@@ -2195,73 +2195,73 @@
         <v>53</v>
       </c>
       <c r="B23">
-        <v>-22.777681923327435</v>
+        <v>3.356046230563523</v>
       </c>
       <c r="C23">
-        <v>-0.0011421058980991157</v>
+        <v>-0.00026782037041550523</v>
       </c>
       <c r="D23">
-        <v>-0.034068304683519832</v>
+        <v>-0.0017924371667468965</v>
       </c>
       <c r="E23">
-        <v>0.037329020849452166</v>
+        <v>-0.0057993087758113574</v>
       </c>
       <c r="F23">
-        <v>-0.0057985832469997951</v>
+        <v>0.0035692276467660811</v>
       </c>
       <c r="G23">
-        <v>0.00094012714511956157</v>
+        <v>-0.00246090698286843</v>
       </c>
       <c r="H23">
-        <v>-0.0087091976760404581</v>
+        <v>-0.00010043214947687935</v>
       </c>
       <c r="I23">
-        <v>-0.00063166482585753697</v>
+        <v>-0.00050835998413518773</v>
       </c>
       <c r="J23">
-        <v>-0.004887594910949926</v>
+        <v>-0.0025009936575565114</v>
       </c>
       <c r="K23">
-        <v>-0.0083148960405415445</v>
+        <v>-0.0042472755154065941</v>
       </c>
       <c r="L23">
-        <v>-0.0078344464290013675</v>
+        <v>-0.0045334035957148369</v>
       </c>
       <c r="M23">
-        <v>-0.0048819682986149891</v>
+        <v>-0.0034036755612217328</v>
       </c>
       <c r="N23">
-        <v>-0.0037597706085894063</v>
+        <v>-0.003106592029700316</v>
       </c>
       <c r="O23">
-        <v>-0.0039998827815752895</v>
+        <v>-0.003050127409013211</v>
       </c>
       <c r="P23">
-        <v>-0.0043026246343775849</v>
+        <v>-0.0034833036844281588</v>
       </c>
       <c r="Q23">
-        <v>-0.0039917000963350449</v>
+        <v>-0.0033494268064500916</v>
       </c>
       <c r="R23">
-        <v>-0.00373289604320955</v>
+        <v>-0.0036125684484087962</v>
       </c>
       <c r="S23">
-        <v>-0.0001550940309811374</v>
+        <v>-0.00020014573082023952</v>
       </c>
       <c r="T23">
-        <v>0.0015815161396942694</v>
+        <v>0.00035609015579773614</v>
       </c>
       <c r="U23">
-        <v>-0.0022393863416426021</v>
+        <v>0.00099488919988803353</v>
       </c>
       <c r="V23">
-        <v>-0.0014450452046893365</v>
+        <v>0.00084561858084993761</v>
       </c>
       <c r="W23">
-        <v>-0.0011619669450318182</v>
+        <v>0.00093904132100188279</v>
       </c>
       <c r="X23">
-        <v>0.58069563771739219</v>
+        <v>0.044690740252647215</v>
       </c>
     </row>
   </sheetData>
@@ -2355,76 +2355,76 @@
         <v>32</v>
       </c>
       <c r="B2">
-        <v>-0.12335951518423222</v>
+        <v>-0.10516592963401891</v>
       </c>
       <c r="C2">
-        <v>0.0010263188482494614</v>
+        <v>0.0010414703858404382</v>
       </c>
       <c r="D2">
-        <v>1.9770337033769216e-05</v>
+        <v>2.2689686324859411e-05</v>
       </c>
       <c r="E2">
-        <v>-1.1344446212514782e-07</v>
+        <v>-1.401745090157859e-07</v>
       </c>
       <c r="F2">
-        <v>0.0001305604986741176</v>
+        <v>4.7898491892627563e-05</v>
       </c>
       <c r="G2">
-        <v>-4.6953982352436669e-05</v>
+        <v>-6.2665817317111367e-05</v>
       </c>
       <c r="H2">
-        <v>-8.2967655155957541e-06</v>
+        <v>-2.8272501896750454e-05</v>
       </c>
       <c r="I2">
-        <v>-2.9130691504846969e-05</v>
+        <v>-9.3251104221907938e-05</v>
       </c>
       <c r="J2">
-        <v>9.279445759539256e-05</v>
+        <v>0.00030103970649047389</v>
       </c>
       <c r="K2">
-        <v>0.00011869882155937785</v>
+        <v>9.6947005363065466e-05</v>
       </c>
       <c r="L2">
-        <v>7.7485199431631062e-05</v>
+        <v>8.7501969426333358e-05</v>
       </c>
       <c r="M2">
-        <v>0.00010307607714710979</v>
+        <v>4.4072736987518614e-05</v>
       </c>
       <c r="N2">
-        <v>-0.00016137487932603998</v>
+        <v>-0.00024798988705884847</v>
       </c>
       <c r="O2">
-        <v>5.5580705715231322e-05</v>
+        <v>-4.3354700673628335e-05</v>
       </c>
       <c r="P2">
-        <v>-0.00014712627961490559</v>
+        <v>-0.00014200963026318346</v>
       </c>
       <c r="Q2">
-        <v>-0.00013905400908720245</v>
+        <v>-0.00012522312480704311</v>
       </c>
       <c r="R2">
-        <v>-0.00030572636535757664</v>
+        <v>-0.00030147975062645856</v>
       </c>
       <c r="S2">
-        <v>-0.00011169895751166531</v>
+        <v>-0.00010618077141089381</v>
       </c>
       <c r="T2">
-        <v>-0.00023702489388634145</v>
+        <v>-0.00023626449790101856</v>
       </c>
       <c r="U2">
-        <v>-0.0001052849513155987</v>
+        <v>-0.0001067016134874232</v>
       </c>
       <c r="V2">
-        <v>-4.5097523308253304e-07</v>
+        <v>-1.8578409950131022e-05</v>
       </c>
       <c r="W2">
-        <v>-1.5435887112877119e-07</v>
+        <v>3.6957396003354273e-07</v>
       </c>
       <c r="X2">
-        <v>0.00040515824311563778</v>
+        <v>0.00040605087269702308</v>
       </c>
       <c r="Y2">
-        <v>-0.00078231217948731397</v>
+        <v>-0.00064072713251467611</v>
       </c>
     </row>
     <row r="3">
@@ -2432,76 +2432,76 @@
         <v>33</v>
       </c>
       <c r="B3">
-        <v>-0.2784254154626738</v>
+        <v>-0.27718535375410508</v>
       </c>
       <c r="C3">
-        <v>1.9770337033769216e-05</v>
+        <v>2.2689686324859411e-05</v>
       </c>
       <c r="D3">
-        <v>6.2304642041479544e-05</v>
+        <v>6.2109706963282306e-05</v>
       </c>
       <c r="E3">
-        <v>-6.7450874203429087e-07</v>
+        <v>-6.7919828341109835e-07</v>
       </c>
       <c r="F3">
-        <v>-0.00015637650776053607</v>
+        <v>-0.00014851875007472636</v>
       </c>
       <c r="G3">
-        <v>-6.4595368238345606e-05</v>
+        <v>-6.4594788351051986e-05</v>
       </c>
       <c r="H3">
-        <v>0.0001233425813489588</v>
+        <v>0.00012766222915591274</v>
       </c>
       <c r="I3">
-        <v>6.6189747597079863e-05</v>
+        <v>7.5707544513289762e-05</v>
       </c>
       <c r="J3">
-        <v>-2.3788423798261848e-05</v>
+        <v>-5.2432708882674066e-05</v>
       </c>
       <c r="K3">
-        <v>2.6802266137555792e-05</v>
+        <v>4.5115871436520117e-05</v>
       </c>
       <c r="L3">
-        <v>4.1490763368514082e-06</v>
+        <v>5.5894183560801627e-06</v>
       </c>
       <c r="M3">
-        <v>8.1455575184811047e-05</v>
+        <v>8.8339397258271955e-05</v>
       </c>
       <c r="N3">
-        <v>3.0232086566340838e-05</v>
+        <v>3.6260641992722257e-05</v>
       </c>
       <c r="O3">
-        <v>6.1672242337944445e-05</v>
+        <v>7.3638442767134157e-05</v>
       </c>
       <c r="P3">
-        <v>-9.2018241352017065e-05</v>
+        <v>-9.4467209312991624e-05</v>
       </c>
       <c r="Q3">
-        <v>-8.247356632221938e-05</v>
+        <v>-8.4259634673183089e-05</v>
       </c>
       <c r="R3">
-        <v>-0.00014702202221685259</v>
+        <v>-0.0001534083384292492</v>
       </c>
       <c r="S3">
-        <v>-9.4183580531167045e-05</v>
+        <v>-9.6273463748948332e-05</v>
       </c>
       <c r="T3">
-        <v>-9.8696738343614199e-05</v>
+        <v>-0.00010269571052179063</v>
       </c>
       <c r="U3">
-        <v>-8.4830482037715502e-05</v>
+        <v>-8.7694124992735865e-05</v>
       </c>
       <c r="V3">
-        <v>1.8879868408814768e-06</v>
+        <v>2.1588259854252818e-06</v>
       </c>
       <c r="W3">
-        <v>-2.986566566533992e-08</v>
+        <v>-3.6527149167597014e-08</v>
       </c>
       <c r="X3">
-        <v>0.00013799114114260798</v>
+        <v>0.00014318931613301316</v>
       </c>
       <c r="Y3">
-        <v>-0.0011418651733905343</v>
+        <v>-0.0011462157289324768</v>
       </c>
     </row>
     <row r="4">
@@ -2509,76 +2509,76 @@
         <v>55</v>
       </c>
       <c r="B4">
-        <v>0.0025423206278136</v>
+        <v>0.0025357016355371104</v>
       </c>
       <c r="C4">
-        <v>-1.1344446212514782e-07</v>
+        <v>-1.401745090157859e-07</v>
       </c>
       <c r="D4">
-        <v>-6.7450874203429087e-07</v>
+        <v>-6.7919828341109835e-07</v>
       </c>
       <c r="E4">
-        <v>7.4963566545554145e-09</v>
+        <v>7.6406709953534946e-09</v>
       </c>
       <c r="F4">
-        <v>1.6822573796108074e-06</v>
+        <v>1.6207731948509151e-06</v>
       </c>
       <c r="G4">
-        <v>7.0873866200974718e-07</v>
+        <v>7.1009551664734623e-07</v>
       </c>
       <c r="H4">
-        <v>-1.3318713733695255e-06</v>
+        <v>-1.3886701539828775e-06</v>
       </c>
       <c r="I4">
-        <v>-8.4311965545320949e-07</v>
+        <v>-9.5922416645605086e-07</v>
       </c>
       <c r="J4">
-        <v>3.1268467717826739e-07</v>
+        <v>6.8302643421499648e-07</v>
       </c>
       <c r="K4">
-        <v>-2.3656557657970406e-07</v>
+        <v>-4.3777024707720391e-07</v>
       </c>
       <c r="L4">
-        <v>-1.015181768263723e-07</v>
+        <v>-1.1630476870012958e-07</v>
       </c>
       <c r="M4">
-        <v>-9.801323605569858e-07</v>
+        <v>-1.0716737691840824e-06</v>
       </c>
       <c r="N4">
-        <v>-3.7684438499711829e-07</v>
+        <v>-4.614025020600736e-07</v>
       </c>
       <c r="O4">
-        <v>-8.4175355510667989e-07</v>
+        <v>-1.0040026530557901e-06</v>
       </c>
       <c r="P4">
-        <v>1.0479529721598419e-06</v>
+        <v>1.0889955995314589e-06</v>
       </c>
       <c r="Q4">
-        <v>9.7768489001470958e-07</v>
+        <v>1.0186033031790421e-06</v>
       </c>
       <c r="R4">
-        <v>1.6662088472752944e-06</v>
+        <v>1.7586514952034964e-06</v>
       </c>
       <c r="S4">
-        <v>1.1042349509448927e-06</v>
+        <v>1.1423584650951928e-06</v>
       </c>
       <c r="T4">
-        <v>1.1460042064690112e-06</v>
+        <v>1.2044401160805025e-06</v>
       </c>
       <c r="U4">
-        <v>1.014605839650147e-06</v>
+        <v>1.0586655867577116e-06</v>
       </c>
       <c r="V4">
-        <v>-1.3652395972898416e-08</v>
+        <v>-2.076352929334024e-08</v>
       </c>
       <c r="W4">
-        <v>7.191387132339477e-11</v>
+        <v>2.6096527946280807e-10</v>
       </c>
       <c r="X4">
-        <v>-1.4878247063804279e-06</v>
+        <v>-1.553139525100811e-06</v>
       </c>
       <c r="Y4">
-        <v>1.2149445833475276e-05</v>
+        <v>1.2330475292843683e-05</v>
       </c>
     </row>
     <row r="5">
@@ -2586,76 +2586,76 @@
         <v>56</v>
       </c>
       <c r="B5">
-        <v>-0.68690144028644828</v>
+        <v>-0.73250707416732597</v>
       </c>
       <c r="C5">
-        <v>0.0001305604986741176</v>
+        <v>4.7898491892627563e-05</v>
       </c>
       <c r="D5">
-        <v>-0.00015637650776053607</v>
+        <v>-0.00014851875007472636</v>
       </c>
       <c r="E5">
-        <v>1.6822573796108074e-06</v>
+        <v>1.6207731948509151e-06</v>
       </c>
       <c r="F5">
-        <v>0.0031891898461017675</v>
+        <v>0.0030362600533719183</v>
       </c>
       <c r="G5">
-        <v>2.4482085200723145e-05</v>
+        <v>6.179614481721012e-05</v>
       </c>
       <c r="H5">
-        <v>-5.9612035390465906e-05</v>
+        <v>2.2166240914944465e-05</v>
       </c>
       <c r="I5">
-        <v>-0.00061266592896367972</v>
+        <v>-0.00046359002183755417</v>
       </c>
       <c r="J5">
-        <v>-0.00026214016576745034</v>
+        <v>-0.00055639725060458074</v>
       </c>
       <c r="K5">
-        <v>-0.00098399175298390356</v>
+        <v>-0.00091510875205691705</v>
       </c>
       <c r="L5">
-        <v>0.00018686297664680953</v>
+        <v>8.6356717252268359e-05</v>
       </c>
       <c r="M5">
-        <v>-0.00088022949061900631</v>
+        <v>-0.00076715276307682406</v>
       </c>
       <c r="N5">
-        <v>-0.00073381814249405032</v>
+        <v>-0.00057828191856048824</v>
       </c>
       <c r="O5">
-        <v>-0.00057663168183453824</v>
+        <v>-0.00039592467716675147</v>
       </c>
       <c r="P5">
-        <v>0.00045333071601917499</v>
+        <v>0.00038918850312243212</v>
       </c>
       <c r="Q5">
-        <v>0.00043471408465598155</v>
+        <v>0.00037730115177640874</v>
       </c>
       <c r="R5">
-        <v>0.00044431568107399769</v>
+        <v>0.00037182164260355169</v>
       </c>
       <c r="S5">
-        <v>0.00034141739371359439</v>
+        <v>0.00027991125727617246</v>
       </c>
       <c r="T5">
-        <v>0.00029227640866403648</v>
+        <v>0.00019965189751300469</v>
       </c>
       <c r="U5">
-        <v>0.00034648903732523975</v>
+        <v>0.00028409978934083077</v>
       </c>
       <c r="V5">
-        <v>8.9164045851898967e-05</v>
+        <v>0.00010188428781165038</v>
       </c>
       <c r="W5">
-        <v>-2.0513277986783357e-06</v>
+        <v>-2.4806172044277065e-06</v>
       </c>
       <c r="X5">
-        <v>-0.00038583197251775643</v>
+        <v>-0.00033826202136013359</v>
       </c>
       <c r="Y5">
-        <v>0.0021216745808754368</v>
+        <v>0.0018597307786262195</v>
       </c>
     </row>
     <row r="6">
@@ -2663,76 +2663,76 @@
         <v>57</v>
       </c>
       <c r="B6">
-        <v>-0.012839109716243115</v>
+        <v>-0.00020654906223617522</v>
       </c>
       <c r="C6">
-        <v>-4.6953982352436669e-05</v>
+        <v>-6.2665817317111367e-05</v>
       </c>
       <c r="D6">
-        <v>-6.4595368238345606e-05</v>
+        <v>-6.4594788351051986e-05</v>
       </c>
       <c r="E6">
-        <v>7.0873866200974718e-07</v>
+        <v>7.1009551664734623e-07</v>
       </c>
       <c r="F6">
-        <v>2.4482085200723145e-05</v>
+        <v>6.179614481721012e-05</v>
       </c>
       <c r="G6">
-        <v>0.0017141231928165259</v>
+        <v>0.0016770775061145697</v>
       </c>
       <c r="H6">
-        <v>0.00066858985017792137</v>
+        <v>0.00065890715562034324</v>
       </c>
       <c r="I6">
-        <v>-5.260018293022135e-05</v>
+        <v>-6.0481085084913866e-05</v>
       </c>
       <c r="J6">
-        <v>3.1968357835038079e-06</v>
+        <v>-3.2970900957301011e-05</v>
       </c>
       <c r="K6">
-        <v>8.7197090384412369e-05</v>
+        <v>5.2755928004254773e-05</v>
       </c>
       <c r="L6">
-        <v>-0.00011993320927850591</v>
+        <v>-9.699410517809151e-05</v>
       </c>
       <c r="M6">
-        <v>-5.9888555008695869e-05</v>
+        <v>-6.4747722016447154e-05</v>
       </c>
       <c r="N6">
-        <v>8.2709698929671555e-05</v>
+        <v>9.2795118525209133e-05</v>
       </c>
       <c r="O6">
-        <v>-0.0002869173384438517</v>
+        <v>-0.00029295529434542853</v>
       </c>
       <c r="P6">
-        <v>-1.4713406266438642e-05</v>
+        <v>-1.878125672484369e-05</v>
       </c>
       <c r="Q6">
-        <v>-0.00013840414846298362</v>
+        <v>-0.00013856462330770573</v>
       </c>
       <c r="R6">
-        <v>0.00020728802717378007</v>
+        <v>0.00021377016904325558</v>
       </c>
       <c r="S6">
-        <v>3.5230936701424786e-05</v>
+        <v>2.4593469304240814e-05</v>
       </c>
       <c r="T6">
-        <v>9.7094084690957388e-05</v>
+        <v>0.00010310362064095571</v>
       </c>
       <c r="U6">
-        <v>6.0713086828814104e-06</v>
+        <v>-2.7361004778752966e-07</v>
       </c>
       <c r="V6">
-        <v>6.3083784258589052e-05</v>
+        <v>7.0075343305214235e-05</v>
       </c>
       <c r="W6">
-        <v>-1.7662675331666006e-06</v>
+        <v>-1.9475581026191977e-06</v>
       </c>
       <c r="X6">
-        <v>-0.00030288121258248467</v>
+        <v>-0.00031986747097120869</v>
       </c>
       <c r="Y6">
-        <v>-5.1157242649800885e-05</v>
+        <v>-8.5958005699835263e-05</v>
       </c>
     </row>
     <row r="7">
@@ -2740,76 +2740,76 @@
         <v>58</v>
       </c>
       <c r="B7">
-        <v>-0.4622756931237248</v>
+        <v>-0.47965387673722154</v>
       </c>
       <c r="C7">
-        <v>-8.2967655155957541e-06</v>
+        <v>-2.8272501896750454e-05</v>
       </c>
       <c r="D7">
-        <v>0.0001233425813489588</v>
+        <v>0.00012766222915591274</v>
       </c>
       <c r="E7">
-        <v>-1.3318713733695255e-06</v>
+        <v>-1.3886701539828775e-06</v>
       </c>
       <c r="F7">
-        <v>-5.9612035390465906e-05</v>
+        <v>2.2166240914944465e-05</v>
       </c>
       <c r="G7">
-        <v>0.00066858985017792137</v>
+        <v>0.00065890715562034324</v>
       </c>
       <c r="H7">
-        <v>0.0017511380540055751</v>
+        <v>0.0018271581295787862</v>
       </c>
       <c r="I7">
-        <v>-0.00034895311116687577</v>
+        <v>-0.00026456376505132827</v>
       </c>
       <c r="J7">
-        <v>-0.00012582313623023532</v>
+        <v>-0.00042522202352942705</v>
       </c>
       <c r="K7">
-        <v>0.00014056301940321942</v>
+        <v>0.00024471381668401493</v>
       </c>
       <c r="L7">
-        <v>7.6702942285277839e-05</v>
+        <v>5.7520290748594503e-05</v>
       </c>
       <c r="M7">
-        <v>0.00012034118039045745</v>
+        <v>0.00019991471964613921</v>
       </c>
       <c r="N7">
-        <v>2.6484486818118165e-05</v>
+        <v>0.00011996605467738653</v>
       </c>
       <c r="O7">
-        <v>-0.0001002682580491022</v>
+        <v>4.3935556218021449e-06</v>
       </c>
       <c r="P7">
-        <v>-0.00055073786407386079</v>
+        <v>-0.00060393342880913216</v>
       </c>
       <c r="Q7">
-        <v>-0.00059048181485999514</v>
+        <v>-0.00063608904394316926</v>
       </c>
       <c r="R7">
-        <v>-0.00061470706142919326</v>
+        <v>-0.00068492230749241123</v>
       </c>
       <c r="S7">
-        <v>-0.00070328673173986013</v>
+        <v>-0.00076683805291578497</v>
       </c>
       <c r="T7">
-        <v>-0.00070380274549863863</v>
+        <v>-0.00076198019743176819</v>
       </c>
       <c r="U7">
-        <v>-0.00083406685264045971</v>
+        <v>-0.00090537719573867469</v>
       </c>
       <c r="V7">
-        <v>-3.6547808124052107e-05</v>
+        <v>-1.1840614098766571e-05</v>
       </c>
       <c r="W7">
-        <v>1.5486314260097478e-06</v>
+        <v>8.231670790197127e-07</v>
       </c>
       <c r="X7">
-        <v>0.00070286816011258936</v>
+        <v>0.00076866577025371593</v>
       </c>
       <c r="Y7">
-        <v>-0.0021188255796329852</v>
+        <v>-0.002393620323857786</v>
       </c>
     </row>
     <row r="8">
@@ -2817,76 +2817,76 @@
         <v>59</v>
       </c>
       <c r="B8">
-        <v>0.97718117221387224</v>
+        <v>0.92193513989901754</v>
       </c>
       <c r="C8">
-        <v>-2.9130691504846969e-05</v>
+        <v>-9.3251104221907938e-05</v>
       </c>
       <c r="D8">
-        <v>6.6189747597079863e-05</v>
+        <v>7.5707544513289762e-05</v>
       </c>
       <c r="E8">
-        <v>-8.4311965545320949e-07</v>
+        <v>-9.5922416645605086e-07</v>
       </c>
       <c r="F8">
-        <v>-0.00061266592896367972</v>
+        <v>-0.00046359002183755417</v>
       </c>
       <c r="G8">
-        <v>-5.260018293022135e-05</v>
+        <v>-6.0481085084913866e-05</v>
       </c>
       <c r="H8">
-        <v>-0.00034895311116687577</v>
+        <v>-0.00026456376505132827</v>
       </c>
       <c r="I8">
-        <v>0.0028190720490790027</v>
+        <v>0.0029761776884421184</v>
       </c>
       <c r="J8">
-        <v>-0.00043252902230919699</v>
+        <v>-0.0011005981332492614</v>
       </c>
       <c r="K8">
-        <v>0.0004120360544030281</v>
+        <v>0.00054985521688195513</v>
       </c>
       <c r="L8">
-        <v>-0.00030904300640025614</v>
+        <v>-0.00033136477948154453</v>
       </c>
       <c r="M8">
-        <v>0.0014433650839545081</v>
+        <v>0.0016217232868646402</v>
       </c>
       <c r="N8">
-        <v>0.0019455526376898733</v>
+        <v>0.0021595988399374312</v>
       </c>
       <c r="O8">
-        <v>0.0024970333395245266</v>
+        <v>0.0027854310682906927</v>
       </c>
       <c r="P8">
-        <v>0.00032572740962724472</v>
+        <v>0.00026730891549349</v>
       </c>
       <c r="Q8">
-        <v>0.00019408848791097879</v>
+        <v>0.00011053670031022393</v>
       </c>
       <c r="R8">
-        <v>2.4960314329084603e-05</v>
+        <v>-5.9101070147346145e-05</v>
       </c>
       <c r="S8">
-        <v>0.00038844943392911564</v>
+        <v>0.00031775102884600589</v>
       </c>
       <c r="T8">
-        <v>0.00036119172476176728</v>
+        <v>0.0002842391503959658</v>
       </c>
       <c r="U8">
-        <v>0.00040991226210796978</v>
+        <v>0.00036062273277431806</v>
       </c>
       <c r="V8">
-        <v>-0.00013970880946656994</v>
+        <v>-8.8788849494841893e-05</v>
       </c>
       <c r="W8">
-        <v>4.1629591432266291e-06</v>
+        <v>2.6912062540689982e-06</v>
       </c>
       <c r="X8">
-        <v>-0.00044564754570640804</v>
+        <v>-0.00039793735217381291</v>
       </c>
       <c r="Y8">
-        <v>-0.0027662965536723039</v>
+        <v>-0.0033765804724193091</v>
       </c>
     </row>
     <row r="9">
@@ -2894,76 +2894,76 @@
         <v>60</v>
       </c>
       <c r="B9">
-        <v>0.2394780216889946</v>
+        <v>0.54435185271379372</v>
       </c>
       <c r="C9">
-        <v>9.279445759539256e-05</v>
+        <v>0.00030103970649047389</v>
       </c>
       <c r="D9">
-        <v>-2.3788423798261848e-05</v>
+        <v>-5.2432708882674066e-05</v>
       </c>
       <c r="E9">
-        <v>3.1268467717826739e-07</v>
+        <v>6.8302643421499648e-07</v>
       </c>
       <c r="F9">
-        <v>-0.00026214016576745034</v>
+        <v>-0.00055639725060458074</v>
       </c>
       <c r="G9">
-        <v>3.1968357835038079e-06</v>
+        <v>-3.2970900957301011e-05</v>
       </c>
       <c r="H9">
-        <v>-0.00012582313623023532</v>
+        <v>-0.00042522202352942705</v>
       </c>
       <c r="I9">
-        <v>-0.00043252902230919699</v>
+        <v>-0.0011005981332492614</v>
       </c>
       <c r="J9">
-        <v>0.00046288659378846157</v>
+        <v>0.0020327817548398516</v>
       </c>
       <c r="K9">
-        <v>-0.00032218325915392589</v>
+        <v>-0.00078473093729380776</v>
       </c>
       <c r="L9">
-        <v>3.9563460748144065e-05</v>
+        <v>0.00021409305721117929</v>
       </c>
       <c r="M9">
-        <v>-0.00039030739345362298</v>
+        <v>-0.0010100957327043606</v>
       </c>
       <c r="N9">
-        <v>-0.00046994859560092186</v>
+        <v>-0.0012569933008860269</v>
       </c>
       <c r="O9">
-        <v>-0.0006130588543436583</v>
+        <v>-0.0015750970317906245</v>
       </c>
       <c r="P9">
-        <v>9.2535730059970628e-05</v>
+        <v>0.00033158422513532391</v>
       </c>
       <c r="Q9">
-        <v>0.00019922673778941847</v>
+        <v>0.00053359369552858759</v>
       </c>
       <c r="R9">
-        <v>9.2426686076226944e-05</v>
+        <v>0.00037364489954270911</v>
       </c>
       <c r="S9">
-        <v>0.00011731721699984266</v>
+        <v>0.00038483094944704438</v>
       </c>
       <c r="T9">
-        <v>0.00012349567934292002</v>
+        <v>0.00041644311192637579</v>
       </c>
       <c r="U9">
-        <v>4.4878628591466083e-05</v>
+        <v>0.00025372480023800351</v>
       </c>
       <c r="V9">
-        <v>-4.6755681448801652e-05</v>
+        <v>-0.00016832105619892304</v>
       </c>
       <c r="W9">
-        <v>1.2992407812464517e-06</v>
+        <v>4.9035815633145568e-06</v>
       </c>
       <c r="X9">
-        <v>-0.00013597277229144471</v>
+        <v>-0.00040854721365483963</v>
       </c>
       <c r="Y9">
-        <v>0.0010800472323120403</v>
+        <v>0.0027713651713157134</v>
       </c>
     </row>
     <row r="10">
@@ -2971,76 +2971,76 @@
         <v>61</v>
       </c>
       <c r="B10">
-        <v>-0.67267026927200513</v>
+        <v>-0.73154584549397561</v>
       </c>
       <c r="C10">
-        <v>0.00011869882155937785</v>
+        <v>9.6947005363065466e-05</v>
       </c>
       <c r="D10">
-        <v>2.6802266137555792e-05</v>
+        <v>4.5115871436520117e-05</v>
       </c>
       <c r="E10">
-        <v>-2.3656557657970406e-07</v>
+        <v>-4.3777024707720391e-07</v>
       </c>
       <c r="F10">
-        <v>-0.00098399175298390356</v>
+        <v>-0.00091510875205691705</v>
       </c>
       <c r="G10">
-        <v>8.7197090384412369e-05</v>
+        <v>5.2755928004254773e-05</v>
       </c>
       <c r="H10">
-        <v>0.00014056301940321942</v>
+        <v>0.00024471381668401493</v>
       </c>
       <c r="I10">
-        <v>0.0004120360544030281</v>
+        <v>0.00054985521688195513</v>
       </c>
       <c r="J10">
-        <v>-0.00032218325915392589</v>
+        <v>-0.00078473093729380776</v>
       </c>
       <c r="K10">
-        <v>0.0076757538564956561</v>
+        <v>0.007908938803011481</v>
       </c>
       <c r="L10">
-        <v>7.5011967372844478e-06</v>
+        <v>-5.9621882055222791e-05</v>
       </c>
       <c r="M10">
-        <v>0.00049803353520960899</v>
+        <v>0.00065642954588992759</v>
       </c>
       <c r="N10">
-        <v>0.00069948082697416974</v>
+        <v>0.00082310988417206741</v>
       </c>
       <c r="O10">
-        <v>0.00079152241918167138</v>
+        <v>0.00091196983084443199</v>
       </c>
       <c r="P10">
-        <v>-0.00013288411796790465</v>
+        <v>-0.00017766968487757629</v>
       </c>
       <c r="Q10">
-        <v>-0.0003324778211371217</v>
+        <v>-0.00035781440481182016</v>
       </c>
       <c r="R10">
-        <v>-7.9194054610868915e-05</v>
+        <v>-0.00015080789714692574</v>
       </c>
       <c r="S10">
-        <v>1.9321746008622159e-05</v>
+        <v>4.661275663022746e-05</v>
       </c>
       <c r="T10">
-        <v>-0.00029517612000919135</v>
+        <v>-0.00031975594095281042</v>
       </c>
       <c r="U10">
-        <v>-0.00017511221270137488</v>
+        <v>-0.00024261148215842641</v>
       </c>
       <c r="V10">
-        <v>-8.292994522919028e-05</v>
+        <v>-6.1980961358985257e-05</v>
       </c>
       <c r="W10">
-        <v>2.611267781523658e-06</v>
+        <v>2.0787268949662982e-06</v>
       </c>
       <c r="X10">
-        <v>0.00015339360454543762</v>
+        <v>0.00021651875307818864</v>
       </c>
       <c r="Y10">
-        <v>-0.0004829792299682592</v>
+        <v>-0.0010801616550446323</v>
       </c>
     </row>
     <row r="11">
@@ -3048,76 +3048,76 @@
         <v>38</v>
       </c>
       <c r="B11">
-        <v>0.21148960652792737</v>
+        <v>0.20470339341355118</v>
       </c>
       <c r="C11">
-        <v>7.7485199431631062e-05</v>
+        <v>8.7501969426333358e-05</v>
       </c>
       <c r="D11">
-        <v>4.1490763368514082e-06</v>
+        <v>5.5894183560801627e-06</v>
       </c>
       <c r="E11">
-        <v>-1.015181768263723e-07</v>
+        <v>-1.1630476870012958e-07</v>
       </c>
       <c r="F11">
-        <v>0.00018686297664680953</v>
+        <v>8.6356717252268359e-05</v>
       </c>
       <c r="G11">
-        <v>-0.00011993320927850591</v>
+        <v>-9.699410517809151e-05</v>
       </c>
       <c r="H11">
-        <v>7.6702942285277839e-05</v>
+        <v>5.7520290748594503e-05</v>
       </c>
       <c r="I11">
-        <v>-0.00030904300640025614</v>
+        <v>-0.00033136477948154453</v>
       </c>
       <c r="J11">
-        <v>3.9563460748144065e-05</v>
+        <v>0.00021409305721117929</v>
       </c>
       <c r="K11">
-        <v>7.5011967372844478e-06</v>
+        <v>-5.9621882055222791e-05</v>
       </c>
       <c r="L11">
-        <v>0.0023692153017712435</v>
+        <v>0.0023314396716454969</v>
       </c>
       <c r="M11">
-        <v>0.00090597402657771045</v>
+        <v>0.00087701668519313898</v>
       </c>
       <c r="N11">
-        <v>0.00082969159077514389</v>
+        <v>0.00079115130447603794</v>
       </c>
       <c r="O11">
-        <v>0.00089583423980372308</v>
+        <v>0.00085820400072814931</v>
       </c>
       <c r="P11">
-        <v>-0.00028624902585771119</v>
+        <v>-0.00028715978742984555</v>
       </c>
       <c r="Q11">
-        <v>-0.00031531627888759027</v>
+        <v>-0.00032287123491371941</v>
       </c>
       <c r="R11">
-        <v>-0.00013739269309938603</v>
+        <v>-0.00014823362481000983</v>
       </c>
       <c r="S11">
-        <v>-0.00023900550001831953</v>
+        <v>-0.00023177558722434612</v>
       </c>
       <c r="T11">
-        <v>-0.00018580742745564791</v>
+        <v>-0.00019470231209771309</v>
       </c>
       <c r="U11">
-        <v>-0.00017143974310056541</v>
+        <v>-0.00017025064309124908</v>
       </c>
       <c r="V11">
-        <v>5.563842565082459e-05</v>
+        <v>4.2655189718628236e-05</v>
       </c>
       <c r="W11">
-        <v>-1.1684762608862309e-06</v>
+        <v>-8.3545309797524779e-07</v>
       </c>
       <c r="X11">
-        <v>-6.728109728381304e-05</v>
+        <v>-5.91656264793806e-05</v>
       </c>
       <c r="Y11">
-        <v>-0.0012785370826041195</v>
+        <v>-0.0011724076670993505</v>
       </c>
     </row>
     <row r="12">
@@ -3125,76 +3125,76 @@
         <v>39</v>
       </c>
       <c r="B12">
-        <v>0.57709356718959037</v>
+        <v>0.52646574087326214</v>
       </c>
       <c r="C12">
-        <v>0.00010307607714710979</v>
+        <v>4.4072736987518614e-05</v>
       </c>
       <c r="D12">
-        <v>8.1455575184811047e-05</v>
+        <v>8.8339397258271955e-05</v>
       </c>
       <c r="E12">
-        <v>-9.801323605569858e-07</v>
+        <v>-1.0716737691840824e-06</v>
       </c>
       <c r="F12">
-        <v>-0.00088022949061900631</v>
+        <v>-0.00076715276307682406</v>
       </c>
       <c r="G12">
-        <v>-5.9888555008695869e-05</v>
+        <v>-6.4747722016447154e-05</v>
       </c>
       <c r="H12">
-        <v>0.00012034118039045745</v>
+        <v>0.00019991471964613921</v>
       </c>
       <c r="I12">
-        <v>0.0014433650839545081</v>
+        <v>0.0016217232868646402</v>
       </c>
       <c r="J12">
-        <v>-0.00039030739345362298</v>
+        <v>-0.0010100957327043606</v>
       </c>
       <c r="K12">
-        <v>0.00049803353520960899</v>
+        <v>0.00065642954588992759</v>
       </c>
       <c r="L12">
-        <v>0.00090597402657771045</v>
+        <v>0.00087701668519313898</v>
       </c>
       <c r="M12">
-        <v>0.0030151101513105098</v>
+        <v>0.0031832563790043984</v>
       </c>
       <c r="N12">
-        <v>0.0022544556298131121</v>
+        <v>0.0024747605991170818</v>
       </c>
       <c r="O12">
-        <v>0.0026655224052302296</v>
+        <v>0.0029447905646110542</v>
       </c>
       <c r="P12">
-        <v>-0.00057724814150458869</v>
+        <v>-0.00064925441384789144</v>
       </c>
       <c r="Q12">
-        <v>-0.00075465153686537405</v>
+        <v>-0.00085760771717028087</v>
       </c>
       <c r="R12">
-        <v>-0.0006911830589961406</v>
+        <v>-0.00080061695025426252</v>
       </c>
       <c r="S12">
-        <v>-0.00045870238366936761</v>
+        <v>-0.00054133821832844532</v>
       </c>
       <c r="T12">
-        <v>-0.00050055988365204046</v>
+        <v>-0.00059039673588021254</v>
       </c>
       <c r="U12">
-        <v>-0.00030500915440439061</v>
+        <v>-0.00038028109305375611</v>
       </c>
       <c r="V12">
-        <v>-5.3042300189517014e-05</v>
+        <v>-6.6651350535923241e-06</v>
       </c>
       <c r="W12">
-        <v>1.3790833769171409e-06</v>
+        <v>2.4641475995340308e-08</v>
       </c>
       <c r="X12">
-        <v>0.00041423750175097207</v>
+        <v>0.00048124408255867846</v>
       </c>
       <c r="Y12">
-        <v>-0.0030037757370181585</v>
+        <v>-0.0035261338360540045</v>
       </c>
     </row>
     <row r="13">
@@ -3202,76 +3202,76 @@
         <v>40</v>
       </c>
       <c r="B13">
-        <v>0.47895704041146109</v>
+        <v>0.406738950568586</v>
       </c>
       <c r="C13">
-        <v>-0.00016137487932603998</v>
+        <v>-0.00024798988705884847</v>
       </c>
       <c r="D13">
-        <v>3.0232086566340838e-05</v>
+        <v>3.6260641992722257e-05</v>
       </c>
       <c r="E13">
-        <v>-3.7684438499711829e-07</v>
+        <v>-4.614025020600736e-07</v>
       </c>
       <c r="F13">
-        <v>-0.00073381814249405032</v>
+        <v>-0.00057828191856048824</v>
       </c>
       <c r="G13">
-        <v>8.2709698929671555e-05</v>
+        <v>9.2795118525209133e-05</v>
       </c>
       <c r="H13">
-        <v>2.6484486818118165e-05</v>
+        <v>0.00011996605467738653</v>
       </c>
       <c r="I13">
-        <v>0.0019455526376898733</v>
+        <v>0.0021595988399374312</v>
       </c>
       <c r="J13">
-        <v>-0.00046994859560092186</v>
+        <v>-0.0012569933008860269</v>
       </c>
       <c r="K13">
-        <v>0.00069948082697416974</v>
+        <v>0.00082310988417206741</v>
       </c>
       <c r="L13">
-        <v>0.00082969159077514389</v>
+        <v>0.00079115130447603794</v>
       </c>
       <c r="M13">
-        <v>0.0022544556298131121</v>
+        <v>0.0024747605991170818</v>
       </c>
       <c r="N13">
-        <v>0.003675359007943392</v>
+        <v>0.0039722101808654774</v>
       </c>
       <c r="O13">
-        <v>0.0029808137121442235</v>
+        <v>0.0033271608995573249</v>
       </c>
       <c r="P13">
-        <v>-0.0001700688973161257</v>
+        <v>-0.00025406301875142414</v>
       </c>
       <c r="Q13">
-        <v>-0.00040529728431891454</v>
+        <v>-0.00052685941179111441</v>
       </c>
       <c r="R13">
-        <v>-0.00016625772257355606</v>
+        <v>-0.00026585666922590513</v>
       </c>
       <c r="S13">
-        <v>-6.8651377466315017e-05</v>
+        <v>-0.00016816901312838003</v>
       </c>
       <c r="T13">
-        <v>-5.9036918332849918e-05</v>
+        <v>-0.00015610367056595605</v>
       </c>
       <c r="U13">
-        <v>4.5048703903949458e-05</v>
+        <v>-2.7276161831403436e-05</v>
       </c>
       <c r="V13">
-        <v>-1.0795414257249673e-05</v>
+        <v>5.0862450693369169e-05</v>
       </c>
       <c r="W13">
-        <v>6.2645465994611612e-07</v>
+        <v>-1.1738295259111609e-06</v>
       </c>
       <c r="X13">
-        <v>-0.00029653214974489353</v>
+        <v>-0.00021953717562188271</v>
       </c>
       <c r="Y13">
-        <v>-0.0032956994931737649</v>
+        <v>-0.0039333849864819862</v>
       </c>
     </row>
     <row r="14">
@@ -3279,76 +3279,76 @@
         <v>41</v>
       </c>
       <c r="B14">
-        <v>0.60820442044079182</v>
+        <v>0.53198698623233343</v>
       </c>
       <c r="C14">
-        <v>5.5580705715231322e-05</v>
+        <v>-4.3354700673628335e-05</v>
       </c>
       <c r="D14">
-        <v>6.1672242337944445e-05</v>
+        <v>7.3638442767134157e-05</v>
       </c>
       <c r="E14">
-        <v>-8.4175355510667989e-07</v>
+        <v>-1.0040026530557901e-06</v>
       </c>
       <c r="F14">
-        <v>-0.00057663168183453824</v>
+        <v>-0.00039592467716675147</v>
       </c>
       <c r="G14">
-        <v>-0.0002869173384438517</v>
+        <v>-0.00029295529434542853</v>
       </c>
       <c r="H14">
-        <v>-0.0001002682580491022</v>
+        <v>4.3935556218021449e-06</v>
       </c>
       <c r="I14">
-        <v>0.0024970333395245266</v>
+        <v>0.0027854310682906927</v>
       </c>
       <c r="J14">
-        <v>-0.0006130588543436583</v>
+        <v>-0.0015750970317906245</v>
       </c>
       <c r="K14">
-        <v>0.00079152241918167138</v>
+        <v>0.00091196983084443199</v>
       </c>
       <c r="L14">
-        <v>0.00089583423980372308</v>
+        <v>0.00085820400072814931</v>
       </c>
       <c r="M14">
-        <v>0.0026655224052302296</v>
+        <v>0.0029447905646110542</v>
       </c>
       <c r="N14">
-        <v>0.0029808137121442235</v>
+        <v>0.0033271608995573249</v>
       </c>
       <c r="O14">
-        <v>0.0051502159239327442</v>
+        <v>0.0056509231037101017</v>
       </c>
       <c r="P14">
-        <v>-0.00025304422155654612</v>
+        <v>-0.00035302660894007826</v>
       </c>
       <c r="Q14">
-        <v>-0.00058454336032147088</v>
+        <v>-0.00073438305179225356</v>
       </c>
       <c r="R14">
-        <v>-0.00060819128863192327</v>
+        <v>-0.00074003723726554611</v>
       </c>
       <c r="S14">
-        <v>-8.5820822276267816e-05</v>
+        <v>-0.00020633668030225864</v>
       </c>
       <c r="T14">
-        <v>-0.0002089416283879732</v>
+        <v>-0.00032878351087132363</v>
       </c>
       <c r="U14">
-        <v>0.00016730661414725875</v>
+        <v>8.6865241380593237e-05</v>
       </c>
       <c r="V14">
-        <v>-6.5839189962772771e-05</v>
+        <v>3.8734005588616279e-06</v>
       </c>
       <c r="W14">
-        <v>2.2545487640113194e-06</v>
+        <v>2.4589038982603269e-07</v>
       </c>
       <c r="X14">
-        <v>-0.0003326874235283964</v>
+        <v>-0.0002608154928714024</v>
       </c>
       <c r="Y14">
-        <v>-0.0037853907133106254</v>
+        <v>-0.0046300048146747288</v>
       </c>
     </row>
     <row r="15">
@@ -3356,76 +3356,76 @@
         <v>42</v>
       </c>
       <c r="B15">
-        <v>0.018202915311416174</v>
+        <v>0.029673468107554116</v>
       </c>
       <c r="C15">
-        <v>-0.00014712627961490559</v>
+        <v>-0.00014200963026318346</v>
       </c>
       <c r="D15">
-        <v>-9.2018241352017065e-05</v>
+        <v>-9.4467209312991624e-05</v>
       </c>
       <c r="E15">
-        <v>1.0479529721598419e-06</v>
+        <v>1.0889955995314589e-06</v>
       </c>
       <c r="F15">
-        <v>0.00045333071601917499</v>
+        <v>0.00038918850312243212</v>
       </c>
       <c r="G15">
-        <v>-1.4713406266438642e-05</v>
+        <v>-1.878125672484369e-05</v>
       </c>
       <c r="H15">
-        <v>-0.00055073786407386079</v>
+        <v>-0.00060393342880913216</v>
       </c>
       <c r="I15">
-        <v>0.00032572740962724472</v>
+        <v>0.00026730891549349</v>
       </c>
       <c r="J15">
-        <v>9.2535730059970628e-05</v>
+        <v>0.00033158422513532391</v>
       </c>
       <c r="K15">
-        <v>-0.00013288411796790465</v>
+        <v>-0.00017766968487757629</v>
       </c>
       <c r="L15">
-        <v>-0.00028624902585771119</v>
+        <v>-0.00028715978742984555</v>
       </c>
       <c r="M15">
-        <v>-0.00057724814150458869</v>
+        <v>-0.00064925441384789144</v>
       </c>
       <c r="N15">
-        <v>-0.0001700688973161257</v>
+        <v>-0.00025406301875142414</v>
       </c>
       <c r="O15">
-        <v>-0.00025304422155654612</v>
+        <v>-0.00035302660894007826</v>
       </c>
       <c r="P15">
-        <v>0.0072021177654549547</v>
+        <v>0.0073641589396843867</v>
       </c>
       <c r="Q15">
-        <v>0.0056200544618245953</v>
+        <v>0.0057519985316032514</v>
       </c>
       <c r="R15">
-        <v>0.0056329098347400394</v>
+        <v>0.0057621164954803133</v>
       </c>
       <c r="S15">
-        <v>0.0056133378600787941</v>
+        <v>0.005748046337560429</v>
       </c>
       <c r="T15">
-        <v>0.0056202091826650967</v>
+        <v>0.0057475600183019603</v>
       </c>
       <c r="U15">
-        <v>0.0056052671096877065</v>
+        <v>0.0057302867719408587</v>
       </c>
       <c r="V15">
-        <v>-0.00011243851393458767</v>
+        <v>-0.00012686056970893185</v>
       </c>
       <c r="W15">
-        <v>3.2376678129030498e-06</v>
+        <v>3.6525038280720818e-06</v>
       </c>
       <c r="X15">
-        <v>-0.0025960876047159847</v>
+        <v>-0.0027039905890799999</v>
       </c>
       <c r="Y15">
-        <v>-0.0026634275192257452</v>
+        <v>-0.0025691016129792583</v>
       </c>
     </row>
     <row r="16">
@@ -3433,76 +3433,76 @@
         <v>43</v>
       </c>
       <c r="B16">
-        <v>0.0047263927723643863</v>
+        <v>0.022493894579605201</v>
       </c>
       <c r="C16">
-        <v>-0.00013905400908720245</v>
+        <v>-0.00012522312480704311</v>
       </c>
       <c r="D16">
-        <v>-8.247356632221938e-05</v>
+        <v>-8.4259634673183089e-05</v>
       </c>
       <c r="E16">
-        <v>9.7768489001470958e-07</v>
+        <v>1.0186033031790421e-06</v>
       </c>
       <c r="F16">
-        <v>0.00043471408465598155</v>
+        <v>0.00037730115177640874</v>
       </c>
       <c r="G16">
-        <v>-0.00013840414846298362</v>
+        <v>-0.00013856462330770573</v>
       </c>
       <c r="H16">
-        <v>-0.00059048181485999514</v>
+        <v>-0.00063608904394316926</v>
       </c>
       <c r="I16">
-        <v>0.00019408848791097879</v>
+        <v>0.00011053670031022393</v>
       </c>
       <c r="J16">
-        <v>0.00019922673778941847</v>
+        <v>0.00053359369552858759</v>
       </c>
       <c r="K16">
-        <v>-0.0003324778211371217</v>
+        <v>-0.00035781440481182016</v>
       </c>
       <c r="L16">
-        <v>-0.00031531627888759027</v>
+        <v>-0.00032287123491371941</v>
       </c>
       <c r="M16">
-        <v>-0.00075465153686537405</v>
+        <v>-0.00085760771717028087</v>
       </c>
       <c r="N16">
-        <v>-0.00040529728431891454</v>
+        <v>-0.00052685941179111441</v>
       </c>
       <c r="O16">
-        <v>-0.00058454336032147088</v>
+        <v>-0.00073438305179225356</v>
       </c>
       <c r="P16">
-        <v>0.0056200544618245953</v>
+        <v>0.0057519985316032514</v>
       </c>
       <c r="Q16">
-        <v>0.0072246038605502383</v>
+        <v>0.007423145140247737</v>
       </c>
       <c r="R16">
-        <v>0.0056391343288207385</v>
+        <v>0.0057820749256751163</v>
       </c>
       <c r="S16">
-        <v>0.0056135873421223372</v>
+        <v>0.005768196364043186</v>
       </c>
       <c r="T16">
-        <v>0.0056218794636675147</v>
+        <v>0.0057659160653479044</v>
       </c>
       <c r="U16">
-        <v>0.0055858745965527961</v>
+        <v>0.0057233691572018191</v>
       </c>
       <c r="V16">
-        <v>-6.0711441196741219e-05</v>
+        <v>-6.9610037324200052e-05</v>
       </c>
       <c r="W16">
-        <v>1.7713503694160028e-06</v>
+        <v>2.0305276606834906e-06</v>
       </c>
       <c r="X16">
-        <v>-0.0025809551073256104</v>
+        <v>-0.0027022685811751478</v>
       </c>
       <c r="Y16">
-        <v>-0.0030539136715293999</v>
+        <v>-0.0030203754859823798</v>
       </c>
     </row>
     <row r="17">
@@ -3510,76 +3510,76 @@
         <v>44</v>
       </c>
       <c r="B17">
-        <v>0.049501621655311128</v>
+        <v>0.067238956412377759</v>
       </c>
       <c r="C17">
-        <v>-0.00030572636535757664</v>
+        <v>-0.00030147975062645856</v>
       </c>
       <c r="D17">
-        <v>-0.00014702202221685259</v>
+        <v>-0.0001534083384292492</v>
       </c>
       <c r="E17">
-        <v>1.6662088472752944e-06</v>
+        <v>1.7586514952034964e-06</v>
       </c>
       <c r="F17">
-        <v>0.00044431568107399769</v>
+        <v>0.00037182164260355169</v>
       </c>
       <c r="G17">
-        <v>0.00020728802717378007</v>
+        <v>0.00021377016904325558</v>
       </c>
       <c r="H17">
-        <v>-0.00061470706142919326</v>
+        <v>-0.00068492230749241123</v>
       </c>
       <c r="I17">
-        <v>2.4960314329084603e-05</v>
+        <v>-5.9101070147346145e-05</v>
       </c>
       <c r="J17">
-        <v>9.2426686076226944e-05</v>
+        <v>0.00037364489954270911</v>
       </c>
       <c r="K17">
-        <v>-7.9194054610868915e-05</v>
+        <v>-0.00015080789714692574</v>
       </c>
       <c r="L17">
-        <v>-0.00013739269309938603</v>
+        <v>-0.00014823362481000983</v>
       </c>
       <c r="M17">
-        <v>-0.0006911830589961406</v>
+        <v>-0.00080061695025426252</v>
       </c>
       <c r="N17">
-        <v>-0.00016625772257355606</v>
+        <v>-0.00026585666922590513</v>
       </c>
       <c r="O17">
-        <v>-0.00060819128863192327</v>
+        <v>-0.00074003723726554611</v>
       </c>
       <c r="P17">
-        <v>0.0056329098347400394</v>
+        <v>0.0057621164954803133</v>
       </c>
       <c r="Q17">
-        <v>0.0056391343288207385</v>
+        <v>0.0057820749256751163</v>
       </c>
       <c r="R17">
-        <v>0.0074866505614026085</v>
+        <v>0.007620725193648036</v>
       </c>
       <c r="S17">
-        <v>0.0056370804905889705</v>
+        <v>0.0057831518425601452</v>
       </c>
       <c r="T17">
-        <v>0.0056098884882618489</v>
+        <v>0.0057444467854675507</v>
       </c>
       <c r="U17">
-        <v>0.0056391258176383529</v>
+        <v>0.0057739817528537282</v>
       </c>
       <c r="V17">
-        <v>-0.00020319775287346172</v>
+        <v>-0.00021946842601090538</v>
       </c>
       <c r="W17">
-        <v>5.8739222405455782e-06</v>
+        <v>6.3135464531531322e-06</v>
       </c>
       <c r="X17">
-        <v>-0.0027002942286874325</v>
+        <v>-0.002819930306646813</v>
       </c>
       <c r="Y17">
-        <v>-0.00069196789339229237</v>
+        <v>-0.00048798749397827024</v>
       </c>
     </row>
     <row r="18">
@@ -3587,76 +3587,76 @@
         <v>45</v>
       </c>
       <c r="B18">
-        <v>-0.13428705982454761</v>
+        <v>-0.11198854882235947</v>
       </c>
       <c r="C18">
-        <v>-0.00011169895751166531</v>
+        <v>-0.00010618077141089381</v>
       </c>
       <c r="D18">
-        <v>-9.4183580531167045e-05</v>
+        <v>-9.6273463748948332e-05</v>
       </c>
       <c r="E18">
-        <v>1.1042349509448927e-06</v>
+        <v>1.1423584650951928e-06</v>
       </c>
       <c r="F18">
-        <v>0.00034141739371359439</v>
+        <v>0.00027991125727617246</v>
       </c>
       <c r="G18">
-        <v>3.5230936701424786e-05</v>
+        <v>2.4593469304240814e-05</v>
       </c>
       <c r="H18">
-        <v>-0.00070328673173986013</v>
+        <v>-0.00076683805291578497</v>
       </c>
       <c r="I18">
-        <v>0.00038844943392911564</v>
+        <v>0.00031775102884600589</v>
       </c>
       <c r="J18">
-        <v>0.00011731721699984266</v>
+        <v>0.00038483094944704438</v>
       </c>
       <c r="K18">
-        <v>1.9321746008622159e-05</v>
+        <v>4.661275663022746e-05</v>
       </c>
       <c r="L18">
-        <v>-0.00023900550001831953</v>
+        <v>-0.00023177558722434612</v>
       </c>
       <c r="M18">
-        <v>-0.00045870238366936761</v>
+        <v>-0.00054133821832844532</v>
       </c>
       <c r="N18">
-        <v>-6.8651377466315017e-05</v>
+        <v>-0.00016816901312838003</v>
       </c>
       <c r="O18">
-        <v>-8.5820822276267816e-05</v>
+        <v>-0.00020633668030225864</v>
       </c>
       <c r="P18">
-        <v>0.0056133378600787941</v>
+        <v>0.005748046337560429</v>
       </c>
       <c r="Q18">
-        <v>0.0056135873421223372</v>
+        <v>0.005768196364043186</v>
       </c>
       <c r="R18">
-        <v>0.0056370804905889705</v>
+        <v>0.0057831518425601452</v>
       </c>
       <c r="S18">
-        <v>0.0069137921099324609</v>
+        <v>0.0070774015499866956</v>
       </c>
       <c r="T18">
-        <v>0.0056473241639659654</v>
+        <v>0.0057926916540816144</v>
       </c>
       <c r="U18">
-        <v>0.0056783692782430301</v>
+        <v>0.0058188896979016157</v>
       </c>
       <c r="V18">
-        <v>-0.00016124773268678559</v>
+        <v>-0.00016950048967623549</v>
       </c>
       <c r="W18">
-        <v>4.4744108789443441e-06</v>
+        <v>4.7219325105643222e-06</v>
       </c>
       <c r="X18">
-        <v>-0.0026473700712584718</v>
+        <v>-0.0027740657972945885</v>
       </c>
       <c r="Y18">
-        <v>-0.0023154164028938422</v>
+        <v>-0.0022863386262962412</v>
       </c>
     </row>
     <row r="19">
@@ -3664,76 +3664,76 @@
         <v>46</v>
       </c>
       <c r="B19">
-        <v>-0.042590721719855139</v>
+        <v>-0.023262007702806398</v>
       </c>
       <c r="C19">
-        <v>-0.00023702489388634145</v>
+        <v>-0.00023626449790101856</v>
       </c>
       <c r="D19">
-        <v>-9.8696738343614199e-05</v>
+        <v>-0.00010269571052179063</v>
       </c>
       <c r="E19">
-        <v>1.1460042064690112e-06</v>
+        <v>1.2044401160805025e-06</v>
       </c>
       <c r="F19">
-        <v>0.00029227640866403648</v>
+        <v>0.00019965189751300469</v>
       </c>
       <c r="G19">
-        <v>9.7094084690957388e-05</v>
+        <v>0.00010310362064095571</v>
       </c>
       <c r="H19">
-        <v>-0.00070380274549863863</v>
+        <v>-0.00076198019743176819</v>
       </c>
       <c r="I19">
-        <v>0.00036119172476176728</v>
+        <v>0.0002842391503959658</v>
       </c>
       <c r="J19">
-        <v>0.00012349567934292002</v>
+        <v>0.00041644311192637579</v>
       </c>
       <c r="K19">
-        <v>-0.00029517612000919135</v>
+        <v>-0.00031975594095281042</v>
       </c>
       <c r="L19">
-        <v>-0.00018580742745564791</v>
+        <v>-0.00019470231209771309</v>
       </c>
       <c r="M19">
-        <v>-0.00050055988365204046</v>
+        <v>-0.00059039673588021254</v>
       </c>
       <c r="N19">
-        <v>-5.9036918332849918e-05</v>
+        <v>-0.00015610367056595605</v>
       </c>
       <c r="O19">
-        <v>-0.0002089416283879732</v>
+        <v>-0.00032878351087132363</v>
       </c>
       <c r="P19">
-        <v>0.0056202091826650967</v>
+        <v>0.0057475600183019603</v>
       </c>
       <c r="Q19">
-        <v>0.0056218794636675147</v>
+        <v>0.0057659160653479044</v>
       </c>
       <c r="R19">
-        <v>0.0056098884882618489</v>
+        <v>0.0057444467854675507</v>
       </c>
       <c r="S19">
-        <v>0.0056473241639659654</v>
+        <v>0.0057926916540816144</v>
       </c>
       <c r="T19">
-        <v>0.0066520444306834995</v>
+        <v>0.0067775132420447226</v>
       </c>
       <c r="U19">
-        <v>0.005663205960881568</v>
+        <v>0.0057960764175303443</v>
       </c>
       <c r="V19">
-        <v>9.676109267998988e-05</v>
+        <v>7.5043096419072711e-05</v>
       </c>
       <c r="W19">
-        <v>-2.6225565759957912e-06</v>
+        <v>-1.9926144851385984e-06</v>
       </c>
       <c r="X19">
-        <v>-0.002793907781763731</v>
+        <v>-0.0029016296484143103</v>
       </c>
       <c r="Y19">
-        <v>-0.004350389833250182</v>
+        <v>-0.0041605238901346753</v>
       </c>
     </row>
     <row r="20">
@@ -3741,76 +3741,76 @@
         <v>47</v>
       </c>
       <c r="B20">
-        <v>-0.11134068181596507</v>
+        <v>-0.095288721702322735</v>
       </c>
       <c r="C20">
-        <v>-0.0001052849513155987</v>
+        <v>-0.0001067016134874232</v>
       </c>
       <c r="D20">
-        <v>-8.4830482037715502e-05</v>
+        <v>-8.7694124992735865e-05</v>
       </c>
       <c r="E20">
-        <v>1.014605839650147e-06</v>
+        <v>1.0586655867577116e-06</v>
       </c>
       <c r="F20">
-        <v>0.00034648903732523975</v>
+        <v>0.00028409978934083077</v>
       </c>
       <c r="G20">
-        <v>6.0713086828814104e-06</v>
+        <v>-2.7361004778752966e-07</v>
       </c>
       <c r="H20">
-        <v>-0.00083406685264045971</v>
+        <v>-0.00090537719573867469</v>
       </c>
       <c r="I20">
-        <v>0.00040991226210796978</v>
+        <v>0.00036062273277431806</v>
       </c>
       <c r="J20">
-        <v>4.4878628591466083e-05</v>
+        <v>0.00025372480023800351</v>
       </c>
       <c r="K20">
-        <v>-0.00017511221270137488</v>
+        <v>-0.00024261148215842641</v>
       </c>
       <c r="L20">
-        <v>-0.00017143974310056541</v>
+        <v>-0.00017025064309124908</v>
       </c>
       <c r="M20">
-        <v>-0.00030500915440439061</v>
+        <v>-0.00038028109305375611</v>
       </c>
       <c r="N20">
-        <v>4.5048703903949458e-05</v>
+        <v>-2.7276161831403436e-05</v>
       </c>
       <c r="O20">
-        <v>0.00016730661414725875</v>
+        <v>8.6865241380593237e-05</v>
       </c>
       <c r="P20">
-        <v>0.0056052671096877065</v>
+        <v>0.0057302867719408587</v>
       </c>
       <c r="Q20">
-        <v>0.0055858745965527961</v>
+        <v>0.0057233691572018191</v>
       </c>
       <c r="R20">
-        <v>0.0056391258176383529</v>
+        <v>0.0057739817528537282</v>
       </c>
       <c r="S20">
-        <v>0.0056783692782430301</v>
+        <v>0.0058188896979016157</v>
       </c>
       <c r="T20">
-        <v>0.005663205960881568</v>
+        <v>0.0057960764175303443</v>
       </c>
       <c r="U20">
-        <v>0.0067882626895143378</v>
+        <v>0.0069248228286763426</v>
       </c>
       <c r="V20">
-        <v>2.9547808647560365e-05</v>
+        <v>1.7860126342024267e-05</v>
       </c>
       <c r="W20">
-        <v>-1.0353120301651942e-06</v>
+        <v>-6.9935552874593709e-07</v>
       </c>
       <c r="X20">
-        <v>-0.0025508428342868785</v>
+        <v>-0.0026685125248852716</v>
       </c>
       <c r="Y20">
-        <v>-0.0041077215925956843</v>
+        <v>-0.0040303551283810309</v>
       </c>
     </row>
     <row r="21">
@@ -3818,76 +3818,76 @@
         <v>48</v>
       </c>
       <c r="B21">
-        <v>-0.015639106244972792</v>
+        <v>-0.025573590578274321</v>
       </c>
       <c r="C21">
-        <v>-4.5097523308253304e-07</v>
+        <v>-1.8578409950131022e-05</v>
       </c>
       <c r="D21">
-        <v>1.8879868408814768e-06</v>
+        <v>2.1588259854252818e-06</v>
       </c>
       <c r="E21">
-        <v>-1.3652395972898416e-08</v>
+        <v>-2.076352929334024e-08</v>
       </c>
       <c r="F21">
-        <v>8.9164045851898967e-05</v>
+        <v>0.00010188428781165038</v>
       </c>
       <c r="G21">
-        <v>6.3083784258589052e-05</v>
+        <v>7.0075343305214235e-05</v>
       </c>
       <c r="H21">
-        <v>-3.6547808124052107e-05</v>
+        <v>-1.1840614098766571e-05</v>
       </c>
       <c r="I21">
-        <v>-0.00013970880946656994</v>
+        <v>-8.8788849494841893e-05</v>
       </c>
       <c r="J21">
-        <v>-4.6755681448801652e-05</v>
+        <v>-0.00016832105619892304</v>
       </c>
       <c r="K21">
-        <v>-8.292994522919028e-05</v>
+        <v>-6.1980961358985257e-05</v>
       </c>
       <c r="L21">
-        <v>5.563842565082459e-05</v>
+        <v>4.2655189718628236e-05</v>
       </c>
       <c r="M21">
-        <v>-5.3042300189517014e-05</v>
+        <v>-6.6651350535923241e-06</v>
       </c>
       <c r="N21">
-        <v>-1.0795414257249673e-05</v>
+        <v>5.0862450693369169e-05</v>
       </c>
       <c r="O21">
-        <v>-6.5839189962772771e-05</v>
+        <v>3.8734005588616279e-06</v>
       </c>
       <c r="P21">
-        <v>-0.00011243851393458767</v>
+        <v>-0.00012686056970893185</v>
       </c>
       <c r="Q21">
-        <v>-6.0711441196741219e-05</v>
+        <v>-6.9610037324200052e-05</v>
       </c>
       <c r="R21">
-        <v>-0.00020319775287346172</v>
+        <v>-0.00021946842601090538</v>
       </c>
       <c r="S21">
-        <v>-0.00016124773268678559</v>
+        <v>-0.00016950048967623549</v>
       </c>
       <c r="T21">
-        <v>9.676109267998988e-05</v>
+        <v>7.5043096419072711e-05</v>
       </c>
       <c r="U21">
-        <v>2.9547808647560365e-05</v>
+        <v>1.7860126342024267e-05</v>
       </c>
       <c r="V21">
-        <v>0.0012625240136863785</v>
+        <v>0.0012671306669734773</v>
       </c>
       <c r="W21">
-        <v>-3.545146721327112e-05</v>
+        <v>-3.558219854460926e-05</v>
       </c>
       <c r="X21">
-        <v>-0.00028040594119535566</v>
+        <v>-0.00027247313344117702</v>
       </c>
       <c r="Y21">
-        <v>-0.01043177433460675</v>
+        <v>-0.010495916611979662</v>
       </c>
     </row>
     <row r="22">
@@ -3895,76 +3895,76 @@
         <v>62</v>
       </c>
       <c r="B22">
-        <v>0.00059444203919890339</v>
+        <v>0.0008733889608624803</v>
       </c>
       <c r="C22">
-        <v>-1.5435887112877119e-07</v>
+        <v>3.6957396003354273e-07</v>
       </c>
       <c r="D22">
-        <v>-2.986566566533992e-08</v>
+        <v>-3.6527149167597014e-08</v>
       </c>
       <c r="E22">
-        <v>7.191387132339477e-11</v>
+        <v>2.6096527946280807e-10</v>
       </c>
       <c r="F22">
-        <v>-2.0513277986783357e-06</v>
+        <v>-2.4806172044277065e-06</v>
       </c>
       <c r="G22">
-        <v>-1.7662675331666006e-06</v>
+        <v>-1.9475581026191977e-06</v>
       </c>
       <c r="H22">
-        <v>1.5486314260097478e-06</v>
+        <v>8.231670790197127e-07</v>
       </c>
       <c r="I22">
-        <v>4.1629591432266291e-06</v>
+        <v>2.6912062540689982e-06</v>
       </c>
       <c r="J22">
-        <v>1.2992407812464517e-06</v>
+        <v>4.9035815633145568e-06</v>
       </c>
       <c r="K22">
-        <v>2.611267781523658e-06</v>
+        <v>2.0787268949662982e-06</v>
       </c>
       <c r="L22">
-        <v>-1.1684762608862309e-06</v>
+        <v>-8.3545309797524779e-07</v>
       </c>
       <c r="M22">
-        <v>1.3790833769171409e-06</v>
+        <v>2.4641475995340308e-08</v>
       </c>
       <c r="N22">
-        <v>6.2645465994611612e-07</v>
+        <v>-1.1738295259111609e-06</v>
       </c>
       <c r="O22">
-        <v>2.2545487640113194e-06</v>
+        <v>2.4589038982603269e-07</v>
       </c>
       <c r="P22">
-        <v>3.2376678129030498e-06</v>
+        <v>3.6525038280720818e-06</v>
       </c>
       <c r="Q22">
-        <v>1.7713503694160028e-06</v>
+        <v>2.0305276606834906e-06</v>
       </c>
       <c r="R22">
-        <v>5.8739222405455782e-06</v>
+        <v>6.3135464531531322e-06</v>
       </c>
       <c r="S22">
-        <v>4.4744108789443441e-06</v>
+        <v>4.7219325105643222e-06</v>
       </c>
       <c r="T22">
-        <v>-2.6225565759957912e-06</v>
+        <v>-1.9926144851385984e-06</v>
       </c>
       <c r="U22">
-        <v>-1.0353120301651942e-06</v>
+        <v>-6.9935552874593709e-07</v>
       </c>
       <c r="V22">
-        <v>-3.545146721327112e-05</v>
+        <v>-3.558219854460926e-05</v>
       </c>
       <c r="W22">
-        <v>1.0056890311431855e-06</v>
+        <v>1.0093361317555429e-06</v>
       </c>
       <c r="X22">
-        <v>6.4853057976959927e-06</v>
+        <v>6.2693171507788824e-06</v>
       </c>
       <c r="Y22">
-        <v>0.00028888509011620433</v>
+        <v>0.00029072189055955391</v>
       </c>
     </row>
     <row r="23">
@@ -3972,76 +3972,76 @@
         <v>50</v>
       </c>
       <c r="B23">
-        <v>0.16343553923983442</v>
+        <v>0.15692480982865656</v>
       </c>
       <c r="C23">
-        <v>0.00040515824311563778</v>
+        <v>0.00040605087269702308</v>
       </c>
       <c r="D23">
-        <v>0.00013799114114260798</v>
+        <v>0.00014318931613301316</v>
       </c>
       <c r="E23">
-        <v>-1.4878247063804279e-06</v>
+        <v>-1.553139525100811e-06</v>
       </c>
       <c r="F23">
-        <v>-0.00038583197251775643</v>
+        <v>-0.00033826202136013359</v>
       </c>
       <c r="G23">
-        <v>-0.00030288121258248467</v>
+        <v>-0.00031986747097120869</v>
       </c>
       <c r="H23">
-        <v>0.00070286816011258936</v>
+        <v>0.00076866577025371593</v>
       </c>
       <c r="I23">
-        <v>-0.00044564754570640804</v>
+        <v>-0.00039793735217381291</v>
       </c>
       <c r="J23">
-        <v>-0.00013597277229144471</v>
+        <v>-0.00040854721365483963</v>
       </c>
       <c r="K23">
-        <v>0.00015339360454543762</v>
+        <v>0.00021651875307818864</v>
       </c>
       <c r="L23">
-        <v>-6.728109728381304e-05</v>
+        <v>-5.91656264793806e-05</v>
       </c>
       <c r="M23">
-        <v>0.00041423750175097207</v>
+        <v>0.00048124408255867846</v>
       </c>
       <c r="N23">
-        <v>-0.00029653214974489353</v>
+        <v>-0.00021953717562188271</v>
       </c>
       <c r="O23">
-        <v>-0.0003326874235283964</v>
+        <v>-0.0002608154928714024</v>
       </c>
       <c r="P23">
-        <v>-0.0025960876047159847</v>
+        <v>-0.0027039905890799999</v>
       </c>
       <c r="Q23">
-        <v>-0.0025809551073256104</v>
+        <v>-0.0027022685811751478</v>
       </c>
       <c r="R23">
-        <v>-0.0027002942286874325</v>
+        <v>-0.002819930306646813</v>
       </c>
       <c r="S23">
-        <v>-0.0026473700712584718</v>
+        <v>-0.0027740657972945885</v>
       </c>
       <c r="T23">
-        <v>-0.002793907781763731</v>
+        <v>-0.0029016296484143103</v>
       </c>
       <c r="U23">
-        <v>-0.0025508428342868785</v>
+        <v>-0.0026685125248852716</v>
       </c>
       <c r="V23">
-        <v>-0.00028040594119535566</v>
+        <v>-0.00027247313344117702</v>
       </c>
       <c r="W23">
-        <v>6.4853057976959927e-06</v>
+        <v>6.2693171507788824e-06</v>
       </c>
       <c r="X23">
-        <v>0.0067184451283048242</v>
+        <v>0.0068969093903318889</v>
       </c>
       <c r="Y23">
-        <v>0.0025378391209590033</v>
+        <v>0.0024338262007297593</v>
       </c>
     </row>
     <row r="24">
@@ -4049,76 +4049,76 @@
         <v>53</v>
       </c>
       <c r="B24">
-        <v>3.5861583069426741</v>
+        <v>3.6611367231697436</v>
       </c>
       <c r="C24">
-        <v>-0.00078231217948731397</v>
+        <v>-0.00064072713251467611</v>
       </c>
       <c r="D24">
-        <v>-0.0011418651733905343</v>
+        <v>-0.0011462157289324768</v>
       </c>
       <c r="E24">
-        <v>1.2149445833475276e-05</v>
+        <v>1.2330475292843683e-05</v>
       </c>
       <c r="F24">
-        <v>0.0021216745808754368</v>
+        <v>0.0018597307786262195</v>
       </c>
       <c r="G24">
-        <v>-5.1157242649800885e-05</v>
+        <v>-8.5958005699835263e-05</v>
       </c>
       <c r="H24">
-        <v>-0.0021188255796329852</v>
+        <v>-0.002393620323857786</v>
       </c>
       <c r="I24">
-        <v>-0.0027662965536723039</v>
+        <v>-0.0033765804724193091</v>
       </c>
       <c r="J24">
-        <v>0.0010800472323120403</v>
+        <v>0.0027713651713157134</v>
       </c>
       <c r="K24">
-        <v>-0.0004829792299682592</v>
+        <v>-0.0010801616550446323</v>
       </c>
       <c r="L24">
-        <v>-0.0012785370826041195</v>
+        <v>-0.0011724076670993505</v>
       </c>
       <c r="M24">
-        <v>-0.0030037757370181585</v>
+        <v>-0.0035261338360540045</v>
       </c>
       <c r="N24">
-        <v>-0.0032956994931737649</v>
+        <v>-0.0039333849864819862</v>
       </c>
       <c r="O24">
-        <v>-0.0037853907133106254</v>
+        <v>-0.0046300048146747288</v>
       </c>
       <c r="P24">
-        <v>-0.0026634275192257452</v>
+        <v>-0.0025691016129792583</v>
       </c>
       <c r="Q24">
-        <v>-0.0030539136715293999</v>
+        <v>-0.0030203754859823798</v>
       </c>
       <c r="R24">
-        <v>-0.00069196789339229237</v>
+        <v>-0.00048798749397827024</v>
       </c>
       <c r="S24">
-        <v>-0.0023154164028938422</v>
+        <v>-0.0022863386262962412</v>
       </c>
       <c r="T24">
-        <v>-0.004350389833250182</v>
+        <v>-0.0041605238901346753</v>
       </c>
       <c r="U24">
-        <v>-0.0041077215925956843</v>
+        <v>-0.0040303551283810309</v>
       </c>
       <c r="V24">
-        <v>-0.01043177433460675</v>
+        <v>-0.010495916611979662</v>
       </c>
       <c r="W24">
-        <v>0.00028888509011620433</v>
+        <v>0.00029072189055955391</v>
       </c>
       <c r="X24">
-        <v>0.0025378391209590033</v>
+        <v>0.0024338262007297593</v>
       </c>
       <c r="Y24">
-        <v>0.11682571697437566</v>
+        <v>0.11774114826019216</v>
       </c>
     </row>
   </sheetData>
@@ -4194,58 +4194,58 @@
         <v>63</v>
       </c>
       <c r="B2">
-        <v>-0.34384223445862344</v>
+        <v>-0.34384339576882689</v>
       </c>
       <c r="C2">
-        <v>0.0047408463500227529</v>
+        <v>0.0047408545202349151</v>
       </c>
       <c r="D2">
-        <v>3.3546270809529499e-05</v>
+        <v>3.3549608911996793e-05</v>
       </c>
       <c r="E2">
-        <v>4.848830979354058e-08</v>
+        <v>4.8475830316550012e-08</v>
       </c>
       <c r="F2">
-        <v>0.00069933906276795543</v>
+        <v>0.00069935305752798942</v>
       </c>
       <c r="G2">
-        <v>0.00089330961594276251</v>
+        <v>0.00089332229105994285</v>
       </c>
       <c r="H2">
-        <v>0.00060713369144091021</v>
+        <v>0.00060714102305479078</v>
       </c>
       <c r="I2">
-        <v>0.00045085271710642065</v>
+        <v>0.00045085057145506738</v>
       </c>
       <c r="J2">
-        <v>0.00029919365280544014</v>
+        <v>0.00029920623485892852</v>
       </c>
       <c r="K2">
-        <v>0.00044647559864528818</v>
+        <v>0.00044650399206512954</v>
       </c>
       <c r="L2">
-        <v>-5.6156001167476728e-05</v>
+        <v>-5.6143517142952845e-05</v>
       </c>
       <c r="M2">
-        <v>5.2165245694072996e-07</v>
+        <v>5.2129077420807045e-07</v>
       </c>
       <c r="N2">
-        <v>0.00067955416262298449</v>
+        <v>0.00067955237250882006</v>
       </c>
       <c r="O2">
-        <v>-0.0031707258245782994</v>
+        <v>-0.0031709098771127292</v>
       </c>
       <c r="P2">
-        <v>0.00034517497425493515</v>
+        <v>0.00034517945257483984</v>
       </c>
       <c r="Q2">
-        <v>-4.3585185088648457e-06</v>
+        <v>-4.3585590347688733e-06</v>
       </c>
       <c r="R2">
-        <v>0.0011215823973077792</v>
+        <v>0.0011215947385701391</v>
       </c>
       <c r="S2">
-        <v>-0.0080586503042711921</v>
+        <v>-0.0080588512357431929</v>
       </c>
     </row>
     <row r="3">
@@ -4253,58 +4253,58 @@
         <v>64</v>
       </c>
       <c r="B3">
-        <v>0.90167798862901671</v>
+        <v>0.90167762596967116</v>
       </c>
       <c r="C3">
-        <v>3.3546270809529499e-05</v>
+        <v>3.3549608911996793e-05</v>
       </c>
       <c r="D3">
-        <v>0.0016200794062160892</v>
+        <v>0.0016200789567591923</v>
       </c>
       <c r="E3">
-        <v>-2.755175021851471e-05</v>
+        <v>-2.7551714393709548e-05</v>
       </c>
       <c r="F3">
-        <v>0.0005426667031674685</v>
+        <v>0.00054266348566108132</v>
       </c>
       <c r="G3">
-        <v>0.00076893998632029861</v>
+        <v>0.00076894658936941217</v>
       </c>
       <c r="H3">
-        <v>0.00060769525711936931</v>
+        <v>0.00060769674414479485</v>
       </c>
       <c r="I3">
-        <v>0.00066461397949225953</v>
+        <v>0.00066461314363860501</v>
       </c>
       <c r="J3">
-        <v>0.00042111836339599207</v>
+        <v>0.00042111561825826669</v>
       </c>
       <c r="K3">
-        <v>0.00054958063572024861</v>
+        <v>0.00054957811341819303</v>
       </c>
       <c r="L3">
-        <v>6.1811053340988034e-05</v>
+        <v>6.181451888983636e-05</v>
       </c>
       <c r="M3">
-        <v>-3.0883561007032545e-06</v>
+        <v>-3.0884311127745161e-06</v>
       </c>
       <c r="N3">
-        <v>4.5012046992287322e-05</v>
+        <v>4.5001108053279674e-05</v>
       </c>
       <c r="O3">
-        <v>-0.021717912306418383</v>
+        <v>-0.021717950404806973</v>
       </c>
       <c r="P3">
-        <v>0.0012489398148944008</v>
+        <v>0.0012489417495879561</v>
       </c>
       <c r="Q3">
-        <v>-2.1883572248745064e-05</v>
+        <v>-2.1883601159983474e-05</v>
       </c>
       <c r="R3">
-        <v>0.00079141316810822301</v>
+        <v>0.00079141467250392825</v>
       </c>
       <c r="S3">
-        <v>-0.017346150189492881</v>
+        <v>-0.017346213057188059</v>
       </c>
     </row>
     <row r="4">
@@ -4312,58 +4312,58 @@
         <v>65</v>
       </c>
       <c r="B4">
-        <v>-0.012767048594032996</v>
+        <v>-0.012767053130261989</v>
       </c>
       <c r="C4">
-        <v>4.848830979354058e-08</v>
+        <v>4.8475830316550012e-08</v>
       </c>
       <c r="D4">
-        <v>-2.755175021851471e-05</v>
+        <v>-2.7551714393709548e-05</v>
       </c>
       <c r="E4">
-        <v>5.0220119764223196e-07</v>
+        <v>5.02200488462599e-07</v>
       </c>
       <c r="F4">
-        <v>-7.1454131388794983e-06</v>
+        <v>-7.1453699565580237e-06</v>
       </c>
       <c r="G4">
-        <v>-1.1566753022097671e-05</v>
+        <v>-1.1566858536051148e-05</v>
       </c>
       <c r="H4">
-        <v>-9.1370504756058701e-06</v>
+        <v>-9.1370466998804035e-06</v>
       </c>
       <c r="I4">
-        <v>-1.0778210888306517e-05</v>
+        <v>-1.077817698784182e-05</v>
       </c>
       <c r="J4">
-        <v>-6.312575224162534e-06</v>
+        <v>-6.3125027169153167e-06</v>
       </c>
       <c r="K4">
-        <v>-8.6786552658839528e-06</v>
+        <v>-8.6785006021177565e-06</v>
       </c>
       <c r="L4">
-        <v>3.9116222164441909e-07</v>
+        <v>3.911895678807039e-07</v>
       </c>
       <c r="M4">
-        <v>9.5092398022287452e-09</v>
+        <v>9.5081830099841993e-09</v>
       </c>
       <c r="N4">
-        <v>-1.9337602451717915e-06</v>
+        <v>-1.9336532215322207e-06</v>
       </c>
       <c r="O4">
-        <v>0.00034309773763268746</v>
+        <v>0.00034309708374387045</v>
       </c>
       <c r="P4">
-        <v>-2.3356896763932824e-05</v>
+        <v>-2.3356952482577525e-05</v>
       </c>
       <c r="Q4">
-        <v>4.2796604704766799e-07</v>
+        <v>4.2796717183586185e-07</v>
       </c>
       <c r="R4">
-        <v>-1.2226863990702822e-05</v>
+        <v>-1.2226856217339435e-05</v>
       </c>
       <c r="S4">
-        <v>0.00030122477669473029</v>
+        <v>0.00030122523417498509</v>
       </c>
     </row>
     <row r="5">
@@ -4371,58 +4371,58 @@
         <v>66</v>
       </c>
       <c r="B5">
-        <v>0.29092072114962719</v>
+        <v>0.29091498766006829</v>
       </c>
       <c r="C5">
-        <v>0.00069933906276795543</v>
+        <v>0.00069935305752798942</v>
       </c>
       <c r="D5">
-        <v>0.0005426667031674685</v>
+        <v>0.00054266348566108132</v>
       </c>
       <c r="E5">
-        <v>-7.1454131388794983e-06</v>
+        <v>-7.1453699565580237e-06</v>
       </c>
       <c r="F5">
-        <v>0.036708466624551753</v>
+        <v>0.036708495038783789</v>
       </c>
       <c r="G5">
-        <v>0.029089220397590022</v>
+        <v>0.029089265529951301</v>
       </c>
       <c r="H5">
-        <v>0.028855398903574879</v>
+        <v>0.028855440583342606</v>
       </c>
       <c r="I5">
-        <v>0.028624490863654654</v>
+        <v>0.02862453380676238</v>
       </c>
       <c r="J5">
-        <v>0.029046766551023426</v>
+        <v>0.029046810441847603</v>
       </c>
       <c r="K5">
-        <v>0.028859902499393915</v>
+        <v>0.028859945722801747</v>
       </c>
       <c r="L5">
-        <v>-0.00038589719321702968</v>
+        <v>-0.00038587491489086145</v>
       </c>
       <c r="M5">
-        <v>1.0628204526326506e-05</v>
+        <v>1.0627521491872748e-05</v>
       </c>
       <c r="N5">
-        <v>0.0013347358693372073</v>
+        <v>0.0013347553250575217</v>
       </c>
       <c r="O5">
-        <v>-0.033897632813967044</v>
+        <v>-0.033897809845662673</v>
       </c>
       <c r="P5">
-        <v>0.00078184929934796161</v>
+        <v>0.00078184918466903553</v>
       </c>
       <c r="Q5">
-        <v>-1.0786553269770264e-05</v>
+        <v>-1.0786541446868475e-05</v>
       </c>
       <c r="R5">
-        <v>0.029386576944365226</v>
+        <v>0.029386620811073593</v>
       </c>
       <c r="S5">
-        <v>-0.038316288395299422</v>
+        <v>-0.038316511694891656</v>
       </c>
     </row>
     <row r="6">
@@ -4430,58 +4430,58 @@
         <v>67</v>
       </c>
       <c r="B6">
-        <v>0.48107130413092802</v>
+        <v>0.48106191673915738</v>
       </c>
       <c r="C6">
-        <v>0.00089330961594276251</v>
+        <v>0.00089332229105994285</v>
       </c>
       <c r="D6">
-        <v>0.00076893998632029861</v>
+        <v>0.00076894658936941217</v>
       </c>
       <c r="E6">
-        <v>-1.1566753022097671e-05</v>
+        <v>-1.1566858536051148e-05</v>
       </c>
       <c r="F6">
-        <v>0.029089220397590022</v>
+        <v>0.029089265529951301</v>
       </c>
       <c r="G6">
-        <v>0.038196303692432654</v>
+        <v>0.0381962614335715</v>
       </c>
       <c r="H6">
-        <v>0.029027183876352166</v>
+        <v>0.029027227940033255</v>
       </c>
       <c r="I6">
-        <v>0.028827196325503186</v>
+        <v>0.028827246607432574</v>
       </c>
       <c r="J6">
-        <v>0.029089222359823908</v>
+        <v>0.029089268352236537</v>
       </c>
       <c r="K6">
-        <v>0.029039944865076394</v>
+        <v>0.029039992870557963</v>
       </c>
       <c r="L6">
-        <v>-0.00087101050807494081</v>
+        <v>-0.00087098462835618652</v>
       </c>
       <c r="M6">
-        <v>2.2211051523286161e-05</v>
+        <v>2.2210212965035952e-05</v>
       </c>
       <c r="N6">
-        <v>0.0018875825098776276</v>
+        <v>0.0018876123630718498</v>
       </c>
       <c r="O6">
-        <v>-0.032242738463293952</v>
+        <v>-0.032243071721375402</v>
       </c>
       <c r="P6">
-        <v>0.0010833128376405458</v>
+        <v>0.001083322222903917</v>
       </c>
       <c r="Q6">
-        <v>-1.5999264411419416e-05</v>
+        <v>-1.5999396080784822e-05</v>
       </c>
       <c r="R6">
-        <v>0.0295674360525531</v>
+        <v>0.029567483525021893</v>
       </c>
       <c r="S6">
-        <v>-0.03790694282677301</v>
+        <v>-0.037907319250174737</v>
       </c>
     </row>
     <row r="7">
@@ -4489,58 +4489,58 @@
         <v>68</v>
       </c>
       <c r="B7">
-        <v>0.39993189534111079</v>
+        <v>0.39992789709898413</v>
       </c>
       <c r="C7">
-        <v>0.00060713369144091021</v>
+        <v>0.00060714102305479078</v>
       </c>
       <c r="D7">
-        <v>0.00060769525711936931</v>
+        <v>0.00060769674414479485</v>
       </c>
       <c r="E7">
-        <v>-9.1370504756058701e-06</v>
+        <v>-9.1370466998804035e-06</v>
       </c>
       <c r="F7">
-        <v>0.028855398903574879</v>
+        <v>0.028855440583342606</v>
       </c>
       <c r="G7">
-        <v>0.029027183876352166</v>
+        <v>0.029027227940033255</v>
       </c>
       <c r="H7">
-        <v>0.036901621022633759</v>
+        <v>0.036901732063608632</v>
       </c>
       <c r="I7">
-        <v>0.028564151490851144</v>
+        <v>0.028564191974431233</v>
       </c>
       <c r="J7">
-        <v>0.028964468819586749</v>
+        <v>0.028964512564592391</v>
       </c>
       <c r="K7">
-        <v>0.028826647900084934</v>
+        <v>0.028826690199441382</v>
       </c>
       <c r="L7">
-        <v>-0.00056373390648640706</v>
+        <v>-0.00056369962915729394</v>
       </c>
       <c r="M7">
-        <v>1.3576271531284633e-05</v>
+        <v>1.3575291613361976e-05</v>
       </c>
       <c r="N7">
-        <v>0.0011120879398615483</v>
+        <v>0.0011120870778538686</v>
       </c>
       <c r="O7">
-        <v>-0.032045647308106336</v>
+        <v>-0.032046006027079008</v>
       </c>
       <c r="P7">
-        <v>0.00079163577403029966</v>
+        <v>0.00079163275171501533</v>
       </c>
       <c r="Q7">
-        <v>-1.1818681031318661e-05</v>
+        <v>-1.1818615921872845e-05</v>
       </c>
       <c r="R7">
-        <v>0.029260649587548204</v>
+        <v>0.029260694782256444</v>
       </c>
       <c r="S7">
-        <v>-0.035657106948281447</v>
+        <v>-0.035657403591001571</v>
       </c>
     </row>
     <row r="8">
@@ -4548,58 +4548,58 @@
         <v>69</v>
       </c>
       <c r="B8">
-        <v>0.15482002437774481</v>
+        <v>0.15481289208388305</v>
       </c>
       <c r="C8">
-        <v>0.00045085271710642065</v>
+        <v>0.00045085057145506738</v>
       </c>
       <c r="D8">
-        <v>0.00066461397949225953</v>
+        <v>0.00066461314363860501</v>
       </c>
       <c r="E8">
-        <v>-1.0778210888306517e-05</v>
+        <v>-1.077817698784182e-05</v>
       </c>
       <c r="F8">
-        <v>0.028624490863654654</v>
+        <v>0.02862453380676238</v>
       </c>
       <c r="G8">
-        <v>0.028827196325503186</v>
+        <v>0.028827246607432574</v>
       </c>
       <c r="H8">
-        <v>0.028564151490851144</v>
+        <v>0.028564191974431233</v>
       </c>
       <c r="I8">
-        <v>0.040686735455103054</v>
+        <v>0.040686759049641474</v>
       </c>
       <c r="J8">
-        <v>0.028941145479729872</v>
+        <v>0.028941194990458961</v>
       </c>
       <c r="K8">
-        <v>0.028611325301793427</v>
+        <v>0.028611370508207223</v>
       </c>
       <c r="L8">
-        <v>-0.00025065655968133181</v>
+        <v>-0.00025062989652656874</v>
       </c>
       <c r="M8">
-        <v>6.088349062278851e-06</v>
+        <v>6.0875126661998817e-06</v>
       </c>
       <c r="N8">
-        <v>0.0010341026736974254</v>
+        <v>0.0010341246454369834</v>
       </c>
       <c r="O8">
-        <v>-0.036004015395052484</v>
+        <v>-0.036004254583368839</v>
       </c>
       <c r="P8">
-        <v>0.00064198395175827164</v>
+        <v>0.0006419821466063071</v>
       </c>
       <c r="Q8">
-        <v>-9.2790882155353171e-06</v>
+        <v>-9.279031428991954e-06</v>
       </c>
       <c r="R8">
-        <v>0.03265471304475133</v>
+        <v>0.032654749516482784</v>
       </c>
       <c r="S8">
-        <v>-0.035776964908991814</v>
+        <v>-0.035777194380549757</v>
       </c>
     </row>
     <row r="9">
@@ -4607,58 +4607,58 @@
         <v>70</v>
       </c>
       <c r="B9">
-        <v>0.31670290055235928</v>
+        <v>0.31669907720553103</v>
       </c>
       <c r="C9">
-        <v>0.00029919365280544014</v>
+        <v>0.00029920623485892852</v>
       </c>
       <c r="D9">
-        <v>0.00042111836339599207</v>
+        <v>0.00042111561825826669</v>
       </c>
       <c r="E9">
-        <v>-6.312575224162534e-06</v>
+        <v>-6.3125027169153167e-06</v>
       </c>
       <c r="F9">
-        <v>0.029046766551023426</v>
+        <v>0.029046810441847603</v>
       </c>
       <c r="G9">
-        <v>0.029089222359823908</v>
+        <v>0.029089268352236537</v>
       </c>
       <c r="H9">
-        <v>0.028964468819586749</v>
+        <v>0.028964512564592391</v>
       </c>
       <c r="I9">
-        <v>0.028941145479729872</v>
+        <v>0.028941194990458961</v>
       </c>
       <c r="J9">
-        <v>0.034757117067634145</v>
+        <v>0.034757171786793689</v>
       </c>
       <c r="K9">
-        <v>0.028961505841370708</v>
+        <v>0.028961553952568678</v>
       </c>
       <c r="L9">
-        <v>0.00020300495658516146</v>
+        <v>0.0002030236665577995</v>
       </c>
       <c r="M9">
-        <v>-6.2012888405334448e-06</v>
+        <v>-6.2018395343834765e-06</v>
       </c>
       <c r="N9">
-        <v>0.00099182730159896437</v>
+        <v>0.00099183598366570092</v>
       </c>
       <c r="O9">
-        <v>-0.036561279816974629</v>
+        <v>-0.036561460405948258</v>
       </c>
       <c r="P9">
-        <v>0.00035108567784532078</v>
+        <v>0.00035108136568654056</v>
       </c>
       <c r="Q9">
-        <v>-5.1998425277631076e-06</v>
+        <v>-5.1997567080126045e-06</v>
       </c>
       <c r="R9">
-        <v>0.029125472826613742</v>
+        <v>0.029125515018551013</v>
       </c>
       <c r="S9">
-        <v>-0.036013048562121439</v>
+        <v>-0.036013194098387706</v>
       </c>
     </row>
     <row r="10">
@@ -4666,58 +4666,58 @@
         <v>71</v>
       </c>
       <c r="B10">
-        <v>0.039476150826392914</v>
+        <v>0.039469032857187322</v>
       </c>
       <c r="C10">
-        <v>0.00044647559864528818</v>
+        <v>0.00044650399206512954</v>
       </c>
       <c r="D10">
-        <v>0.00054958063572024861</v>
+        <v>0.00054957811341819303</v>
       </c>
       <c r="E10">
-        <v>-8.6786552658839528e-06</v>
+        <v>-8.6785006021177565e-06</v>
       </c>
       <c r="F10">
-        <v>0.028859902499393915</v>
+        <v>0.028859945722801747</v>
       </c>
       <c r="G10">
-        <v>0.029039944865076394</v>
+        <v>0.029039992870557963</v>
       </c>
       <c r="H10">
-        <v>0.028826647900084934</v>
+        <v>0.028826690199441382</v>
       </c>
       <c r="I10">
-        <v>0.028611325301793427</v>
+        <v>0.028611370508207223</v>
       </c>
       <c r="J10">
-        <v>0.028961505841370708</v>
+        <v>0.028961553952568678</v>
       </c>
       <c r="K10">
-        <v>0.033809310022086293</v>
+        <v>0.033809383160356206</v>
       </c>
       <c r="L10">
-        <v>-0.0003627984068277695</v>
+        <v>-0.00036276171113166882</v>
       </c>
       <c r="M10">
-        <v>8.4055540775917895e-06</v>
+        <v>8.4044476629377754e-06</v>
       </c>
       <c r="N10">
-        <v>0.0014628876556811166</v>
+        <v>0.0014628945427379659</v>
       </c>
       <c r="O10">
-        <v>-0.032946055684993328</v>
+        <v>-0.032946418043253198</v>
       </c>
       <c r="P10">
-        <v>0.00079902603340508555</v>
+        <v>0.00079902019737406339</v>
       </c>
       <c r="Q10">
-        <v>-1.2013585750847913e-05</v>
+        <v>-1.2013419276710527e-05</v>
       </c>
       <c r="R10">
-        <v>0.029226262522152158</v>
+        <v>0.029226311008889498</v>
       </c>
       <c r="S10">
-        <v>-0.037508418127997732</v>
+        <v>-0.037508718657555964</v>
       </c>
     </row>
     <row r="11">
@@ -4725,58 +4725,58 @@
         <v>72</v>
       </c>
       <c r="B11">
-        <v>0.15589157091584738</v>
+        <v>0.15588801605997718</v>
       </c>
       <c r="C11">
-        <v>-5.6156001167476728e-05</v>
+        <v>-5.6143517142952845e-05</v>
       </c>
       <c r="D11">
-        <v>6.1811053340988034e-05</v>
+        <v>6.181451888983636e-05</v>
       </c>
       <c r="E11">
-        <v>3.9116222164441909e-07</v>
+        <v>3.911895678807039e-07</v>
       </c>
       <c r="F11">
-        <v>-0.00038589719321702968</v>
+        <v>-0.00038587491489086145</v>
       </c>
       <c r="G11">
-        <v>-0.00087101050807494081</v>
+        <v>-0.00087098462835618652</v>
       </c>
       <c r="H11">
-        <v>-0.00056373390648640706</v>
+        <v>-0.00056369962915729394</v>
       </c>
       <c r="I11">
-        <v>-0.00025065655968133181</v>
+        <v>-0.00025062989652656874</v>
       </c>
       <c r="J11">
-        <v>0.00020300495658516146</v>
+        <v>0.0002030236665577995</v>
       </c>
       <c r="K11">
-        <v>-0.0003627984068277695</v>
+        <v>-0.00036276171113166882</v>
       </c>
       <c r="L11">
-        <v>0.006060972215988638</v>
+        <v>0.0060609916706444063</v>
       </c>
       <c r="M11">
-        <v>-0.00016709422550698522</v>
+        <v>-0.00016709476725540375</v>
       </c>
       <c r="N11">
-        <v>-0.00075716463551773333</v>
+        <v>-0.000757175421846841</v>
       </c>
       <c r="O11">
-        <v>-0.052892052915025287</v>
+        <v>-0.052892333265037769</v>
       </c>
       <c r="P11">
-        <v>-0.00016351573837822785</v>
+        <v>-0.00016351676263185594</v>
       </c>
       <c r="Q11">
-        <v>3.2277039031301346e-06</v>
+        <v>3.2277705558795894e-06</v>
       </c>
       <c r="R11">
-        <v>-0.00058790980317351138</v>
+        <v>-0.00058788877811521284</v>
       </c>
       <c r="S11">
-        <v>-0.049294990074712664</v>
+        <v>-0.049295193671009457</v>
       </c>
     </row>
     <row r="12">
@@ -4784,58 +4784,58 @@
         <v>73</v>
       </c>
       <c r="B12">
-        <v>-0.0038566938702232056</v>
+        <v>-0.003856579120107082</v>
       </c>
       <c r="C12">
-        <v>5.2165245694072996e-07</v>
+        <v>5.2129077420807045e-07</v>
       </c>
       <c r="D12">
-        <v>-3.0883561007032545e-06</v>
+        <v>-3.0884311127745161e-06</v>
       </c>
       <c r="E12">
-        <v>9.5092398022287452e-09</v>
+        <v>9.5081830099841993e-09</v>
       </c>
       <c r="F12">
-        <v>1.0628204526326506e-05</v>
+        <v>1.0627521491872748e-05</v>
       </c>
       <c r="G12">
-        <v>2.2211051523286161e-05</v>
+        <v>2.2210212965035952e-05</v>
       </c>
       <c r="H12">
-        <v>1.3576271531284633e-05</v>
+        <v>1.3575291613361976e-05</v>
       </c>
       <c r="I12">
-        <v>6.088349062278851e-06</v>
+        <v>6.0875126661998817e-06</v>
       </c>
       <c r="J12">
-        <v>-6.2012888405334448e-06</v>
+        <v>-6.2018395343834765e-06</v>
       </c>
       <c r="K12">
-        <v>8.4055540775917895e-06</v>
+        <v>8.4044476629377754e-06</v>
       </c>
       <c r="L12">
-        <v>-0.00016709422550698522</v>
+        <v>-0.00016709476725540375</v>
       </c>
       <c r="M12">
-        <v>4.6566657436945431e-06</v>
+        <v>4.6566808416483394e-06</v>
       </c>
       <c r="N12">
-        <v>1.3338945719253397e-05</v>
+        <v>1.33392243403259e-05</v>
       </c>
       <c r="O12">
-        <v>0.0014635399933425825</v>
+        <v>0.001463547582177516</v>
       </c>
       <c r="P12">
-        <v>2.9763327639188166e-06</v>
+        <v>2.9763659789035614e-06</v>
       </c>
       <c r="Q12">
-        <v>-6.7146475739469809e-08</v>
+        <v>-6.7148394356183032e-08</v>
       </c>
       <c r="R12">
-        <v>1.4987185249836464e-05</v>
+        <v>1.4986538893700533e-05</v>
       </c>
       <c r="S12">
-        <v>0.0013674714524322131</v>
+        <v>0.0013674771125605587</v>
       </c>
     </row>
     <row r="13">
@@ -4843,58 +4843,58 @@
         <v>74</v>
       </c>
       <c r="B13">
-        <v>-0.054815453823790994</v>
+        <v>-0.054818361539778496</v>
       </c>
       <c r="C13">
-        <v>0.00067955416262298449</v>
+        <v>0.00067955237250882006</v>
       </c>
       <c r="D13">
-        <v>4.5012046992287322e-05</v>
+        <v>4.5001108053279674e-05</v>
       </c>
       <c r="E13">
-        <v>-1.9337602451717915e-06</v>
+        <v>-1.9336532215322207e-06</v>
       </c>
       <c r="F13">
-        <v>0.0013347358693372073</v>
+        <v>0.0013347553250575217</v>
       </c>
       <c r="G13">
-        <v>0.0018875825098776276</v>
+        <v>0.0018876123630718498</v>
       </c>
       <c r="H13">
-        <v>0.0011120879398615483</v>
+        <v>0.0011120870778538686</v>
       </c>
       <c r="I13">
-        <v>0.0010341026736974254</v>
+        <v>0.0010341246454369834</v>
       </c>
       <c r="J13">
-        <v>0.00099182730159896437</v>
+        <v>0.00099183598366570092</v>
       </c>
       <c r="K13">
-        <v>0.0014628876556811166</v>
+        <v>0.0014628945427379659</v>
       </c>
       <c r="L13">
-        <v>-0.00075716463551773333</v>
+        <v>-0.000757175421846841</v>
       </c>
       <c r="M13">
-        <v>1.3338945719253397e-05</v>
+        <v>1.33392243403259e-05</v>
       </c>
       <c r="N13">
-        <v>0.01718263797749035</v>
+        <v>0.017182633389525904</v>
       </c>
       <c r="O13">
-        <v>0.0061302781795929649</v>
+        <v>0.0061305279915795522</v>
       </c>
       <c r="P13">
-        <v>0.00020306271941000504</v>
+        <v>0.00020306282943048453</v>
       </c>
       <c r="Q13">
-        <v>-3.4911726396678043e-06</v>
+        <v>-3.4912051564507005e-06</v>
       </c>
       <c r="R13">
-        <v>0.0015840560310706028</v>
+        <v>0.0015840710192995254</v>
       </c>
       <c r="S13">
-        <v>0.0031494813564720454</v>
+        <v>0.0031495781414323598</v>
       </c>
     </row>
     <row r="14">
@@ -4902,58 +4902,58 @@
         <v>75</v>
       </c>
       <c r="B14">
-        <v>-13.83851357138953</v>
+        <v>-13.838473818388014</v>
       </c>
       <c r="C14">
-        <v>-0.0031707258245782994</v>
+        <v>-0.0031709098771127292</v>
       </c>
       <c r="D14">
-        <v>-0.021717912306418383</v>
+        <v>-0.021717950404806973</v>
       </c>
       <c r="E14">
-        <v>0.00034309773763268746</v>
+        <v>0.00034309708374387045</v>
       </c>
       <c r="F14">
-        <v>-0.033897632813967044</v>
+        <v>-0.033897809845662673</v>
       </c>
       <c r="G14">
-        <v>-0.032242738463293952</v>
+        <v>-0.032243071721375402</v>
       </c>
       <c r="H14">
-        <v>-0.032045647308106336</v>
+        <v>-0.032046006027079008</v>
       </c>
       <c r="I14">
-        <v>-0.036004015395052484</v>
+        <v>-0.036004254583368839</v>
       </c>
       <c r="J14">
-        <v>-0.036561279816974629</v>
+        <v>-0.036561460405948258</v>
       </c>
       <c r="K14">
-        <v>-0.032946055684993328</v>
+        <v>-0.032946418043253198</v>
       </c>
       <c r="L14">
-        <v>-0.052892052915025287</v>
+        <v>-0.052892333265037769</v>
       </c>
       <c r="M14">
-        <v>0.0014635399933425825</v>
+        <v>0.001463547582177516</v>
       </c>
       <c r="N14">
-        <v>0.0061302781795929649</v>
+        <v>0.0061305279915795522</v>
       </c>
       <c r="O14">
-        <v>0.7800425371574875</v>
+        <v>0.78004631295220961</v>
       </c>
       <c r="P14">
-        <v>-0.014816676402668205</v>
+        <v>-0.014816684952673548</v>
       </c>
       <c r="Q14">
-        <v>0.00024609670109968559</v>
+        <v>0.00024609623347665241</v>
       </c>
       <c r="R14">
-        <v>-0.034850332607294199</v>
+        <v>-0.034850580696924482</v>
       </c>
       <c r="S14">
-        <v>0.68940470770676132</v>
+        <v>0.68940785937921678</v>
       </c>
     </row>
     <row r="15">
@@ -4961,58 +4961,58 @@
         <v>76</v>
       </c>
       <c r="B15">
-        <v>0.71898625683064377</v>
+        <v>0.71898666183229454</v>
       </c>
       <c r="C15">
-        <v>0.00034517497425493515</v>
+        <v>0.00034517945257483984</v>
       </c>
       <c r="D15">
-        <v>0.0012489398148944008</v>
+        <v>0.0012489417495879561</v>
       </c>
       <c r="E15">
-        <v>-2.3356896763932824e-05</v>
+        <v>-2.3356952482577525e-05</v>
       </c>
       <c r="F15">
-        <v>0.00078184929934796161</v>
+        <v>0.00078184918466903553</v>
       </c>
       <c r="G15">
-        <v>0.0010833128376405458</v>
+        <v>0.001083322222903917</v>
       </c>
       <c r="H15">
-        <v>0.00079163577403029966</v>
+        <v>0.00079163275171501533</v>
       </c>
       <c r="I15">
-        <v>0.00064198395175827164</v>
+        <v>0.0006419821466063071</v>
       </c>
       <c r="J15">
-        <v>0.00035108567784532078</v>
+        <v>0.00035108136568654056</v>
       </c>
       <c r="K15">
-        <v>0.00079902603340508555</v>
+        <v>0.00079902019737406339</v>
       </c>
       <c r="L15">
-        <v>-0.00016351573837822785</v>
+        <v>-0.00016351676263185594</v>
       </c>
       <c r="M15">
-        <v>2.9763327639188166e-06</v>
+        <v>2.9763659789035614e-06</v>
       </c>
       <c r="N15">
-        <v>0.00020306271941000504</v>
+        <v>0.00020306282943048453</v>
       </c>
       <c r="O15">
-        <v>-0.014816676402668205</v>
+        <v>-0.014816684952673548</v>
       </c>
       <c r="P15">
-        <v>0.00210998258666081</v>
+        <v>0.002109984982179645</v>
       </c>
       <c r="Q15">
-        <v>-3.4958209622076153e-05</v>
+        <v>-3.4958262999321722e-05</v>
       </c>
       <c r="R15">
-        <v>0.0014626444793660355</v>
+        <v>0.0014626462374035636</v>
       </c>
       <c r="S15">
-        <v>-0.028663007489489686</v>
+        <v>-0.028663026869547571</v>
       </c>
     </row>
     <row r="16">
@@ -5020,58 +5020,58 @@
         <v>77</v>
       </c>
       <c r="B16">
-        <v>-0.010089666071275516</v>
+        <v>-0.010089679546184413</v>
       </c>
       <c r="C16">
-        <v>-4.3585185088648457e-06</v>
+        <v>-4.3585590347688733e-06</v>
       </c>
       <c r="D16">
-        <v>-2.1883572248745064e-05</v>
+        <v>-2.1883601159983474e-05</v>
       </c>
       <c r="E16">
-        <v>4.2796604704766799e-07</v>
+        <v>4.2796717183586185e-07</v>
       </c>
       <c r="F16">
-        <v>-1.0786553269770264e-05</v>
+        <v>-1.0786541446868475e-05</v>
       </c>
       <c r="G16">
-        <v>-1.5999264411419416e-05</v>
+        <v>-1.5999396080784822e-05</v>
       </c>
       <c r="H16">
-        <v>-1.1818681031318661e-05</v>
+        <v>-1.1818615921872845e-05</v>
       </c>
       <c r="I16">
-        <v>-9.2790882155353171e-06</v>
+        <v>-9.279031428991954e-06</v>
       </c>
       <c r="J16">
-        <v>-5.1998425277631076e-06</v>
+        <v>-5.1997567080126045e-06</v>
       </c>
       <c r="K16">
-        <v>-1.2013585750847913e-05</v>
+        <v>-1.2013419276710527e-05</v>
       </c>
       <c r="L16">
-        <v>3.2277039031301346e-06</v>
+        <v>3.2277705558795894e-06</v>
       </c>
       <c r="M16">
-        <v>-6.7146475739469809e-08</v>
+        <v>-6.7148394356183032e-08</v>
       </c>
       <c r="N16">
-        <v>-3.4911726396678043e-06</v>
+        <v>-3.4912051564507005e-06</v>
       </c>
       <c r="O16">
-        <v>0.00024609670109968559</v>
+        <v>0.00024609623347665241</v>
       </c>
       <c r="P16">
-        <v>-3.4958209622076153e-05</v>
+        <v>-3.4958262999321722e-05</v>
       </c>
       <c r="Q16">
-        <v>6.0538167544874871e-07</v>
+        <v>6.0538295384272415e-07</v>
       </c>
       <c r="R16">
-        <v>-2.2235868602990782e-05</v>
+        <v>-2.2235865740993305e-05</v>
       </c>
       <c r="S16">
-        <v>0.00045482580851503185</v>
+        <v>0.0004548257664344913</v>
       </c>
     </row>
     <row r="17">
@@ -5079,58 +5079,58 @@
         <v>78</v>
       </c>
       <c r="B17">
-        <v>0.3837433992304698</v>
+        <v>0.38373508100055981</v>
       </c>
       <c r="C17">
-        <v>0.0011215823973077792</v>
+        <v>0.0011215947385701391</v>
       </c>
       <c r="D17">
-        <v>0.00079141316810822301</v>
+        <v>0.00079141467250392825</v>
       </c>
       <c r="E17">
-        <v>-1.2226863990702822e-05</v>
+        <v>-1.2226856217339435e-05</v>
       </c>
       <c r="F17">
-        <v>0.029386576944365226</v>
+        <v>0.029386620811073593</v>
       </c>
       <c r="G17">
-        <v>0.0295674360525531</v>
+        <v>0.029567483525021893</v>
       </c>
       <c r="H17">
-        <v>0.029260649587548204</v>
+        <v>0.029260694782256444</v>
       </c>
       <c r="I17">
-        <v>0.03265471304475133</v>
+        <v>0.032654749516482784</v>
       </c>
       <c r="J17">
-        <v>0.029125472826613742</v>
+        <v>0.029125515018551013</v>
       </c>
       <c r="K17">
-        <v>0.029226262522152158</v>
+        <v>0.029226311008889498</v>
       </c>
       <c r="L17">
-        <v>-0.00058790980317351138</v>
+        <v>-0.00058788877811521284</v>
       </c>
       <c r="M17">
-        <v>1.4987185249836464e-05</v>
+        <v>1.4986538893700533e-05</v>
       </c>
       <c r="N17">
-        <v>0.0015840560310706028</v>
+        <v>0.0015840710192995254</v>
       </c>
       <c r="O17">
-        <v>-0.034850332607294199</v>
+        <v>-0.034850580696924482</v>
       </c>
       <c r="P17">
-        <v>0.0014626444793660355</v>
+        <v>0.0014626462374035636</v>
       </c>
       <c r="Q17">
-        <v>-2.2235868602990782e-05</v>
+        <v>-2.2235865740993305e-05</v>
       </c>
       <c r="R17">
-        <v>0.038153650551711507</v>
+        <v>0.038153668883674365</v>
       </c>
       <c r="S17">
-        <v>-0.046667955251417252</v>
+        <v>-0.046668206924535119</v>
       </c>
     </row>
     <row r="18">
@@ -5138,58 +5138,58 @@
         <v>79</v>
       </c>
       <c r="B18">
-        <v>-12.878876165951466</v>
+        <v>-12.878845217387573</v>
       </c>
       <c r="C18">
-        <v>-0.0080586503042711921</v>
+        <v>-0.0080588512357431929</v>
       </c>
       <c r="D18">
-        <v>-0.017346150189492881</v>
+        <v>-0.017346213057188059</v>
       </c>
       <c r="E18">
-        <v>0.00030122477669473029</v>
+        <v>0.00030122523417498509</v>
       </c>
       <c r="F18">
-        <v>-0.038316288395299422</v>
+        <v>-0.038316511694891656</v>
       </c>
       <c r="G18">
-        <v>-0.03790694282677301</v>
+        <v>-0.037907319250174737</v>
       </c>
       <c r="H18">
-        <v>-0.035657106948281447</v>
+        <v>-0.035657403591001571</v>
       </c>
       <c r="I18">
-        <v>-0.035776964908991814</v>
+        <v>-0.035777194380549757</v>
       </c>
       <c r="J18">
-        <v>-0.036013048562121439</v>
+        <v>-0.036013194098387706</v>
       </c>
       <c r="K18">
-        <v>-0.037508418127997732</v>
+        <v>-0.037508718657555964</v>
       </c>
       <c r="L18">
-        <v>-0.049294990074712664</v>
+        <v>-0.049295193671009457</v>
       </c>
       <c r="M18">
-        <v>0.0013674714524322131</v>
+        <v>0.0013674771125605587</v>
       </c>
       <c r="N18">
-        <v>0.0031494813564720454</v>
+        <v>0.0031495781414323598</v>
       </c>
       <c r="O18">
-        <v>0.68940470770676132</v>
+        <v>0.68940785937921678</v>
       </c>
       <c r="P18">
-        <v>-0.028663007489489686</v>
+        <v>-0.028663026869547571</v>
       </c>
       <c r="Q18">
-        <v>0.00045482580851503185</v>
+        <v>0.0004548257664344913</v>
       </c>
       <c r="R18">
-        <v>-0.046667955251417252</v>
+        <v>-0.046668206924535119</v>
       </c>
       <c r="S18">
-        <v>0.87363407701261697</v>
+        <v>0.87363656195137507</v>
       </c>
     </row>
   </sheetData>

--- a/input/ES/reg_education.xlsx
+++ b/input/ES/reg_education.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="167" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="163" uniqueCount="77">
   <si>
     <t>Description</t>
   </si>
@@ -202,12 +202,6 @@
     <t>Dnc1_plus_L1</t>
   </si>
   <si>
-    <t>Dnc02_yes_L1</t>
-  </si>
-  <si>
-    <t>Year_transformed_sq</t>
-  </si>
-  <si>
     <t>Dgn_</t>
   </si>
   <si>
@@ -236,9 +230,6 @@
   </si>
   <si>
     <t>Year_transformed_</t>
-  </si>
-  <si>
-    <t>Year_transformed_sq_</t>
   </si>
   <si>
     <t>Y2022_</t>
@@ -430,7 +421,7 @@
         <v>20</v>
       </c>
       <c r="B5">
-        <v>0.12245687569794139</v>
+        <v>0.12245459918360735</v>
       </c>
       <c r="C5"/>
       <c r="D5"/>
@@ -438,7 +429,7 @@
         <v>28</v>
       </c>
       <c r="F5">
-        <v>1758.7106271074354</v>
+        <v>1760.2718418765032</v>
       </c>
     </row>
     <row r="6">
@@ -454,7 +445,7 @@
         <v>29</v>
       </c>
       <c r="F6">
-        <v>-16413827.602108937</v>
+        <v>-16413939.267560342</v>
       </c>
     </row>
     <row r="7">
@@ -483,7 +474,7 @@
         <v>20</v>
       </c>
       <c r="B10">
-        <v>0.57370596602107504</v>
+        <v>0.56996282811306831</v>
       </c>
       <c r="C10"/>
       <c r="D10"/>
@@ -491,7 +482,7 @@
         <v>28</v>
       </c>
       <c r="F10">
-        <v>4603.6455857170358</v>
+        <v>4403.7871942301008</v>
       </c>
     </row>
     <row r="11">
@@ -507,7 +498,7 @@
         <v>29</v>
       </c>
       <c r="F11">
-        <v>-10698186.240769662</v>
+        <v>-10792138.445079073</v>
       </c>
     </row>
     <row r="12">
@@ -536,7 +527,7 @@
         <v>20</v>
       </c>
       <c r="B15">
-        <v>0.18881926192104559</v>
+        <v>0.18790239160332234</v>
       </c>
       <c r="C15"/>
       <c r="D15"/>
@@ -641,73 +632,73 @@
         <v>32</v>
       </c>
       <c r="B2">
-        <v>-0.11662447696316315</v>
+        <v>-0.11646956735264642</v>
       </c>
       <c r="C2">
-        <v>0.00059812867888842374</v>
+        <v>0.00059808908876510659</v>
       </c>
       <c r="D2">
-        <v>1.7651026892560023e-06</v>
+        <v>1.9488103395676283e-06</v>
       </c>
       <c r="E2">
-        <v>-5.1429849423037284e-05</v>
+        <v>-5.133875874763818e-05</v>
       </c>
       <c r="F2">
-        <v>-7.0556998576366222e-06</v>
+        <v>-7.3625945037398838e-06</v>
       </c>
       <c r="G2">
-        <v>1.0886439448035665e-05</v>
+        <v>1.1054460435203857e-05</v>
       </c>
       <c r="H2">
-        <v>1.2530577705779919e-05</v>
+        <v>1.276518845022195e-05</v>
       </c>
       <c r="I2">
-        <v>-1.0829388282259129e-05</v>
+        <v>-1.1380726729727655e-05</v>
       </c>
       <c r="J2">
-        <v>-8.9154141434915328e-07</v>
+        <v>5.8306440264823242e-07</v>
       </c>
       <c r="K2">
-        <v>2.4510385167041444e-05</v>
+        <v>2.5552427083685517e-05</v>
       </c>
       <c r="L2">
-        <v>-2.3997063754733366e-05</v>
+        <v>-2.3270957972627249e-05</v>
       </c>
       <c r="M2">
-        <v>-2.8196457508709166e-05</v>
+        <v>-2.8260875892740665e-05</v>
       </c>
       <c r="N2">
-        <v>-4.5227974366673126e-05</v>
+        <v>-4.5332756772375213e-05</v>
       </c>
       <c r="O2">
-        <v>-2.5841294697318413e-05</v>
+        <v>-2.6030787126567166e-05</v>
       </c>
       <c r="P2">
-        <v>-3.19522070572313e-05</v>
+        <v>-3.1951245269935119e-05</v>
       </c>
       <c r="Q2">
-        <v>-5.5036374184787003e-05</v>
+        <v>-5.507550833823332e-05</v>
       </c>
       <c r="R2">
-        <v>-5.4894143815320052e-05</v>
+        <v>-5.5041332143276523e-05</v>
       </c>
       <c r="S2">
-        <v>-1.4008057441146856e-06</v>
+        <v>-1.38405756557253e-06</v>
       </c>
       <c r="T2">
-        <v>7.6602284271958237e-06</v>
+        <v>7.3249055982587763e-06</v>
       </c>
       <c r="U2">
-        <v>-1.6930302265998695e-05</v>
+        <v>-1.7092488571668567e-05</v>
       </c>
       <c r="V2">
-        <v>-1.6729711706180123e-05</v>
+        <v>-1.6752814167593104e-05</v>
       </c>
       <c r="W2">
-        <v>2.9216267533437298e-05</v>
+        <v>2.9231494845983084e-05</v>
       </c>
       <c r="X2">
-        <v>-0.00026782037041550523</v>
+        <v>-0.0002720611607212399</v>
       </c>
     </row>
     <row r="3">
@@ -715,73 +706,73 @@
         <v>33</v>
       </c>
       <c r="B3">
-        <v>-0.14559711954200455</v>
+        <v>-0.14614507498297236</v>
       </c>
       <c r="C3">
-        <v>1.7651026892560023e-06</v>
+        <v>1.9488103395676283e-06</v>
       </c>
       <c r="D3">
-        <v>8.7674227140811044e-05</v>
+        <v>8.7505451891110967e-05</v>
       </c>
       <c r="E3">
-        <v>0.00029724376059475058</v>
+        <v>0.0002969872437400033</v>
       </c>
       <c r="F3">
-        <v>-0.00018019225085596068</v>
+        <v>-0.00017985299107891681</v>
       </c>
       <c r="G3">
-        <v>0.00011002334803386221</v>
+        <v>0.00010979551085336763</v>
       </c>
       <c r="H3">
-        <v>-4.4521885406181616e-05</v>
+        <v>-4.4548407069825108e-05</v>
       </c>
       <c r="I3">
-        <v>-2.1589168437395894e-06</v>
+        <v>-1.9584188272895654e-06</v>
       </c>
       <c r="J3">
-        <v>8.6514903466760977e-05</v>
+        <v>8.6106860369117861e-05</v>
       </c>
       <c r="K3">
-        <v>0.00017205609895866247</v>
+        <v>0.0001716893785905782</v>
       </c>
       <c r="L3">
-        <v>0.00018131654951066521</v>
+        <v>0.00018096839143208948</v>
       </c>
       <c r="M3">
-        <v>-2.0444164833006507e-05</v>
+        <v>-2.0346613448131564e-05</v>
       </c>
       <c r="N3">
-        <v>-2.9149268702997368e-05</v>
+        <v>-2.9005552255030684e-05</v>
       </c>
       <c r="O3">
-        <v>-2.9131533922440117e-05</v>
+        <v>-2.8957396012170241e-05</v>
       </c>
       <c r="P3">
-        <v>-1.6142784236935397e-05</v>
+        <v>-1.5986335605171643e-05</v>
       </c>
       <c r="Q3">
-        <v>-1.6520012026069276e-05</v>
+        <v>-1.6281221913368787e-05</v>
       </c>
       <c r="R3">
-        <v>-7.2687491563628388e-06</v>
+        <v>-7.0016122684143499e-06</v>
       </c>
       <c r="S3">
-        <v>1.5913813405596874e-06</v>
+        <v>1.5976973339831922e-06</v>
       </c>
       <c r="T3">
-        <v>-2.9280593706172784e-06</v>
+        <v>-2.9307829013420096e-06</v>
       </c>
       <c r="U3">
-        <v>-2.1535077201024439e-05</v>
+        <v>-2.1846187251463271e-05</v>
       </c>
       <c r="V3">
-        <v>-1.5924522668357439e-05</v>
+        <v>-1.6207183915359466e-05</v>
       </c>
       <c r="W3">
-        <v>-7.9848367730172469e-06</v>
+        <v>-8.1051178447871016e-06</v>
       </c>
       <c r="X3">
-        <v>-0.0017924371667468965</v>
+        <v>-0.0017893630481715995</v>
       </c>
     </row>
     <row r="4">
@@ -789,73 +780,73 @@
         <v>34</v>
       </c>
       <c r="B4">
-        <v>-1.5372786640638925</v>
+        <v>-1.5367459549832458</v>
       </c>
       <c r="C4">
-        <v>-5.1429849423037284e-05</v>
+        <v>-5.133875874763818e-05</v>
       </c>
       <c r="D4">
-        <v>0.00029724376059475058</v>
+        <v>0.0002969872437400033</v>
       </c>
       <c r="E4">
-        <v>0.0025369555023489346</v>
+        <v>0.0025329483324169704</v>
       </c>
       <c r="F4">
-        <v>-0.0005510471422363022</v>
+        <v>-0.00055064812366191777</v>
       </c>
       <c r="G4">
-        <v>0.00020006144129067752</v>
+        <v>0.00019991832954099296</v>
       </c>
       <c r="H4">
-        <v>-0.00050639727639288483</v>
+        <v>-0.00050607386823679963</v>
       </c>
       <c r="I4">
-        <v>-7.2530235086693288e-06</v>
+        <v>-5.6401825943824379e-06</v>
       </c>
       <c r="J4">
-        <v>-0.00014038751107323859</v>
+        <v>-0.00013543146612350092</v>
       </c>
       <c r="K4">
-        <v>-0.00023927141411159061</v>
+        <v>-0.00023624392555496158</v>
       </c>
       <c r="L4">
-        <v>-0.00019417807775790291</v>
+        <v>-0.00019054510654706097</v>
       </c>
       <c r="M4">
-        <v>-8.6955610511307412e-05</v>
+        <v>-8.6660424805947919e-05</v>
       </c>
       <c r="N4">
-        <v>-3.8418787722349721e-05</v>
+        <v>-3.8107708286064679e-05</v>
       </c>
       <c r="O4">
-        <v>-5.5868557601869342e-05</v>
+        <v>-5.5452482649360254e-05</v>
       </c>
       <c r="P4">
-        <v>-4.8192904526197285e-05</v>
+        <v>-4.7962815156179887e-05</v>
       </c>
       <c r="Q4">
-        <v>-3.7776783440613177e-05</v>
+        <v>-3.743478803600236e-05</v>
       </c>
       <c r="R4">
-        <v>-7.0752729348080509e-06</v>
+        <v>-6.3839353967824883e-06</v>
       </c>
       <c r="S4">
-        <v>2.6499221390003936e-06</v>
+        <v>2.6620169559592562e-06</v>
       </c>
       <c r="T4">
-        <v>7.2082010005209557e-05</v>
+        <v>7.2169135818662272e-05</v>
       </c>
       <c r="U4">
-        <v>-0.00019024964748715122</v>
+        <v>-0.00019094319503624177</v>
       </c>
       <c r="V4">
-        <v>-0.00013474371578078349</v>
+        <v>-0.0001347416131791707</v>
       </c>
       <c r="W4">
-        <v>-0.00012358751192967344</v>
+        <v>-0.00012367314094885429</v>
       </c>
       <c r="X4">
-        <v>-0.0057993087758113574</v>
+        <v>-0.0057960402472572135</v>
       </c>
     </row>
     <row r="5">
@@ -863,73 +854,73 @@
         <v>35</v>
       </c>
       <c r="B5">
-        <v>-0.045832274175645074</v>
+        <v>-0.044988002485590636</v>
       </c>
       <c r="C5">
-        <v>-7.0556998576366222e-06</v>
+        <v>-7.3625945037398838e-06</v>
       </c>
       <c r="D5">
-        <v>-0.00018019225085596068</v>
+        <v>-0.00017985299107891681</v>
       </c>
       <c r="E5">
-        <v>-0.0005510471422363022</v>
+        <v>-0.00055064812366191777</v>
       </c>
       <c r="F5">
-        <v>0.00064988441010083858</v>
+        <v>0.00064926099893205624</v>
       </c>
       <c r="G5">
-        <v>-0.00086476740349140544</v>
+        <v>-0.00086434271039442497</v>
       </c>
       <c r="H5">
-        <v>9.2192680585024157e-05</v>
+        <v>9.241398027864966e-05</v>
       </c>
       <c r="I5">
-        <v>-1.278108997361608e-05</v>
+        <v>-1.3342616587056269e-05</v>
       </c>
       <c r="J5">
-        <v>-0.00015614960831265709</v>
+        <v>-0.00015507156521237374</v>
       </c>
       <c r="K5">
-        <v>-0.000276637659283532</v>
+        <v>-0.00027577076972511399</v>
       </c>
       <c r="L5">
-        <v>-0.00029534326502125055</v>
+        <v>-0.00029455272036834078</v>
       </c>
       <c r="M5">
-        <v>2.7962621392732707e-05</v>
+        <v>2.7561426761518217e-05</v>
       </c>
       <c r="N5">
-        <v>5.0104063907688637e-05</v>
+        <v>4.9639587999507784e-05</v>
       </c>
       <c r="O5">
-        <v>4.5110121240774913e-05</v>
+        <v>4.4597633397449894e-05</v>
       </c>
       <c r="P5">
-        <v>3.2548177969952442e-05</v>
+        <v>3.2084103206722614e-05</v>
       </c>
       <c r="Q5">
-        <v>2.8866317913841348e-05</v>
+        <v>2.8403179923142725e-05</v>
       </c>
       <c r="R5">
-        <v>2.9248414192957928e-05</v>
+        <v>2.8613473755967377e-05</v>
       </c>
       <c r="S5">
-        <v>-2.8927603308168332e-06</v>
+        <v>-2.8981748534000543e-06</v>
       </c>
       <c r="T5">
-        <v>3.553832431412449e-05</v>
+        <v>3.5884766545517515e-05</v>
       </c>
       <c r="U5">
-        <v>3.7496946559498488e-05</v>
+        <v>3.8019498947896647e-05</v>
       </c>
       <c r="V5">
-        <v>2.9925794256317707e-05</v>
+        <v>3.0326767678386145e-05</v>
       </c>
       <c r="W5">
-        <v>2.5668704388639605e-06</v>
+        <v>2.7223854920857679e-06</v>
       </c>
       <c r="X5">
-        <v>0.0035692276467660811</v>
+        <v>0.0035628364151353877</v>
       </c>
     </row>
     <row r="6">
@@ -937,73 +928,73 @@
         <v>36</v>
       </c>
       <c r="B6">
-        <v>0.26606349634549448</v>
+        <v>0.26555097545693584</v>
       </c>
       <c r="C6">
-        <v>1.0886439448035665e-05</v>
+        <v>1.1054460435203857e-05</v>
       </c>
       <c r="D6">
-        <v>0.00011002334803386221</v>
+        <v>0.00010979551085336763</v>
       </c>
       <c r="E6">
-        <v>0.00020006144129067752</v>
+        <v>0.00019991832954099296</v>
       </c>
       <c r="F6">
-        <v>-0.00086476740349140544</v>
+        <v>-0.00086434271039442497</v>
       </c>
       <c r="G6">
-        <v>0.0026981185158032025</v>
+        <v>0.0026977055473326513</v>
       </c>
       <c r="H6">
-        <v>0.00032841930053446877</v>
+        <v>0.00032812130002539235</v>
       </c>
       <c r="I6">
-        <v>4.6636211371820348e-05</v>
+        <v>4.5442728520343745e-05</v>
       </c>
       <c r="J6">
-        <v>0.00011295289957566473</v>
+        <v>0.00011102661297750501</v>
       </c>
       <c r="K6">
-        <v>0.00013673657893888759</v>
+        <v>0.00013518379020379816</v>
       </c>
       <c r="L6">
-        <v>0.00015516340464972388</v>
+        <v>0.00015367850324260728</v>
       </c>
       <c r="M6">
-        <v>-8.6605854461921372e-08</v>
+        <v>4.883848170320667e-07</v>
       </c>
       <c r="N6">
-        <v>-3.3534860002313715e-06</v>
+        <v>-2.9234180232962613e-06</v>
       </c>
       <c r="O6">
-        <v>4.1301294243326092e-06</v>
+        <v>4.6112438096655045e-06</v>
       </c>
       <c r="P6">
-        <v>7.1158286582024156e-06</v>
+        <v>7.6525541569424753e-06</v>
       </c>
       <c r="Q6">
-        <v>1.7500937488835574e-05</v>
+        <v>1.7903599447417527e-05</v>
       </c>
       <c r="R6">
-        <v>-3.4985097604349588e-05</v>
+        <v>-3.4351594892887186e-05</v>
       </c>
       <c r="S6">
-        <v>2.1730594511169837e-06</v>
+        <v>2.152890091293391e-06</v>
       </c>
       <c r="T6">
-        <v>-1.3190440475201832e-05</v>
+        <v>-1.3862526754995427e-05</v>
       </c>
       <c r="U6">
-        <v>1.1618287407189176e-05</v>
+        <v>1.1628737978713679e-05</v>
       </c>
       <c r="V6">
-        <v>3.8741080464001795e-05</v>
+        <v>3.8686227267573483e-05</v>
       </c>
       <c r="W6">
-        <v>4.4606115886502962e-05</v>
+        <v>4.4736235413993827e-05</v>
       </c>
       <c r="X6">
-        <v>-0.00246090698286843</v>
+        <v>-0.0024553318173381788</v>
       </c>
     </row>
     <row r="7">
@@ -1011,73 +1002,73 @@
         <v>37</v>
       </c>
       <c r="B7">
-        <v>0.1837903568861094</v>
+        <v>0.18353393272523935</v>
       </c>
       <c r="C7">
-        <v>1.2530577705779919e-05</v>
+        <v>1.276518845022195e-05</v>
       </c>
       <c r="D7">
-        <v>-4.4521885406181616e-05</v>
+        <v>-4.4548407069825108e-05</v>
       </c>
       <c r="E7">
-        <v>-0.00050639727639288483</v>
+        <v>-0.00050607386823679963</v>
       </c>
       <c r="F7">
-        <v>9.2192680585024157e-05</v>
+        <v>9.241398027864966e-05</v>
       </c>
       <c r="G7">
-        <v>0.00032841930053446877</v>
+        <v>0.00032812130002539235</v>
       </c>
       <c r="H7">
-        <v>0.0012667759019090829</v>
+        <v>0.001267014578580981</v>
       </c>
       <c r="I7">
-        <v>1.7293387898520228e-05</v>
+        <v>1.6182760257900449e-05</v>
       </c>
       <c r="J7">
-        <v>5.5390732907903214e-05</v>
+        <v>5.3585217095280612e-05</v>
       </c>
       <c r="K7">
-        <v>0.00011280351142830191</v>
+        <v>0.00011228267061366071</v>
       </c>
       <c r="L7">
-        <v>0.00010553261768774734</v>
+        <v>0.00010453438599147423</v>
       </c>
       <c r="M7">
-        <v>-1.6292918739662228e-05</v>
+        <v>-1.655286905757322e-05</v>
       </c>
       <c r="N7">
-        <v>-8.1340843056609824e-05</v>
+        <v>-8.1647099933679481e-05</v>
       </c>
       <c r="O7">
-        <v>-6.5614278631255125e-05</v>
+        <v>-6.6109622909688688e-05</v>
       </c>
       <c r="P7">
-        <v>-5.6172970668571213e-05</v>
+        <v>-5.6415696520949378e-05</v>
       </c>
       <c r="Q7">
-        <v>-7.9396741760532917e-05</v>
+        <v>-7.9633047079400194e-05</v>
       </c>
       <c r="R7">
-        <v>-9.2733346618528999e-05</v>
+        <v>-9.2952006554972454e-05</v>
       </c>
       <c r="S7">
-        <v>-3.2418698911375941e-07</v>
+        <v>-3.6377221385323801e-07</v>
       </c>
       <c r="T7">
-        <v>-2.5305530055338125e-05</v>
+        <v>-2.5288293787748272e-05</v>
       </c>
       <c r="U7">
-        <v>6.1628758911100887e-05</v>
+        <v>6.2397455134502534e-05</v>
       </c>
       <c r="V7">
-        <v>0.0002620191602555103</v>
+        <v>0.00026217846067737104</v>
       </c>
       <c r="W7">
-        <v>0.0001472388666721383</v>
+        <v>0.0001476501992311943</v>
       </c>
       <c r="X7">
-        <v>-0.00010043214947687935</v>
+        <v>-9.8679339674429543e-05</v>
       </c>
     </row>
     <row r="8">
@@ -1085,73 +1076,73 @@
         <v>38</v>
       </c>
       <c r="B8">
-        <v>0.17524740922346632</v>
+        <v>0.17873273116657199</v>
       </c>
       <c r="C8">
-        <v>-1.0829388282259129e-05</v>
+        <v>-1.1380726729727655e-05</v>
       </c>
       <c r="D8">
-        <v>-2.1589168437395894e-06</v>
+        <v>-1.9584188272895654e-06</v>
       </c>
       <c r="E8">
-        <v>-7.2530235086693288e-06</v>
+        <v>-5.6401825943824379e-06</v>
       </c>
       <c r="F8">
-        <v>-1.278108997361608e-05</v>
+        <v>-1.3342616587056269e-05</v>
       </c>
       <c r="G8">
-        <v>4.6636211371820348e-05</v>
+        <v>4.5442728520343745e-05</v>
       </c>
       <c r="H8">
-        <v>1.7293387898520228e-05</v>
+        <v>1.6182760257900449e-05</v>
       </c>
       <c r="I8">
-        <v>0.00095421900206692873</v>
+        <v>0.00095619428892731756</v>
       </c>
       <c r="J8">
-        <v>0.00054290811050876516</v>
+        <v>0.00054421907457499622</v>
       </c>
       <c r="K8">
-        <v>0.0005392274558404538</v>
+        <v>0.00054076357496786855</v>
       </c>
       <c r="L8">
-        <v>0.0005468550263626194</v>
+        <v>0.00054842434134435051</v>
       </c>
       <c r="M8">
-        <v>-9.0388836317207465e-05</v>
+        <v>-9.0911023812305275e-05</v>
       </c>
       <c r="N8">
-        <v>-9.6410998299437575e-05</v>
+        <v>-9.8104025494364521e-05</v>
       </c>
       <c r="O8">
-        <v>-0.00012952807267497285</v>
+        <v>-0.00013088984251906198</v>
       </c>
       <c r="P8">
-        <v>-8.2871565907973965e-05</v>
+        <v>-8.4367701777185138e-05</v>
       </c>
       <c r="Q8">
-        <v>-0.00011042738596135537</v>
+        <v>-0.00011414253206704439</v>
       </c>
       <c r="R8">
-        <v>-5.9125238864812872e-05</v>
+        <v>-6.0061136065945288e-05</v>
       </c>
       <c r="S8">
-        <v>5.5968767735519801e-06</v>
+        <v>5.4920872460212021e-06</v>
       </c>
       <c r="T8">
-        <v>-6.4442836347353749e-05</v>
+        <v>-6.8189978583488664e-05</v>
       </c>
       <c r="U8">
-        <v>-1.1316703399615107e-05</v>
+        <v>-8.302228995382926e-06</v>
       </c>
       <c r="V8">
-        <v>1.8159333328198641e-05</v>
+        <v>2.0405745842343471e-05</v>
       </c>
       <c r="W8">
-        <v>-3.2134967341227819e-05</v>
+        <v>-2.9489284404706859e-05</v>
       </c>
       <c r="X8">
-        <v>-0.00050835998413518773</v>
+        <v>-0.00050938541831626629</v>
       </c>
     </row>
     <row r="9">
@@ -1159,73 +1150,73 @@
         <v>39</v>
       </c>
       <c r="B9">
-        <v>0.23190674790880267</v>
+        <v>0.22834191739231802</v>
       </c>
       <c r="C9">
-        <v>-8.9154141434915328e-07</v>
+        <v>5.8306440264823242e-07</v>
       </c>
       <c r="D9">
-        <v>8.6514903466760977e-05</v>
+        <v>8.6106860369117861e-05</v>
       </c>
       <c r="E9">
-        <v>-0.00014038751107323859</v>
+        <v>-0.00013543146612350092</v>
       </c>
       <c r="F9">
-        <v>-0.00015614960831265709</v>
+        <v>-0.00015507156521237374</v>
       </c>
       <c r="G9">
-        <v>0.00011295289957566473</v>
+        <v>0.00011102661297750501</v>
       </c>
       <c r="H9">
-        <v>5.5390732907903214e-05</v>
+        <v>5.3585217095280612e-05</v>
       </c>
       <c r="I9">
-        <v>0.00054290811050876516</v>
+        <v>0.00054421907457499622</v>
       </c>
       <c r="J9">
-        <v>0.0016613185852550078</v>
+        <v>0.0016526193765797176</v>
       </c>
       <c r="K9">
-        <v>0.00096394314566897827</v>
+        <v>0.00096102232650368603</v>
       </c>
       <c r="L9">
-        <v>0.00097834125852321085</v>
+        <v>0.00097540416534114814</v>
       </c>
       <c r="M9">
-        <v>-9.6037099052273317e-05</v>
+        <v>-9.5754157910514937e-05</v>
       </c>
       <c r="N9">
-        <v>-0.0001023684546753497</v>
+        <v>-0.00010272848895685337</v>
       </c>
       <c r="O9">
-        <v>-0.00010509838355078426</v>
+        <v>-0.00010590045680778433</v>
       </c>
       <c r="P9">
-        <v>-6.727988575313008e-05</v>
+        <v>-6.6637993258357974e-05</v>
       </c>
       <c r="Q9">
-        <v>-5.7388991244186518e-05</v>
+        <v>-5.7359153085030144e-05</v>
       </c>
       <c r="R9">
-        <v>-4.8932099875027477e-05</v>
+        <v>-4.8831376289633452e-05</v>
       </c>
       <c r="S9">
-        <v>1.0675856802272877e-05</v>
+        <v>1.0745776938473883e-05</v>
       </c>
       <c r="T9">
-        <v>-2.0756253359436108e-05</v>
+        <v>-2.4628053995732211e-05</v>
       </c>
       <c r="U9">
-        <v>-8.4348409378344103e-05</v>
+        <v>-8.9394754522013599e-05</v>
       </c>
       <c r="V9">
-        <v>-3.8109229291328475e-05</v>
+        <v>-3.9732056429816229e-05</v>
       </c>
       <c r="W9">
-        <v>-7.7111327278098435e-06</v>
+        <v>-7.3694741155884945e-06</v>
       </c>
       <c r="X9">
-        <v>-0.0025009936575565114</v>
+        <v>-0.0024940081247746358</v>
       </c>
     </row>
     <row r="10">
@@ -1233,73 +1224,73 @@
         <v>40</v>
       </c>
       <c r="B10">
-        <v>0.27766658031748337</v>
+        <v>0.27539616536036199</v>
       </c>
       <c r="C10">
-        <v>2.4510385167041444e-05</v>
+        <v>2.5552427083685517e-05</v>
       </c>
       <c r="D10">
-        <v>0.00017205609895866247</v>
+        <v>0.0001716893785905782</v>
       </c>
       <c r="E10">
-        <v>-0.00023927141411159061</v>
+        <v>-0.00023624392555496158</v>
       </c>
       <c r="F10">
-        <v>-0.000276637659283532</v>
+        <v>-0.00027577076972511399</v>
       </c>
       <c r="G10">
-        <v>0.00013673657893888759</v>
+        <v>0.00013518379020379816</v>
       </c>
       <c r="H10">
-        <v>0.00011280351142830191</v>
+        <v>0.00011228267061366071</v>
       </c>
       <c r="I10">
-        <v>0.0005392274558404538</v>
+        <v>0.00054076357496786855</v>
       </c>
       <c r="J10">
-        <v>0.00096394314566897827</v>
+        <v>0.00096102232650368603</v>
       </c>
       <c r="K10">
-        <v>0.0026691732283158362</v>
+        <v>0.0026686344292708372</v>
       </c>
       <c r="L10">
-        <v>0.0014023872457685569</v>
+        <v>0.001400281302828391</v>
       </c>
       <c r="M10">
-        <v>-9.8268229473548983e-05</v>
+        <v>-9.8524181647958401e-05</v>
       </c>
       <c r="N10">
-        <v>-0.00021447845653637917</v>
+        <v>-0.00021499653107708494</v>
       </c>
       <c r="O10">
-        <v>-0.0002154225704627782</v>
+        <v>-0.00021512108826686276</v>
       </c>
       <c r="P10">
-        <v>-0.00010796767401879048</v>
+        <v>-0.00010826604348756954</v>
       </c>
       <c r="Q10">
-        <v>-0.00017126113878212942</v>
+        <v>-0.00017249577446618256</v>
       </c>
       <c r="R10">
-        <v>-4.9034975211005583e-05</v>
+        <v>-4.8048250963928917e-05</v>
       </c>
       <c r="S10">
-        <v>8.783004711298111e-06</v>
+        <v>8.7703658756554281e-06</v>
       </c>
       <c r="T10">
-        <v>-0.00011358015980964279</v>
+        <v>-0.00011598847574612482</v>
       </c>
       <c r="U10">
-        <v>-6.7102564024877891e-05</v>
+        <v>-6.4415936709057446e-05</v>
       </c>
       <c r="V10">
-        <v>-1.547961679484967e-05</v>
+        <v>-1.6449097339529643e-05</v>
       </c>
       <c r="W10">
-        <v>3.1540406941475783e-05</v>
+        <v>3.2206533836783816e-05</v>
       </c>
       <c r="X10">
-        <v>-0.0042472755154065941</v>
+        <v>-0.0042406520628242642</v>
       </c>
     </row>
     <row r="11">
@@ -1307,73 +1298,73 @@
         <v>41</v>
       </c>
       <c r="B11">
-        <v>0.47490578906085984</v>
+        <v>0.47327202860990603</v>
       </c>
       <c r="C11">
-        <v>-2.3997063754733366e-05</v>
+        <v>-2.3270957972627249e-05</v>
       </c>
       <c r="D11">
-        <v>0.00018131654951066521</v>
+        <v>0.00018096839143208948</v>
       </c>
       <c r="E11">
-        <v>-0.00019417807775790291</v>
+        <v>-0.00019054510654706097</v>
       </c>
       <c r="F11">
-        <v>-0.00029534326502125055</v>
+        <v>-0.00029455272036834078</v>
       </c>
       <c r="G11">
-        <v>0.00015516340464972388</v>
+        <v>0.00015367850324260728</v>
       </c>
       <c r="H11">
-        <v>0.00010553261768774734</v>
+        <v>0.00010453438599147423</v>
       </c>
       <c r="I11">
-        <v>0.0005468550263626194</v>
+        <v>0.00054842434134435051</v>
       </c>
       <c r="J11">
-        <v>0.00097834125852321085</v>
+        <v>0.00097540416534114814</v>
       </c>
       <c r="K11">
-        <v>0.0014023872457685569</v>
+        <v>0.001400281302828391</v>
       </c>
       <c r="L11">
-        <v>0.0032711015761770364</v>
+        <v>0.0032681242172454975</v>
       </c>
       <c r="M11">
-        <v>-7.0491929602225709e-05</v>
+        <v>-7.0681162947343074e-05</v>
       </c>
       <c r="N11">
-        <v>-0.00025104600977592399</v>
+        <v>-0.00025166467281551594</v>
       </c>
       <c r="O11">
-        <v>-0.00026613082485046143</v>
+        <v>-0.0002664888368138598</v>
       </c>
       <c r="P11">
-        <v>-3.7054164029303067e-05</v>
+        <v>-3.738454837627506e-05</v>
       </c>
       <c r="Q11">
-        <v>-0.00016676909247221195</v>
+        <v>-0.00016786538347233294</v>
       </c>
       <c r="R11">
-        <v>6.8463871906335161e-05</v>
+        <v>6.8752253410458519e-05</v>
       </c>
       <c r="S11">
-        <v>1.4560298566931645e-05</v>
+        <v>1.4557923173846277e-05</v>
       </c>
       <c r="T11">
-        <v>-0.00015028077791048042</v>
+        <v>-0.00015277485555255897</v>
       </c>
       <c r="U11">
-        <v>-0.00016275318016031369</v>
+        <v>-0.00016300125420515049</v>
       </c>
       <c r="V11">
-        <v>-6.4631717847807996e-05</v>
+        <v>-6.5220768115095999e-05</v>
       </c>
       <c r="W11">
-        <v>-3.5151370033865829e-05</v>
+        <v>-3.4441338183214035e-05</v>
       </c>
       <c r="X11">
-        <v>-0.0045334035957148369</v>
+        <v>-0.0045265426090361112</v>
       </c>
     </row>
     <row r="12">
@@ -1381,73 +1372,73 @@
         <v>42</v>
       </c>
       <c r="B12">
-        <v>-0.036474548956195722</v>
+        <v>-0.036817810742166036</v>
       </c>
       <c r="C12">
-        <v>-2.8196457508709166e-05</v>
+        <v>-2.8260875892740665e-05</v>
       </c>
       <c r="D12">
-        <v>-2.0444164833006507e-05</v>
+        <v>-2.0346613448131564e-05</v>
       </c>
       <c r="E12">
-        <v>-8.6955610511307412e-05</v>
+        <v>-8.6660424805947919e-05</v>
       </c>
       <c r="F12">
-        <v>2.7962621392732707e-05</v>
+        <v>2.7561426761518217e-05</v>
       </c>
       <c r="G12">
-        <v>-8.6605854461921372e-08</v>
+        <v>4.883848170320667e-07</v>
       </c>
       <c r="H12">
-        <v>-1.6292918739662228e-05</v>
+        <v>-1.655286905757322e-05</v>
       </c>
       <c r="I12">
-        <v>-9.0388836317207465e-05</v>
+        <v>-9.0911023812305275e-05</v>
       </c>
       <c r="J12">
-        <v>-9.6037099052273317e-05</v>
+        <v>-9.5754157910514937e-05</v>
       </c>
       <c r="K12">
-        <v>-9.8268229473548983e-05</v>
+        <v>-9.8524181647958401e-05</v>
       </c>
       <c r="L12">
-        <v>-7.0491929602225709e-05</v>
+        <v>-7.0681162947343074e-05</v>
       </c>
       <c r="M12">
-        <v>0.0050663860419252948</v>
+        <v>0.0050674606806236375</v>
       </c>
       <c r="N12">
-        <v>0.0038805056949495274</v>
+        <v>0.0038817169158048628</v>
       </c>
       <c r="O12">
-        <v>0.0038837774293781001</v>
+        <v>0.0038849516884137351</v>
       </c>
       <c r="P12">
-        <v>0.0038772135642165103</v>
+        <v>0.0038783903283093205</v>
       </c>
       <c r="Q12">
-        <v>0.0038853946959927386</v>
+        <v>0.003886830811910132</v>
       </c>
       <c r="R12">
-        <v>0.0038759532011701861</v>
+        <v>0.003876976130582493</v>
       </c>
       <c r="S12">
-        <v>2.6895318857309418e-06</v>
+        <v>2.7216671889898026e-06</v>
       </c>
       <c r="T12">
-        <v>2.2843894055343036e-05</v>
+        <v>2.2455355669528335e-05</v>
       </c>
       <c r="U12">
-        <v>-3.0058754792146336e-05</v>
+        <v>-3.0741558713016129e-05</v>
       </c>
       <c r="V12">
-        <v>-3.5206270989632292e-05</v>
+        <v>-3.5602634885121068e-05</v>
       </c>
       <c r="W12">
-        <v>-5.5574648317858457e-05</v>
+        <v>-5.5862690318777999e-05</v>
       </c>
       <c r="X12">
-        <v>-0.0034036755612217328</v>
+        <v>-0.0034067571677651163</v>
       </c>
     </row>
     <row r="13">
@@ -1455,73 +1446,73 @@
         <v>43</v>
       </c>
       <c r="B13">
-        <v>0.028700698626239644</v>
+        <v>0.028225583875224905</v>
       </c>
       <c r="C13">
-        <v>-4.5227974366673126e-05</v>
+        <v>-4.5332756772375213e-05</v>
       </c>
       <c r="D13">
-        <v>-2.9149268702997368e-05</v>
+        <v>-2.9005552255030684e-05</v>
       </c>
       <c r="E13">
-        <v>-3.8418787722349721e-05</v>
+        <v>-3.8107708286064679e-05</v>
       </c>
       <c r="F13">
-        <v>5.0104063907688637e-05</v>
+        <v>4.9639587999507784e-05</v>
       </c>
       <c r="G13">
-        <v>-3.3534860002313715e-06</v>
+        <v>-2.9234180232962613e-06</v>
       </c>
       <c r="H13">
-        <v>-8.1340843056609824e-05</v>
+        <v>-8.1647099933679481e-05</v>
       </c>
       <c r="I13">
-        <v>-9.6410998299437575e-05</v>
+        <v>-9.8104025494364521e-05</v>
       </c>
       <c r="J13">
-        <v>-0.0001023684546753497</v>
+        <v>-0.00010272848895685337</v>
       </c>
       <c r="K13">
-        <v>-0.00021447845653637917</v>
+        <v>-0.00021499653107708494</v>
       </c>
       <c r="L13">
-        <v>-0.00025104600977592399</v>
+        <v>-0.00025166467281551594</v>
       </c>
       <c r="M13">
-        <v>0.0038805056949495274</v>
+        <v>0.0038817169158048628</v>
       </c>
       <c r="N13">
-        <v>0.0049099138110512185</v>
+        <v>0.0049109150360035492</v>
       </c>
       <c r="O13">
-        <v>0.0039019710887432555</v>
+        <v>0.0039031966070286963</v>
       </c>
       <c r="P13">
-        <v>0.0038824694256181574</v>
+        <v>0.0038837154212461346</v>
       </c>
       <c r="Q13">
-        <v>0.0039014927038091749</v>
+        <v>0.0039030494206723433</v>
       </c>
       <c r="R13">
-        <v>0.0038757630256736494</v>
+        <v>0.0038767749881175192</v>
       </c>
       <c r="S13">
-        <v>-6.7311660324824815e-07</v>
+        <v>-6.5342749210885279e-07</v>
       </c>
       <c r="T13">
-        <v>4.9300053457845741e-05</v>
+        <v>4.9062219081101024e-05</v>
       </c>
       <c r="U13">
-        <v>-2.8369510054613358e-06</v>
+        <v>-3.8147210840897515e-06</v>
       </c>
       <c r="V13">
-        <v>-2.9512044145471659e-05</v>
+        <v>-2.9880126272694265e-05</v>
       </c>
       <c r="W13">
-        <v>-4.7447769892382643e-05</v>
+        <v>-4.7695244758435684e-05</v>
       </c>
       <c r="X13">
-        <v>-0.003106592029700316</v>
+        <v>-0.0031097753746780719</v>
       </c>
     </row>
     <row r="14">
@@ -1529,73 +1520,73 @@
         <v>44</v>
       </c>
       <c r="B14">
-        <v>-0.052637815371653775</v>
+        <v>-0.052939045553858241</v>
       </c>
       <c r="C14">
-        <v>-2.5841294697318413e-05</v>
+        <v>-2.6030787126567166e-05</v>
       </c>
       <c r="D14">
-        <v>-2.9131533922440117e-05</v>
+        <v>-2.8957396012170241e-05</v>
       </c>
       <c r="E14">
-        <v>-5.5868557601869342e-05</v>
+        <v>-5.5452482649360254e-05</v>
       </c>
       <c r="F14">
-        <v>4.5110121240774913e-05</v>
+        <v>4.4597633397449894e-05</v>
       </c>
       <c r="G14">
-        <v>4.1301294243326092e-06</v>
+        <v>4.6112438096655045e-06</v>
       </c>
       <c r="H14">
-        <v>-6.5614278631255125e-05</v>
+        <v>-6.6109622909688688e-05</v>
       </c>
       <c r="I14">
-        <v>-0.00012952807267497285</v>
+        <v>-0.00013088984251906198</v>
       </c>
       <c r="J14">
-        <v>-0.00010509838355078426</v>
+        <v>-0.00010590045680778433</v>
       </c>
       <c r="K14">
-        <v>-0.0002154225704627782</v>
+        <v>-0.00021512108826686276</v>
       </c>
       <c r="L14">
-        <v>-0.00026613082485046143</v>
+        <v>-0.0002664888368138598</v>
       </c>
       <c r="M14">
-        <v>0.0038837774293781001</v>
+        <v>0.0038849516884137351</v>
       </c>
       <c r="N14">
-        <v>0.0039019710887432555</v>
+        <v>0.0039031966070286963</v>
       </c>
       <c r="O14">
-        <v>0.004961502865514192</v>
+        <v>0.0049624793457946339</v>
       </c>
       <c r="P14">
-        <v>0.0038831754775257954</v>
+        <v>0.0038844208824492434</v>
       </c>
       <c r="Q14">
-        <v>0.0038987426195524703</v>
+        <v>0.003900162289348464</v>
       </c>
       <c r="R14">
-        <v>0.0038741029270415216</v>
+        <v>0.0038751549393777722</v>
       </c>
       <c r="S14">
-        <v>-4.0864270777853218e-06</v>
+        <v>-4.0415293265588597e-06</v>
       </c>
       <c r="T14">
-        <v>4.2631616529122682e-05</v>
+        <v>4.2580542231541964e-05</v>
       </c>
       <c r="U14">
-        <v>-3.0817792982529426e-05</v>
+        <v>-3.2014411999890349e-05</v>
       </c>
       <c r="V14">
-        <v>-4.8975607964531621e-05</v>
+        <v>-4.9439602074253597e-05</v>
       </c>
       <c r="W14">
-        <v>-2.694158706709692e-05</v>
+        <v>-2.7277535470586738e-05</v>
       </c>
       <c r="X14">
-        <v>-0.003050127409013211</v>
+        <v>-0.0030542918075739511</v>
       </c>
     </row>
     <row r="15">
@@ -1603,73 +1594,73 @@
         <v>45</v>
       </c>
       <c r="B15">
-        <v>-0.049909564482433964</v>
+        <v>-0.050412118008601153</v>
       </c>
       <c r="C15">
-        <v>-3.19522070572313e-05</v>
+        <v>-3.1951245269935119e-05</v>
       </c>
       <c r="D15">
-        <v>-1.6142784236935397e-05</v>
+        <v>-1.5986335605171643e-05</v>
       </c>
       <c r="E15">
-        <v>-4.8192904526197285e-05</v>
+        <v>-4.7962815156179887e-05</v>
       </c>
       <c r="F15">
-        <v>3.2548177969952442e-05</v>
+        <v>3.2084103206722614e-05</v>
       </c>
       <c r="G15">
-        <v>7.1158286582024156e-06</v>
+        <v>7.6525541569424753e-06</v>
       </c>
       <c r="H15">
-        <v>-5.6172970668571213e-05</v>
+        <v>-5.6415696520949378e-05</v>
       </c>
       <c r="I15">
-        <v>-8.2871565907973965e-05</v>
+        <v>-8.4367701777185138e-05</v>
       </c>
       <c r="J15">
-        <v>-6.727988575313008e-05</v>
+        <v>-6.6637993258357974e-05</v>
       </c>
       <c r="K15">
-        <v>-0.00010796767401879048</v>
+        <v>-0.00010826604348756954</v>
       </c>
       <c r="L15">
-        <v>-3.7054164029303067e-05</v>
+        <v>-3.738454837627506e-05</v>
       </c>
       <c r="M15">
-        <v>0.0038772135642165103</v>
+        <v>0.0038783903283093205</v>
       </c>
       <c r="N15">
-        <v>0.0038824694256181574</v>
+        <v>0.0038837154212461346</v>
       </c>
       <c r="O15">
-        <v>0.0038831754775257954</v>
+        <v>0.0038844208824492434</v>
       </c>
       <c r="P15">
-        <v>0.0046989448140561125</v>
+        <v>0.0047002865957919094</v>
       </c>
       <c r="Q15">
-        <v>0.0038871296090359189</v>
+        <v>0.0038887103503880477</v>
       </c>
       <c r="R15">
-        <v>0.0038793170582723997</v>
+        <v>0.0038804114951039373</v>
       </c>
       <c r="S15">
-        <v>2.9128911858045434e-06</v>
+        <v>2.9453270013539052e-06</v>
       </c>
       <c r="T15">
-        <v>2.8892822648469074e-05</v>
+        <v>2.8633168505836585e-05</v>
       </c>
       <c r="U15">
-        <v>-3.207345260224613e-05</v>
+        <v>-3.3125937762476293e-05</v>
       </c>
       <c r="V15">
-        <v>-3.5885215201416081e-05</v>
+        <v>-3.6416480972297849e-05</v>
       </c>
       <c r="W15">
-        <v>-4.8243077861052897e-05</v>
+        <v>-4.8518008187526502e-05</v>
       </c>
       <c r="X15">
-        <v>-0.0034833036844281588</v>
+        <v>-0.0034873771852293976</v>
       </c>
     </row>
     <row r="16">
@@ -1677,73 +1668,73 @@
         <v>46</v>
       </c>
       <c r="B16">
-        <v>-0.056202180904038987</v>
+        <v>-0.056916565680939675</v>
       </c>
       <c r="C16">
-        <v>-5.5036374184787003e-05</v>
+        <v>-5.507550833823332e-05</v>
       </c>
       <c r="D16">
-        <v>-1.6520012026069276e-05</v>
+        <v>-1.6281221913368787e-05</v>
       </c>
       <c r="E16">
-        <v>-3.7776783440613177e-05</v>
+        <v>-3.743478803600236e-05</v>
       </c>
       <c r="F16">
-        <v>2.8866317913841348e-05</v>
+        <v>2.8403179923142725e-05</v>
       </c>
       <c r="G16">
-        <v>1.7500937488835574e-05</v>
+        <v>1.7903599447417527e-05</v>
       </c>
       <c r="H16">
-        <v>-7.9396741760532917e-05</v>
+        <v>-7.9633047079400194e-05</v>
       </c>
       <c r="I16">
-        <v>-0.00011042738596135537</v>
+        <v>-0.00011414253206704439</v>
       </c>
       <c r="J16">
-        <v>-5.7388991244186518e-05</v>
+        <v>-5.7359153085030144e-05</v>
       </c>
       <c r="K16">
-        <v>-0.00017126113878212942</v>
+        <v>-0.00017249577446618256</v>
       </c>
       <c r="L16">
-        <v>-0.00016676909247221195</v>
+        <v>-0.00016786538347233294</v>
       </c>
       <c r="M16">
-        <v>0.0038853946959927386</v>
+        <v>0.003886830811910132</v>
       </c>
       <c r="N16">
-        <v>0.0039014927038091749</v>
+        <v>0.0039030494206723433</v>
       </c>
       <c r="O16">
-        <v>0.0038987426195524703</v>
+        <v>0.003900162289348464</v>
       </c>
       <c r="P16">
-        <v>0.0038871296090359189</v>
+        <v>0.0038887103503880477</v>
       </c>
       <c r="Q16">
-        <v>0.0045811661521422773</v>
+        <v>0.0045828879574468691</v>
       </c>
       <c r="R16">
-        <v>0.0038830929992130564</v>
+        <v>0.003884383719957937</v>
       </c>
       <c r="S16">
-        <v>-2.2305747263225335e-06</v>
+        <v>-2.2168544883133793e-06</v>
       </c>
       <c r="T16">
-        <v>0.00015289556543355881</v>
+        <v>0.00015293347471400471</v>
       </c>
       <c r="U16">
-        <v>-1.5604999875911947e-05</v>
+        <v>-1.6664693129737039e-05</v>
       </c>
       <c r="V16">
-        <v>-4.9392499122509373e-05</v>
+        <v>-4.9797969748219088e-05</v>
       </c>
       <c r="W16">
-        <v>-8.0542882071318509e-05</v>
+        <v>-8.0719469348065117e-05</v>
       </c>
       <c r="X16">
-        <v>-0.0033494268064500916</v>
+        <v>-0.0033541223069299057</v>
       </c>
     </row>
     <row r="17">
@@ -1751,73 +1742,73 @@
         <v>47</v>
       </c>
       <c r="B17">
-        <v>-0.039452231840961173</v>
+        <v>-0.039563958722327083</v>
       </c>
       <c r="C17">
-        <v>-5.4894143815320052e-05</v>
+        <v>-5.5041332143276523e-05</v>
       </c>
       <c r="D17">
-        <v>-7.2687491563628388e-06</v>
+        <v>-7.0016122684143499e-06</v>
       </c>
       <c r="E17">
-        <v>-7.0752729348080509e-06</v>
+        <v>-6.3839353967824883e-06</v>
       </c>
       <c r="F17">
-        <v>2.9248414192957928e-05</v>
+        <v>2.8613473755967377e-05</v>
       </c>
       <c r="G17">
-        <v>-3.4985097604349588e-05</v>
+        <v>-3.4351594892887186e-05</v>
       </c>
       <c r="H17">
-        <v>-9.2733346618528999e-05</v>
+        <v>-9.2952006554972454e-05</v>
       </c>
       <c r="I17">
-        <v>-5.9125238864812872e-05</v>
+        <v>-6.0061136065945288e-05</v>
       </c>
       <c r="J17">
-        <v>-4.8932099875027477e-05</v>
+        <v>-4.8831376289633452e-05</v>
       </c>
       <c r="K17">
-        <v>-4.9034975211005583e-05</v>
+        <v>-4.8048250963928917e-05</v>
       </c>
       <c r="L17">
-        <v>6.8463871906335161e-05</v>
+        <v>6.8752253410458519e-05</v>
       </c>
       <c r="M17">
-        <v>0.0038759532011701861</v>
+        <v>0.003876976130582493</v>
       </c>
       <c r="N17">
-        <v>0.0038757630256736494</v>
+        <v>0.0038767749881175192</v>
       </c>
       <c r="O17">
-        <v>0.0038741029270415216</v>
+        <v>0.0038751549393777722</v>
       </c>
       <c r="P17">
-        <v>0.0038793170582723997</v>
+        <v>0.0038804114951039373</v>
       </c>
       <c r="Q17">
-        <v>0.0038830929992130564</v>
+        <v>0.003884383719957937</v>
       </c>
       <c r="R17">
-        <v>0.0045719145913298131</v>
+        <v>0.004572776922183751</v>
       </c>
       <c r="S17">
-        <v>7.6941130727885705e-07</v>
+        <v>8.0353552875701975e-07</v>
       </c>
       <c r="T17">
-        <v>6.5605083411572184e-05</v>
+        <v>6.5247449432754515e-05</v>
       </c>
       <c r="U17">
-        <v>-3.9207255258127006e-05</v>
+        <v>-3.9914109004138531e-05</v>
       </c>
       <c r="V17">
-        <v>-7.6603401658696386e-05</v>
+        <v>-7.6980974994749147e-05</v>
       </c>
       <c r="W17">
-        <v>-6.7721247831995673e-05</v>
+        <v>-6.7890422235781633e-05</v>
       </c>
       <c r="X17">
-        <v>-0.0036125684484087962</v>
+        <v>-0.0036190591929841374</v>
       </c>
     </row>
     <row r="18">
@@ -1825,73 +1816,73 @@
         <v>48</v>
       </c>
       <c r="B18">
-        <v>0.020278810072804784</v>
+        <v>0.020238956720677551</v>
       </c>
       <c r="C18">
-        <v>-1.4008057441146856e-06</v>
+        <v>-1.38405756557253e-06</v>
       </c>
       <c r="D18">
-        <v>1.5913813405596874e-06</v>
+        <v>1.5976973339831922e-06</v>
       </c>
       <c r="E18">
-        <v>2.6499221390003936e-06</v>
+        <v>2.6620169559592562e-06</v>
       </c>
       <c r="F18">
-        <v>-2.8927603308168332e-06</v>
+        <v>-2.8981748534000543e-06</v>
       </c>
       <c r="G18">
-        <v>2.1730594511169837e-06</v>
+        <v>2.152890091293391e-06</v>
       </c>
       <c r="H18">
-        <v>-3.2418698911375941e-07</v>
+        <v>-3.6377221385323801e-07</v>
       </c>
       <c r="I18">
-        <v>5.5968767735519801e-06</v>
+        <v>5.4920872460212021e-06</v>
       </c>
       <c r="J18">
-        <v>1.0675856802272877e-05</v>
+        <v>1.0745776938473883e-05</v>
       </c>
       <c r="K18">
-        <v>8.783004711298111e-06</v>
+        <v>8.7703658756554281e-06</v>
       </c>
       <c r="L18">
-        <v>1.4560298566931645e-05</v>
+        <v>1.4557923173846277e-05</v>
       </c>
       <c r="M18">
-        <v>2.6895318857309418e-06</v>
+        <v>2.7216671889898026e-06</v>
       </c>
       <c r="N18">
-        <v>-6.7311660324824815e-07</v>
+        <v>-6.5342749210885279e-07</v>
       </c>
       <c r="O18">
-        <v>-4.0864270777853218e-06</v>
+        <v>-4.0415293265588597e-06</v>
       </c>
       <c r="P18">
-        <v>2.9128911858045434e-06</v>
+        <v>2.9453270013539052e-06</v>
       </c>
       <c r="Q18">
-        <v>-2.2305747263225335e-06</v>
+        <v>-2.2168544883133793e-06</v>
       </c>
       <c r="R18">
-        <v>7.6941130727885705e-07</v>
+        <v>8.0353552875701975e-07</v>
       </c>
       <c r="S18">
-        <v>9.8016326339319552e-06</v>
+        <v>9.8016797014218347e-06</v>
       </c>
       <c r="T18">
-        <v>-3.1958200906701467e-05</v>
+        <v>-3.198990227583023e-05</v>
       </c>
       <c r="U18">
-        <v>-4.2820290373907706e-05</v>
+        <v>-4.2833546113699281e-05</v>
       </c>
       <c r="V18">
-        <v>-5.190217687613927e-05</v>
+        <v>-5.1909066545225365e-05</v>
       </c>
       <c r="W18">
-        <v>-6.1495867770999216e-05</v>
+        <v>-6.1484184016498514e-05</v>
       </c>
       <c r="X18">
-        <v>-0.00020014573082023952</v>
+        <v>-0.00020025893068150417</v>
       </c>
     </row>
     <row r="19">
@@ -1899,73 +1890,73 @@
         <v>49</v>
       </c>
       <c r="B19">
-        <v>-0.26606533252041181</v>
+        <v>-0.26647368889414541</v>
       </c>
       <c r="C19">
-        <v>7.6602284271958237e-06</v>
+        <v>7.3249055982587763e-06</v>
       </c>
       <c r="D19">
-        <v>-2.9280593706172784e-06</v>
+        <v>-2.9307829013420096e-06</v>
       </c>
       <c r="E19">
-        <v>7.2082010005209557e-05</v>
+        <v>7.2169135818662272e-05</v>
       </c>
       <c r="F19">
-        <v>3.553832431412449e-05</v>
+        <v>3.5884766545517515e-05</v>
       </c>
       <c r="G19">
-        <v>-1.3190440475201832e-05</v>
+        <v>-1.3862526754995427e-05</v>
       </c>
       <c r="H19">
-        <v>-2.5305530055338125e-05</v>
+        <v>-2.5288293787748272e-05</v>
       </c>
       <c r="I19">
-        <v>-6.4442836347353749e-05</v>
+        <v>-6.8189978583488664e-05</v>
       </c>
       <c r="J19">
-        <v>-2.0756253359436108e-05</v>
+        <v>-2.4628053995732211e-05</v>
       </c>
       <c r="K19">
-        <v>-0.00011358015980964279</v>
+        <v>-0.00011598847574612482</v>
       </c>
       <c r="L19">
-        <v>-0.00015028077791048042</v>
+        <v>-0.00015277485555255897</v>
       </c>
       <c r="M19">
-        <v>2.2843894055343036e-05</v>
+        <v>2.2455355669528335e-05</v>
       </c>
       <c r="N19">
-        <v>4.9300053457845741e-05</v>
+        <v>4.9062219081101024e-05</v>
       </c>
       <c r="O19">
-        <v>4.2631616529122682e-05</v>
+        <v>4.2580542231541964e-05</v>
       </c>
       <c r="P19">
-        <v>2.8892822648469074e-05</v>
+        <v>2.8633168505836585e-05</v>
       </c>
       <c r="Q19">
-        <v>0.00015289556543355881</v>
+        <v>0.00015293347471400471</v>
       </c>
       <c r="R19">
-        <v>6.5605083411572184e-05</v>
+        <v>6.5247449432754515e-05</v>
       </c>
       <c r="S19">
-        <v>-3.1958200906701467e-05</v>
+        <v>-3.198990227583023e-05</v>
       </c>
       <c r="T19">
-        <v>0.0028069101300403116</v>
+        <v>0.0028073373306718662</v>
       </c>
       <c r="U19">
-        <v>0.00033201114459715755</v>
+        <v>0.00033183765923717172</v>
       </c>
       <c r="V19">
-        <v>0.00035605014978948974</v>
+        <v>0.00035591952107894367</v>
       </c>
       <c r="W19">
-        <v>0.00038489454480272268</v>
+        <v>0.00038491934378419475</v>
       </c>
       <c r="X19">
-        <v>0.00035609015579773614</v>
+        <v>0.00035937116225963432</v>
       </c>
     </row>
     <row r="20">
@@ -1973,73 +1964,73 @@
         <v>50</v>
       </c>
       <c r="B20">
-        <v>0.34017059044499881</v>
+        <v>0.34040250683097051</v>
       </c>
       <c r="C20">
-        <v>-1.6930302265998695e-05</v>
+        <v>-1.7092488571668567e-05</v>
       </c>
       <c r="D20">
-        <v>-2.1535077201024439e-05</v>
+        <v>-2.1846187251463271e-05</v>
       </c>
       <c r="E20">
-        <v>-0.00019024964748715122</v>
+        <v>-0.00019094319503624177</v>
       </c>
       <c r="F20">
-        <v>3.7496946559498488e-05</v>
+        <v>3.8019498947896647e-05</v>
       </c>
       <c r="G20">
-        <v>1.1618287407189176e-05</v>
+        <v>1.1628737978713679e-05</v>
       </c>
       <c r="H20">
-        <v>6.1628758911100887e-05</v>
+        <v>6.2397455134502534e-05</v>
       </c>
       <c r="I20">
-        <v>-1.1316703399615107e-05</v>
+        <v>-8.302228995382926e-06</v>
       </c>
       <c r="J20">
-        <v>-8.4348409378344103e-05</v>
+        <v>-8.9394754522013599e-05</v>
       </c>
       <c r="K20">
-        <v>-6.7102564024877891e-05</v>
+        <v>-6.4415936709057446e-05</v>
       </c>
       <c r="L20">
-        <v>-0.00016275318016031369</v>
+        <v>-0.00016300125420515049</v>
       </c>
       <c r="M20">
-        <v>-3.0058754792146336e-05</v>
+        <v>-3.0741558713016129e-05</v>
       </c>
       <c r="N20">
-        <v>-2.8369510054613358e-06</v>
+        <v>-3.8147210840897515e-06</v>
       </c>
       <c r="O20">
-        <v>-3.0817792982529426e-05</v>
+        <v>-3.2014411999890349e-05</v>
       </c>
       <c r="P20">
-        <v>-3.207345260224613e-05</v>
+        <v>-3.3125937762476293e-05</v>
       </c>
       <c r="Q20">
-        <v>-1.5604999875911947e-05</v>
+        <v>-1.6664693129737039e-05</v>
       </c>
       <c r="R20">
-        <v>-3.9207255258127006e-05</v>
+        <v>-3.9914109004138531e-05</v>
       </c>
       <c r="S20">
-        <v>-4.2820290373907706e-05</v>
+        <v>-4.2833546113699281e-05</v>
       </c>
       <c r="T20">
-        <v>0.00033201114459715755</v>
+        <v>0.00033183765923717172</v>
       </c>
       <c r="U20">
-        <v>0.0042466795588720196</v>
+        <v>0.0042476209918174144</v>
       </c>
       <c r="V20">
-        <v>0.00042788862498169522</v>
+        <v>0.00042818885711444444</v>
       </c>
       <c r="W20">
-        <v>0.00046212687161064248</v>
+        <v>0.00046206665297462296</v>
       </c>
       <c r="X20">
-        <v>0.00099488919988803353</v>
+        <v>0.0010013789462656299</v>
       </c>
     </row>
     <row r="21">
@@ -2047,73 +2038,73 @@
         <v>51</v>
       </c>
       <c r="B21">
-        <v>0.41933051322313097</v>
+        <v>0.41947513102623252</v>
       </c>
       <c r="C21">
-        <v>-1.6729711706180123e-05</v>
+        <v>-1.6752814167593104e-05</v>
       </c>
       <c r="D21">
-        <v>-1.5924522668357439e-05</v>
+        <v>-1.6207183915359466e-05</v>
       </c>
       <c r="E21">
-        <v>-0.00013474371578078349</v>
+        <v>-0.0001347416131791707</v>
       </c>
       <c r="F21">
-        <v>2.9925794256317707e-05</v>
+        <v>3.0326767678386145e-05</v>
       </c>
       <c r="G21">
-        <v>3.8741080464001795e-05</v>
+        <v>3.8686227267573483e-05</v>
       </c>
       <c r="H21">
-        <v>0.0002620191602555103</v>
+        <v>0.00026217846067737104</v>
       </c>
       <c r="I21">
-        <v>1.8159333328198641e-05</v>
+        <v>2.0405745842343471e-05</v>
       </c>
       <c r="J21">
-        <v>-3.8109229291328475e-05</v>
+        <v>-3.9732056429816229e-05</v>
       </c>
       <c r="K21">
-        <v>-1.547961679484967e-05</v>
+        <v>-1.6449097339529643e-05</v>
       </c>
       <c r="L21">
-        <v>-6.4631717847807996e-05</v>
+        <v>-6.5220768115095999e-05</v>
       </c>
       <c r="M21">
-        <v>-3.5206270989632292e-05</v>
+        <v>-3.5602634885121068e-05</v>
       </c>
       <c r="N21">
-        <v>-2.9512044145471659e-05</v>
+        <v>-2.9880126272694265e-05</v>
       </c>
       <c r="O21">
-        <v>-4.8975607964531621e-05</v>
+        <v>-4.9439602074253597e-05</v>
       </c>
       <c r="P21">
-        <v>-3.5885215201416081e-05</v>
+        <v>-3.6416480972297849e-05</v>
       </c>
       <c r="Q21">
-        <v>-4.9392499122509373e-05</v>
+        <v>-4.9797969748219088e-05</v>
       </c>
       <c r="R21">
-        <v>-7.6603401658696386e-05</v>
+        <v>-7.6980974994749147e-05</v>
       </c>
       <c r="S21">
-        <v>-5.190217687613927e-05</v>
+        <v>-5.1909066545225365e-05</v>
       </c>
       <c r="T21">
-        <v>0.00035605014978948974</v>
+        <v>0.00035591952107894367</v>
       </c>
       <c r="U21">
-        <v>0.00042788862498169522</v>
+        <v>0.00042818885711444444</v>
       </c>
       <c r="V21">
-        <v>0.0020087136516202019</v>
+        <v>0.0020091075516404963</v>
       </c>
       <c r="W21">
-        <v>0.00054469042251637651</v>
+        <v>0.00054459979312604791</v>
       </c>
       <c r="X21">
-        <v>0.00084561858084993761</v>
+        <v>0.00085134405912632425</v>
       </c>
     </row>
     <row r="22">
@@ -2121,73 +2112,73 @@
         <v>52</v>
       </c>
       <c r="B22">
-        <v>0.26056826108764686</v>
+        <v>0.26074083245979152</v>
       </c>
       <c r="C22">
-        <v>2.9216267533437298e-05</v>
+        <v>2.9231494845983084e-05</v>
       </c>
       <c r="D22">
-        <v>-7.9848367730172469e-06</v>
+        <v>-8.1051178447871016e-06</v>
       </c>
       <c r="E22">
-        <v>-0.00012358751192967344</v>
+        <v>-0.00012367314094885429</v>
       </c>
       <c r="F22">
-        <v>2.5668704388639605e-06</v>
+        <v>2.7223854920857679e-06</v>
       </c>
       <c r="G22">
-        <v>4.4606115886502962e-05</v>
+        <v>4.4736235413993827e-05</v>
       </c>
       <c r="H22">
-        <v>0.0001472388666721383</v>
+        <v>0.0001476501992311943</v>
       </c>
       <c r="I22">
-        <v>-3.2134967341227819e-05</v>
+        <v>-2.9489284404706859e-05</v>
       </c>
       <c r="J22">
-        <v>-7.7111327278098435e-06</v>
+        <v>-7.3694741155884945e-06</v>
       </c>
       <c r="K22">
-        <v>3.1540406941475783e-05</v>
+        <v>3.2206533836783816e-05</v>
       </c>
       <c r="L22">
-        <v>-3.5151370033865829e-05</v>
+        <v>-3.4441338183214035e-05</v>
       </c>
       <c r="M22">
-        <v>-5.5574648317858457e-05</v>
+        <v>-5.5862690318777999e-05</v>
       </c>
       <c r="N22">
-        <v>-4.7447769892382643e-05</v>
+        <v>-4.7695244758435684e-05</v>
       </c>
       <c r="O22">
-        <v>-2.694158706709692e-05</v>
+        <v>-2.7277535470586738e-05</v>
       </c>
       <c r="P22">
-        <v>-4.8243077861052897e-05</v>
+        <v>-4.8518008187526502e-05</v>
       </c>
       <c r="Q22">
-        <v>-8.0542882071318509e-05</v>
+        <v>-8.0719469348065117e-05</v>
       </c>
       <c r="R22">
-        <v>-6.7721247831995673e-05</v>
+        <v>-6.7890422235781633e-05</v>
       </c>
       <c r="S22">
-        <v>-6.1495867770999216e-05</v>
+        <v>-6.1484184016498514e-05</v>
       </c>
       <c r="T22">
-        <v>0.00038489454480272268</v>
+        <v>0.00038491934378419475</v>
       </c>
       <c r="U22">
-        <v>0.00046212687161064248</v>
+        <v>0.00046206665297462296</v>
       </c>
       <c r="V22">
-        <v>0.00054469042251637651</v>
+        <v>0.00054459979312604791</v>
       </c>
       <c r="W22">
-        <v>0.0019701635726684483</v>
+        <v>0.0019700715490882786</v>
       </c>
       <c r="X22">
-        <v>0.00093904132100188279</v>
+        <v>0.00094003475618229589</v>
       </c>
     </row>
     <row r="23">
@@ -2195,73 +2186,73 @@
         <v>53</v>
       </c>
       <c r="B23">
-        <v>3.356046230563523</v>
+        <v>3.3677437972389259</v>
       </c>
       <c r="C23">
-        <v>-0.00026782037041550523</v>
+        <v>-0.0002720611607212399</v>
       </c>
       <c r="D23">
-        <v>-0.0017924371667468965</v>
+        <v>-0.0017893630481715995</v>
       </c>
       <c r="E23">
-        <v>-0.0057993087758113574</v>
+        <v>-0.0057960402472572135</v>
       </c>
       <c r="F23">
-        <v>0.0035692276467660811</v>
+        <v>0.0035628364151353877</v>
       </c>
       <c r="G23">
-        <v>-0.00246090698286843</v>
+        <v>-0.0024553318173381788</v>
       </c>
       <c r="H23">
-        <v>-0.00010043214947687935</v>
+        <v>-9.8679339674429543e-05</v>
       </c>
       <c r="I23">
-        <v>-0.00050835998413518773</v>
+        <v>-0.00050938541831626629</v>
       </c>
       <c r="J23">
-        <v>-0.0025009936575565114</v>
+        <v>-0.0024940081247746358</v>
       </c>
       <c r="K23">
-        <v>-0.0042472755154065941</v>
+        <v>-0.0042406520628242642</v>
       </c>
       <c r="L23">
-        <v>-0.0045334035957148369</v>
+        <v>-0.0045265426090361112</v>
       </c>
       <c r="M23">
-        <v>-0.0034036755612217328</v>
+        <v>-0.0034067571677651163</v>
       </c>
       <c r="N23">
-        <v>-0.003106592029700316</v>
+        <v>-0.0031097753746780719</v>
       </c>
       <c r="O23">
-        <v>-0.003050127409013211</v>
+        <v>-0.0030542918075739511</v>
       </c>
       <c r="P23">
-        <v>-0.0034833036844281588</v>
+        <v>-0.0034873771852293976</v>
       </c>
       <c r="Q23">
-        <v>-0.0033494268064500916</v>
+        <v>-0.0033541223069299057</v>
       </c>
       <c r="R23">
-        <v>-0.0036125684484087962</v>
+        <v>-0.0036190591929841374</v>
       </c>
       <c r="S23">
-        <v>-0.00020014573082023952</v>
+        <v>-0.00020025893068150417</v>
       </c>
       <c r="T23">
-        <v>0.00035609015579773614</v>
+        <v>0.00035937116225963432</v>
       </c>
       <c r="U23">
-        <v>0.00099488919988803353</v>
+        <v>0.0010013789462656299</v>
       </c>
       <c r="V23">
-        <v>0.00084561858084993761</v>
+        <v>0.00085134405912632425</v>
       </c>
       <c r="W23">
-        <v>0.00093904132100188279</v>
+        <v>0.00094003475618229589</v>
       </c>
       <c r="X23">
-        <v>0.044690740252647215</v>
+        <v>0.044634974595049115</v>
       </c>
     </row>
   </sheetData>
@@ -2270,7 +2261,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Y24"/>
+  <dimension ref="A1:X23"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2305,48 +2296,45 @@
         <v>60</v>
       </c>
       <c r="K1" t="s">
-        <v>61</v>
+        <v>38</v>
       </c>
       <c r="L1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="M1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="N1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="O1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="P1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="Q1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="R1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="S1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="T1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="U1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="V1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="W1" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="X1" t="s">
-        <v>50</v>
-      </c>
-      <c r="Y1" t="s">
         <v>53</v>
       </c>
     </row>
@@ -2355,76 +2343,73 @@
         <v>32</v>
       </c>
       <c r="B2">
-        <v>-0.10516592963401891</v>
+        <v>-0.095298105629226179</v>
       </c>
       <c r="C2">
-        <v>0.0010414703858404382</v>
+        <v>0.0010437326266580615</v>
       </c>
       <c r="D2">
-        <v>2.2689686324859411e-05</v>
+        <v>2.2601931473813025e-05</v>
       </c>
       <c r="E2">
-        <v>-1.401745090157859e-07</v>
+        <v>-1.3064620533752677e-07</v>
       </c>
       <c r="F2">
-        <v>4.7898491892627563e-05</v>
+        <v>6.1521208753834459e-05</v>
       </c>
       <c r="G2">
-        <v>-6.2665817317111367e-05</v>
+        <v>-6.3813940677653644e-05</v>
       </c>
       <c r="H2">
-        <v>-2.8272501896750454e-05</v>
+        <v>-3.4384581939129577e-05</v>
       </c>
       <c r="I2">
-        <v>-9.3251104221907938e-05</v>
+        <v>-0.00011305708020917964</v>
       </c>
       <c r="J2">
-        <v>0.00030103970649047389</v>
+        <v>0.00034082808829945401</v>
       </c>
       <c r="K2">
-        <v>9.6947005363065466e-05</v>
+        <v>8.8915238200703369e-05</v>
       </c>
       <c r="L2">
-        <v>8.7501969426333358e-05</v>
+        <v>2.2518691298354271e-05</v>
       </c>
       <c r="M2">
-        <v>4.4072736987518614e-05</v>
+        <v>-0.00028463225949549085</v>
       </c>
       <c r="N2">
-        <v>-0.00024798988705884847</v>
+        <v>-8.9750651379478879e-05</v>
       </c>
       <c r="O2">
-        <v>-4.3354700673628335e-05</v>
+        <v>-0.00013847242554323102</v>
       </c>
       <c r="P2">
-        <v>-0.00014200963026318346</v>
+        <v>-0.00011221579967702337</v>
       </c>
       <c r="Q2">
-        <v>-0.00012522312480704311</v>
+        <v>-0.00029295302450764812</v>
       </c>
       <c r="R2">
-        <v>-0.00030147975062645856</v>
+        <v>-9.9370182917451902e-05</v>
       </c>
       <c r="S2">
-        <v>-0.00010618077141089381</v>
+        <v>-0.00022817471093144933</v>
       </c>
       <c r="T2">
-        <v>-0.00023626449790101856</v>
+        <v>-0.00010821631387866433</v>
       </c>
       <c r="U2">
-        <v>-0.0001067016134874232</v>
+        <v>-6.9321024940633276e-06</v>
       </c>
       <c r="V2">
-        <v>-1.8578409950131022e-05</v>
+        <v>0.00040157041528798257</v>
       </c>
       <c r="W2">
-        <v>3.6957396003354273e-07</v>
+        <v>5.6577398037686562e-05</v>
       </c>
       <c r="X2">
-        <v>0.00040605087269702308</v>
-      </c>
-      <c r="Y2">
-        <v>-0.00064072713251467611</v>
+        <v>-0.00072011313282233916</v>
       </c>
     </row>
     <row r="3">
@@ -2432,76 +2417,73 @@
         <v>33</v>
       </c>
       <c r="B3">
-        <v>-0.27718535375410508</v>
+        <v>-0.27826422488624331</v>
       </c>
       <c r="C3">
-        <v>2.2689686324859411e-05</v>
+        <v>2.2601931473813025e-05</v>
       </c>
       <c r="D3">
-        <v>6.2109706963282306e-05</v>
+        <v>6.2391491287775902e-05</v>
       </c>
       <c r="E3">
-        <v>-6.7919828341109835e-07</v>
+        <v>-6.778457594025871e-07</v>
       </c>
       <c r="F3">
-        <v>-0.00014851875007472636</v>
+        <v>-0.00014297425702937405</v>
       </c>
       <c r="G3">
-        <v>-6.4594788351051986e-05</v>
+        <v>-6.6058436388056465e-05</v>
       </c>
       <c r="H3">
-        <v>0.00012766222915591274</v>
+        <v>0.00012530184531136992</v>
       </c>
       <c r="I3">
-        <v>7.5707544513289762e-05</v>
+        <v>6.5634448482752091e-05</v>
       </c>
       <c r="J3">
-        <v>-5.2432708882674066e-05</v>
+        <v>-2.5852937065833168e-05</v>
       </c>
       <c r="K3">
-        <v>4.5115871436520117e-05</v>
+        <v>5.6815143964197148e-06</v>
       </c>
       <c r="L3">
-        <v>5.5894183560801627e-06</v>
+        <v>7.7808870106821566e-05</v>
       </c>
       <c r="M3">
-        <v>8.8339397258271955e-05</v>
+        <v>2.3600689169367818e-05</v>
       </c>
       <c r="N3">
-        <v>3.6260641992722257e-05</v>
+        <v>5.4331762009441785e-05</v>
       </c>
       <c r="O3">
-        <v>7.3638442767134157e-05</v>
+        <v>-9.1506885663547154e-05</v>
       </c>
       <c r="P3">
-        <v>-9.4467209312991624e-05</v>
+        <v>-7.981290981518268e-05</v>
       </c>
       <c r="Q3">
-        <v>-8.4259634673183089e-05</v>
+        <v>-0.00014872351794657432</v>
       </c>
       <c r="R3">
-        <v>-0.0001534083384292492</v>
+        <v>-9.4522262570792027e-05</v>
       </c>
       <c r="S3">
-        <v>-9.6273463748948332e-05</v>
+        <v>-9.9054917092345645e-05</v>
       </c>
       <c r="T3">
-        <v>-0.00010269571052179063</v>
+        <v>-8.3885481310229805e-05</v>
       </c>
       <c r="U3">
-        <v>-8.7694124992735865e-05</v>
+        <v>7.5202704928168751e-07</v>
       </c>
       <c r="V3">
-        <v>2.1588259854252818e-06</v>
+        <v>0.00013649220948483475</v>
       </c>
       <c r="W3">
-        <v>-3.6527149167597014e-08</v>
+        <v>-5.0547253262777682e-06</v>
       </c>
       <c r="X3">
-        <v>0.00014318931613301316</v>
-      </c>
-      <c r="Y3">
-        <v>-0.0011462157289324768</v>
+        <v>-0.0011345328519525664</v>
       </c>
     </row>
     <row r="4">
@@ -2509,76 +2491,73 @@
         <v>55</v>
       </c>
       <c r="B4">
-        <v>0.0025357016355371104</v>
+        <v>0.0025651193940754331</v>
       </c>
       <c r="C4">
-        <v>-1.401745090157859e-07</v>
+        <v>-1.3064620533752677e-07</v>
       </c>
       <c r="D4">
-        <v>-6.7919828341109835e-07</v>
+        <v>-6.778457594025871e-07</v>
       </c>
       <c r="E4">
-        <v>7.6406709953534946e-09</v>
+        <v>7.5643136133459055e-09</v>
       </c>
       <c r="F4">
-        <v>1.6207731948509151e-06</v>
+        <v>1.6019173016753625e-06</v>
       </c>
       <c r="G4">
-        <v>7.1009551664734623e-07</v>
+        <v>7.1794860731352265e-07</v>
       </c>
       <c r="H4">
-        <v>-1.3886701539828775e-06</v>
+        <v>-1.3701376468002774e-06</v>
       </c>
       <c r="I4">
-        <v>-9.5922416645605086e-07</v>
+        <v>-8.7410745276182499e-07</v>
       </c>
       <c r="J4">
-        <v>6.8302643421499648e-07</v>
+        <v>4.3759171861429675e-07</v>
       </c>
       <c r="K4">
-        <v>-4.3777024707720391e-07</v>
+        <v>-1.0746646030948579e-07</v>
       </c>
       <c r="L4">
-        <v>-1.1630476870012958e-07</v>
+        <v>-9.8559503557207274e-07</v>
       </c>
       <c r="M4">
-        <v>-1.0716737691840824e-06</v>
+        <v>-3.6016174007484137e-07</v>
       </c>
       <c r="N4">
-        <v>-4.614025020600736e-07</v>
+        <v>-8.2476281307687229e-07</v>
       </c>
       <c r="O4">
-        <v>-1.0040026530557901e-06</v>
+        <v>1.0633376342336799e-06</v>
       </c>
       <c r="P4">
-        <v>1.0889955995314589e-06</v>
+        <v>9.8326912203852812e-07</v>
       </c>
       <c r="Q4">
-        <v>1.0186033031790421e-06</v>
+        <v>1.7113118790426884e-06</v>
       </c>
       <c r="R4">
-        <v>1.7586514952034964e-06</v>
+        <v>1.1294189529173196e-06</v>
       </c>
       <c r="S4">
-        <v>1.1423584650951928e-06</v>
+        <v>1.1732345985135603e-06</v>
       </c>
       <c r="T4">
-        <v>1.2044401160805025e-06</v>
+        <v>1.0223614038889259e-06</v>
       </c>
       <c r="U4">
-        <v>1.0586655867577116e-06</v>
+        <v>-8.4777212930309144e-09</v>
       </c>
       <c r="V4">
-        <v>-2.076352929334024e-08</v>
+        <v>-1.4995439368411866e-06</v>
       </c>
       <c r="W4">
-        <v>2.6096527946280807e-10</v>
+        <v>3.1812329163913154e-09</v>
       </c>
       <c r="X4">
-        <v>-1.553139525100811e-06</v>
-      </c>
-      <c r="Y4">
-        <v>1.2330475292843683e-05</v>
+        <v>1.2160635972344815e-05</v>
       </c>
     </row>
     <row r="5">
@@ -2586,76 +2565,73 @@
         <v>56</v>
       </c>
       <c r="B5">
-        <v>-0.73250707416732597</v>
+        <v>-0.8429623141535505</v>
       </c>
       <c r="C5">
-        <v>4.7898491892627563e-05</v>
+        <v>6.1521208753834459e-05</v>
       </c>
       <c r="D5">
-        <v>-0.00014851875007472636</v>
+        <v>-0.00014297425702937405</v>
       </c>
       <c r="E5">
-        <v>1.6207731948509151e-06</v>
+        <v>1.6019173016753625e-06</v>
       </c>
       <c r="F5">
-        <v>0.0030362600533719183</v>
+        <v>0.0031633790622092686</v>
       </c>
       <c r="G5">
-        <v>6.179614481721012e-05</v>
+        <v>5.7240234919485843e-05</v>
       </c>
       <c r="H5">
-        <v>2.2166240914944465e-05</v>
+        <v>0.00010818109021677519</v>
       </c>
       <c r="I5">
-        <v>-0.00046359002183755417</v>
+        <v>-0.00031533583358902238</v>
       </c>
       <c r="J5">
-        <v>-0.00055639725060458074</v>
+        <v>-0.00091752691421883345</v>
       </c>
       <c r="K5">
-        <v>-0.00091510875205691705</v>
+        <v>8.293361062148629e-05</v>
       </c>
       <c r="L5">
-        <v>8.6356717252268359e-05</v>
+        <v>-0.00060934318306670886</v>
       </c>
       <c r="M5">
-        <v>-0.00076715276307682406</v>
+        <v>-0.00038016221606359624</v>
       </c>
       <c r="N5">
-        <v>-0.00057828191856048824</v>
+        <v>-0.00012187286941909301</v>
       </c>
       <c r="O5">
-        <v>-0.00039592467716675147</v>
+        <v>0.00033803621963605229</v>
       </c>
       <c r="P5">
-        <v>0.00038918850312243212</v>
+        <v>0.0002719930433817022</v>
       </c>
       <c r="Q5">
-        <v>0.00037730115177640874</v>
+        <v>0.00033106935769794908</v>
       </c>
       <c r="R5">
-        <v>0.00037182164260355169</v>
+        <v>0.00022582791828269387</v>
       </c>
       <c r="S5">
-        <v>0.00027991125727617246</v>
+        <v>0.00011801533174869087</v>
       </c>
       <c r="T5">
-        <v>0.00019965189751300469</v>
+        <v>0.00022810414041111613</v>
       </c>
       <c r="U5">
-        <v>0.00028409978934083077</v>
+        <v>2.0459051801049969e-05</v>
       </c>
       <c r="V5">
-        <v>0.00010188428781165038</v>
+        <v>-0.00027644164177490567</v>
       </c>
       <c r="W5">
-        <v>-2.4806172044277065e-06</v>
+        <v>-0.00013432855475457601</v>
       </c>
       <c r="X5">
-        <v>-0.00033826202136013359</v>
-      </c>
-      <c r="Y5">
-        <v>0.0018597307786262195</v>
+        <v>0.0022417792098019958</v>
       </c>
     </row>
     <row r="6">
@@ -2663,76 +2639,73 @@
         <v>57</v>
       </c>
       <c r="B6">
-        <v>-0.00020654906223617522</v>
+        <v>-0.0057787576936733989</v>
       </c>
       <c r="C6">
-        <v>-6.2665817317111367e-05</v>
+        <v>-6.3813940677653644e-05</v>
       </c>
       <c r="D6">
-        <v>-6.4594788351051986e-05</v>
+        <v>-6.6058436388056465e-05</v>
       </c>
       <c r="E6">
-        <v>7.1009551664734623e-07</v>
+        <v>7.1794860731352265e-07</v>
       </c>
       <c r="F6">
-        <v>6.179614481721012e-05</v>
+        <v>5.7240234919485843e-05</v>
       </c>
       <c r="G6">
-        <v>0.0016770775061145697</v>
+        <v>0.0016943233419582564</v>
       </c>
       <c r="H6">
-        <v>0.00065890715562034324</v>
+        <v>0.00066977887716762629</v>
       </c>
       <c r="I6">
-        <v>-6.0481085084913866e-05</v>
+        <v>-5.5687918629306125e-05</v>
       </c>
       <c r="J6">
-        <v>-3.2970900957301011e-05</v>
+        <v>-5.752108105342029e-05</v>
       </c>
       <c r="K6">
-        <v>5.2755928004254773e-05</v>
+        <v>-0.00010808809285006185</v>
       </c>
       <c r="L6">
-        <v>-9.699410517809151e-05</v>
+        <v>-5.6462045598308159e-05</v>
       </c>
       <c r="M6">
-        <v>-6.4747722016447154e-05</v>
+        <v>9.5595119520046389e-05</v>
       </c>
       <c r="N6">
-        <v>9.2795118525209133e-05</v>
+        <v>-0.0002902814960097272</v>
       </c>
       <c r="O6">
-        <v>-0.00029295529434542853</v>
+        <v>-3.233330550941226e-05</v>
       </c>
       <c r="P6">
-        <v>-1.878125672484369e-05</v>
+        <v>-0.00015333856084332988</v>
       </c>
       <c r="Q6">
-        <v>-0.00013856462330770573</v>
+        <v>0.00019725082795417023</v>
       </c>
       <c r="R6">
-        <v>0.00021377016904325558</v>
+        <v>1.7390659400292393e-05</v>
       </c>
       <c r="S6">
-        <v>2.4593469304240814e-05</v>
+        <v>8.7714028910309213e-05</v>
       </c>
       <c r="T6">
-        <v>0.00010310362064095571</v>
+        <v>-9.6561788926988624e-06</v>
       </c>
       <c r="U6">
-        <v>-2.7361004778752966e-07</v>
+        <v>6.8518628871108378e-06</v>
       </c>
       <c r="V6">
-        <v>7.0075343305214235e-05</v>
+        <v>-0.00033019620567532307</v>
       </c>
       <c r="W6">
-        <v>-1.9475581026191977e-06</v>
+        <v>-0.00021823713896273526</v>
       </c>
       <c r="X6">
-        <v>-0.00031986747097120869</v>
-      </c>
-      <c r="Y6">
-        <v>-8.5958005699835263e-05</v>
+        <v>0.00044527321146397973</v>
       </c>
     </row>
     <row r="7">
@@ -2740,76 +2713,73 @@
         <v>58</v>
       </c>
       <c r="B7">
-        <v>-0.47965387673722154</v>
+        <v>-0.47476786743986949</v>
       </c>
       <c r="C7">
-        <v>-2.8272501896750454e-05</v>
+        <v>-3.4384581939129577e-05</v>
       </c>
       <c r="D7">
-        <v>0.00012766222915591274</v>
+        <v>0.00012530184531136992</v>
       </c>
       <c r="E7">
-        <v>-1.3886701539828775e-06</v>
+        <v>-1.3701376468002774e-06</v>
       </c>
       <c r="F7">
-        <v>2.2166240914944465e-05</v>
+        <v>0.00010818109021677519</v>
       </c>
       <c r="G7">
-        <v>0.00065890715562034324</v>
+        <v>0.00066977887716762629</v>
       </c>
       <c r="H7">
-        <v>0.0018271581295787862</v>
+        <v>0.00181299809498742</v>
       </c>
       <c r="I7">
-        <v>-0.00026456376505132827</v>
+        <v>-0.00026162236527246655</v>
       </c>
       <c r="J7">
-        <v>-0.00042522202352942705</v>
+        <v>-0.00041735847187467827</v>
       </c>
       <c r="K7">
-        <v>0.00024471381668401493</v>
+        <v>4.305720949670425e-05</v>
       </c>
       <c r="L7">
-        <v>5.7520290748594503e-05</v>
+        <v>0.00018963489964538875</v>
       </c>
       <c r="M7">
-        <v>0.00019991471964613921</v>
+        <v>0.00011965890061636016</v>
       </c>
       <c r="N7">
-        <v>0.00011996605467738653</v>
+        <v>1.3486121366241329e-06</v>
       </c>
       <c r="O7">
-        <v>4.3935556218021449e-06</v>
+        <v>-0.00059723368872112307</v>
       </c>
       <c r="P7">
-        <v>-0.00060393342880913216</v>
+        <v>-0.00062672655019994266</v>
       </c>
       <c r="Q7">
-        <v>-0.00063608904394316926</v>
+        <v>-0.00068159554447576461</v>
       </c>
       <c r="R7">
-        <v>-0.00068492230749241123</v>
+        <v>-0.00076840491580497188</v>
       </c>
       <c r="S7">
-        <v>-0.00076683805291578497</v>
+        <v>-0.00075609783866176184</v>
       </c>
       <c r="T7">
-        <v>-0.00076198019743176819</v>
+        <v>-0.00088185503902758603</v>
       </c>
       <c r="U7">
-        <v>-0.00090537719573867469</v>
+        <v>1.7053546738623702e-05</v>
       </c>
       <c r="V7">
-        <v>-1.1840614098766571e-05</v>
+        <v>0.00072219725086755595</v>
       </c>
       <c r="W7">
-        <v>8.231670790197127e-07</v>
+        <v>-5.580709770888607e-05</v>
       </c>
       <c r="X7">
-        <v>0.00076866577025371593</v>
-      </c>
-      <c r="Y7">
-        <v>-0.002393620323857786</v>
+        <v>-0.0025789095078409237</v>
       </c>
     </row>
     <row r="8">
@@ -2817,76 +2787,73 @@
         <v>59</v>
       </c>
       <c r="B8">
-        <v>0.92193513989901754</v>
+        <v>0.93750421186777755</v>
       </c>
       <c r="C8">
-        <v>-9.3251104221907938e-05</v>
+        <v>-0.00011305708020917964</v>
       </c>
       <c r="D8">
-        <v>7.5707544513289762e-05</v>
+        <v>6.5634448482752091e-05</v>
       </c>
       <c r="E8">
-        <v>-9.5922416645605086e-07</v>
+        <v>-8.7410745276182499e-07</v>
       </c>
       <c r="F8">
-        <v>-0.00046359002183755417</v>
+        <v>-0.00031533583358902238</v>
       </c>
       <c r="G8">
-        <v>-6.0481085084913866e-05</v>
+        <v>-5.5687918629306125e-05</v>
       </c>
       <c r="H8">
-        <v>-0.00026456376505132827</v>
+        <v>-0.00026162236527246655</v>
       </c>
       <c r="I8">
-        <v>0.0029761776884421184</v>
+        <v>0.0030176555271030975</v>
       </c>
       <c r="J8">
-        <v>-0.0011005981332492614</v>
+        <v>-0.0011360907547083307</v>
       </c>
       <c r="K8">
-        <v>0.00054985521688195513</v>
+        <v>-0.00033461964570190967</v>
       </c>
       <c r="L8">
-        <v>-0.00033136477948154453</v>
+        <v>0.0015860052655194872</v>
       </c>
       <c r="M8">
-        <v>0.0016217232868646402</v>
+        <v>0.0022032273785876806</v>
       </c>
       <c r="N8">
-        <v>0.0021595988399374312</v>
+        <v>0.0028372932368571297</v>
       </c>
       <c r="O8">
-        <v>0.0027854310682906927</v>
+        <v>0.00024959660832207971</v>
       </c>
       <c r="P8">
-        <v>0.00026730891549349</v>
+        <v>9.4972354863021372e-05</v>
       </c>
       <c r="Q8">
-        <v>0.00011053670031022393</v>
+        <v>-9.0052503706154123e-05</v>
       </c>
       <c r="R8">
-        <v>-5.9101070147346145e-05</v>
+        <v>0.00028447059687925673</v>
       </c>
       <c r="S8">
-        <v>0.00031775102884600589</v>
+        <v>0.0002845578009622058</v>
       </c>
       <c r="T8">
-        <v>0.0002842391503959658</v>
+        <v>0.0003701180278214099</v>
       </c>
       <c r="U8">
-        <v>0.00036062273277431806</v>
+        <v>-8.5035544809324785e-07</v>
       </c>
       <c r="V8">
-        <v>-8.8788849494841893e-05</v>
+        <v>-0.00037172107304085916</v>
       </c>
       <c r="W8">
-        <v>2.6912062540689982e-06</v>
+        <v>0.00037913961581995852</v>
       </c>
       <c r="X8">
-        <v>-0.00039793735217381291</v>
-      </c>
-      <c r="Y8">
-        <v>-0.0033765804724193091</v>
+        <v>-0.0038732700851372235</v>
       </c>
     </row>
     <row r="9">
@@ -2894,1231 +2861,1109 @@
         <v>60</v>
       </c>
       <c r="B9">
-        <v>0.54435185271379372</v>
+        <v>0.44489558192862527</v>
       </c>
       <c r="C9">
-        <v>0.00030103970649047389</v>
+        <v>0.00034082808829945401</v>
       </c>
       <c r="D9">
-        <v>-5.2432708882674066e-05</v>
+        <v>-2.5852937065833168e-05</v>
       </c>
       <c r="E9">
-        <v>6.8302643421499648e-07</v>
+        <v>4.3759171861429675e-07</v>
       </c>
       <c r="F9">
-        <v>-0.00055639725060458074</v>
+        <v>-0.00091752691421883345</v>
       </c>
       <c r="G9">
-        <v>-3.2970900957301011e-05</v>
+        <v>-5.752108105342029e-05</v>
       </c>
       <c r="H9">
-        <v>-0.00042522202352942705</v>
+        <v>-0.00041735847187467827</v>
       </c>
       <c r="I9">
-        <v>-0.0011005981332492614</v>
+        <v>-0.0011360907547083307</v>
       </c>
       <c r="J9">
-        <v>0.0020327817548398516</v>
+        <v>0.0021071006990368247</v>
       </c>
       <c r="K9">
-        <v>-0.00078473093729380776</v>
+        <v>0.00021467655957055202</v>
       </c>
       <c r="L9">
-        <v>0.00021409305721117929</v>
+        <v>-0.00097343630030568315</v>
       </c>
       <c r="M9">
-        <v>-0.0010100957327043606</v>
+        <v>-0.001267175288682859</v>
       </c>
       <c r="N9">
-        <v>-0.0012569933008860269</v>
+        <v>-0.0016286367406073826</v>
       </c>
       <c r="O9">
-        <v>-0.0015750970317906245</v>
+        <v>0.00029198335029505316</v>
       </c>
       <c r="P9">
-        <v>0.00033158422513532391</v>
+        <v>0.00049525873916396132</v>
       </c>
       <c r="Q9">
-        <v>0.00053359369552858759</v>
+        <v>0.0003179776587181325</v>
       </c>
       <c r="R9">
-        <v>0.00037364489954270911</v>
+        <v>0.00037859260144083499</v>
       </c>
       <c r="S9">
-        <v>0.00038483094944704438</v>
+        <v>0.00038904607666953844</v>
       </c>
       <c r="T9">
-        <v>0.00041644311192637579</v>
+        <v>0.00020380764841475675</v>
       </c>
       <c r="U9">
-        <v>0.00025372480023800351</v>
+        <v>4.3910361324551279e-06</v>
       </c>
       <c r="V9">
-        <v>-0.00016832105619892304</v>
+        <v>-0.00036433122970908391</v>
       </c>
       <c r="W9">
-        <v>4.9035815633145568e-06</v>
+        <v>2.7994241299931422e-05</v>
       </c>
       <c r="X9">
-        <v>-0.00040854721365483963</v>
-      </c>
-      <c r="Y9">
-        <v>0.0027713651713157134</v>
+        <v>0.00084423847422780772</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>61</v>
+        <v>38</v>
       </c>
       <c r="B10">
-        <v>-0.73154584549397561</v>
+        <v>0.20644638256596629</v>
       </c>
       <c r="C10">
-        <v>9.6947005363065466e-05</v>
+        <v>8.8915238200703369e-05</v>
       </c>
       <c r="D10">
-        <v>4.5115871436520117e-05</v>
+        <v>5.6815143964197148e-06</v>
       </c>
       <c r="E10">
-        <v>-4.3777024707720391e-07</v>
+        <v>-1.0746646030948579e-07</v>
       </c>
       <c r="F10">
-        <v>-0.00091510875205691705</v>
+        <v>8.293361062148629e-05</v>
       </c>
       <c r="G10">
-        <v>5.2755928004254773e-05</v>
+        <v>-0.00010808809285006185</v>
       </c>
       <c r="H10">
-        <v>0.00024471381668401493</v>
+        <v>4.305720949670425e-05</v>
       </c>
       <c r="I10">
-        <v>0.00054985521688195513</v>
+        <v>-0.00033461964570190967</v>
       </c>
       <c r="J10">
-        <v>-0.00078473093729380776</v>
+        <v>0.00021467655957055202</v>
       </c>
       <c r="K10">
-        <v>0.007908938803011481</v>
+        <v>0.0023118429144961816</v>
       </c>
       <c r="L10">
-        <v>-5.9621882055222791e-05</v>
+        <v>0.00086642935936201513</v>
       </c>
       <c r="M10">
-        <v>0.00065642954588992759</v>
+        <v>0.00078057163660374376</v>
       </c>
       <c r="N10">
-        <v>0.00082310988417206741</v>
+        <v>0.00084722437440853319</v>
       </c>
       <c r="O10">
-        <v>0.00091196983084443199</v>
+        <v>-0.00029185670829086341</v>
       </c>
       <c r="P10">
-        <v>-0.00017766968487757629</v>
+        <v>-0.00032508693657849188</v>
       </c>
       <c r="Q10">
-        <v>-0.00035781440481182016</v>
+        <v>-0.00015643077917438356</v>
       </c>
       <c r="R10">
-        <v>-0.00015080789714692574</v>
+        <v>-0.00023469951494034676</v>
       </c>
       <c r="S10">
-        <v>4.661275663022746e-05</v>
+        <v>-0.00019163499080495527</v>
       </c>
       <c r="T10">
-        <v>-0.00031975594095281042</v>
+        <v>-0.00017424493903524338</v>
       </c>
       <c r="U10">
-        <v>-0.00024261148215842641</v>
+        <v>1.453275710173959e-05</v>
       </c>
       <c r="V10">
-        <v>-6.1980961358985257e-05</v>
+        <v>-6.1238467038893723e-05</v>
       </c>
       <c r="W10">
-        <v>2.0787268949662982e-06</v>
+        <v>-4.7476312130766835e-05</v>
       </c>
       <c r="X10">
-        <v>0.00021651875307818864</v>
-      </c>
-      <c r="Y10">
-        <v>-0.0010801616550446323</v>
+        <v>-0.0009377342215026094</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B11">
-        <v>0.20470339341355118</v>
+        <v>0.53941899967421436</v>
       </c>
       <c r="C11">
-        <v>8.7501969426333358e-05</v>
+        <v>2.2518691298354271e-05</v>
       </c>
       <c r="D11">
-        <v>5.5894183560801627e-06</v>
+        <v>7.7808870106821566e-05</v>
       </c>
       <c r="E11">
-        <v>-1.1630476870012958e-07</v>
+        <v>-9.8559503557207274e-07</v>
       </c>
       <c r="F11">
-        <v>8.6356717252268359e-05</v>
+        <v>-0.00060934318306670886</v>
       </c>
       <c r="G11">
-        <v>-9.699410517809151e-05</v>
+        <v>-5.6462045598308159e-05</v>
       </c>
       <c r="H11">
-        <v>5.7520290748594503e-05</v>
+        <v>0.00018963489964538875</v>
       </c>
       <c r="I11">
-        <v>-0.00033136477948154453</v>
+        <v>0.0015860052655194872</v>
       </c>
       <c r="J11">
-        <v>0.00021409305721117929</v>
+        <v>-0.00097343630030568315</v>
       </c>
       <c r="K11">
-        <v>-5.9621882055222791e-05</v>
+        <v>0.00086642935936201513</v>
       </c>
       <c r="L11">
-        <v>0.0023314396716454969</v>
+        <v>0.0031098541093288407</v>
       </c>
       <c r="M11">
-        <v>0.00087701668519313898</v>
+        <v>0.0024332699258320175</v>
       </c>
       <c r="N11">
-        <v>0.00079115130447603794</v>
+        <v>0.0028959895500655459</v>
       </c>
       <c r="O11">
-        <v>0.00085820400072814931</v>
+        <v>-0.00065870874727564158</v>
       </c>
       <c r="P11">
-        <v>-0.00028715978742984555</v>
+        <v>-0.00084032296268217194</v>
       </c>
       <c r="Q11">
-        <v>-0.00032287123491371941</v>
+        <v>-0.00080134447282981193</v>
       </c>
       <c r="R11">
-        <v>-0.00014823362481000983</v>
+        <v>-0.00056009537539158027</v>
       </c>
       <c r="S11">
-        <v>-0.00023177558722434612</v>
+        <v>-0.00058770908704499367</v>
       </c>
       <c r="T11">
-        <v>-0.00019470231209771309</v>
+        <v>-0.00035918477392987485</v>
       </c>
       <c r="U11">
-        <v>-0.00017025064309124908</v>
+        <v>-9.9355374871763541e-06</v>
       </c>
       <c r="V11">
-        <v>4.2655189718628236e-05</v>
+        <v>0.00047931725768046946</v>
       </c>
       <c r="W11">
-        <v>-8.3545309797524779e-07</v>
+        <v>0.00017878871810228037</v>
       </c>
       <c r="X11">
-        <v>-5.91656264793806e-05</v>
-      </c>
-      <c r="Y11">
-        <v>-0.0011724076670993505</v>
+        <v>-0.0031997154103937738</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B12">
-        <v>0.52646574087326214</v>
+        <v>0.44037313553150431</v>
       </c>
       <c r="C12">
-        <v>4.4072736987518614e-05</v>
+        <v>-0.00028463225949549085</v>
       </c>
       <c r="D12">
-        <v>8.8339397258271955e-05</v>
+        <v>2.3600689169367818e-05</v>
       </c>
       <c r="E12">
-        <v>-1.0716737691840824e-06</v>
+        <v>-3.6016174007484137e-07</v>
       </c>
       <c r="F12">
-        <v>-0.00076715276307682406</v>
+        <v>-0.00038016221606359624</v>
       </c>
       <c r="G12">
-        <v>-6.4747722016447154e-05</v>
+        <v>9.5595119520046389e-05</v>
       </c>
       <c r="H12">
-        <v>0.00019991471964613921</v>
+        <v>0.00011965890061636016</v>
       </c>
       <c r="I12">
-        <v>0.0016217232868646402</v>
+        <v>0.0022032273785876806</v>
       </c>
       <c r="J12">
-        <v>-0.0010100957327043606</v>
+        <v>-0.001267175288682859</v>
       </c>
       <c r="K12">
-        <v>0.00065642954588992759</v>
+        <v>0.00078057163660374376</v>
       </c>
       <c r="L12">
-        <v>0.00087701668519313898</v>
+        <v>0.0024332699258320175</v>
       </c>
       <c r="M12">
-        <v>0.0031832563790043984</v>
+        <v>0.0039898763579951646</v>
       </c>
       <c r="N12">
-        <v>0.0024747605991170818</v>
+        <v>0.0033631888046579067</v>
       </c>
       <c r="O12">
-        <v>0.0029447905646110542</v>
+        <v>-0.00027149617315768391</v>
       </c>
       <c r="P12">
-        <v>-0.00064925441384789144</v>
+        <v>-0.0005273057718902267</v>
       </c>
       <c r="Q12">
-        <v>-0.00085760771717028087</v>
+        <v>-0.00028772734838074503</v>
       </c>
       <c r="R12">
-        <v>-0.00080061695025426252</v>
+        <v>-0.00020113951451158647</v>
       </c>
       <c r="S12">
-        <v>-0.00054133821832844532</v>
+        <v>-0.00015263942728835855</v>
       </c>
       <c r="T12">
-        <v>-0.00059039673588021254</v>
+        <v>-1.202917384056628e-05</v>
       </c>
       <c r="U12">
-        <v>-0.00038028109305375611</v>
+        <v>8.1396332543183519e-06</v>
       </c>
       <c r="V12">
-        <v>-6.6651350535923241e-06</v>
+        <v>-0.0002246066967197081</v>
       </c>
       <c r="W12">
-        <v>2.4641475995340308e-08</v>
+        <v>0.00011122971900492636</v>
       </c>
       <c r="X12">
-        <v>0.00048124408255867846</v>
-      </c>
-      <c r="Y12">
-        <v>-0.0035261338360540045</v>
+        <v>-0.0033092744992974281</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B13">
-        <v>0.406738950568586</v>
+        <v>0.57537425577030532</v>
       </c>
       <c r="C13">
-        <v>-0.00024798988705884847</v>
+        <v>-8.9750651379478879e-05</v>
       </c>
       <c r="D13">
-        <v>3.6260641992722257e-05</v>
+        <v>5.4331762009441785e-05</v>
       </c>
       <c r="E13">
-        <v>-4.614025020600736e-07</v>
+        <v>-8.2476281307687229e-07</v>
       </c>
       <c r="F13">
-        <v>-0.00057828191856048824</v>
+        <v>-0.00012187286941909301</v>
       </c>
       <c r="G13">
-        <v>9.2795118525209133e-05</v>
+        <v>-0.0002902814960097272</v>
       </c>
       <c r="H13">
-        <v>0.00011996605467738653</v>
+        <v>1.3486121366241329e-06</v>
       </c>
       <c r="I13">
-        <v>0.0021595988399374312</v>
+        <v>0.0028372932368571297</v>
       </c>
       <c r="J13">
-        <v>-0.0012569933008860269</v>
+        <v>-0.0016286367406073826</v>
       </c>
       <c r="K13">
-        <v>0.00082310988417206741</v>
+        <v>0.00084722437440853319</v>
       </c>
       <c r="L13">
-        <v>0.00079115130447603794</v>
+        <v>0.0028959895500655459</v>
       </c>
       <c r="M13">
-        <v>0.0024747605991170818</v>
+        <v>0.0033631888046579067</v>
       </c>
       <c r="N13">
-        <v>0.0039722101808654774</v>
+        <v>0.005664106867557272</v>
       </c>
       <c r="O13">
-        <v>0.0033271608995573249</v>
+        <v>-0.00035623509574636081</v>
       </c>
       <c r="P13">
-        <v>-0.00025406301875142414</v>
+        <v>-0.00073096015111432386</v>
       </c>
       <c r="Q13">
-        <v>-0.00052685941179111441</v>
+        <v>-0.0007576090463308271</v>
       </c>
       <c r="R13">
-        <v>-0.00026585666922590513</v>
+        <v>-0.00023895471369643788</v>
       </c>
       <c r="S13">
-        <v>-0.00016816901312838003</v>
+        <v>-0.00031958515481583663</v>
       </c>
       <c r="T13">
-        <v>-0.00015610367056595605</v>
+        <v>0.00011544528608480552</v>
       </c>
       <c r="U13">
-        <v>-2.7276161831403436e-05</v>
+        <v>6.2240642530676424e-06</v>
       </c>
       <c r="V13">
-        <v>5.0862450693369169e-05</v>
+        <v>-0.00023805746492108119</v>
       </c>
       <c r="W13">
-        <v>-1.1738295259111609e-06</v>
+        <v>0.00038347599303256751</v>
       </c>
       <c r="X13">
-        <v>-0.00021953717562188271</v>
-      </c>
-      <c r="Y13">
-        <v>-0.0039333849864819862</v>
+        <v>-0.0042414041325411619</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B14">
-        <v>0.53198698623233343</v>
+        <v>0.033285856404519601</v>
       </c>
       <c r="C14">
-        <v>-4.3354700673628335e-05</v>
+        <v>-0.00013847242554323102</v>
       </c>
       <c r="D14">
-        <v>7.3638442767134157e-05</v>
+        <v>-9.1506885663547154e-05</v>
       </c>
       <c r="E14">
-        <v>-1.0040026530557901e-06</v>
+        <v>1.0633376342336799e-06</v>
       </c>
       <c r="F14">
-        <v>-0.00039592467716675147</v>
+        <v>0.00033803621963605229</v>
       </c>
       <c r="G14">
-        <v>-0.00029295529434542853</v>
+        <v>-3.233330550941226e-05</v>
       </c>
       <c r="H14">
-        <v>4.3935556218021449e-06</v>
+        <v>-0.00059723368872112307</v>
       </c>
       <c r="I14">
-        <v>0.0027854310682906927</v>
+        <v>0.00024959660832207971</v>
       </c>
       <c r="J14">
-        <v>-0.0015750970317906245</v>
+        <v>0.00029198335029505316</v>
       </c>
       <c r="K14">
-        <v>0.00091196983084443199</v>
+        <v>-0.00029185670829086341</v>
       </c>
       <c r="L14">
-        <v>0.00085820400072814931</v>
+        <v>-0.00065870874727564158</v>
       </c>
       <c r="M14">
-        <v>0.0029447905646110542</v>
+        <v>-0.00027149617315768391</v>
       </c>
       <c r="N14">
-        <v>0.0033271608995573249</v>
+        <v>-0.00035623509574636081</v>
       </c>
       <c r="O14">
-        <v>0.0056509231037101017</v>
+        <v>0.0073552671818671771</v>
       </c>
       <c r="P14">
-        <v>-0.00035302660894007826</v>
+        <v>0.0057566436128687164</v>
       </c>
       <c r="Q14">
-        <v>-0.00073438305179225356</v>
+        <v>0.0057718667346482074</v>
       </c>
       <c r="R14">
-        <v>-0.00074003723726554611</v>
+        <v>0.0057541536294530189</v>
       </c>
       <c r="S14">
-        <v>-0.00020633668030225864</v>
+        <v>0.0057560776808683357</v>
       </c>
       <c r="T14">
-        <v>-0.00032878351087132363</v>
+        <v>0.0057331526139639778</v>
       </c>
       <c r="U14">
-        <v>8.6865241380593237e-05</v>
+        <v>4.3742425236167177e-07</v>
       </c>
       <c r="V14">
-        <v>3.8734005588616279e-06</v>
+        <v>-0.0026664312010428294</v>
       </c>
       <c r="W14">
-        <v>2.4589038982603269e-07</v>
+        <v>4.3547638806642683e-05</v>
       </c>
       <c r="X14">
-        <v>-0.0002608154928714024</v>
-      </c>
-      <c r="Y14">
-        <v>-0.0046300048146747288</v>
+        <v>-0.0036648491749037078</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B15">
-        <v>0.029673468107554116</v>
+        <v>0.017177556497424237</v>
       </c>
       <c r="C15">
-        <v>-0.00014200963026318346</v>
+        <v>-0.00011221579967702337</v>
       </c>
       <c r="D15">
-        <v>-9.4467209312991624e-05</v>
+        <v>-7.981290981518268e-05</v>
       </c>
       <c r="E15">
-        <v>1.0889955995314589e-06</v>
+        <v>9.8326912203852812e-07</v>
       </c>
       <c r="F15">
-        <v>0.00038918850312243212</v>
+        <v>0.0002719930433817022</v>
       </c>
       <c r="G15">
-        <v>-1.878125672484369e-05</v>
+        <v>-0.00015333856084332988</v>
       </c>
       <c r="H15">
-        <v>-0.00060393342880913216</v>
+        <v>-0.00062672655019994266</v>
       </c>
       <c r="I15">
-        <v>0.00026730891549349</v>
+        <v>9.4972354863021372e-05</v>
       </c>
       <c r="J15">
-        <v>0.00033158422513532391</v>
+        <v>0.00049525873916396132</v>
       </c>
       <c r="K15">
-        <v>-0.00017766968487757629</v>
+        <v>-0.00032508693657849188</v>
       </c>
       <c r="L15">
-        <v>-0.00028715978742984555</v>
+        <v>-0.00084032296268217194</v>
       </c>
       <c r="M15">
-        <v>-0.00064925441384789144</v>
+        <v>-0.0005273057718902267</v>
       </c>
       <c r="N15">
-        <v>-0.00025406301875142414</v>
+        <v>-0.00073096015111432386</v>
       </c>
       <c r="O15">
-        <v>-0.00035302660894007826</v>
+        <v>0.0057566436128687164</v>
       </c>
       <c r="P15">
-        <v>0.0073641589396843867</v>
+        <v>0.0074014646283387595</v>
       </c>
       <c r="Q15">
-        <v>0.0057519985316032514</v>
+        <v>0.0057848357929516309</v>
       </c>
       <c r="R15">
-        <v>0.0057621164954803133</v>
+        <v>0.005768353693555146</v>
       </c>
       <c r="S15">
-        <v>0.005748046337560429</v>
+        <v>0.0057641655154606671</v>
       </c>
       <c r="T15">
-        <v>0.0057475600183019603</v>
+        <v>0.0057171600518556142</v>
       </c>
       <c r="U15">
-        <v>0.0057302867719408587</v>
+        <v>-5.5314161728314652e-08</v>
       </c>
       <c r="V15">
-        <v>-0.00012686056970893185</v>
+        <v>-0.0026377364984271805</v>
       </c>
       <c r="W15">
-        <v>3.6525038280720818e-06</v>
+        <v>8.0817208774079143e-05</v>
       </c>
       <c r="X15">
-        <v>-0.0027039905890799999</v>
-      </c>
-      <c r="Y15">
-        <v>-0.0025691016129792583</v>
+        <v>-0.0036737343105442094</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B16">
-        <v>0.022493894579605201</v>
+        <v>0.063152380159758201</v>
       </c>
       <c r="C16">
-        <v>-0.00012522312480704311</v>
+        <v>-0.00029295302450764812</v>
       </c>
       <c r="D16">
-        <v>-8.4259634673183089e-05</v>
+        <v>-0.00014872351794657432</v>
       </c>
       <c r="E16">
-        <v>1.0186033031790421e-06</v>
+        <v>1.7113118790426884e-06</v>
       </c>
       <c r="F16">
-        <v>0.00037730115177640874</v>
+        <v>0.00033106935769794908</v>
       </c>
       <c r="G16">
-        <v>-0.00013856462330770573</v>
+        <v>0.00019725082795417023</v>
       </c>
       <c r="H16">
-        <v>-0.00063608904394316926</v>
+        <v>-0.00068159554447576461</v>
       </c>
       <c r="I16">
-        <v>0.00011053670031022393</v>
+        <v>-9.0052503706154123e-05</v>
       </c>
       <c r="J16">
-        <v>0.00053359369552858759</v>
+        <v>0.0003179776587181325</v>
       </c>
       <c r="K16">
-        <v>-0.00035781440481182016</v>
+        <v>-0.00015643077917438356</v>
       </c>
       <c r="L16">
-        <v>-0.00032287123491371941</v>
+        <v>-0.00080134447282981193</v>
       </c>
       <c r="M16">
-        <v>-0.00085760771717028087</v>
+        <v>-0.00028772734838074503</v>
       </c>
       <c r="N16">
-        <v>-0.00052685941179111441</v>
+        <v>-0.0007576090463308271</v>
       </c>
       <c r="O16">
-        <v>-0.00073438305179225356</v>
+        <v>0.0057718667346482074</v>
       </c>
       <c r="P16">
-        <v>0.0057519985316032514</v>
+        <v>0.0057848357929516309</v>
       </c>
       <c r="Q16">
-        <v>0.007423145140247737</v>
+        <v>0.0076134513863191228</v>
       </c>
       <c r="R16">
-        <v>0.0057820749256751163</v>
+        <v>0.0057871303408496564</v>
       </c>
       <c r="S16">
-        <v>0.005768196364043186</v>
+        <v>0.0057484446472102864</v>
       </c>
       <c r="T16">
-        <v>0.0057659160653479044</v>
+        <v>0.0057692718753511842</v>
       </c>
       <c r="U16">
-        <v>0.0057233691572018191</v>
+        <v>4.5736760741217603e-06</v>
       </c>
       <c r="V16">
-        <v>-6.9610037324200052e-05</v>
+        <v>-0.0028176159796168675</v>
       </c>
       <c r="W16">
-        <v>2.0305276606834906e-06</v>
+        <v>-0.00020145030779158881</v>
       </c>
       <c r="X16">
-        <v>-0.0027022685811751478</v>
-      </c>
-      <c r="Y16">
-        <v>-0.0030203754859823798</v>
+        <v>-0.0024157867628509886</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B17">
-        <v>0.067238956412377759</v>
+        <v>-0.11173185004290141</v>
       </c>
       <c r="C17">
-        <v>-0.00030147975062645856</v>
+        <v>-9.9370182917451902e-05</v>
       </c>
       <c r="D17">
-        <v>-0.0001534083384292492</v>
+        <v>-9.4522262570792027e-05</v>
       </c>
       <c r="E17">
-        <v>1.7586514952034964e-06</v>
+        <v>1.1294189529173196e-06</v>
       </c>
       <c r="F17">
-        <v>0.00037182164260355169</v>
+        <v>0.00022582791828269387</v>
       </c>
       <c r="G17">
-        <v>0.00021377016904325558</v>
+        <v>1.7390659400292393e-05</v>
       </c>
       <c r="H17">
-        <v>-0.00068492230749241123</v>
+        <v>-0.00076840491580497188</v>
       </c>
       <c r="I17">
-        <v>-5.9101070147346145e-05</v>
+        <v>0.00028447059687925673</v>
       </c>
       <c r="J17">
-        <v>0.00037364489954270911</v>
+        <v>0.00037859260144083499</v>
       </c>
       <c r="K17">
-        <v>-0.00015080789714692574</v>
+        <v>-0.00023469951494034676</v>
       </c>
       <c r="L17">
-        <v>-0.00014823362481000983</v>
+        <v>-0.00056009537539158027</v>
       </c>
       <c r="M17">
-        <v>-0.00080061695025426252</v>
+        <v>-0.00020113951451158647</v>
       </c>
       <c r="N17">
-        <v>-0.00026585666922590513</v>
+        <v>-0.00023895471369643788</v>
       </c>
       <c r="O17">
-        <v>-0.00074003723726554611</v>
+        <v>0.0057541536294530189</v>
       </c>
       <c r="P17">
-        <v>0.0057621164954803133</v>
+        <v>0.005768353693555146</v>
       </c>
       <c r="Q17">
-        <v>0.0057820749256751163</v>
+        <v>0.0057871303408496564</v>
       </c>
       <c r="R17">
-        <v>0.007620725193648036</v>
+        <v>0.0070466363198167115</v>
       </c>
       <c r="S17">
-        <v>0.0057831518425601452</v>
+        <v>0.0057996176813646157</v>
       </c>
       <c r="T17">
-        <v>0.0057444467854675507</v>
+        <v>0.0058185640541186931</v>
       </c>
       <c r="U17">
-        <v>0.0057739817528537282</v>
+        <v>-6.3104088685286868e-06</v>
       </c>
       <c r="V17">
-        <v>-0.00021946842601090538</v>
+        <v>-0.0027234798389865695</v>
       </c>
       <c r="W17">
-        <v>6.3135464531531322e-06</v>
+        <v>8.8480518575858626e-05</v>
       </c>
       <c r="X17">
-        <v>-0.002819930306646813</v>
-      </c>
-      <c r="Y17">
-        <v>-0.00048798749397827024</v>
+        <v>-0.003623998948298306</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B18">
-        <v>-0.11198854882235947</v>
+        <v>-0.028060130339037249</v>
       </c>
       <c r="C18">
-        <v>-0.00010618077141089381</v>
+        <v>-0.00022817471093144933</v>
       </c>
       <c r="D18">
-        <v>-9.6273463748948332e-05</v>
+        <v>-9.9054917092345645e-05</v>
       </c>
       <c r="E18">
-        <v>1.1423584650951928e-06</v>
+        <v>1.1732345985135603e-06</v>
       </c>
       <c r="F18">
-        <v>0.00027991125727617246</v>
+        <v>0.00011801533174869087</v>
       </c>
       <c r="G18">
-        <v>2.4593469304240814e-05</v>
+        <v>8.7714028910309213e-05</v>
       </c>
       <c r="H18">
-        <v>-0.00076683805291578497</v>
+        <v>-0.00075609783866176184</v>
       </c>
       <c r="I18">
-        <v>0.00031775102884600589</v>
+        <v>0.0002845578009622058</v>
       </c>
       <c r="J18">
-        <v>0.00038483094944704438</v>
+        <v>0.00038904607666953844</v>
       </c>
       <c r="K18">
-        <v>4.661275663022746e-05</v>
+        <v>-0.00019163499080495527</v>
       </c>
       <c r="L18">
-        <v>-0.00023177558722434612</v>
+        <v>-0.00058770908704499367</v>
       </c>
       <c r="M18">
-        <v>-0.00054133821832844532</v>
+        <v>-0.00015263942728835855</v>
       </c>
       <c r="N18">
-        <v>-0.00016816901312838003</v>
+        <v>-0.00031958515481583663</v>
       </c>
       <c r="O18">
-        <v>-0.00020633668030225864</v>
+        <v>0.0057560776808683357</v>
       </c>
       <c r="P18">
-        <v>0.005748046337560429</v>
+        <v>0.0057641655154606671</v>
       </c>
       <c r="Q18">
-        <v>0.005768196364043186</v>
+        <v>0.0057484446472102864</v>
       </c>
       <c r="R18">
-        <v>0.0057831518425601452</v>
+        <v>0.0057996176813646157</v>
       </c>
       <c r="S18">
-        <v>0.0070774015499866956</v>
+        <v>0.0067756277049650466</v>
       </c>
       <c r="T18">
-        <v>0.0057926916540816144</v>
+        <v>0.0057935992253189969</v>
       </c>
       <c r="U18">
-        <v>0.0058188896979016157</v>
+        <v>7.9648020267373345e-06</v>
       </c>
       <c r="V18">
-        <v>-0.00016950048967623549</v>
+        <v>-0.0028540982183731392</v>
       </c>
       <c r="W18">
-        <v>4.7219325105643222e-06</v>
+        <v>-0.0001234594939325262</v>
       </c>
       <c r="X18">
-        <v>-0.0027740657972945885</v>
-      </c>
-      <c r="Y18">
-        <v>-0.0022863386262962412</v>
+        <v>-0.0037044019217954867</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B19">
-        <v>-0.023262007702806398</v>
+        <v>-0.099116672791960486</v>
       </c>
       <c r="C19">
-        <v>-0.00023626449790101856</v>
+        <v>-0.00010821631387866433</v>
       </c>
       <c r="D19">
-        <v>-0.00010269571052179063</v>
+        <v>-8.3885481310229805e-05</v>
       </c>
       <c r="E19">
-        <v>1.2044401160805025e-06</v>
+        <v>1.0223614038889259e-06</v>
       </c>
       <c r="F19">
-        <v>0.00019965189751300469</v>
+        <v>0.00022810414041111613</v>
       </c>
       <c r="G19">
-        <v>0.00010310362064095571</v>
+        <v>-9.6561788926988624e-06</v>
       </c>
       <c r="H19">
-        <v>-0.00076198019743176819</v>
+        <v>-0.00088185503902758603</v>
       </c>
       <c r="I19">
-        <v>0.0002842391503959658</v>
+        <v>0.0003701180278214099</v>
       </c>
       <c r="J19">
-        <v>0.00041644311192637579</v>
+        <v>0.00020380764841475675</v>
       </c>
       <c r="K19">
-        <v>-0.00031975594095281042</v>
+        <v>-0.00017424493903524338</v>
       </c>
       <c r="L19">
-        <v>-0.00019470231209771309</v>
+        <v>-0.00035918477392987485</v>
       </c>
       <c r="M19">
-        <v>-0.00059039673588021254</v>
+        <v>-1.202917384056628e-05</v>
       </c>
       <c r="N19">
-        <v>-0.00015610367056595605</v>
+        <v>0.00011544528608480552</v>
       </c>
       <c r="O19">
-        <v>-0.00032878351087132363</v>
+        <v>0.0057331526139639778</v>
       </c>
       <c r="P19">
-        <v>0.0057475600183019603</v>
+        <v>0.0057171600518556142</v>
       </c>
       <c r="Q19">
-        <v>0.0057659160653479044</v>
+        <v>0.0057692718753511842</v>
       </c>
       <c r="R19">
-        <v>0.0057444467854675507</v>
+        <v>0.0058185640541186931</v>
       </c>
       <c r="S19">
-        <v>0.0057926916540816144</v>
+        <v>0.0057935992253189969</v>
       </c>
       <c r="T19">
-        <v>0.0067775132420447226</v>
+        <v>0.0069149117910419682</v>
       </c>
       <c r="U19">
-        <v>0.0057960764175303443</v>
+        <v>-4.1628717525110849e-06</v>
       </c>
       <c r="V19">
-        <v>7.5043096419072711e-05</v>
+        <v>-0.0026258835697140297</v>
       </c>
       <c r="W19">
-        <v>-1.9926144851385984e-06</v>
+        <v>-6.6630248629776304e-05</v>
       </c>
       <c r="X19">
-        <v>-0.0029016296484143103</v>
-      </c>
-      <c r="Y19">
-        <v>-0.0041605238901346753</v>
+        <v>-0.0039541082576806195</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B20">
-        <v>-0.095288721702322735</v>
+        <v>0.0059025714645199994</v>
       </c>
       <c r="C20">
-        <v>-0.0001067016134874232</v>
+        <v>-6.9321024940633276e-06</v>
       </c>
       <c r="D20">
-        <v>-8.7694124992735865e-05</v>
+        <v>7.5202704928168751e-07</v>
       </c>
       <c r="E20">
-        <v>1.0586655867577116e-06</v>
+        <v>-8.4777212930309144e-09</v>
       </c>
       <c r="F20">
-        <v>0.00028409978934083077</v>
+        <v>2.0459051801049969e-05</v>
       </c>
       <c r="G20">
-        <v>-2.7361004778752966e-07</v>
+        <v>6.8518628871108378e-06</v>
       </c>
       <c r="H20">
-        <v>-0.00090537719573867469</v>
+        <v>1.7053546738623702e-05</v>
       </c>
       <c r="I20">
-        <v>0.00036062273277431806</v>
+        <v>-8.5035544809324785e-07</v>
       </c>
       <c r="J20">
-        <v>0.00025372480023800351</v>
+        <v>4.3910361324551279e-06</v>
       </c>
       <c r="K20">
-        <v>-0.00024261148215842641</v>
+        <v>1.453275710173959e-05</v>
       </c>
       <c r="L20">
-        <v>-0.00017025064309124908</v>
+        <v>-9.9355374871763541e-06</v>
       </c>
       <c r="M20">
-        <v>-0.00038028109305375611</v>
+        <v>8.1396332543183519e-06</v>
       </c>
       <c r="N20">
-        <v>-2.7276161831403436e-05</v>
+        <v>6.2240642530676424e-06</v>
       </c>
       <c r="O20">
-        <v>8.6865241380593237e-05</v>
+        <v>4.3742425236167177e-07</v>
       </c>
       <c r="P20">
-        <v>0.0057302867719408587</v>
+        <v>-5.5314161728314652e-08</v>
       </c>
       <c r="Q20">
-        <v>0.0057233691572018191</v>
+        <v>4.5736760741217603e-06</v>
       </c>
       <c r="R20">
-        <v>0.0057739817528537282</v>
+        <v>-6.3104088685286868e-06</v>
       </c>
       <c r="S20">
-        <v>0.0058188896979016157</v>
+        <v>7.9648020267373345e-06</v>
       </c>
       <c r="T20">
-        <v>0.0057960764175303443</v>
+        <v>-4.1628717525110849e-06</v>
       </c>
       <c r="U20">
-        <v>0.0069248228286763426</v>
+        <v>1.4955456692080656e-05</v>
       </c>
       <c r="V20">
-        <v>1.7860126342024267e-05</v>
+        <v>-6.7605363243405136e-05</v>
       </c>
       <c r="W20">
-        <v>-6.9935552874593709e-07</v>
+        <v>-8.0751454120666689e-05</v>
       </c>
       <c r="X20">
-        <v>-0.0026685125248852716</v>
-      </c>
-      <c r="Y20">
-        <v>-0.0040303551283810309</v>
+        <v>-0.00027202396336519093</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B21">
-        <v>-0.025573590578274321</v>
+        <v>0.15841378114189855</v>
       </c>
       <c r="C21">
-        <v>-1.8578409950131022e-05</v>
+        <v>0.00040157041528798257</v>
       </c>
       <c r="D21">
-        <v>2.1588259854252818e-06</v>
+        <v>0.00013649220948483475</v>
       </c>
       <c r="E21">
-        <v>-2.076352929334024e-08</v>
+        <v>-1.4995439368411866e-06</v>
       </c>
       <c r="F21">
-        <v>0.00010188428781165038</v>
+        <v>-0.00027644164177490567</v>
       </c>
       <c r="G21">
-        <v>7.0075343305214235e-05</v>
+        <v>-0.00033019620567532307</v>
       </c>
       <c r="H21">
-        <v>-1.1840614098766571e-05</v>
+        <v>0.00072219725086755595</v>
       </c>
       <c r="I21">
-        <v>-8.8788849494841893e-05</v>
+        <v>-0.00037172107304085916</v>
       </c>
       <c r="J21">
-        <v>-0.00016832105619892304</v>
+        <v>-0.00036433122970908391</v>
       </c>
       <c r="K21">
-        <v>-6.1980961358985257e-05</v>
+        <v>-6.1238467038893723e-05</v>
       </c>
       <c r="L21">
-        <v>4.2655189718628236e-05</v>
+        <v>0.00047931725768046946</v>
       </c>
       <c r="M21">
-        <v>-6.6651350535923241e-06</v>
+        <v>-0.0002246066967197081</v>
       </c>
       <c r="N21">
-        <v>5.0862450693369169e-05</v>
+        <v>-0.00023805746492108119</v>
       </c>
       <c r="O21">
-        <v>3.8734005588616279e-06</v>
+        <v>-0.0026664312010428294</v>
       </c>
       <c r="P21">
-        <v>-0.00012686056970893185</v>
+        <v>-0.0026377364984271805</v>
       </c>
       <c r="Q21">
-        <v>-6.9610037324200052e-05</v>
+        <v>-0.0028176159796168675</v>
       </c>
       <c r="R21">
-        <v>-0.00021946842601090538</v>
+        <v>-0.0027234798389865695</v>
       </c>
       <c r="S21">
-        <v>-0.00016950048967623549</v>
+        <v>-0.0028540982183731392</v>
       </c>
       <c r="T21">
-        <v>7.5043096419072711e-05</v>
+        <v>-0.0026258835697140297</v>
       </c>
       <c r="U21">
-        <v>1.7860126342024267e-05</v>
+        <v>-6.7605363243405136e-05</v>
       </c>
       <c r="V21">
-        <v>0.0012671306669734773</v>
+        <v>0.0067794907749155536</v>
       </c>
       <c r="W21">
-        <v>-3.558219854460926e-05</v>
+        <v>0.00058562618029462917</v>
       </c>
       <c r="X21">
-        <v>-0.00027247313344117702</v>
-      </c>
-      <c r="Y21">
-        <v>-0.010495916611979662</v>
+        <v>0.00093428246179980514</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="B22">
-        <v>0.0008733889608624803</v>
+        <v>-0.0019375779580146401</v>
       </c>
       <c r="C22">
-        <v>3.6957396003354273e-07</v>
+        <v>5.6577398037686562e-05</v>
       </c>
       <c r="D22">
-        <v>-3.6527149167597014e-08</v>
+        <v>-5.0547253262777682e-06</v>
       </c>
       <c r="E22">
-        <v>2.6096527946280807e-10</v>
+        <v>3.1812329163913154e-09</v>
       </c>
       <c r="F22">
-        <v>-2.4806172044277065e-06</v>
+        <v>-0.00013432855475457601</v>
       </c>
       <c r="G22">
-        <v>-1.9475581026191977e-06</v>
+        <v>-0.00021823713896273526</v>
       </c>
       <c r="H22">
-        <v>8.231670790197127e-07</v>
+        <v>-5.580709770888607e-05</v>
       </c>
       <c r="I22">
-        <v>2.6912062540689982e-06</v>
+        <v>0.00037913961581995852</v>
       </c>
       <c r="J22">
-        <v>4.9035815633145568e-06</v>
+        <v>2.7994241299931422e-05</v>
       </c>
       <c r="K22">
-        <v>2.0787268949662982e-06</v>
+        <v>-4.7476312130766835e-05</v>
       </c>
       <c r="L22">
-        <v>-8.3545309797524779e-07</v>
+        <v>0.00017878871810228037</v>
       </c>
       <c r="M22">
-        <v>2.4641475995340308e-08</v>
+        <v>0.00011122971900492636</v>
       </c>
       <c r="N22">
-        <v>-1.1738295259111609e-06</v>
+        <v>0.00038347599303256751</v>
       </c>
       <c r="O22">
-        <v>2.4589038982603269e-07</v>
+        <v>4.3547638806642683e-05</v>
       </c>
       <c r="P22">
-        <v>3.6525038280720818e-06</v>
+        <v>8.0817208774079143e-05</v>
       </c>
       <c r="Q22">
-        <v>2.0305276606834906e-06</v>
+        <v>-0.00020145030779158881</v>
       </c>
       <c r="R22">
-        <v>6.3135464531531322e-06</v>
+        <v>8.8480518575858626e-05</v>
       </c>
       <c r="S22">
-        <v>4.7219325105643222e-06</v>
+        <v>-0.0001234594939325262</v>
       </c>
       <c r="T22">
-        <v>-1.9926144851385984e-06</v>
+        <v>-6.6630248629776304e-05</v>
       </c>
       <c r="U22">
-        <v>-6.9935552874593709e-07</v>
+        <v>-8.0751454120666689e-05</v>
       </c>
       <c r="V22">
-        <v>-3.558219854460926e-05</v>
+        <v>0.00058562618029462917</v>
       </c>
       <c r="W22">
-        <v>1.0093361317555429e-06</v>
+        <v>0.003445720518748828</v>
       </c>
       <c r="X22">
-        <v>6.2693171507788824e-06</v>
-      </c>
-      <c r="Y22">
-        <v>0.00029072189055955391</v>
+        <v>0.00095807992966701842</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="B23">
-        <v>0.15692480982865656</v>
+        <v>3.374888349881024</v>
       </c>
       <c r="C23">
-        <v>0.00040605087269702308</v>
+        <v>-0.00072011313282233916</v>
       </c>
       <c r="D23">
-        <v>0.00014318931613301316</v>
+        <v>-0.0011345328519525664</v>
       </c>
       <c r="E23">
-        <v>-1.553139525100811e-06</v>
+        <v>1.2160635972344815e-05</v>
       </c>
       <c r="F23">
-        <v>-0.00033826202136013359</v>
+        <v>0.0022417792098019958</v>
       </c>
       <c r="G23">
-        <v>-0.00031986747097120869</v>
+        <v>0.00044527321146397973</v>
       </c>
       <c r="H23">
-        <v>0.00076866577025371593</v>
+        <v>-0.0025789095078409237</v>
       </c>
       <c r="I23">
-        <v>-0.00039793735217381291</v>
+        <v>-0.0038732700851372235</v>
       </c>
       <c r="J23">
-        <v>-0.00040854721365483963</v>
+        <v>0.00084423847422780772</v>
       </c>
       <c r="K23">
-        <v>0.00021651875307818864</v>
+        <v>-0.0009377342215026094</v>
       </c>
       <c r="L23">
-        <v>-5.91656264793806e-05</v>
+        <v>-0.0031997154103937738</v>
       </c>
       <c r="M23">
-        <v>0.00048124408255867846</v>
+        <v>-0.0033092744992974281</v>
       </c>
       <c r="N23">
-        <v>-0.00021953717562188271</v>
+        <v>-0.0042414041325411619</v>
       </c>
       <c r="O23">
-        <v>-0.0002608154928714024</v>
+        <v>-0.0036648491749037078</v>
       </c>
       <c r="P23">
-        <v>-0.0027039905890799999</v>
+        <v>-0.0036737343105442094</v>
       </c>
       <c r="Q23">
-        <v>-0.0027022685811751478</v>
+        <v>-0.0024157867628509886</v>
       </c>
       <c r="R23">
-        <v>-0.002819930306646813</v>
+        <v>-0.003623998948298306</v>
       </c>
       <c r="S23">
-        <v>-0.0027740657972945885</v>
+        <v>-0.0037044019217954867</v>
       </c>
       <c r="T23">
-        <v>-0.0029016296484143103</v>
+        <v>-0.0039541082576806195</v>
       </c>
       <c r="U23">
-        <v>-0.0026685125248852716</v>
+        <v>-0.00027202396336519093</v>
       </c>
       <c r="V23">
-        <v>-0.00027247313344117702</v>
+        <v>0.00093428246179980514</v>
       </c>
       <c r="W23">
-        <v>6.2693171507788824e-06</v>
+        <v>0.00095807992966701842</v>
       </c>
       <c r="X23">
-        <v>0.0068969093903318889</v>
-      </c>
-      <c r="Y23">
-        <v>0.0024338262007297593</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="s">
-        <v>53</v>
-      </c>
-      <c r="B24">
-        <v>3.6611367231697436</v>
-      </c>
-      <c r="C24">
-        <v>-0.00064072713251467611</v>
-      </c>
-      <c r="D24">
-        <v>-0.0011462157289324768</v>
-      </c>
-      <c r="E24">
-        <v>1.2330475292843683e-05</v>
-      </c>
-      <c r="F24">
-        <v>0.0018597307786262195</v>
-      </c>
-      <c r="G24">
-        <v>-8.5958005699835263e-05</v>
-      </c>
-      <c r="H24">
-        <v>-0.002393620323857786</v>
-      </c>
-      <c r="I24">
-        <v>-0.0033765804724193091</v>
-      </c>
-      <c r="J24">
-        <v>0.0027713651713157134</v>
-      </c>
-      <c r="K24">
-        <v>-0.0010801616550446323</v>
-      </c>
-      <c r="L24">
-        <v>-0.0011724076670993505</v>
-      </c>
-      <c r="M24">
-        <v>-0.0035261338360540045</v>
-      </c>
-      <c r="N24">
-        <v>-0.0039333849864819862</v>
-      </c>
-      <c r="O24">
-        <v>-0.0046300048146747288</v>
-      </c>
-      <c r="P24">
-        <v>-0.0025691016129792583</v>
-      </c>
-      <c r="Q24">
-        <v>-0.0030203754859823798</v>
-      </c>
-      <c r="R24">
-        <v>-0.00048798749397827024</v>
-      </c>
-      <c r="S24">
-        <v>-0.0022863386262962412</v>
-      </c>
-      <c r="T24">
-        <v>-0.0041605238901346753</v>
-      </c>
-      <c r="U24">
-        <v>-0.0040303551283810309</v>
-      </c>
-      <c r="V24">
-        <v>-0.010495916611979662</v>
-      </c>
-      <c r="W24">
-        <v>0.00029072189055955391</v>
-      </c>
-      <c r="X24">
-        <v>0.0024338262007297593</v>
-      </c>
-      <c r="Y24">
-        <v>0.11774114826019216</v>
+        <v>0.03417419939313867</v>
       </c>
     </row>
   </sheetData>
@@ -4127,7 +3972,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:S18"/>
+  <dimension ref="A1:R17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4138,1058 +3983,948 @@
         <v>54</v>
       </c>
       <c r="C1" t="s">
+        <v>61</v>
+      </c>
+      <c r="D1" t="s">
+        <v>62</v>
+      </c>
+      <c r="E1" t="s">
         <v>63</v>
       </c>
-      <c r="D1" t="s">
+      <c r="F1" t="s">
         <v>64</v>
       </c>
-      <c r="E1" t="s">
+      <c r="G1" t="s">
         <v>65</v>
       </c>
-      <c r="F1" t="s">
+      <c r="H1" t="s">
         <v>66</v>
       </c>
-      <c r="G1" t="s">
+      <c r="I1" t="s">
         <v>67</v>
       </c>
-      <c r="H1" t="s">
+      <c r="J1" t="s">
         <v>68</v>
       </c>
-      <c r="I1" t="s">
+      <c r="K1" t="s">
         <v>69</v>
       </c>
-      <c r="J1" t="s">
+      <c r="L1" t="s">
         <v>70</v>
       </c>
-      <c r="K1" t="s">
+      <c r="M1" t="s">
         <v>71</v>
       </c>
-      <c r="L1" t="s">
+      <c r="N1" t="s">
         <v>72</v>
       </c>
-      <c r="M1" t="s">
+      <c r="O1" t="s">
         <v>73</v>
       </c>
-      <c r="N1" t="s">
+      <c r="P1" t="s">
         <v>74</v>
       </c>
-      <c r="O1" t="s">
+      <c r="Q1" t="s">
         <v>75</v>
       </c>
-      <c r="P1" t="s">
+      <c r="R1" t="s">
         <v>76</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>77</v>
-      </c>
-      <c r="R1" t="s">
-        <v>78</v>
-      </c>
-      <c r="S1" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B2">
-        <v>-0.34384339576882689</v>
+        <v>-0.35122706167694562</v>
       </c>
       <c r="C2">
-        <v>0.0047408545202349151</v>
+        <v>0.0047491487464665378</v>
       </c>
       <c r="D2">
-        <v>3.3549608911996793e-05</v>
+        <v>4.1105731198627044e-05</v>
       </c>
       <c r="E2">
-        <v>4.8475830316550012e-08</v>
+        <v>-1.0770395602398522e-07</v>
       </c>
       <c r="F2">
-        <v>0.00069935305752798942</v>
+        <v>0.00072051214917701306</v>
       </c>
       <c r="G2">
-        <v>0.00089332229105994285</v>
+        <v>0.00093528318741142435</v>
       </c>
       <c r="H2">
-        <v>0.00060714102305479078</v>
+        <v>0.00062497917760674193</v>
       </c>
       <c r="I2">
-        <v>0.00045085057145506738</v>
+        <v>0.00046715485674410199</v>
       </c>
       <c r="J2">
-        <v>0.00029920623485892852</v>
+        <v>0.00030595319816199216</v>
       </c>
       <c r="K2">
-        <v>0.00044650399206512954</v>
+        <v>0.00045749844088750129</v>
       </c>
       <c r="L2">
-        <v>-5.6143517142952845e-05</v>
+        <v>-4.1935989597488851e-05</v>
       </c>
       <c r="M2">
-        <v>5.2129077420807045e-07</v>
+        <v>0.00070963663174204196</v>
       </c>
       <c r="N2">
-        <v>0.00067955237250882006</v>
+        <v>-0.0033759297345495056</v>
       </c>
       <c r="O2">
-        <v>-0.0031709098771127292</v>
+        <v>0.00034923860705901209</v>
       </c>
       <c r="P2">
-        <v>0.00034517945257483984</v>
+        <v>-4.4698298881771349e-06</v>
       </c>
       <c r="Q2">
-        <v>-4.3585590347688733e-06</v>
+        <v>0.0011274229937864068</v>
       </c>
       <c r="R2">
-        <v>0.0011215947385701391</v>
-      </c>
-      <c r="S2">
-        <v>-0.0080588512357431929</v>
+        <v>-0.0082017590272386917</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B3">
-        <v>0.90167762596967116</v>
+        <v>0.8937067770233802</v>
       </c>
       <c r="C3">
-        <v>3.3549608911996793e-05</v>
+        <v>4.1105731198627044e-05</v>
       </c>
       <c r="D3">
-        <v>0.0016200789567591923</v>
+        <v>0.0016174831733119855</v>
       </c>
       <c r="E3">
-        <v>-2.7551714393709548e-05</v>
+        <v>-2.7550073280868673e-05</v>
       </c>
       <c r="F3">
-        <v>0.00054266348566108132</v>
+        <v>0.00055204231380608787</v>
       </c>
       <c r="G3">
-        <v>0.00076894658936941217</v>
+        <v>0.00079423981635799463</v>
       </c>
       <c r="H3">
-        <v>0.00060769674414479485</v>
+        <v>0.00062130310470680521</v>
       </c>
       <c r="I3">
-        <v>0.00066461314363860501</v>
+        <v>0.000658633826340938</v>
       </c>
       <c r="J3">
-        <v>0.00042111561825826669</v>
+        <v>0.00040434253956156483</v>
       </c>
       <c r="K3">
-        <v>0.00054957811341819303</v>
+        <v>0.00055265442358295091</v>
       </c>
       <c r="L3">
-        <v>6.181451888983636e-05</v>
+        <v>-5.361393262816107e-05</v>
       </c>
       <c r="M3">
-        <v>-3.0884311127745161e-06</v>
+        <v>8.4554146685256529e-05</v>
       </c>
       <c r="N3">
-        <v>4.5001108053279674e-05</v>
+        <v>-0.020672082544343665</v>
       </c>
       <c r="O3">
-        <v>-0.021717950404806973</v>
+        <v>0.0012512692037557757</v>
       </c>
       <c r="P3">
-        <v>0.0012489417495879561</v>
+        <v>-2.1933951192738993e-05</v>
       </c>
       <c r="Q3">
-        <v>-2.1883601159983474e-05</v>
+        <v>0.00080307930557372599</v>
       </c>
       <c r="R3">
-        <v>0.00079141467250392825</v>
-      </c>
-      <c r="S3">
-        <v>-0.017346213057188059</v>
+        <v>-0.016377558285024796</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B4">
-        <v>-0.012767053130261989</v>
+        <v>-0.012666405975215914</v>
       </c>
       <c r="C4">
-        <v>4.8475830316550012e-08</v>
+        <v>-1.0770395602398522e-07</v>
       </c>
       <c r="D4">
-        <v>-2.7551714393709548e-05</v>
+        <v>-2.7550073280868673e-05</v>
       </c>
       <c r="E4">
-        <v>5.02200488462599e-07</v>
+        <v>5.0240508236122775e-07</v>
       </c>
       <c r="F4">
-        <v>-7.1453699565580237e-06</v>
+        <v>-7.1962184296137826e-06</v>
       </c>
       <c r="G4">
-        <v>-1.1566858536051148e-05</v>
+        <v>-1.1834909184732745e-05</v>
       </c>
       <c r="H4">
-        <v>-9.1370466998804035e-06</v>
+        <v>-9.2428584925257498e-06</v>
       </c>
       <c r="I4">
-        <v>-1.077817698784182e-05</v>
+        <v>-1.0569706576433179e-05</v>
       </c>
       <c r="J4">
-        <v>-6.3125027169153167e-06</v>
+        <v>-6.0436863089081685e-06</v>
       </c>
       <c r="K4">
-        <v>-8.6785006021177565e-06</v>
+        <v>-8.6220882946365894e-06</v>
       </c>
       <c r="L4">
-        <v>3.911895678807039e-07</v>
+        <v>8.1617813445249337e-07</v>
       </c>
       <c r="M4">
-        <v>9.5081830099841993e-09</v>
+        <v>-2.5515479222276461e-06</v>
       </c>
       <c r="N4">
-        <v>-1.9336532215322207e-06</v>
+        <v>0.00033894265362058984</v>
       </c>
       <c r="O4">
-        <v>0.00034309708374387045</v>
+        <v>-2.3359172365067495e-05</v>
       </c>
       <c r="P4">
-        <v>-2.3356952482577525e-05</v>
+        <v>4.2802073430867914e-07</v>
       </c>
       <c r="Q4">
-        <v>4.2796717183586185e-07</v>
+        <v>-1.2322930923123847e-05</v>
       </c>
       <c r="R4">
-        <v>-1.2226856217339435e-05</v>
-      </c>
-      <c r="S4">
-        <v>0.00030122523417498509</v>
+        <v>0.00029721007302726046</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B5">
-        <v>0.29091498766006829</v>
+        <v>0.29259596485483275</v>
       </c>
       <c r="C5">
-        <v>0.00069935305752798942</v>
+        <v>0.00072051214917701306</v>
       </c>
       <c r="D5">
-        <v>0.00054266348566108132</v>
+        <v>0.00055204231380608787</v>
       </c>
       <c r="E5">
-        <v>-7.1453699565580237e-06</v>
+        <v>-7.1962184296137826e-06</v>
       </c>
       <c r="F5">
-        <v>0.036708495038783789</v>
+        <v>0.036832712105465279</v>
       </c>
       <c r="G5">
-        <v>0.029089265529951301</v>
+        <v>0.029190450192717311</v>
       </c>
       <c r="H5">
-        <v>0.028855440583342606</v>
+        <v>0.028971465012560441</v>
       </c>
       <c r="I5">
-        <v>0.02862453380676238</v>
+        <v>0.028736875510538561</v>
       </c>
       <c r="J5">
-        <v>0.029046810441847603</v>
+        <v>0.029183328317584276</v>
       </c>
       <c r="K5">
-        <v>0.028859945722801747</v>
+        <v>0.028964176629697847</v>
       </c>
       <c r="L5">
-        <v>-0.00038587491489086145</v>
+        <v>-1.3930154357415654e-05</v>
       </c>
       <c r="M5">
-        <v>1.0627521491872748e-05</v>
+        <v>0.0013609416988880664</v>
       </c>
       <c r="N5">
-        <v>0.0013347553250575217</v>
+        <v>-0.037284706994675648</v>
       </c>
       <c r="O5">
-        <v>-0.033897809845662673</v>
+        <v>0.00079974099503155472</v>
       </c>
       <c r="P5">
-        <v>0.00078184918466903553</v>
+        <v>-1.097974502253118e-05</v>
       </c>
       <c r="Q5">
-        <v>-1.0786541446868475e-05</v>
+        <v>0.029496654528626518</v>
       </c>
       <c r="R5">
-        <v>0.029386620811073593</v>
-      </c>
-      <c r="S5">
-        <v>-0.038316511694891656</v>
+        <v>-0.0418243862399231</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B6">
-        <v>0.48106191673915738</v>
+        <v>0.486102158385816</v>
       </c>
       <c r="C6">
-        <v>0.00089332229105994285</v>
+        <v>0.00093528318741142435</v>
       </c>
       <c r="D6">
-        <v>0.00076894658936941217</v>
+        <v>0.00079423981635799463</v>
       </c>
       <c r="E6">
-        <v>-1.1566858536051148e-05</v>
+        <v>-1.1834909184732745e-05</v>
       </c>
       <c r="F6">
-        <v>0.029089265529951301</v>
+        <v>0.029190450192717311</v>
       </c>
       <c r="G6">
-        <v>0.0381962614335715</v>
+        <v>0.038274900818509192</v>
       </c>
       <c r="H6">
-        <v>0.029027227940033255</v>
+        <v>0.029128716535858919</v>
       </c>
       <c r="I6">
-        <v>0.028827246607432574</v>
+        <v>0.028927149886225759</v>
       </c>
       <c r="J6">
-        <v>0.029089268352236537</v>
+        <v>0.029233813548163012</v>
       </c>
       <c r="K6">
-        <v>0.029039992870557963</v>
+        <v>0.029126242545409284</v>
       </c>
       <c r="L6">
-        <v>-0.00087098462835618652</v>
+        <v>-9.1765039931104782e-05</v>
       </c>
       <c r="M6">
-        <v>2.2210212965035952e-05</v>
+        <v>0.001941924043161806</v>
       </c>
       <c r="N6">
-        <v>0.0018876123630718498</v>
+        <v>-0.039254096154599023</v>
       </c>
       <c r="O6">
-        <v>-0.032243071721375402</v>
+        <v>0.0011087539647977041</v>
       </c>
       <c r="P6">
-        <v>0.001083322222903917</v>
+        <v>-1.6272063434050882e-05</v>
       </c>
       <c r="Q6">
-        <v>-1.5999396080784822e-05</v>
+        <v>0.029657776556731803</v>
       </c>
       <c r="R6">
-        <v>0.029567483525021893</v>
-      </c>
-      <c r="S6">
-        <v>-0.037907319250174737</v>
+        <v>-0.04492646974378825</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B7">
-        <v>0.39992789709898413</v>
+        <v>0.40007154815243884</v>
       </c>
       <c r="C7">
-        <v>0.00060714102305479078</v>
+        <v>0.00062497917760674193</v>
       </c>
       <c r="D7">
-        <v>0.00060769674414479485</v>
+        <v>0.00062130310470680521</v>
       </c>
       <c r="E7">
-        <v>-9.1370466998804035e-06</v>
+        <v>-9.2428584925257498e-06</v>
       </c>
       <c r="F7">
-        <v>0.028855440583342606</v>
+        <v>0.028971465012560441</v>
       </c>
       <c r="G7">
-        <v>0.029027227940033255</v>
+        <v>0.029128716535858919</v>
       </c>
       <c r="H7">
-        <v>0.036901732063608632</v>
+        <v>0.037034055701205486</v>
       </c>
       <c r="I7">
-        <v>0.028564191974431233</v>
+        <v>0.028677022005493901</v>
       </c>
       <c r="J7">
-        <v>0.028964512564592391</v>
+        <v>0.029098300019217125</v>
       </c>
       <c r="K7">
-        <v>0.028826690199441382</v>
+        <v>0.028926864583988569</v>
       </c>
       <c r="L7">
-        <v>-0.00056369962915729394</v>
+        <v>-8.8467751503705164e-05</v>
       </c>
       <c r="M7">
-        <v>1.3575291613361976e-05</v>
+        <v>0.0011538951554637081</v>
       </c>
       <c r="N7">
-        <v>0.0011120870778538686</v>
+        <v>-0.036364952367985384</v>
       </c>
       <c r="O7">
-        <v>-0.032046006027079008</v>
+        <v>0.00081489358602144547</v>
       </c>
       <c r="P7">
-        <v>0.00079163275171501533</v>
+        <v>-1.207128037805839e-05</v>
       </c>
       <c r="Q7">
-        <v>-1.1818615921872845e-05</v>
+        <v>0.029371102133802909</v>
       </c>
       <c r="R7">
-        <v>0.029260694782256444</v>
-      </c>
-      <c r="S7">
-        <v>-0.035657403591001571</v>
+        <v>-0.040116283798193236</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B8">
-        <v>0.15481289208388305</v>
+        <v>0.15550177013700275</v>
       </c>
       <c r="C8">
-        <v>0.00045085057145506738</v>
+        <v>0.00046715485674410199</v>
       </c>
       <c r="D8">
-        <v>0.00066461314363860501</v>
+        <v>0.000658633826340938</v>
       </c>
       <c r="E8">
-        <v>-1.077817698784182e-05</v>
+        <v>-1.0569706576433179e-05</v>
       </c>
       <c r="F8">
-        <v>0.02862453380676238</v>
+        <v>0.028736875510538561</v>
       </c>
       <c r="G8">
-        <v>0.028827246607432574</v>
+        <v>0.028927149886225759</v>
       </c>
       <c r="H8">
-        <v>0.028564191974431233</v>
+        <v>0.028677022005493901</v>
       </c>
       <c r="I8">
-        <v>0.040686759049641474</v>
+        <v>0.040730767098061997</v>
       </c>
       <c r="J8">
-        <v>0.028941194990458961</v>
+        <v>0.029067133707782328</v>
       </c>
       <c r="K8">
-        <v>0.028611370508207223</v>
+        <v>0.028728548119665489</v>
       </c>
       <c r="L8">
-        <v>-0.00025062989652656874</v>
+        <v>-3.6051418472146391e-05</v>
       </c>
       <c r="M8">
-        <v>6.0875126661998817e-06</v>
+        <v>0.0010435144961389222</v>
       </c>
       <c r="N8">
-        <v>0.0010341246454369834</v>
+        <v>-0.0378947125877801</v>
       </c>
       <c r="O8">
-        <v>-0.036004254583368839</v>
+        <v>0.0006532139621407097</v>
       </c>
       <c r="P8">
-        <v>0.0006419821466063071</v>
+        <v>-9.3775546338557174e-06</v>
       </c>
       <c r="Q8">
-        <v>-9.279031428991954e-06</v>
+        <v>0.032722036852653083</v>
       </c>
       <c r="R8">
-        <v>0.032654749516482784</v>
-      </c>
-      <c r="S8">
-        <v>-0.035777194380549757</v>
+        <v>-0.037883143132607669</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B9">
-        <v>0.31669907720553103</v>
+        <v>0.32248867507780776</v>
       </c>
       <c r="C9">
-        <v>0.00029920623485892852</v>
+        <v>0.00030595319816199216</v>
       </c>
       <c r="D9">
-        <v>0.00042111561825826669</v>
+        <v>0.00040434253956156483</v>
       </c>
       <c r="E9">
-        <v>-6.3125027169153167e-06</v>
+        <v>-6.0436863089081685e-06</v>
       </c>
       <c r="F9">
-        <v>0.029046810441847603</v>
+        <v>0.029183328317584276</v>
       </c>
       <c r="G9">
-        <v>0.029089268352236537</v>
+        <v>0.029233813548163012</v>
       </c>
       <c r="H9">
-        <v>0.028964512564592391</v>
+        <v>0.029098300019217125</v>
       </c>
       <c r="I9">
-        <v>0.028941194990458961</v>
+        <v>0.029067133707782328</v>
       </c>
       <c r="J9">
-        <v>0.034757171786793689</v>
+        <v>0.034896533725664668</v>
       </c>
       <c r="K9">
-        <v>0.028961553952568678</v>
+        <v>0.029098018188787843</v>
       </c>
       <c r="L9">
-        <v>0.0002030236665577995</v>
+        <v>-1.284996878838301e-05</v>
       </c>
       <c r="M9">
-        <v>-6.2018395343834765e-06</v>
+        <v>0.00096639963610046543</v>
       </c>
       <c r="N9">
-        <v>0.00099183598366570092</v>
+        <v>-0.034698392110393377</v>
       </c>
       <c r="O9">
-        <v>-0.036561460405948258</v>
+        <v>0.000360856962240216</v>
       </c>
       <c r="P9">
-        <v>0.00035108136568654056</v>
+        <v>-5.2853895708522764e-06</v>
       </c>
       <c r="Q9">
-        <v>-5.1997567080126045e-06</v>
+        <v>0.02927542196470918</v>
       </c>
       <c r="R9">
-        <v>0.029125515018551013</v>
-      </c>
-      <c r="S9">
-        <v>-0.036013194098387706</v>
+        <v>-0.034564932597856965</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B10">
-        <v>0.039469032857187322</v>
+        <v>0.045148461696831642</v>
       </c>
       <c r="C10">
-        <v>0.00044650399206512954</v>
+        <v>0.00045749844088750129</v>
       </c>
       <c r="D10">
-        <v>0.00054957811341819303</v>
+        <v>0.00055265442358295091</v>
       </c>
       <c r="E10">
-        <v>-8.6785006021177565e-06</v>
+        <v>-8.6220882946365894e-06</v>
       </c>
       <c r="F10">
-        <v>0.028859945722801747</v>
+        <v>0.028964176629697847</v>
       </c>
       <c r="G10">
-        <v>0.029039992870557963</v>
+        <v>0.029126242545409284</v>
       </c>
       <c r="H10">
-        <v>0.028826690199441382</v>
+        <v>0.028926864583988569</v>
       </c>
       <c r="I10">
-        <v>0.028611370508207223</v>
+        <v>0.028728548119665489</v>
       </c>
       <c r="J10">
-        <v>0.028961553952568678</v>
+        <v>0.029098018188787843</v>
       </c>
       <c r="K10">
-        <v>0.033809383160356206</v>
+        <v>0.033924748248957033</v>
       </c>
       <c r="L10">
-        <v>-0.00036276171113166882</v>
+        <v>-6.4138630384448812e-05</v>
       </c>
       <c r="M10">
-        <v>8.4044476629377754e-06</v>
+        <v>0.0014501789718770692</v>
       </c>
       <c r="N10">
-        <v>0.0014628945427379659</v>
+        <v>-0.035662893284682556</v>
       </c>
       <c r="O10">
-        <v>-0.032946418043253198</v>
+        <v>0.00080457323008500167</v>
       </c>
       <c r="P10">
-        <v>0.00079902019737406339</v>
+        <v>-1.2015752453627834e-05</v>
       </c>
       <c r="Q10">
-        <v>-1.2013419276710527e-05</v>
+        <v>0.029322022889212766</v>
       </c>
       <c r="R10">
-        <v>0.029226311008889498</v>
-      </c>
-      <c r="S10">
-        <v>-0.037508718657555964</v>
+        <v>-0.040241020944762687</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B11">
-        <v>0.15588801605997718</v>
+        <v>0.021535792779736385</v>
       </c>
       <c r="C11">
-        <v>-5.6143517142952845e-05</v>
+        <v>-4.1935989597488851e-05</v>
       </c>
       <c r="D11">
-        <v>6.181451888983636e-05</v>
+        <v>-5.361393262816107e-05</v>
       </c>
       <c r="E11">
-        <v>3.911895678807039e-07</v>
+        <v>8.1617813445249337e-07</v>
       </c>
       <c r="F11">
-        <v>-0.00038587491489086145</v>
+        <v>-1.3930154357415654e-05</v>
       </c>
       <c r="G11">
-        <v>-0.00087098462835618652</v>
+        <v>-9.1765039931104782e-05</v>
       </c>
       <c r="H11">
-        <v>-0.00056369962915729394</v>
+        <v>-8.8467751503705164e-05</v>
       </c>
       <c r="I11">
-        <v>-0.00025062989652656874</v>
+        <v>-3.6051418472146391e-05</v>
       </c>
       <c r="J11">
-        <v>0.0002030236665577995</v>
+        <v>-1.284996878838301e-05</v>
       </c>
       <c r="K11">
-        <v>-0.00036276171113166882</v>
+        <v>-6.4138630384448812e-05</v>
       </c>
       <c r="L11">
-        <v>0.0060609916706444063</v>
+        <v>6.9690784926529581e-05</v>
       </c>
       <c r="M11">
-        <v>-0.00016709476725540375</v>
+        <v>-0.00031145287976044319</v>
       </c>
       <c r="N11">
-        <v>-0.000757175421846841</v>
+        <v>-0.00037156190999832221</v>
       </c>
       <c r="O11">
-        <v>-0.052892333265037769</v>
+        <v>-6.5022547779576665e-05</v>
       </c>
       <c r="P11">
-        <v>-0.00016351676263185594</v>
+        <v>9.4685681341809306e-07</v>
       </c>
       <c r="Q11">
-        <v>3.2277705558795894e-06</v>
+        <v>-6.1216805498152775e-05</v>
       </c>
       <c r="R11">
-        <v>-0.00058788877811521284</v>
-      </c>
-      <c r="S11">
-        <v>-0.049295193671009457</v>
+        <v>-0.00016066768859581988</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B12">
-        <v>-0.003856579120107082</v>
+        <v>-0.071367498930058559</v>
       </c>
       <c r="C12">
-        <v>5.2129077420807045e-07</v>
+        <v>0.00070963663174204196</v>
       </c>
       <c r="D12">
-        <v>-3.0884311127745161e-06</v>
+        <v>8.4554146685256529e-05</v>
       </c>
       <c r="E12">
-        <v>9.5081830099841993e-09</v>
+        <v>-2.5515479222276461e-06</v>
       </c>
       <c r="F12">
-        <v>1.0627521491872748e-05</v>
+        <v>0.0013609416988880664</v>
       </c>
       <c r="G12">
-        <v>2.2210212965035952e-05</v>
+        <v>0.001941924043161806</v>
       </c>
       <c r="H12">
-        <v>1.3575291613361976e-05</v>
+        <v>0.0011538951554637081</v>
       </c>
       <c r="I12">
-        <v>6.0875126661998817e-06</v>
+        <v>0.0010435144961389222</v>
       </c>
       <c r="J12">
-        <v>-6.2018395343834765e-06</v>
+        <v>0.00096639963610046543</v>
       </c>
       <c r="K12">
-        <v>8.4044476629377754e-06</v>
+        <v>0.0014501789718770692</v>
       </c>
       <c r="L12">
-        <v>-0.00016709476725540375</v>
+        <v>-0.00031145287976044319</v>
       </c>
       <c r="M12">
-        <v>4.6566808416483394e-06</v>
+        <v>0.017346038444110246</v>
       </c>
       <c r="N12">
-        <v>1.33392243403259e-05</v>
+        <v>0.001978026497936625</v>
       </c>
       <c r="O12">
-        <v>0.001463547582177516</v>
+        <v>0.00024901328124476291</v>
       </c>
       <c r="P12">
-        <v>2.9763659789035614e-06</v>
+        <v>-4.1737864785901347e-06</v>
       </c>
       <c r="Q12">
-        <v>-6.7148394356183032e-08</v>
+        <v>0.0016231405111975777</v>
       </c>
       <c r="R12">
-        <v>1.4986538893700533e-05</v>
-      </c>
-      <c r="S12">
-        <v>0.0013674771125605587</v>
+        <v>-0.0011265997268665451</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B13">
-        <v>-0.054818361539778496</v>
+        <v>-12.604449226554603</v>
       </c>
       <c r="C13">
-        <v>0.00067955237250882006</v>
+        <v>-0.0033759297345495056</v>
       </c>
       <c r="D13">
-        <v>4.5001108053279674e-05</v>
+        <v>-0.020672082544343665</v>
       </c>
       <c r="E13">
-        <v>-1.9336532215322207e-06</v>
+        <v>0.00033894265362058984</v>
       </c>
       <c r="F13">
-        <v>0.0013347553250575217</v>
+        <v>-0.037284706994675648</v>
       </c>
       <c r="G13">
-        <v>0.0018876123630718498</v>
+        <v>-0.039254096154599023</v>
       </c>
       <c r="H13">
-        <v>0.0011120870778538686</v>
+        <v>-0.036364952367985384</v>
       </c>
       <c r="I13">
-        <v>0.0010341246454369834</v>
+        <v>-0.0378947125877801</v>
       </c>
       <c r="J13">
-        <v>0.00099183598366570092</v>
+        <v>-0.034698392110393377</v>
       </c>
       <c r="K13">
-        <v>0.0014628945427379659</v>
+        <v>-0.035662893284682556</v>
       </c>
       <c r="L13">
-        <v>-0.000757175421846841</v>
+        <v>-0.00037156190999832221</v>
       </c>
       <c r="M13">
-        <v>1.33392243403259e-05</v>
+        <v>0.001978026497936625</v>
       </c>
       <c r="N13">
-        <v>0.017182633389525904</v>
+        <v>0.31901376700178286</v>
       </c>
       <c r="O13">
-        <v>0.0061305279915795522</v>
+        <v>-0.015661080489898179</v>
       </c>
       <c r="P13">
-        <v>0.00020306282943048453</v>
+        <v>0.00026578374927163423</v>
       </c>
       <c r="Q13">
-        <v>-3.4912051564507005e-06</v>
+        <v>-0.039554241119650835</v>
       </c>
       <c r="R13">
-        <v>0.0015840710192995254</v>
-      </c>
-      <c r="S13">
-        <v>0.0031495781414323598</v>
+        <v>0.25821674883469714</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B14">
-        <v>-13.838473818388014</v>
+        <v>0.71544520020009572</v>
       </c>
       <c r="C14">
-        <v>-0.0031709098771127292</v>
+        <v>0.00034923860705901209</v>
       </c>
       <c r="D14">
-        <v>-0.021717950404806973</v>
+        <v>0.0012512692037557757</v>
       </c>
       <c r="E14">
-        <v>0.00034309708374387045</v>
+        <v>-2.3359172365067495e-05</v>
       </c>
       <c r="F14">
-        <v>-0.033897809845662673</v>
+        <v>0.00079974099503155472</v>
       </c>
       <c r="G14">
-        <v>-0.032243071721375402</v>
+        <v>0.0011087539647977041</v>
       </c>
       <c r="H14">
-        <v>-0.032046006027079008</v>
+        <v>0.00081489358602144547</v>
       </c>
       <c r="I14">
-        <v>-0.036004254583368839</v>
+        <v>0.0006532139621407097</v>
       </c>
       <c r="J14">
-        <v>-0.036561460405948258</v>
+        <v>0.000360856962240216</v>
       </c>
       <c r="K14">
-        <v>-0.032946418043253198</v>
+        <v>0.00080457323008500167</v>
       </c>
       <c r="L14">
-        <v>-0.052892333265037769</v>
+        <v>-6.5022547779576665e-05</v>
       </c>
       <c r="M14">
-        <v>0.001463547582177516</v>
+        <v>0.00024901328124476291</v>
       </c>
       <c r="N14">
-        <v>0.0061305279915795522</v>
+        <v>-0.015661080489898179</v>
       </c>
       <c r="O14">
-        <v>0.78004631295220961</v>
+        <v>0.0021295452507010832</v>
       </c>
       <c r="P14">
-        <v>-0.014816684952673548</v>
+        <v>-3.5281412177833615e-05</v>
       </c>
       <c r="Q14">
-        <v>0.00024609623347665241</v>
+        <v>0.0014784177506935049</v>
       </c>
       <c r="R14">
-        <v>-0.034850580696924482</v>
-      </c>
-      <c r="S14">
-        <v>0.68940785937921678</v>
+        <v>-0.02973456094953475</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B15">
-        <v>0.71898666183229454</v>
+        <v>-0.010050128997704024</v>
       </c>
       <c r="C15">
-        <v>0.00034517945257483984</v>
+        <v>-4.4698298881771349e-06</v>
       </c>
       <c r="D15">
-        <v>0.0012489417495879561</v>
+        <v>-2.1933951192738993e-05</v>
       </c>
       <c r="E15">
-        <v>-2.3356952482577525e-05</v>
+        <v>4.2802073430867914e-07</v>
       </c>
       <c r="F15">
-        <v>0.00078184918466903553</v>
+        <v>-1.097974502253118e-05</v>
       </c>
       <c r="G15">
-        <v>0.001083322222903917</v>
+        <v>-1.6272063434050882e-05</v>
       </c>
       <c r="H15">
-        <v>0.00079163275171501533</v>
+        <v>-1.207128037805839e-05</v>
       </c>
       <c r="I15">
-        <v>0.0006419821466063071</v>
+        <v>-9.3775546338557174e-06</v>
       </c>
       <c r="J15">
-        <v>0.00035108136568654056</v>
+        <v>-5.2853895708522764e-06</v>
       </c>
       <c r="K15">
-        <v>0.00079902019737406339</v>
+        <v>-1.2015752453627834e-05</v>
       </c>
       <c r="L15">
-        <v>-0.00016351676263185594</v>
+        <v>9.4685681341809306e-07</v>
       </c>
       <c r="M15">
-        <v>2.9763659789035614e-06</v>
+        <v>-4.1737864785901347e-06</v>
       </c>
       <c r="N15">
-        <v>0.00020306282943048453</v>
+        <v>0.00026578374927163423</v>
       </c>
       <c r="O15">
-        <v>-0.014816684952673548</v>
+        <v>-3.5281412177833615e-05</v>
       </c>
       <c r="P15">
-        <v>0.002109984982179645</v>
+        <v>6.1088000719465977e-07</v>
       </c>
       <c r="Q15">
-        <v>-3.4958262999321722e-05</v>
+        <v>-2.2395519491194912e-05</v>
       </c>
       <c r="R15">
-        <v>0.0014626462374035636</v>
-      </c>
-      <c r="S15">
-        <v>-0.028663026869547571</v>
+        <v>0.00047793267522489935</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B16">
-        <v>-0.010089679546184413</v>
+        <v>0.38880775015687302</v>
       </c>
       <c r="C16">
-        <v>-4.3585590347688733e-06</v>
+        <v>0.0011274229937864068</v>
       </c>
       <c r="D16">
-        <v>-2.1883601159983474e-05</v>
+        <v>0.00080307930557372599</v>
       </c>
       <c r="E16">
-        <v>4.2796717183586185e-07</v>
+        <v>-1.2322930923123847e-05</v>
       </c>
       <c r="F16">
-        <v>-1.0786541446868475e-05</v>
+        <v>0.029496654528626518</v>
       </c>
       <c r="G16">
-        <v>-1.5999396080784822e-05</v>
+        <v>0.029657776556731803</v>
       </c>
       <c r="H16">
-        <v>-1.1818615921872845e-05</v>
+        <v>0.029371102133802909</v>
       </c>
       <c r="I16">
-        <v>-9.279031428991954e-06</v>
+        <v>0.032722036852653083</v>
       </c>
       <c r="J16">
-        <v>-5.1997567080126045e-06</v>
+        <v>0.02927542196470918</v>
       </c>
       <c r="K16">
-        <v>-1.2013419276710527e-05</v>
+        <v>0.029322022889212766</v>
       </c>
       <c r="L16">
-        <v>3.2277705558795894e-06</v>
+        <v>-6.1216805498152775e-05</v>
       </c>
       <c r="M16">
-        <v>-6.7148394356183032e-08</v>
+        <v>0.0016231405111975777</v>
       </c>
       <c r="N16">
-        <v>-3.4912051564507005e-06</v>
+        <v>-0.039554241119650835</v>
       </c>
       <c r="O16">
-        <v>0.00024609623347665241</v>
+        <v>0.0014784177506935049</v>
       </c>
       <c r="P16">
-        <v>-3.4958262999321722e-05</v>
+        <v>-2.2395519491194912e-05</v>
       </c>
       <c r="Q16">
-        <v>6.0538295384272415e-07</v>
+        <v>0.038214109886157199</v>
       </c>
       <c r="R16">
-        <v>-2.2235865740993305e-05</v>
-      </c>
-      <c r="S16">
-        <v>0.0004548257664344913</v>
+        <v>-0.051435790038815182</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B17">
-        <v>0.38373508100055981</v>
+        <v>-11.711916678161582</v>
       </c>
       <c r="C17">
-        <v>0.0011215947385701391</v>
+        <v>-0.0082017590272386917</v>
       </c>
       <c r="D17">
-        <v>0.00079141467250392825</v>
+        <v>-0.016377558285024796</v>
       </c>
       <c r="E17">
-        <v>-1.2226856217339435e-05</v>
+        <v>0.00029721007302726046</v>
       </c>
       <c r="F17">
-        <v>0.029386620811073593</v>
+        <v>-0.0418243862399231</v>
       </c>
       <c r="G17">
-        <v>0.029567483525021893</v>
+        <v>-0.04492646974378825</v>
       </c>
       <c r="H17">
-        <v>0.029260694782256444</v>
+        <v>-0.040116283798193236</v>
       </c>
       <c r="I17">
-        <v>0.032654749516482784</v>
+        <v>-0.037883143132607669</v>
       </c>
       <c r="J17">
-        <v>0.029125515018551013</v>
+        <v>-0.034564932597856965</v>
       </c>
       <c r="K17">
-        <v>0.029226311008889498</v>
+        <v>-0.040241020944762687</v>
       </c>
       <c r="L17">
-        <v>-0.00058788877811521284</v>
+        <v>-0.00016066768859581988</v>
       </c>
       <c r="M17">
-        <v>1.4986538893700533e-05</v>
+        <v>-0.0011265997268665451</v>
       </c>
       <c r="N17">
-        <v>0.0015840710192995254</v>
+        <v>0.25821674883469714</v>
       </c>
       <c r="O17">
-        <v>-0.034850580696924482</v>
+        <v>-0.02973456094953475</v>
       </c>
       <c r="P17">
-        <v>0.0014626462374035636</v>
+        <v>0.00047793267522489935</v>
       </c>
       <c r="Q17">
-        <v>-2.2235865740993305e-05</v>
+        <v>-0.051435790038815182</v>
       </c>
       <c r="R17">
-        <v>0.038153668883674365</v>
-      </c>
-      <c r="S17">
-        <v>-0.046668206924535119</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="s">
-        <v>79</v>
-      </c>
-      <c r="B18">
-        <v>-12.878845217387573</v>
-      </c>
-      <c r="C18">
-        <v>-0.0080588512357431929</v>
-      </c>
-      <c r="D18">
-        <v>-0.017346213057188059</v>
-      </c>
-      <c r="E18">
-        <v>0.00030122523417498509</v>
-      </c>
-      <c r="F18">
-        <v>-0.038316511694891656</v>
-      </c>
-      <c r="G18">
-        <v>-0.037907319250174737</v>
-      </c>
-      <c r="H18">
-        <v>-0.035657403591001571</v>
-      </c>
-      <c r="I18">
-        <v>-0.035777194380549757</v>
-      </c>
-      <c r="J18">
-        <v>-0.036013194098387706</v>
-      </c>
-      <c r="K18">
-        <v>-0.037508718657555964</v>
-      </c>
-      <c r="L18">
-        <v>-0.049295193671009457</v>
-      </c>
-      <c r="M18">
-        <v>0.0013674771125605587</v>
-      </c>
-      <c r="N18">
-        <v>0.0031495781414323598</v>
-      </c>
-      <c r="O18">
-        <v>0.68940785937921678</v>
-      </c>
-      <c r="P18">
-        <v>-0.028663026869547571</v>
-      </c>
-      <c r="Q18">
-        <v>0.0004548257664344913</v>
-      </c>
-      <c r="R18">
-        <v>-0.046668206924535119</v>
-      </c>
-      <c r="S18">
-        <v>0.87363656195137507</v>
+        <v>0.47415982739722784</v>
       </c>
     </row>
   </sheetData>

--- a/input/ES/reg_education.xlsx
+++ b/input/ES/reg_education.xlsx
@@ -10,73 +10,143 @@
     <sheet name="Gof" sheetId="2" r:id="rId4"/>
     <sheet name="E1a" sheetId="3" r:id="rId5"/>
     <sheet name="E1b" sheetId="4" r:id="rId6"/>
-    <sheet name="E2a" sheetId="5" r:id="rId7"/>
+    <sheet name="E2a_raw" sheetId="5" r:id="rId7"/>
+    <sheet name="E2a" sheetId="6" r:id="rId8"/>
   </sheets>
   <calcPr calcId="125725" fullCalcOnLoad="true"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="163" uniqueCount="77">
-  <si>
-    <t>Description</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="250" uniqueCount="97">
+  <si>
+    <t>Description:</t>
+  </si>
+  <si>
+    <t>Model parameters governing projection of education status</t>
   </si>
   <si>
     <t>Authors:</t>
   </si>
   <si>
+    <t>Ashley Burdett, Aleksandra Kolndrekaj</t>
+  </si>
+  <si>
     <t>Last edit:</t>
   </si>
   <si>
+    <t>07 Oct. 2026 AK</t>
+  </si>
+  <si>
     <t>Process:</t>
   </si>
   <si>
     <t>E1a</t>
   </si>
   <si>
+    <t>Probit regression estimates of exiting education</t>
+  </si>
+  <si>
     <t>E1b</t>
   </si>
   <si>
+    <t>Probit regression estimates of returning to education</t>
+  </si>
+  <si>
     <t>E2</t>
   </si>
   <si>
+    <t>Generalized ordered logit regression estimates of education attainment - individuals aged 16+ exiting education in t.</t>
+  </si>
+  <si>
     <t>E2a_raw</t>
   </si>
   <si>
+    <t>Raw generalized ordered logit regression estimates of education attainment - individuals aged 16+ exiting education. Useful for the 'Gologit predictor' file.</t>
+  </si>
+  <si>
     <t>Notes:</t>
   </si>
   <si>
-    <t>Modelparametersgoverningproje</t>
-  </si>
-  <si>
-    <t>Ashley Burdett, Aleksandra Kolndrekaj</t>
-  </si>
-  <si>
-    <t>15 June 2016 AK</t>
-  </si>
-  <si>
-    <t>Description:</t>
-  </si>
-  <si>
-    <t>Probit regression estimates of exiting education</t>
-  </si>
-  <si>
-    <t>Probit regression estimates of returning to education</t>
-  </si>
-  <si>
-    <t>Generalized ordered logit regression estimates of education attainment - individuals aged 16+ exiting education in t.</t>
-  </si>
-  <si>
-    <t>Raw generalized ordered logit regression estimates of education attainment - individuals aged 16+ exiting education. Useful for the 'Gologit predictor' file.</t>
-  </si>
-  <si>
     <t>Regions: ES1 =  Noroeste , ES2 = Noreste , ES3 = Madrid , ES4 =  Centro , ES5 = Este , ES6=  Sur , ES7 = ,  Canarias.</t>
   </si>
   <si>
-    <t>Goodnessoffit</t>
-  </si>
-  <si>
-    <t>E1a - Leaving education</t>
+    <t>Goodness of fit</t>
+  </si>
+  <si>
+    <t>REGRESSOR</t>
+  </si>
+  <si>
+    <t>COEFFICIENT</t>
+  </si>
+  <si>
+    <t>Dgn</t>
+  </si>
+  <si>
+    <t>Dag</t>
+  </si>
+  <si>
+    <t>Dag16</t>
+  </si>
+  <si>
+    <t>Dag_knot23</t>
+  </si>
+  <si>
+    <t>Dag_knot26</t>
+  </si>
+  <si>
+    <t>Ded_L1</t>
+  </si>
+  <si>
+    <t>Parents_ypnb_Q2_L1</t>
+  </si>
+  <si>
+    <t>Parents_ypnb_Q3_L1</t>
+  </si>
+  <si>
+    <t>Parents_ypnb_Q4_L1</t>
+  </si>
+  <si>
+    <t>Parents_ypnb_Q5_L1</t>
+  </si>
+  <si>
+    <t>ES1</t>
+  </si>
+  <si>
+    <t>ES2</t>
+  </si>
+  <si>
+    <t>ES3</t>
+  </si>
+  <si>
+    <t>ES4</t>
+  </si>
+  <si>
+    <t>ES5</t>
+  </si>
+  <si>
+    <t>ES6</t>
+  </si>
+  <si>
+    <t>Year_transformed</t>
+  </si>
+  <si>
+    <t>Y2020</t>
+  </si>
+  <si>
+    <t>Y2021</t>
+  </si>
+  <si>
+    <t>Y2022</t>
+  </si>
+  <si>
+    <t>Y2023</t>
+  </si>
+  <si>
+    <t>Constant</t>
+  </si>
+  <si>
+    <t>E1a - Remain in education</t>
   </si>
   <si>
     <t>Pseudo R-squared</t>
@@ -85,105 +155,12 @@
     <t>N</t>
   </si>
   <si>
-    <t>E1b - Returning to education</t>
-  </si>
-  <si>
-    <t>E2a - Educational attainment</t>
-  </si>
-  <si>
-    <t>B</t>
-  </si>
-  <si>
-    <t>C</t>
-  </si>
-  <si>
-    <t>D</t>
-  </si>
-  <si>
-    <t>E</t>
-  </si>
-  <si>
     <t>Chi^2</t>
   </si>
   <si>
     <t>Log likelihood</t>
   </si>
   <si>
-    <t>F</t>
-  </si>
-  <si>
-    <t>REGRESSOR</t>
-  </si>
-  <si>
-    <t>Dgn</t>
-  </si>
-  <si>
-    <t>Dag</t>
-  </si>
-  <si>
-    <t>Dag16</t>
-  </si>
-  <si>
-    <t>Dag_knot23</t>
-  </si>
-  <si>
-    <t>Dag_knot26</t>
-  </si>
-  <si>
-    <t>Ded_L1</t>
-  </si>
-  <si>
-    <t>Ydses_c5_Q2_L1</t>
-  </si>
-  <si>
-    <t>Ydses_c5_Q3_L1</t>
-  </si>
-  <si>
-    <t>Ydses_c5_Q4_L1</t>
-  </si>
-  <si>
-    <t>Ydses_c5_Q5_L1</t>
-  </si>
-  <si>
-    <t>ES1</t>
-  </si>
-  <si>
-    <t>ES2</t>
-  </si>
-  <si>
-    <t>ES3</t>
-  </si>
-  <si>
-    <t>ES4</t>
-  </si>
-  <si>
-    <t>ES5</t>
-  </si>
-  <si>
-    <t>ES6</t>
-  </si>
-  <si>
-    <t>Year_transformed</t>
-  </si>
-  <si>
-    <t>Y2020</t>
-  </si>
-  <si>
-    <t>Y2021</t>
-  </si>
-  <si>
-    <t>Y2022</t>
-  </si>
-  <si>
-    <t>Y2023</t>
-  </si>
-  <si>
-    <t>Constant</t>
-  </si>
-  <si>
-    <t>COEFFICIENT</t>
-  </si>
-  <si>
     <t>Dag_sq</t>
   </si>
   <si>
@@ -202,6 +179,87 @@
     <t>Dnc1_plus_L1</t>
   </si>
   <si>
+    <t>Parents_known_L1</t>
+  </si>
+  <si>
+    <t>Parents_known_Ydses_Q2_L1</t>
+  </si>
+  <si>
+    <t>Parents_known_Ydses_Q3_L1</t>
+  </si>
+  <si>
+    <t>Parents_known_Ydses_Q4_L1</t>
+  </si>
+  <si>
+    <t>Parents_known_Ydses_Q5_L1</t>
+  </si>
+  <si>
+    <t>E1b - Return to education</t>
+  </si>
+  <si>
+    <t>Low</t>
+  </si>
+  <si>
+    <t>Medium</t>
+  </si>
+  <si>
+    <t>0b.Dgn</t>
+  </si>
+  <si>
+    <t>1.Dgn</t>
+  </si>
+  <si>
+    <t>0b.ES1</t>
+  </si>
+  <si>
+    <t>1.ES1</t>
+  </si>
+  <si>
+    <t>0b.ES2</t>
+  </si>
+  <si>
+    <t>1.ES2</t>
+  </si>
+  <si>
+    <t>0b.ES3</t>
+  </si>
+  <si>
+    <t>1.ES3</t>
+  </si>
+  <si>
+    <t>0b.ES4</t>
+  </si>
+  <si>
+    <t>1.ES4</t>
+  </si>
+  <si>
+    <t>0b.ES5</t>
+  </si>
+  <si>
+    <t>1.ES5</t>
+  </si>
+  <si>
+    <t>0b.ES6</t>
+  </si>
+  <si>
+    <t>1.ES6</t>
+  </si>
+  <si>
+    <t>0b.ES7</t>
+  </si>
+  <si>
+    <t>1o.ES7</t>
+  </si>
+  <si>
+    <t>_cons</t>
+  </si>
+  <si>
+    <t>y1</t>
+  </si>
+  <si>
+    <t>CATEGORY</t>
+  </si>
+  <si>
     <t>Dgn_</t>
   </si>
   <si>
@@ -248,16 +306,625 @@
   </si>
   <si>
     <t>Constant_Medium</t>
+  </si>
+  <si>
+    <t>E2 - Education attainment</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <fonts count="1">
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
+  <fonts count="150">
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
     </font>
   </fonts>
   <fills count="2">
@@ -268,7 +935,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="140">
     <border>
       <left/>
       <right/>
@@ -276,12 +943,1541 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="140">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="19" fillId="0" borderId="10" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="20" fillId="0" borderId="11" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="21" fillId="0" borderId="12" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="22" fillId="0" borderId="13" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="23" fillId="0" borderId="14" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="24" fillId="0" borderId="15" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="25" fillId="0" borderId="16" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="26" fillId="0" borderId="17" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="27" fillId="0" borderId="18" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="28" fillId="0" borderId="19" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="29" fillId="0" borderId="20" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="30" fillId="0" borderId="21" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="31" fillId="0" borderId="22" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="32" fillId="0" borderId="23" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="33" fillId="0" borderId="24" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="34" fillId="0" borderId="25" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="35" fillId="0" borderId="26" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="36" fillId="0" borderId="27" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="37" fillId="0" borderId="28" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="38" fillId="0" borderId="29" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="39" fillId="0" borderId="30" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="40" fillId="0" borderId="31" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="41" fillId="0" borderId="32" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="42" fillId="0" borderId="33" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="43" fillId="0" borderId="34" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="44" fillId="0" borderId="35" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="45" fillId="0" borderId="36" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="46" fillId="0" borderId="37" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="47" fillId="0" borderId="38" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="48" fillId="0" borderId="39" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="49" fillId="0" borderId="40" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="50" fillId="0" borderId="41" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="51" fillId="0" borderId="42" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="52" fillId="0" borderId="43" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="53" fillId="0" borderId="44" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="54" fillId="0" borderId="45" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="55" fillId="0" borderId="46" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="56" fillId="0" borderId="47" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="57" fillId="0" borderId="48" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="58" fillId="0" borderId="49" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="59" fillId="0" borderId="50" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="60" fillId="0" borderId="51" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="61" fillId="0" borderId="52" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="62" fillId="0" borderId="53" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="63" fillId="0" borderId="54" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="64" fillId="0" borderId="55" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="65" fillId="0" borderId="56" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="66" fillId="0" borderId="57" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="67" fillId="0" borderId="58" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="68" fillId="0" borderId="59" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="69" fillId="0" borderId="60" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="70" fillId="0" borderId="61" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="71" fillId="0" borderId="62" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="72" fillId="0" borderId="63" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="73" fillId="0" borderId="64" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="74" fillId="0" borderId="65" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="75" fillId="0" borderId="66" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="76" fillId="0" borderId="67" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="77" fillId="0" borderId="68" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="78" fillId="0" borderId="69" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="79" fillId="0" borderId="70" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="80" fillId="0" borderId="71" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="81" fillId="0" borderId="72" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="82" fillId="0" borderId="73" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="83" fillId="0" borderId="74" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="84" fillId="0" borderId="75" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="85" fillId="0" borderId="76" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="86" fillId="0" borderId="77" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="87" fillId="0" borderId="78" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="88" fillId="0" borderId="79" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="89" fillId="0" borderId="80" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="90" fillId="0" borderId="81" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="91" fillId="0" borderId="82" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="92" fillId="0" borderId="83" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="93" fillId="0" borderId="84" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="94" fillId="0" borderId="85" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="95" fillId="0" borderId="86" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="96" fillId="0" borderId="87" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="97" fillId="0" borderId="88" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="98" fillId="0" borderId="89" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="99" fillId="0" borderId="90" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="100" fillId="0" borderId="91" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="101" fillId="0" borderId="92" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="102" fillId="0" borderId="93" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="103" fillId="0" borderId="94" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="104" fillId="0" borderId="95" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="105" fillId="0" borderId="96" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="106" fillId="0" borderId="97" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="107" fillId="0" borderId="98" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="108" fillId="0" borderId="99" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="109" fillId="0" borderId="100" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="110" fillId="0" borderId="101" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="111" fillId="0" borderId="102" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="112" fillId="0" borderId="103" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="113" fillId="0" borderId="104" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="114" fillId="0" borderId="105" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="115" fillId="0" borderId="106" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="116" fillId="0" borderId="107" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="117" fillId="0" borderId="108" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="118" fillId="0" borderId="109" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="119" fillId="0" borderId="110" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="120" fillId="0" borderId="111" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="121" fillId="0" borderId="112" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="122" fillId="0" borderId="113" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="123" fillId="0" borderId="114" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="124" fillId="0" borderId="115" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="125" fillId="0" borderId="116" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="126" fillId="0" borderId="117" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="127" fillId="0" borderId="118" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="128" fillId="0" borderId="119" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="129" fillId="0" borderId="120" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="130" fillId="0" borderId="121" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="131" fillId="0" borderId="122" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="132" fillId="0" borderId="123" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="133" fillId="0" borderId="124" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="134" fillId="0" borderId="125" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="135" fillId="0" borderId="126" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="136" fillId="0" borderId="127" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="137" fillId="0" borderId="128" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="138" fillId="0" borderId="129" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="139" fillId="0" borderId="130" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="140" fillId="0" borderId="131" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="141" fillId="0" borderId="132" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="142" fillId="0" borderId="133" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="143" fillId="0" borderId="134" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="144" fillId="0" borderId="135" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="145" fillId="0" borderId="136" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="146" fillId="0" borderId="137" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="147" fillId="0" borderId="138" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="149" fillId="0" borderId="139" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -295,75 +2491,75 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="s">
-        <v>1</v>
+      <c r="A2" s="2" t="s">
+        <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="s">
-        <v>2</v>
+      <c r="A3" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" t="s">
-        <v>12</v>
+      <c r="A5" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B6" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="B8" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="B9" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B11" t="s">
         <v>16</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="s">
-        <v>8</v>
-      </c>
-      <c r="B11" t="s">
-        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -372,177 +2568,112 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D1" t="s">
-        <v>26</v>
-      </c>
-      <c r="E1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="B2"/>
-      <c r="C2"/>
-      <c r="D2"/>
-      <c r="F2"/>
+      <c r="A1" s="7" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" t="s">
-        <v>19</v>
-      </c>
-      <c r="B3"/>
-      <c r="C3"/>
-      <c r="D3"/>
-      <c r="F3"/>
+      <c r="A3" s="8" t="s">
+        <v>42</v>
+      </c>
     </row>
     <row r="4">
-      <c r="B4"/>
-      <c r="C4"/>
-      <c r="D4"/>
-      <c r="F4"/>
+      <c r="A4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B4">
+        <v>0.12672954670656989</v>
+      </c>
+      <c r="E4" t="s">
+        <v>45</v>
+      </c>
+      <c r="F4">
+        <v>1823.9152379507227</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>20</v>
+        <v>44</v>
       </c>
       <c r="B5">
-        <v>0.12245459918360735</v>
-      </c>
-      <c r="C5"/>
-      <c r="D5"/>
+        <v>25554</v>
+      </c>
       <c r="E5" t="s">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="F5">
-        <v>1760.2718418765032</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="s">
-        <v>21</v>
-      </c>
-      <c r="B6">
-        <v>25974</v>
-      </c>
-      <c r="C6"/>
-      <c r="D6"/>
-      <c r="E6" t="s">
-        <v>29</v>
-      </c>
-      <c r="F6">
-        <v>-16413939.267560342</v>
+        <v>-15943565.892963625</v>
       </c>
     </row>
     <row r="7">
-      <c r="B7"/>
-      <c r="C7"/>
-      <c r="D7"/>
-      <c r="F7"/>
+      <c r="A7" s="9" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>22</v>
-      </c>
-      <c r="B8"/>
-      <c r="C8"/>
-      <c r="D8"/>
-      <c r="F8"/>
+        <v>43</v>
+      </c>
+      <c r="B8">
+        <v>0.57222806617156152</v>
+      </c>
+      <c r="E8" t="s">
+        <v>45</v>
+      </c>
+      <c r="F8">
+        <v>4428.8387179836263</v>
+      </c>
     </row>
     <row r="9">
-      <c r="B9"/>
-      <c r="C9"/>
-      <c r="D9"/>
-      <c r="F9"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="s">
-        <v>20</v>
-      </c>
-      <c r="B10">
-        <v>0.56996282811306831</v>
-      </c>
-      <c r="C10"/>
-      <c r="D10"/>
-      <c r="E10" t="s">
-        <v>28</v>
-      </c>
-      <c r="F10">
-        <v>4403.7871942301008</v>
+      <c r="A9" t="s">
+        <v>44</v>
+      </c>
+      <c r="B9">
+        <v>192146</v>
+      </c>
+      <c r="E9" t="s">
+        <v>46</v>
+      </c>
+      <c r="F9">
+        <v>-10735290.422776602</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="s">
-        <v>21</v>
-      </c>
-      <c r="B11">
-        <v>192146</v>
-      </c>
-      <c r="C11"/>
-      <c r="D11"/>
-      <c r="E11" t="s">
-        <v>29</v>
-      </c>
-      <c r="F11">
-        <v>-10792138.445079073</v>
+      <c r="A11" s="139" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="12">
-      <c r="B12"/>
-      <c r="C12"/>
-      <c r="D12"/>
-      <c r="F12"/>
+      <c r="A12" t="s">
+        <v>43</v>
+      </c>
+      <c r="B12">
+        <v>0.18790239160332234</v>
+      </c>
+      <c r="E12" t="s">
+        <v>45</v>
+      </c>
+      <c r="F12">
+        <v>894.99991527980148</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>23</v>
-      </c>
-      <c r="B13"/>
-      <c r="C13"/>
-      <c r="D13"/>
-      <c r="F13"/>
-    </row>
-    <row r="14">
-      <c r="B14"/>
-      <c r="C14"/>
-      <c r="D14"/>
-      <c r="F14"/>
-    </row>
-    <row r="15">
-      <c r="A15" t="s">
-        <v>20</v>
-      </c>
-      <c r="B15">
-        <v>0.18790239160332234</v>
-      </c>
-      <c r="C15"/>
-      <c r="D15"/>
-      <c r="F15"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="s">
-        <v>21</v>
-      </c>
-      <c r="B16">
+        <v>44</v>
+      </c>
+      <c r="B13">
         <v>5852</v>
       </c>
-      <c r="C16"/>
-      <c r="D16"/>
-      <c r="F16"/>
+      <c r="E13" t="s">
+        <v>46</v>
+      </c>
+      <c r="F13">
+        <v>-5187.4466404954601</v>
+      </c>
     </row>
   </sheetData>
 </worksheet>
@@ -555,1704 +2686,1704 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H1" t="s">
+        <v>25</v>
+      </c>
+      <c r="I1" t="s">
+        <v>26</v>
+      </c>
+      <c r="J1" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" t="s">
+        <v>28</v>
+      </c>
+      <c r="L1" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1" t="s">
+        <v>30</v>
+      </c>
+      <c r="N1" t="s">
         <v>31</v>
       </c>
-      <c r="B1" t="s">
-        <v>54</v>
-      </c>
-      <c r="C1" t="s">
+      <c r="O1" t="s">
         <v>32</v>
       </c>
-      <c r="D1" t="s">
+      <c r="P1" t="s">
         <v>33</v>
       </c>
-      <c r="E1" t="s">
+      <c r="Q1" t="s">
         <v>34</v>
       </c>
-      <c r="F1" t="s">
+      <c r="R1" t="s">
         <v>35</v>
       </c>
-      <c r="G1" t="s">
+      <c r="S1" t="s">
         <v>36</v>
       </c>
-      <c r="H1" t="s">
+      <c r="T1" t="s">
         <v>37</v>
       </c>
-      <c r="I1" t="s">
+      <c r="U1" t="s">
         <v>38</v>
       </c>
-      <c r="J1" t="s">
+      <c r="V1" t="s">
         <v>39</v>
       </c>
-      <c r="K1" t="s">
+      <c r="W1" t="s">
         <v>40</v>
       </c>
-      <c r="L1" t="s">
+      <c r="X1" t="s">
         <v>41</v>
-      </c>
-      <c r="M1" t="s">
-        <v>42</v>
-      </c>
-      <c r="N1" t="s">
-        <v>43</v>
-      </c>
-      <c r="O1" t="s">
-        <v>44</v>
-      </c>
-      <c r="P1" t="s">
-        <v>45</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>46</v>
-      </c>
-      <c r="R1" t="s">
-        <v>47</v>
-      </c>
-      <c r="S1" t="s">
-        <v>48</v>
-      </c>
-      <c r="T1" t="s">
-        <v>49</v>
-      </c>
-      <c r="U1" t="s">
-        <v>50</v>
-      </c>
-      <c r="V1" t="s">
-        <v>51</v>
-      </c>
-      <c r="W1" t="s">
-        <v>52</v>
-      </c>
-      <c r="X1" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="B2">
-        <v>-0.11646956735264642</v>
+        <v>-0.12402958755245555</v>
       </c>
       <c r="C2">
-        <v>0.00059808908876510659</v>
+        <v>0.00061174748940995901</v>
       </c>
       <c r="D2">
-        <v>1.9488103395676283e-06</v>
+        <v>2.4606642822821185e-06</v>
       </c>
       <c r="E2">
-        <v>-5.133875874763818e-05</v>
+        <v>-4.3012505890037097e-05</v>
       </c>
       <c r="F2">
-        <v>-7.3625945037398838e-06</v>
+        <v>-7.6448826259477641e-06</v>
       </c>
       <c r="G2">
-        <v>1.1054460435203857e-05</v>
+        <v>9.9654577685575034e-06</v>
       </c>
       <c r="H2">
-        <v>1.276518845022195e-05</v>
+        <v>1.598153328698391e-05</v>
       </c>
       <c r="I2">
-        <v>-1.1380726729727655e-05</v>
+        <v>-1.2772582500299141e-05</v>
       </c>
       <c r="J2">
-        <v>5.8306440264823242e-07</v>
+        <v>-3.5422218223687087e-06</v>
       </c>
       <c r="K2">
-        <v>2.5552427083685517e-05</v>
+        <v>3.2978994319333706e-06</v>
       </c>
       <c r="L2">
-        <v>-2.3270957972627249e-05</v>
+        <v>-4.4449912862167863e-05</v>
       </c>
       <c r="M2">
-        <v>-2.8260875892740665e-05</v>
+        <v>-2.5746311260147045e-05</v>
       </c>
       <c r="N2">
-        <v>-4.5332756772375213e-05</v>
+        <v>-3.5582438365392528e-05</v>
       </c>
       <c r="O2">
-        <v>-2.6030787126567166e-05</v>
+        <v>-2.5106763894690355e-05</v>
       </c>
       <c r="P2">
-        <v>-3.1951245269935119e-05</v>
+        <v>-3.6222986160605792e-05</v>
       </c>
       <c r="Q2">
-        <v>-5.507550833823332e-05</v>
+        <v>-5.5585708463225874e-05</v>
       </c>
       <c r="R2">
-        <v>-5.5041332143276523e-05</v>
+        <v>-6.1044172642558365e-05</v>
       </c>
       <c r="S2">
-        <v>-1.38405756557253e-06</v>
+        <v>-1.5770969190706375e-06</v>
       </c>
       <c r="T2">
-        <v>7.3249055982587763e-06</v>
+        <v>1.7556077563059714e-05</v>
       </c>
       <c r="U2">
-        <v>-1.7092488571668567e-05</v>
+        <v>-1.1805420377914614e-05</v>
       </c>
       <c r="V2">
-        <v>-1.6752814167593104e-05</v>
+        <v>-2.58876823041253e-05</v>
       </c>
       <c r="W2">
-        <v>2.9231494845983084e-05</v>
+        <v>2.3650241363173323e-05</v>
       </c>
       <c r="X2">
-        <v>-0.0002720611607212399</v>
+        <v>-0.00027813983859165082</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="B3">
-        <v>-0.14614507498297236</v>
+        <v>-0.17445775137089106</v>
       </c>
       <c r="C3">
-        <v>1.9488103395676283e-06</v>
+        <v>2.4606642822821185e-06</v>
       </c>
       <c r="D3">
-        <v>8.7505451891110967e-05</v>
+        <v>6.7616834179704097e-05</v>
       </c>
       <c r="E3">
-        <v>0.0002969872437400033</v>
+        <v>0.00030370544128701705</v>
       </c>
       <c r="F3">
-        <v>-0.00017985299107891681</v>
+        <v>-0.00014944524682805667</v>
       </c>
       <c r="G3">
-        <v>0.00010979551085336763</v>
+        <v>0.00010012683258861265</v>
       </c>
       <c r="H3">
-        <v>-4.4548407069825108e-05</v>
+        <v>-5.1700096511420881e-05</v>
       </c>
       <c r="I3">
-        <v>-1.9584188272895654e-06</v>
+        <v>-9.3974975980766398e-06</v>
       </c>
       <c r="J3">
-        <v>8.6106860369117861e-05</v>
+        <v>-6.901679220770279e-06</v>
       </c>
       <c r="K3">
-        <v>0.0001716893785905782</v>
+        <v>-1.1513016232360179e-05</v>
       </c>
       <c r="L3">
-        <v>0.00018096839143208948</v>
+        <v>-1.276979182951042e-05</v>
       </c>
       <c r="M3">
-        <v>-2.0346613448131564e-05</v>
+        <v>-1.1489674940820191e-05</v>
       </c>
       <c r="N3">
-        <v>-2.9005552255030684e-05</v>
+        <v>-9.0078583115931355e-06</v>
       </c>
       <c r="O3">
-        <v>-2.8957396012170241e-05</v>
+        <v>-1.0023238446408081e-05</v>
       </c>
       <c r="P3">
-        <v>-1.5986335605171643e-05</v>
+        <v>-1.0842713673929146e-05</v>
       </c>
       <c r="Q3">
-        <v>-1.6281221913368787e-05</v>
+        <v>-2.0069550829815544e-06</v>
       </c>
       <c r="R3">
-        <v>-7.0016122684143499e-06</v>
+        <v>-6.3983897796500867e-06</v>
       </c>
       <c r="S3">
-        <v>1.5976973339831922e-06</v>
+        <v>6.0966643171010346e-07</v>
       </c>
       <c r="T3">
-        <v>-2.9307829013420096e-06</v>
+        <v>3.0718429161282791e-06</v>
       </c>
       <c r="U3">
-        <v>-2.1846187251463271e-05</v>
+        <v>-1.3147093236602034e-05</v>
       </c>
       <c r="V3">
-        <v>-1.6207183915359466e-05</v>
+        <v>-1.1900936198789463e-05</v>
       </c>
       <c r="W3">
-        <v>-8.1051178447871016e-06</v>
+        <v>-1.1605111834885192e-05</v>
       </c>
       <c r="X3">
-        <v>-0.0017893630481715995</v>
+        <v>-0.0013253437196956203</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="B4">
-        <v>-1.5367459549832458</v>
+        <v>-1.5246444450986871</v>
       </c>
       <c r="C4">
-        <v>-5.133875874763818e-05</v>
+        <v>-4.3012505890037097e-05</v>
       </c>
       <c r="D4">
-        <v>0.0002969872437400033</v>
+        <v>0.00030370544128701705</v>
       </c>
       <c r="E4">
-        <v>0.0025329483324169704</v>
+        <v>0.0024286471640415008</v>
       </c>
       <c r="F4">
-        <v>-0.00055064812366191777</v>
+        <v>-0.00056062670224766751</v>
       </c>
       <c r="G4">
-        <v>0.00019991832954099296</v>
+        <v>0.00021233968060765951</v>
       </c>
       <c r="H4">
-        <v>-0.00050607386823679963</v>
+        <v>-0.00048965597672222846</v>
       </c>
       <c r="I4">
-        <v>-5.6401825943824379e-06</v>
+        <v>-1.19422263434438e-05</v>
       </c>
       <c r="J4">
-        <v>-0.00013543146612350092</v>
+        <v>-1.4219209410142649e-05</v>
       </c>
       <c r="K4">
-        <v>-0.00023624392555496158</v>
+        <v>-3.649924127333763e-05</v>
       </c>
       <c r="L4">
-        <v>-0.00019054510654706097</v>
+        <v>-1.5433253778550718e-05</v>
       </c>
       <c r="M4">
-        <v>-8.6660424805947919e-05</v>
+        <v>-7.5433770497203116e-05</v>
       </c>
       <c r="N4">
-        <v>-3.8107708286064679e-05</v>
+        <v>-5.2741367637693538e-05</v>
       </c>
       <c r="O4">
-        <v>-5.5452482649360254e-05</v>
+        <v>-6.2753248789853221e-05</v>
       </c>
       <c r="P4">
-        <v>-4.7962815156179887e-05</v>
+        <v>-4.8389903728097376e-05</v>
       </c>
       <c r="Q4">
-        <v>-3.743478803600236e-05</v>
+        <v>-3.0986065076053749e-05</v>
       </c>
       <c r="R4">
-        <v>-6.3839353967824883e-06</v>
+        <v>1.3605179064194654e-05</v>
       </c>
       <c r="S4">
-        <v>2.6620169559592562e-06</v>
+        <v>3.0644012190644111e-06</v>
       </c>
       <c r="T4">
-        <v>7.2169135818662272e-05</v>
+        <v>4.4279422728230392e-05</v>
       </c>
       <c r="U4">
-        <v>-0.00019094319503624177</v>
+        <v>-0.0002146114912879331</v>
       </c>
       <c r="V4">
-        <v>-0.0001347416131791707</v>
+        <v>-0.00015189565455492934</v>
       </c>
       <c r="W4">
-        <v>-0.00012367314094885429</v>
+        <v>-0.00013066645318122604</v>
       </c>
       <c r="X4">
-        <v>-0.0057960402472572135</v>
+        <v>-0.0059720843048415</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="B5">
-        <v>-0.044988002485590636</v>
+        <v>0.0060212345424837397</v>
       </c>
       <c r="C5">
-        <v>-7.3625945037398838e-06</v>
+        <v>-7.6448826259477641e-06</v>
       </c>
       <c r="D5">
-        <v>-0.00017985299107891681</v>
+        <v>-0.00014944524682805667</v>
       </c>
       <c r="E5">
-        <v>-0.00055064812366191777</v>
+        <v>-0.00056062670224766751</v>
       </c>
       <c r="F5">
-        <v>0.00064926099893205624</v>
+        <v>0.00062183428198028063</v>
       </c>
       <c r="G5">
-        <v>-0.00086434271039442497</v>
+        <v>-0.00090995849280878715</v>
       </c>
       <c r="H5">
-        <v>9.241398027864966e-05</v>
+        <v>0.00010020530679492298</v>
       </c>
       <c r="I5">
-        <v>-1.3342616587056269e-05</v>
+        <v>-1.464683248604754e-05</v>
       </c>
       <c r="J5">
-        <v>-0.00015507156521237374</v>
+        <v>-1.8162087622380712e-06</v>
       </c>
       <c r="K5">
-        <v>-0.00027577076972511399</v>
+        <v>2.6648522384365033e-05</v>
       </c>
       <c r="L5">
-        <v>-0.00029455272036834078</v>
+        <v>2.4232917341440556e-05</v>
       </c>
       <c r="M5">
-        <v>2.7561426761518217e-05</v>
+        <v>2.8333554113440639e-06</v>
       </c>
       <c r="N5">
-        <v>4.9639587999507784e-05</v>
+        <v>3.611399712493725e-06</v>
       </c>
       <c r="O5">
-        <v>4.4597633397449894e-05</v>
+        <v>1.3076873825762394e-06</v>
       </c>
       <c r="P5">
-        <v>3.2084103206722614e-05</v>
+        <v>8.4418283834808254e-06</v>
       </c>
       <c r="Q5">
-        <v>2.8403179923142725e-05</v>
+        <v>-5.8165376174466139e-06</v>
       </c>
       <c r="R5">
-        <v>2.8613473755967377e-05</v>
+        <v>1.8479230313117438e-05</v>
       </c>
       <c r="S5">
-        <v>-2.8981748534000543e-06</v>
+        <v>-1.202750410494309e-06</v>
       </c>
       <c r="T5">
-        <v>3.5884766545517515e-05</v>
+        <v>2.6300176602169888e-05</v>
       </c>
       <c r="U5">
-        <v>3.8019498947896647e-05</v>
+        <v>2.4995248953911319e-05</v>
       </c>
       <c r="V5">
-        <v>3.0326767678386145e-05</v>
+        <v>2.0715671599554433e-05</v>
       </c>
       <c r="W5">
-        <v>2.7223854920857679e-06</v>
+        <v>9.8170271323840853e-06</v>
       </c>
       <c r="X5">
-        <v>0.0035628364151353877</v>
+        <v>0.0028493231277876867</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="B6">
-        <v>0.26555097545693584</v>
+        <v>0.23211445041900672</v>
       </c>
       <c r="C6">
-        <v>1.1054460435203857e-05</v>
+        <v>9.9654577685575034e-06</v>
       </c>
       <c r="D6">
-        <v>0.00010979551085336763</v>
+        <v>0.00010012683258861265</v>
       </c>
       <c r="E6">
-        <v>0.00019991832954099296</v>
+        <v>0.00021233968060765951</v>
       </c>
       <c r="F6">
-        <v>-0.00086434271039442497</v>
+        <v>-0.00090995849280878715</v>
       </c>
       <c r="G6">
-        <v>0.0026977055473326513</v>
+        <v>0.003048428738770966</v>
       </c>
       <c r="H6">
-        <v>0.00032812130002539235</v>
+        <v>0.0003401964006983274</v>
       </c>
       <c r="I6">
-        <v>4.5442728520343745e-05</v>
+        <v>5.6394758381411736e-05</v>
       </c>
       <c r="J6">
-        <v>0.00011102661297750501</v>
+        <v>8.0408397376759272e-05</v>
       </c>
       <c r="K6">
-        <v>0.00013518379020379816</v>
+        <v>1.5010532132299251e-05</v>
       </c>
       <c r="L6">
-        <v>0.00015367850324260728</v>
+        <v>3.5938118401467349e-05</v>
       </c>
       <c r="M6">
-        <v>4.883848170320667e-07</v>
+        <v>5.6186159433561792e-05</v>
       </c>
       <c r="N6">
-        <v>-2.9234180232962613e-06</v>
+        <v>6.7018108063702587e-05</v>
       </c>
       <c r="O6">
-        <v>4.6112438096655045e-06</v>
+        <v>6.9527841905245497e-05</v>
       </c>
       <c r="P6">
-        <v>7.6525541569424753e-06</v>
+        <v>7.1903940157519225e-05</v>
       </c>
       <c r="Q6">
-        <v>1.7903599447417527e-05</v>
+        <v>0.00010100168728186917</v>
       </c>
       <c r="R6">
-        <v>-3.4351594892887186e-05</v>
+        <v>9.8317923525409142e-06</v>
       </c>
       <c r="S6">
-        <v>2.152890091293391e-06</v>
+        <v>5.4457719796947412e-07</v>
       </c>
       <c r="T6">
-        <v>-1.3862526754995427e-05</v>
+        <v>-1.1251497669129097e-05</v>
       </c>
       <c r="U6">
-        <v>1.1628737978713679e-05</v>
+        <v>2.5058937526433199e-05</v>
       </c>
       <c r="V6">
-        <v>3.8686227267573483e-05</v>
+        <v>5.0265756194492733e-05</v>
       </c>
       <c r="W6">
-        <v>4.4736235413993827e-05</v>
+        <v>3.8311737595499943e-05</v>
       </c>
       <c r="X6">
-        <v>-0.0024553318173381788</v>
+        <v>-0.0022778149710759176</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="B7">
-        <v>0.18353393272523935</v>
+        <v>0.16609156248120502</v>
       </c>
       <c r="C7">
-        <v>1.276518845022195e-05</v>
+        <v>1.598153328698391e-05</v>
       </c>
       <c r="D7">
-        <v>-4.4548407069825108e-05</v>
+        <v>-5.1700096511420881e-05</v>
       </c>
       <c r="E7">
-        <v>-0.00050607386823679963</v>
+        <v>-0.00048965597672222846</v>
       </c>
       <c r="F7">
-        <v>9.241398027864966e-05</v>
+        <v>0.00010020530679492298</v>
       </c>
       <c r="G7">
-        <v>0.00032812130002539235</v>
+        <v>0.0003401964006983274</v>
       </c>
       <c r="H7">
-        <v>0.001267014578580981</v>
+        <v>0.0012930791258197519</v>
       </c>
       <c r="I7">
-        <v>1.6182760257900449e-05</v>
+        <v>2.2915656025814828e-06</v>
       </c>
       <c r="J7">
-        <v>5.3585217095280612e-05</v>
+        <v>-2.8167463375043851e-05</v>
       </c>
       <c r="K7">
-        <v>0.00011228267061366071</v>
+        <v>-3.4036442622036792e-05</v>
       </c>
       <c r="L7">
-        <v>0.00010453438599147423</v>
+        <v>-4.7327306429370433e-07</v>
       </c>
       <c r="M7">
-        <v>-1.655286905757322e-05</v>
+        <v>-2.0057084075742612e-05</v>
       </c>
       <c r="N7">
-        <v>-8.1647099933679481e-05</v>
+        <v>-8.3242766044292263e-05</v>
       </c>
       <c r="O7">
-        <v>-6.6109622909688688e-05</v>
+        <v>-6.1483251100337823e-05</v>
       </c>
       <c r="P7">
-        <v>-5.6415696520949378e-05</v>
+        <v>-6.0756499646795657e-05</v>
       </c>
       <c r="Q7">
-        <v>-7.9633047079400194e-05</v>
+        <v>-7.4636270556813967e-05</v>
       </c>
       <c r="R7">
-        <v>-9.2952006554972454e-05</v>
+        <v>-0.00011302308738673871</v>
       </c>
       <c r="S7">
-        <v>-3.6377221385323801e-07</v>
+        <v>-8.0641397060144938e-07</v>
       </c>
       <c r="T7">
-        <v>-2.5288293787748272e-05</v>
+        <v>-2.1282062764295487e-05</v>
       </c>
       <c r="U7">
-        <v>6.2397455134502534e-05</v>
+        <v>7.6264128911585386e-05</v>
       </c>
       <c r="V7">
-        <v>0.00026217846067737104</v>
+        <v>0.00026102300204844674</v>
       </c>
       <c r="W7">
-        <v>0.0001476501992311943</v>
+        <v>0.00014878328980789574</v>
       </c>
       <c r="X7">
-        <v>-9.8679339674429543e-05</v>
+        <v>7.9267322360968158e-05</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="B8">
-        <v>0.17873273116657199</v>
+        <v>0.18094009937598848</v>
       </c>
       <c r="C8">
-        <v>-1.1380726729727655e-05</v>
+        <v>-1.2772582500299141e-05</v>
       </c>
       <c r="D8">
-        <v>-1.9584188272895654e-06</v>
+        <v>-9.3974975980766398e-06</v>
       </c>
       <c r="E8">
-        <v>-5.6401825943824379e-06</v>
+        <v>-1.19422263434438e-05</v>
       </c>
       <c r="F8">
-        <v>-1.3342616587056269e-05</v>
+        <v>-1.464683248604754e-05</v>
       </c>
       <c r="G8">
-        <v>4.5442728520343745e-05</v>
+        <v>5.6394758381411736e-05</v>
       </c>
       <c r="H8">
-        <v>1.6182760257900449e-05</v>
+        <v>2.2915656025814828e-06</v>
       </c>
       <c r="I8">
-        <v>0.00095619428892731756</v>
+        <v>0.0037478570411809491</v>
       </c>
       <c r="J8">
-        <v>0.00054421907457499622</v>
+        <v>0.002142722971194797</v>
       </c>
       <c r="K8">
-        <v>0.00054076357496786855</v>
+        <v>0.0021402040820084327</v>
       </c>
       <c r="L8">
-        <v>0.00054842434134435051</v>
+        <v>0.0021301367831902127</v>
       </c>
       <c r="M8">
-        <v>-9.0911023812305275e-05</v>
+        <v>-0.00010551003763364128</v>
       </c>
       <c r="N8">
-        <v>-9.8104025494364521e-05</v>
+        <v>-5.5018015909088602e-05</v>
       </c>
       <c r="O8">
-        <v>-0.00013088984251906198</v>
+        <v>-0.00014712609732585522</v>
       </c>
       <c r="P8">
-        <v>-8.4367701777185138e-05</v>
+        <v>-6.2127891726286924e-05</v>
       </c>
       <c r="Q8">
-        <v>-0.00011414253206704439</v>
+        <v>-8.9904909936068563e-05</v>
       </c>
       <c r="R8">
-        <v>-6.0061136065945288e-05</v>
+        <v>-0.00011924536521393239</v>
       </c>
       <c r="S8">
-        <v>5.4920872460212021e-06</v>
+        <v>-4.8275566420469699e-06</v>
       </c>
       <c r="T8">
-        <v>-6.8189978583488664e-05</v>
+        <v>3.1657130322650497e-05</v>
       </c>
       <c r="U8">
-        <v>-8.302228995382926e-06</v>
+        <v>-1.0368296020932701e-05</v>
       </c>
       <c r="V8">
-        <v>2.0405745842343471e-05</v>
+        <v>5.5554802015448117e-05</v>
       </c>
       <c r="W8">
-        <v>-2.9489284404706859e-05</v>
+        <v>-3.148063734246902e-05</v>
       </c>
       <c r="X8">
-        <v>-0.00050938541831626629</v>
+        <v>-0.0017508778824894555</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="B9">
-        <v>0.22834191739231802</v>
+        <v>0.15079169649961585</v>
       </c>
       <c r="C9">
-        <v>5.8306440264823242e-07</v>
+        <v>-3.5422218223687087e-06</v>
       </c>
       <c r="D9">
-        <v>8.6106860369117861e-05</v>
+        <v>-6.901679220770279e-06</v>
       </c>
       <c r="E9">
-        <v>-0.00013543146612350092</v>
+        <v>-1.4219209410142649e-05</v>
       </c>
       <c r="F9">
-        <v>-0.00015507156521237374</v>
+        <v>-1.8162087622380712e-06</v>
       </c>
       <c r="G9">
-        <v>0.00011102661297750501</v>
+        <v>8.0408397376759272e-05</v>
       </c>
       <c r="H9">
-        <v>5.3585217095280612e-05</v>
+        <v>-2.8167463375043851e-05</v>
       </c>
       <c r="I9">
-        <v>0.00054421907457499622</v>
+        <v>0.002142722971194797</v>
       </c>
       <c r="J9">
-        <v>0.0016526193765797176</v>
+        <v>0.0028365692620244106</v>
       </c>
       <c r="K9">
-        <v>0.00096102232650368603</v>
+        <v>0.0021497486261627327</v>
       </c>
       <c r="L9">
-        <v>0.00097540416534114814</v>
+        <v>0.0021474664446985607</v>
       </c>
       <c r="M9">
-        <v>-9.5754157910514937e-05</v>
+        <v>-0.00015941717598920544</v>
       </c>
       <c r="N9">
-        <v>-0.00010272848895685337</v>
+        <v>-0.00015305342442840659</v>
       </c>
       <c r="O9">
-        <v>-0.00010590045680778433</v>
+        <v>-0.00019031270626754509</v>
       </c>
       <c r="P9">
-        <v>-6.6637993258357974e-05</v>
+        <v>-0.00017269794417961381</v>
       </c>
       <c r="Q9">
-        <v>-5.7359153085030144e-05</v>
+        <v>-0.00014006348013744841</v>
       </c>
       <c r="R9">
-        <v>-4.8831376289633452e-05</v>
+        <v>-0.00014383924610398625</v>
       </c>
       <c r="S9">
-        <v>1.0745776938473883e-05</v>
+        <v>-3.3003792521163471e-06</v>
       </c>
       <c r="T9">
-        <v>-2.4628053995732211e-05</v>
+        <v>4.7639297542916665e-05</v>
       </c>
       <c r="U9">
-        <v>-8.9394754522013599e-05</v>
+        <v>-6.3245297835491142e-05</v>
       </c>
       <c r="V9">
-        <v>-3.9732056429816229e-05</v>
+        <v>4.5929130300299305e-06</v>
       </c>
       <c r="W9">
-        <v>-7.3694741155884945e-06</v>
+        <v>-3.469573557110631e-05</v>
       </c>
       <c r="X9">
-        <v>-0.0024940081247746358</v>
+        <v>-0.0017705081935532167</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="B10">
-        <v>0.27539616536036199</v>
+        <v>0.25336598800425975</v>
       </c>
       <c r="C10">
-        <v>2.5552427083685517e-05</v>
+        <v>3.2978994319333706e-06</v>
       </c>
       <c r="D10">
-        <v>0.0001716893785905782</v>
+        <v>-1.1513016232360179e-05</v>
       </c>
       <c r="E10">
-        <v>-0.00023624392555496158</v>
+        <v>-3.649924127333763e-05</v>
       </c>
       <c r="F10">
-        <v>-0.00027577076972511399</v>
+        <v>2.6648522384365033e-05</v>
       </c>
       <c r="G10">
-        <v>0.00013518379020379816</v>
+        <v>1.5010532132299251e-05</v>
       </c>
       <c r="H10">
-        <v>0.00011228267061366071</v>
+        <v>-3.4036442622036792e-05</v>
       </c>
       <c r="I10">
-        <v>0.00054076357496786855</v>
+        <v>0.0021402040820084327</v>
       </c>
       <c r="J10">
-        <v>0.00096102232650368603</v>
+        <v>0.0021497486261627327</v>
       </c>
       <c r="K10">
-        <v>0.0026686344292708372</v>
+        <v>0.0026836411943656404</v>
       </c>
       <c r="L10">
-        <v>0.001400281302828391</v>
+        <v>0.0021717155184656713</v>
       </c>
       <c r="M10">
-        <v>-9.8524181647958401e-05</v>
+        <v>-0.00019184139925232542</v>
       </c>
       <c r="N10">
-        <v>-0.00021499653107708494</v>
+        <v>-0.00022385365882217942</v>
       </c>
       <c r="O10">
-        <v>-0.00021512108826686276</v>
+        <v>-0.00028886904990832311</v>
       </c>
       <c r="P10">
-        <v>-0.00010826604348756954</v>
+        <v>-0.00015576705060110416</v>
       </c>
       <c r="Q10">
-        <v>-0.00017249577446618256</v>
+        <v>-0.0002313892470018166</v>
       </c>
       <c r="R10">
-        <v>-4.8048250963928917e-05</v>
+        <v>-0.00013169470404340028</v>
       </c>
       <c r="S10">
-        <v>8.7703658756554281e-06</v>
+        <v>-8.5650930642155036e-07</v>
       </c>
       <c r="T10">
-        <v>-0.00011598847574612482</v>
+        <v>-3.232025976871453e-05</v>
       </c>
       <c r="U10">
-        <v>-6.4415936709057446e-05</v>
+        <v>-7.7583729965980774e-05</v>
       </c>
       <c r="V10">
-        <v>-1.6449097339529643e-05</v>
+        <v>5.0772160565126659e-05</v>
       </c>
       <c r="W10">
-        <v>3.2206533836783816e-05</v>
+        <v>-3.6900197501263908e-05</v>
       </c>
       <c r="X10">
-        <v>-0.0042406520628242642</v>
+        <v>-0.0016887081948434401</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="B11">
-        <v>0.47327202860990603</v>
+        <v>0.47168682346735069</v>
       </c>
       <c r="C11">
-        <v>-2.3270957972627249e-05</v>
+        <v>-4.4449912862167863e-05</v>
       </c>
       <c r="D11">
-        <v>0.00018096839143208948</v>
+        <v>-1.276979182951042e-05</v>
       </c>
       <c r="E11">
-        <v>-0.00019054510654706097</v>
+        <v>-1.5433253778550718e-05</v>
       </c>
       <c r="F11">
-        <v>-0.00029455272036834078</v>
+        <v>2.4232917341440556e-05</v>
       </c>
       <c r="G11">
-        <v>0.00015367850324260728</v>
+        <v>3.5938118401467349e-05</v>
       </c>
       <c r="H11">
-        <v>0.00010453438599147423</v>
+        <v>-4.7327306429370433e-07</v>
       </c>
       <c r="I11">
-        <v>0.00054842434134435051</v>
+        <v>0.0021301367831902127</v>
       </c>
       <c r="J11">
-        <v>0.00097540416534114814</v>
+        <v>0.0021474664446985607</v>
       </c>
       <c r="K11">
-        <v>0.001400281302828391</v>
+        <v>0.0021717155184656713</v>
       </c>
       <c r="L11">
-        <v>0.0032681242172454975</v>
+        <v>0.0026495970975932196</v>
       </c>
       <c r="M11">
-        <v>-7.0681162947343074e-05</v>
+        <v>-0.00013751684397931077</v>
       </c>
       <c r="N11">
-        <v>-0.00025166467281551594</v>
+        <v>-0.00029053014122689227</v>
       </c>
       <c r="O11">
-        <v>-0.0002664888368138598</v>
+        <v>-0.00033416895735709424</v>
       </c>
       <c r="P11">
-        <v>-3.738454837627506e-05</v>
+        <v>-0.00012878405718243127</v>
       </c>
       <c r="Q11">
-        <v>-0.00016786538347233294</v>
+        <v>-0.00022549746791025775</v>
       </c>
       <c r="R11">
-        <v>6.8752253410458519e-05</v>
+        <v>-6.1961577408577018e-05</v>
       </c>
       <c r="S11">
-        <v>1.4557923173846277e-05</v>
+        <v>5.7267800889183927e-06</v>
       </c>
       <c r="T11">
-        <v>-0.00015277485555255897</v>
+        <v>-4.7679891279528712e-05</v>
       </c>
       <c r="U11">
-        <v>-0.00016300125420515049</v>
+        <v>-9.1722061661029581e-05</v>
       </c>
       <c r="V11">
-        <v>-6.5220768115095999e-05</v>
+        <v>4.0195281532852563e-05</v>
       </c>
       <c r="W11">
-        <v>-3.4441338183214035e-05</v>
+        <v>-3.5230185738523438e-05</v>
       </c>
       <c r="X11">
-        <v>-0.0045265426090361112</v>
+        <v>-0.0018035943450821</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="B12">
-        <v>-0.036817810742166036</v>
+        <v>-0.064225077405799663</v>
       </c>
       <c r="C12">
-        <v>-2.8260875892740665e-05</v>
+        <v>-2.5746311260147045e-05</v>
       </c>
       <c r="D12">
-        <v>-2.0346613448131564e-05</v>
+        <v>-1.1489674940820191e-05</v>
       </c>
       <c r="E12">
-        <v>-8.6660424805947919e-05</v>
+        <v>-7.5433770497203116e-05</v>
       </c>
       <c r="F12">
-        <v>2.7561426761518217e-05</v>
+        <v>2.8333554113440639e-06</v>
       </c>
       <c r="G12">
-        <v>4.883848170320667e-07</v>
+        <v>5.6186159433561792e-05</v>
       </c>
       <c r="H12">
-        <v>-1.655286905757322e-05</v>
+        <v>-2.0057084075742612e-05</v>
       </c>
       <c r="I12">
-        <v>-9.0911023812305275e-05</v>
+        <v>-0.00010551003763364128</v>
       </c>
       <c r="J12">
-        <v>-9.5754157910514937e-05</v>
+        <v>-0.00015941717598920544</v>
       </c>
       <c r="K12">
-        <v>-9.8524181647958401e-05</v>
+        <v>-0.00019184139925232542</v>
       </c>
       <c r="L12">
-        <v>-7.0681162947343074e-05</v>
+        <v>-0.00013751684397931077</v>
       </c>
       <c r="M12">
-        <v>0.0050674606806236375</v>
+        <v>0.0051469384118784387</v>
       </c>
       <c r="N12">
-        <v>0.0038817169158048628</v>
+        <v>0.0039320616467701693</v>
       </c>
       <c r="O12">
-        <v>0.0038849516884137351</v>
+        <v>0.0039398856641894272</v>
       </c>
       <c r="P12">
-        <v>0.0038783903283093205</v>
+        <v>0.0039301416621888626</v>
       </c>
       <c r="Q12">
-        <v>0.003886830811910132</v>
+        <v>0.0039378968425337682</v>
       </c>
       <c r="R12">
-        <v>0.003876976130582493</v>
+        <v>0.0039305361528000045</v>
       </c>
       <c r="S12">
-        <v>2.7216671889898026e-06</v>
+        <v>3.9884550801216133e-06</v>
       </c>
       <c r="T12">
-        <v>2.2455355669528335e-05</v>
+        <v>2.7176363262126392e-05</v>
       </c>
       <c r="U12">
-        <v>-3.0741558713016129e-05</v>
+        <v>-8.1251173606372617e-07</v>
       </c>
       <c r="V12">
-        <v>-3.5602634885121068e-05</v>
+        <v>-6.0836321878862524e-05</v>
       </c>
       <c r="W12">
-        <v>-5.5862690318777999e-05</v>
+        <v>-5.2467010716652769e-05</v>
       </c>
       <c r="X12">
-        <v>-0.0034067571677651163</v>
+        <v>-0.003575221255376806</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="B13">
-        <v>0.028225583875224905</v>
+        <v>-0.053450527445847676</v>
       </c>
       <c r="C13">
-        <v>-4.5332756772375213e-05</v>
+        <v>-3.5582438365392528e-05</v>
       </c>
       <c r="D13">
-        <v>-2.9005552255030684e-05</v>
+        <v>-9.0078583115931355e-06</v>
       </c>
       <c r="E13">
-        <v>-3.8107708286064679e-05</v>
+        <v>-5.2741367637693538e-05</v>
       </c>
       <c r="F13">
-        <v>4.9639587999507784e-05</v>
+        <v>3.611399712493725e-06</v>
       </c>
       <c r="G13">
-        <v>-2.9234180232962613e-06</v>
+        <v>6.7018108063702587e-05</v>
       </c>
       <c r="H13">
-        <v>-8.1647099933679481e-05</v>
+        <v>-8.3242766044292263e-05</v>
       </c>
       <c r="I13">
-        <v>-9.8104025494364521e-05</v>
+        <v>-5.5018015909088602e-05</v>
       </c>
       <c r="J13">
-        <v>-0.00010272848895685337</v>
+        <v>-0.00015305342442840659</v>
       </c>
       <c r="K13">
-        <v>-0.00021499653107708494</v>
+        <v>-0.00022385365882217942</v>
       </c>
       <c r="L13">
-        <v>-0.00025166467281551594</v>
+        <v>-0.00029053014122689227</v>
       </c>
       <c r="M13">
-        <v>0.0038817169158048628</v>
+        <v>0.0039320616467701693</v>
       </c>
       <c r="N13">
-        <v>0.0049109150360035492</v>
+        <v>0.0050169672162914368</v>
       </c>
       <c r="O13">
-        <v>0.0039031966070286963</v>
+        <v>0.0039729269087373752</v>
       </c>
       <c r="P13">
-        <v>0.0038837154212461346</v>
+        <v>0.0039308557438832124</v>
       </c>
       <c r="Q13">
-        <v>0.0039030494206723433</v>
+        <v>0.0039604887578164813</v>
       </c>
       <c r="R13">
-        <v>0.0038767749881175192</v>
+        <v>0.0039187462481468423</v>
       </c>
       <c r="S13">
-        <v>-6.5342749210885279e-07</v>
+        <v>-1.2497241158657401e-06</v>
       </c>
       <c r="T13">
-        <v>4.9062219081101024e-05</v>
+        <v>6.6293645004977635e-05</v>
       </c>
       <c r="U13">
-        <v>-3.8147210840897515e-06</v>
+        <v>2.6645008205374463e-05</v>
       </c>
       <c r="V13">
-        <v>-2.9880126272694265e-05</v>
+        <v>-5.8194673263803126e-05</v>
       </c>
       <c r="W13">
-        <v>-4.7695244758435684e-05</v>
+        <v>-4.1737493355056051e-05</v>
       </c>
       <c r="X13">
-        <v>-0.0031097753746780719</v>
+        <v>-0.0034435278421685671</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="B14">
-        <v>-0.052939045553858241</v>
+        <v>-0.10180304151668637</v>
       </c>
       <c r="C14">
-        <v>-2.6030787126567166e-05</v>
+        <v>-2.5106763894690355e-05</v>
       </c>
       <c r="D14">
-        <v>-2.8957396012170241e-05</v>
+        <v>-1.0023238446408081e-05</v>
       </c>
       <c r="E14">
-        <v>-5.5452482649360254e-05</v>
+        <v>-6.2753248789853221e-05</v>
       </c>
       <c r="F14">
-        <v>4.4597633397449894e-05</v>
+        <v>1.3076873825762394e-06</v>
       </c>
       <c r="G14">
-        <v>4.6112438096655045e-06</v>
+        <v>6.9527841905245497e-05</v>
       </c>
       <c r="H14">
-        <v>-6.6109622909688688e-05</v>
+        <v>-6.1483251100337823e-05</v>
       </c>
       <c r="I14">
-        <v>-0.00013088984251906198</v>
+        <v>-0.00014712609732585522</v>
       </c>
       <c r="J14">
-        <v>-0.00010590045680778433</v>
+        <v>-0.00019031270626754509</v>
       </c>
       <c r="K14">
-        <v>-0.00021512108826686276</v>
+        <v>-0.00028886904990832311</v>
       </c>
       <c r="L14">
-        <v>-0.0002664888368138598</v>
+        <v>-0.00033416895735709424</v>
       </c>
       <c r="M14">
-        <v>0.0038849516884137351</v>
+        <v>0.0039398856641894272</v>
       </c>
       <c r="N14">
-        <v>0.0039031966070286963</v>
+        <v>0.0039729269087373752</v>
       </c>
       <c r="O14">
-        <v>0.0049624793457946339</v>
+        <v>0.0050638457293142383</v>
       </c>
       <c r="P14">
-        <v>0.0038844208824492434</v>
+        <v>0.0039369215981547162</v>
       </c>
       <c r="Q14">
-        <v>0.003900162289348464</v>
+        <v>0.0039639438137966335</v>
       </c>
       <c r="R14">
-        <v>0.0038751549393777722</v>
+        <v>0.0039257326946251061</v>
       </c>
       <c r="S14">
-        <v>-4.0415293265588597e-06</v>
+        <v>-3.8810452774745108e-06</v>
       </c>
       <c r="T14">
-        <v>4.2580542231541964e-05</v>
+        <v>5.9566158360324899e-05</v>
       </c>
       <c r="U14">
-        <v>-3.2014411999890349e-05</v>
+        <v>1.1740488377247571e-05</v>
       </c>
       <c r="V14">
-        <v>-4.9439602074253597e-05</v>
+        <v>-6.8909141607364751e-05</v>
       </c>
       <c r="W14">
-        <v>-2.7277535470586738e-05</v>
+        <v>-2.420046821072718e-05</v>
       </c>
       <c r="X14">
-        <v>-0.0030542918075739511</v>
+        <v>-0.0033551041724105058</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="B15">
-        <v>-0.050412118008601153</v>
+        <v>-0.083597984689970053</v>
       </c>
       <c r="C15">
-        <v>-3.1951245269935119e-05</v>
+        <v>-3.6222986160605792e-05</v>
       </c>
       <c r="D15">
-        <v>-1.5986335605171643e-05</v>
+        <v>-1.0842713673929146e-05</v>
       </c>
       <c r="E15">
-        <v>-4.7962815156179887e-05</v>
+        <v>-4.8389903728097376e-05</v>
       </c>
       <c r="F15">
-        <v>3.2084103206722614e-05</v>
+        <v>8.4418283834808254e-06</v>
       </c>
       <c r="G15">
-        <v>7.6525541569424753e-06</v>
+        <v>7.1903940157519225e-05</v>
       </c>
       <c r="H15">
-        <v>-5.6415696520949378e-05</v>
+        <v>-6.0756499646795657e-05</v>
       </c>
       <c r="I15">
-        <v>-8.4367701777185138e-05</v>
+        <v>-6.2127891726286924e-05</v>
       </c>
       <c r="J15">
-        <v>-6.6637993258357974e-05</v>
+        <v>-0.00017269794417961381</v>
       </c>
       <c r="K15">
-        <v>-0.00010826604348756954</v>
+        <v>-0.00015576705060110416</v>
       </c>
       <c r="L15">
-        <v>-3.738454837627506e-05</v>
+        <v>-0.00012878405718243127</v>
       </c>
       <c r="M15">
-        <v>0.0038783903283093205</v>
+        <v>0.0039301416621888626</v>
       </c>
       <c r="N15">
-        <v>0.0038837154212461346</v>
+        <v>0.0039308557438832124</v>
       </c>
       <c r="O15">
-        <v>0.0038844208824492434</v>
+        <v>0.0039369215981547162</v>
       </c>
       <c r="P15">
-        <v>0.0047002865957919094</v>
+        <v>0.0047683276109766167</v>
       </c>
       <c r="Q15">
-        <v>0.0038887103503880477</v>
+        <v>0.0039369993656804018</v>
       </c>
       <c r="R15">
-        <v>0.0038804114951039373</v>
+        <v>0.0039290091427941019</v>
       </c>
       <c r="S15">
-        <v>2.9453270013539052e-06</v>
+        <v>4.358083867805795e-06</v>
       </c>
       <c r="T15">
-        <v>2.8633168505836585e-05</v>
+        <v>3.2817196351307264e-05</v>
       </c>
       <c r="U15">
-        <v>-3.3125937762476293e-05</v>
+        <v>1.0177565828314535e-06</v>
       </c>
       <c r="V15">
-        <v>-3.6416480972297849e-05</v>
+        <v>-5.9221869943111723e-05</v>
       </c>
       <c r="W15">
-        <v>-4.8518008187526502e-05</v>
+        <v>-5.0817335526892279e-05</v>
       </c>
       <c r="X15">
-        <v>-0.0034873771852293976</v>
+        <v>-0.0035777032055377585</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="B16">
-        <v>-0.056916565680939675</v>
+        <v>-0.10969528036612212</v>
       </c>
       <c r="C16">
-        <v>-5.507550833823332e-05</v>
+        <v>-5.5585708463225874e-05</v>
       </c>
       <c r="D16">
-        <v>-1.6281221913368787e-05</v>
+        <v>-2.0069550829815544e-06</v>
       </c>
       <c r="E16">
-        <v>-3.743478803600236e-05</v>
+        <v>-3.0986065076053749e-05</v>
       </c>
       <c r="F16">
-        <v>2.8403179923142725e-05</v>
+        <v>-5.8165376174466139e-06</v>
       </c>
       <c r="G16">
-        <v>1.7903599447417527e-05</v>
+        <v>0.00010100168728186917</v>
       </c>
       <c r="H16">
-        <v>-7.9633047079400194e-05</v>
+        <v>-7.4636270556813967e-05</v>
       </c>
       <c r="I16">
-        <v>-0.00011414253206704439</v>
+        <v>-8.9904909936068563e-05</v>
       </c>
       <c r="J16">
-        <v>-5.7359153085030144e-05</v>
+        <v>-0.00014006348013744841</v>
       </c>
       <c r="K16">
-        <v>-0.00017249577446618256</v>
+        <v>-0.0002313892470018166</v>
       </c>
       <c r="L16">
-        <v>-0.00016786538347233294</v>
+        <v>-0.00022549746791025775</v>
       </c>
       <c r="M16">
-        <v>0.003886830811910132</v>
+        <v>0.0039378968425337682</v>
       </c>
       <c r="N16">
-        <v>0.0039030494206723433</v>
+        <v>0.0039604887578164813</v>
       </c>
       <c r="O16">
-        <v>0.003900162289348464</v>
+        <v>0.0039639438137966335</v>
       </c>
       <c r="P16">
-        <v>0.0038887103503880477</v>
+        <v>0.0039369993656804018</v>
       </c>
       <c r="Q16">
-        <v>0.0045828879574468691</v>
+        <v>0.004650413859931808</v>
       </c>
       <c r="R16">
-        <v>0.003884383719957937</v>
+        <v>0.0039310801975659801</v>
       </c>
       <c r="S16">
-        <v>-2.2168544883133793e-06</v>
+        <v>-1.8792153266611376e-06</v>
       </c>
       <c r="T16">
-        <v>0.00015293347471400471</v>
+        <v>0.0001411696228789238</v>
       </c>
       <c r="U16">
-        <v>-1.6664693129737039e-05</v>
+        <v>1.9296979623631779e-05</v>
       </c>
       <c r="V16">
-        <v>-4.9797969748219088e-05</v>
+        <v>-7.5433426436691481e-05</v>
       </c>
       <c r="W16">
-        <v>-8.0719469348065117e-05</v>
+        <v>-7.8450213299086167e-05</v>
       </c>
       <c r="X16">
-        <v>-0.0033541223069299057</v>
+        <v>-0.0036012829359421753</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="B17">
-        <v>-0.039563958722327083</v>
+        <v>-0.070885848105694038</v>
       </c>
       <c r="C17">
-        <v>-5.5041332143276523e-05</v>
+        <v>-6.1044172642558365e-05</v>
       </c>
       <c r="D17">
-        <v>-7.0016122684143499e-06</v>
+        <v>-6.3983897796500867e-06</v>
       </c>
       <c r="E17">
-        <v>-6.3839353967824883e-06</v>
+        <v>1.3605179064194654e-05</v>
       </c>
       <c r="F17">
-        <v>2.8613473755967377e-05</v>
+        <v>1.8479230313117438e-05</v>
       </c>
       <c r="G17">
-        <v>-3.4351594892887186e-05</v>
+        <v>9.8317923525409142e-06</v>
       </c>
       <c r="H17">
-        <v>-9.2952006554972454e-05</v>
+        <v>-0.00011302308738673871</v>
       </c>
       <c r="I17">
-        <v>-6.0061136065945288e-05</v>
+        <v>-0.00011924536521393239</v>
       </c>
       <c r="J17">
-        <v>-4.8831376289633452e-05</v>
+        <v>-0.00014383924610398625</v>
       </c>
       <c r="K17">
-        <v>-4.8048250963928917e-05</v>
+        <v>-0.00013169470404340028</v>
       </c>
       <c r="L17">
-        <v>6.8752253410458519e-05</v>
+        <v>-6.1961577408577018e-05</v>
       </c>
       <c r="M17">
-        <v>0.003876976130582493</v>
+        <v>0.0039305361528000045</v>
       </c>
       <c r="N17">
-        <v>0.0038767749881175192</v>
+        <v>0.0039187462481468423</v>
       </c>
       <c r="O17">
-        <v>0.0038751549393777722</v>
+        <v>0.0039257326946251061</v>
       </c>
       <c r="P17">
-        <v>0.0038804114951039373</v>
+        <v>0.0039290091427941019</v>
       </c>
       <c r="Q17">
-        <v>0.003884383719957937</v>
+        <v>0.0039310801975659801</v>
       </c>
       <c r="R17">
-        <v>0.004572776922183751</v>
+        <v>0.0046383690527696097</v>
       </c>
       <c r="S17">
-        <v>8.0353552875701975e-07</v>
+        <v>1.7974139731771863e-06</v>
       </c>
       <c r="T17">
-        <v>6.5247449432754515e-05</v>
+        <v>7.7608447738375733e-05</v>
       </c>
       <c r="U17">
-        <v>-3.9914109004138531e-05</v>
+        <v>-1.3432509016494363e-05</v>
       </c>
       <c r="V17">
-        <v>-7.6980974994749147e-05</v>
+        <v>-0.00010222879233478437</v>
       </c>
       <c r="W17">
-        <v>-6.7890422235781633e-05</v>
+        <v>-6.8417366246314505e-05</v>
       </c>
       <c r="X17">
-        <v>-0.0036190591929841374</v>
+        <v>-0.0036080494630704976</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="B18">
-        <v>0.020238956720677551</v>
+        <v>0.021044188223740153</v>
       </c>
       <c r="C18">
-        <v>-1.38405756557253e-06</v>
+        <v>-1.5770969190706375e-06</v>
       </c>
       <c r="D18">
-        <v>1.5976973339831922e-06</v>
+        <v>6.0966643171010346e-07</v>
       </c>
       <c r="E18">
-        <v>2.6620169559592562e-06</v>
+        <v>3.0644012190644111e-06</v>
       </c>
       <c r="F18">
-        <v>-2.8981748534000543e-06</v>
+        <v>-1.202750410494309e-06</v>
       </c>
       <c r="G18">
-        <v>2.152890091293391e-06</v>
+        <v>5.4457719796947412e-07</v>
       </c>
       <c r="H18">
-        <v>-3.6377221385323801e-07</v>
+        <v>-8.0641397060144938e-07</v>
       </c>
       <c r="I18">
-        <v>5.4920872460212021e-06</v>
+        <v>-4.8275566420469699e-06</v>
       </c>
       <c r="J18">
-        <v>1.0745776938473883e-05</v>
+        <v>-3.3003792521163471e-06</v>
       </c>
       <c r="K18">
-        <v>8.7703658756554281e-06</v>
+        <v>-8.5650930642155036e-07</v>
       </c>
       <c r="L18">
-        <v>1.4557923173846277e-05</v>
+        <v>5.7267800889183927e-06</v>
       </c>
       <c r="M18">
-        <v>2.7216671889898026e-06</v>
+        <v>3.9884550801216133e-06</v>
       </c>
       <c r="N18">
-        <v>-6.5342749210885279e-07</v>
+        <v>-1.2497241158657401e-06</v>
       </c>
       <c r="O18">
-        <v>-4.0415293265588597e-06</v>
+        <v>-3.8810452774745108e-06</v>
       </c>
       <c r="P18">
-        <v>2.9453270013539052e-06</v>
+        <v>4.358083867805795e-06</v>
       </c>
       <c r="Q18">
-        <v>-2.2168544883133793e-06</v>
+        <v>-1.8792153266611376e-06</v>
       </c>
       <c r="R18">
-        <v>8.0353552875701975e-07</v>
+        <v>1.7974139731771863e-06</v>
       </c>
       <c r="S18">
-        <v>9.8016797014218347e-06</v>
+        <v>9.8997346895161618e-06</v>
       </c>
       <c r="T18">
-        <v>-3.198990227583023e-05</v>
+        <v>-3.2582456745008101e-05</v>
       </c>
       <c r="U18">
-        <v>-4.2833546113699281e-05</v>
+        <v>-4.2911567238635596e-05</v>
       </c>
       <c r="V18">
-        <v>-5.1909066545225365e-05</v>
+        <v>-5.2420592318600285e-05</v>
       </c>
       <c r="W18">
-        <v>-6.1484184016498514e-05</v>
+        <v>-6.2055225138674727e-05</v>
       </c>
       <c r="X18">
-        <v>-0.00020025893068150417</v>
+        <v>-0.00017680219578734521</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="B19">
-        <v>-0.26647368889414541</v>
+        <v>-0.26849540360030261</v>
       </c>
       <c r="C19">
-        <v>7.3249055982587763e-06</v>
+        <v>1.7556077563059714e-05</v>
       </c>
       <c r="D19">
-        <v>-2.9307829013420096e-06</v>
+        <v>3.0718429161282791e-06</v>
       </c>
       <c r="E19">
-        <v>7.2169135818662272e-05</v>
+        <v>4.4279422728230392e-05</v>
       </c>
       <c r="F19">
-        <v>3.5884766545517515e-05</v>
+        <v>2.6300176602169888e-05</v>
       </c>
       <c r="G19">
-        <v>-1.3862526754995427e-05</v>
+        <v>-1.1251497669129097e-05</v>
       </c>
       <c r="H19">
-        <v>-2.5288293787748272e-05</v>
+        <v>-2.1282062764295487e-05</v>
       </c>
       <c r="I19">
-        <v>-6.8189978583488664e-05</v>
+        <v>3.1657130322650497e-05</v>
       </c>
       <c r="J19">
-        <v>-2.4628053995732211e-05</v>
+        <v>4.7639297542916665e-05</v>
       </c>
       <c r="K19">
-        <v>-0.00011598847574612482</v>
+        <v>-3.232025976871453e-05</v>
       </c>
       <c r="L19">
-        <v>-0.00015277485555255897</v>
+        <v>-4.7679891279528712e-05</v>
       </c>
       <c r="M19">
-        <v>2.2455355669528335e-05</v>
+        <v>2.7176363262126392e-05</v>
       </c>
       <c r="N19">
-        <v>4.9062219081101024e-05</v>
+        <v>6.6293645004977635e-05</v>
       </c>
       <c r="O19">
-        <v>4.2580542231541964e-05</v>
+        <v>5.9566158360324899e-05</v>
       </c>
       <c r="P19">
-        <v>2.8633168505836585e-05</v>
+        <v>3.2817196351307264e-05</v>
       </c>
       <c r="Q19">
-        <v>0.00015293347471400471</v>
+        <v>0.0001411696228789238</v>
       </c>
       <c r="R19">
-        <v>6.5247449432754515e-05</v>
+        <v>7.7608447738375733e-05</v>
       </c>
       <c r="S19">
-        <v>-3.198990227583023e-05</v>
+        <v>-3.2582456745008101e-05</v>
       </c>
       <c r="T19">
-        <v>0.0028073373306718662</v>
+        <v>0.0028777566472911955</v>
       </c>
       <c r="U19">
-        <v>0.00033183765923717172</v>
+        <v>0.00033372200238852531</v>
       </c>
       <c r="V19">
-        <v>0.00035591952107894367</v>
+        <v>0.00035930351871743489</v>
       </c>
       <c r="W19">
-        <v>0.00038491934378419475</v>
+        <v>0.00038701624105713769</v>
       </c>
       <c r="X19">
-        <v>0.00035937116225963432</v>
+        <v>0.00019667758075046901</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="B20">
-        <v>0.34040250683097051</v>
+        <v>0.3375039634777845</v>
       </c>
       <c r="C20">
-        <v>-1.7092488571668567e-05</v>
+        <v>-1.1805420377914614e-05</v>
       </c>
       <c r="D20">
-        <v>-2.1846187251463271e-05</v>
+        <v>-1.3147093236602034e-05</v>
       </c>
       <c r="E20">
-        <v>-0.00019094319503624177</v>
+        <v>-0.0002146114912879331</v>
       </c>
       <c r="F20">
-        <v>3.8019498947896647e-05</v>
+        <v>2.4995248953911319e-05</v>
       </c>
       <c r="G20">
-        <v>1.1628737978713679e-05</v>
+        <v>2.5058937526433199e-05</v>
       </c>
       <c r="H20">
-        <v>6.2397455134502534e-05</v>
+        <v>7.6264128911585386e-05</v>
       </c>
       <c r="I20">
-        <v>-8.302228995382926e-06</v>
+        <v>-1.0368296020932701e-05</v>
       </c>
       <c r="J20">
-        <v>-8.9394754522013599e-05</v>
+        <v>-6.3245297835491142e-05</v>
       </c>
       <c r="K20">
-        <v>-6.4415936709057446e-05</v>
+        <v>-7.7583729965980774e-05</v>
       </c>
       <c r="L20">
-        <v>-0.00016300125420515049</v>
+        <v>-9.1722061661029581e-05</v>
       </c>
       <c r="M20">
-        <v>-3.0741558713016129e-05</v>
+        <v>-8.1251173606372617e-07</v>
       </c>
       <c r="N20">
-        <v>-3.8147210840897515e-06</v>
+        <v>2.6645008205374463e-05</v>
       </c>
       <c r="O20">
-        <v>-3.2014411999890349e-05</v>
+        <v>1.1740488377247571e-05</v>
       </c>
       <c r="P20">
-        <v>-3.3125937762476293e-05</v>
+        <v>1.0177565828314535e-06</v>
       </c>
       <c r="Q20">
-        <v>-1.6664693129737039e-05</v>
+        <v>1.9296979623631779e-05</v>
       </c>
       <c r="R20">
-        <v>-3.9914109004138531e-05</v>
+        <v>-1.3432509016494363e-05</v>
       </c>
       <c r="S20">
-        <v>-4.2833546113699281e-05</v>
+        <v>-4.2911567238635596e-05</v>
       </c>
       <c r="T20">
-        <v>0.00033183765923717172</v>
+        <v>0.00033372200238852531</v>
       </c>
       <c r="U20">
-        <v>0.0042476209918174144</v>
+        <v>0.0042710119581773533</v>
       </c>
       <c r="V20">
-        <v>0.00042818885711444444</v>
+        <v>0.00043184978862057579</v>
       </c>
       <c r="W20">
-        <v>0.00046206665297462296</v>
+        <v>0.00046998557957459738</v>
       </c>
       <c r="X20">
-        <v>0.0010013789462656299</v>
+        <v>0.00081150079005790413</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="B21">
-        <v>0.41947513102623252</v>
+        <v>0.41799970214751148</v>
       </c>
       <c r="C21">
-        <v>-1.6752814167593104e-05</v>
+        <v>-2.58876823041253e-05</v>
       </c>
       <c r="D21">
-        <v>-1.6207183915359466e-05</v>
+        <v>-1.1900936198789463e-05</v>
       </c>
       <c r="E21">
-        <v>-0.0001347416131791707</v>
+        <v>-0.00015189565455492934</v>
       </c>
       <c r="F21">
-        <v>3.0326767678386145e-05</v>
+        <v>2.0715671599554433e-05</v>
       </c>
       <c r="G21">
-        <v>3.8686227267573483e-05</v>
+        <v>5.0265756194492733e-05</v>
       </c>
       <c r="H21">
-        <v>0.00026217846067737104</v>
+        <v>0.00026102300204844674</v>
       </c>
       <c r="I21">
-        <v>2.0405745842343471e-05</v>
+        <v>5.5554802015448117e-05</v>
       </c>
       <c r="J21">
-        <v>-3.9732056429816229e-05</v>
+        <v>4.5929130300299305e-06</v>
       </c>
       <c r="K21">
-        <v>-1.6449097339529643e-05</v>
+        <v>5.0772160565126659e-05</v>
       </c>
       <c r="L21">
-        <v>-6.5220768115095999e-05</v>
+        <v>4.0195281532852563e-05</v>
       </c>
       <c r="M21">
-        <v>-3.5602634885121068e-05</v>
+        <v>-6.0836321878862524e-05</v>
       </c>
       <c r="N21">
-        <v>-2.9880126272694265e-05</v>
+        <v>-5.8194673263803126e-05</v>
       </c>
       <c r="O21">
-        <v>-4.9439602074253597e-05</v>
+        <v>-6.8909141607364751e-05</v>
       </c>
       <c r="P21">
-        <v>-3.6416480972297849e-05</v>
+        <v>-5.9221869943111723e-05</v>
       </c>
       <c r="Q21">
-        <v>-4.9797969748219088e-05</v>
+        <v>-7.5433426436691481e-05</v>
       </c>
       <c r="R21">
-        <v>-7.6980974994749147e-05</v>
+        <v>-0.00010222879233478437</v>
       </c>
       <c r="S21">
-        <v>-5.1909066545225365e-05</v>
+        <v>-5.2420592318600285e-05</v>
       </c>
       <c r="T21">
-        <v>0.00035591952107894367</v>
+        <v>0.00035930351871743489</v>
       </c>
       <c r="U21">
-        <v>0.00042818885711444444</v>
+        <v>0.00043184978862057579</v>
       </c>
       <c r="V21">
-        <v>0.0020091075516404963</v>
+        <v>0.0020764814450793417</v>
       </c>
       <c r="W21">
-        <v>0.00054459979312604791</v>
+        <v>0.00055299755591042615</v>
       </c>
       <c r="X21">
-        <v>0.00085134405912632425</v>
+        <v>0.00076395133212142814</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="B22">
-        <v>0.26074083245979152</v>
+        <v>0.26847735648289772</v>
       </c>
       <c r="C22">
-        <v>2.9231494845983084e-05</v>
+        <v>2.3650241363173323e-05</v>
       </c>
       <c r="D22">
-        <v>-8.1051178447871016e-06</v>
+        <v>-1.1605111834885192e-05</v>
       </c>
       <c r="E22">
-        <v>-0.00012367314094885429</v>
+        <v>-0.00013066645318122604</v>
       </c>
       <c r="F22">
-        <v>2.7223854920857679e-06</v>
+        <v>9.8170271323840853e-06</v>
       </c>
       <c r="G22">
-        <v>4.4736235413993827e-05</v>
+        <v>3.8311737595499943e-05</v>
       </c>
       <c r="H22">
-        <v>0.0001476501992311943</v>
+        <v>0.00014878328980789574</v>
       </c>
       <c r="I22">
-        <v>-2.9489284404706859e-05</v>
+        <v>-3.148063734246902e-05</v>
       </c>
       <c r="J22">
-        <v>-7.3694741155884945e-06</v>
+        <v>-3.469573557110631e-05</v>
       </c>
       <c r="K22">
-        <v>3.2206533836783816e-05</v>
+        <v>-3.6900197501263908e-05</v>
       </c>
       <c r="L22">
-        <v>-3.4441338183214035e-05</v>
+        <v>-3.5230185738523438e-05</v>
       </c>
       <c r="M22">
-        <v>-5.5862690318777999e-05</v>
+        <v>-5.2467010716652769e-05</v>
       </c>
       <c r="N22">
-        <v>-4.7695244758435684e-05</v>
+        <v>-4.1737493355056051e-05</v>
       </c>
       <c r="O22">
-        <v>-2.7277535470586738e-05</v>
+        <v>-2.420046821072718e-05</v>
       </c>
       <c r="P22">
-        <v>-4.8518008187526502e-05</v>
+        <v>-5.0817335526892279e-05</v>
       </c>
       <c r="Q22">
-        <v>-8.0719469348065117e-05</v>
+        <v>-7.8450213299086167e-05</v>
       </c>
       <c r="R22">
-        <v>-6.7890422235781633e-05</v>
+        <v>-6.8417366246314505e-05</v>
       </c>
       <c r="S22">
-        <v>-6.1484184016498514e-05</v>
+        <v>-6.2055225138674727e-05</v>
       </c>
       <c r="T22">
-        <v>0.00038491934378419475</v>
+        <v>0.00038701624105713769</v>
       </c>
       <c r="U22">
-        <v>0.00046206665297462296</v>
+        <v>0.00046998557957459738</v>
       </c>
       <c r="V22">
-        <v>0.00054459979312604791</v>
+        <v>0.00055299755591042615</v>
       </c>
       <c r="W22">
-        <v>0.0019700715490882786</v>
+        <v>0.0020075081533197448</v>
       </c>
       <c r="X22">
-        <v>0.00094003475618229589</v>
+        <v>0.0010358320404717047</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="B23">
-        <v>3.3677437972389259</v>
+        <v>3.8752198822121309</v>
       </c>
       <c r="C23">
-        <v>-0.0002720611607212399</v>
+        <v>-0.00027813983859165082</v>
       </c>
       <c r="D23">
-        <v>-0.0017893630481715995</v>
+        <v>-0.0013253437196956203</v>
       </c>
       <c r="E23">
-        <v>-0.0057960402472572135</v>
+        <v>-0.0059720843048415</v>
       </c>
       <c r="F23">
-        <v>0.0035628364151353877</v>
+        <v>0.0028493231277876867</v>
       </c>
       <c r="G23">
-        <v>-0.0024553318173381788</v>
+        <v>-0.0022778149710759176</v>
       </c>
       <c r="H23">
-        <v>-9.8679339674429543e-05</v>
+        <v>7.9267322360968158e-05</v>
       </c>
       <c r="I23">
-        <v>-0.00050938541831626629</v>
+        <v>-0.0017508778824894555</v>
       </c>
       <c r="J23">
-        <v>-0.0024940081247746358</v>
+        <v>-0.0017705081935532167</v>
       </c>
       <c r="K23">
-        <v>-0.0042406520628242642</v>
+        <v>-0.0016887081948434401</v>
       </c>
       <c r="L23">
-        <v>-0.0045265426090361112</v>
+        <v>-0.0018035943450821</v>
       </c>
       <c r="M23">
-        <v>-0.0034067571677651163</v>
+        <v>-0.003575221255376806</v>
       </c>
       <c r="N23">
-        <v>-0.0031097753746780719</v>
+        <v>-0.0034435278421685671</v>
       </c>
       <c r="O23">
-        <v>-0.0030542918075739511</v>
+        <v>-0.0033551041724105058</v>
       </c>
       <c r="P23">
-        <v>-0.0034873771852293976</v>
+        <v>-0.0035777032055377585</v>
       </c>
       <c r="Q23">
-        <v>-0.0033541223069299057</v>
+        <v>-0.0036012829359421753</v>
       </c>
       <c r="R23">
-        <v>-0.0036190591929841374</v>
+        <v>-0.0036080494630704976</v>
       </c>
       <c r="S23">
-        <v>-0.00020025893068150417</v>
+        <v>-0.00017680219578734521</v>
       </c>
       <c r="T23">
-        <v>0.00035937116225963432</v>
+        <v>0.00019667758075046901</v>
       </c>
       <c r="U23">
-        <v>0.0010013789462656299</v>
+        <v>0.00081150079005790413</v>
       </c>
       <c r="V23">
-        <v>0.00085134405912632425</v>
+        <v>0.00076395133212142814</v>
       </c>
       <c r="W23">
-        <v>0.00094003475618229589</v>
+        <v>0.0010358320404717047</v>
       </c>
       <c r="X23">
-        <v>0.044634974595049115</v>
+        <v>0.035252719780018774</v>
       </c>
     </row>
   </sheetData>
@@ -2261,1709 +4392,1855 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:X23"/>
+  <dimension ref="A1:Y24"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E1" t="s">
+        <v>47</v>
+      </c>
+      <c r="F1" t="s">
+        <v>48</v>
+      </c>
+      <c r="G1" t="s">
+        <v>49</v>
+      </c>
+      <c r="H1" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1" t="s">
+        <v>51</v>
+      </c>
+      <c r="J1" t="s">
+        <v>52</v>
+      </c>
+      <c r="K1" t="s">
+        <v>53</v>
+      </c>
+      <c r="L1" t="s">
+        <v>54</v>
+      </c>
+      <c r="M1" t="s">
+        <v>55</v>
+      </c>
+      <c r="N1" t="s">
+        <v>56</v>
+      </c>
+      <c r="O1" t="s">
+        <v>57</v>
+      </c>
+      <c r="P1" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q1" t="s">
         <v>31</v>
       </c>
-      <c r="B1" t="s">
-        <v>54</v>
-      </c>
-      <c r="C1" t="s">
+      <c r="R1" t="s">
         <v>32</v>
       </c>
-      <c r="D1" t="s">
+      <c r="S1" t="s">
         <v>33</v>
       </c>
-      <c r="E1" t="s">
-        <v>55</v>
-      </c>
-      <c r="F1" t="s">
-        <v>56</v>
-      </c>
-      <c r="G1" t="s">
-        <v>57</v>
-      </c>
-      <c r="H1" t="s">
-        <v>58</v>
-      </c>
-      <c r="I1" t="s">
-        <v>59</v>
-      </c>
-      <c r="J1" t="s">
-        <v>60</v>
-      </c>
-      <c r="K1" t="s">
+      <c r="T1" t="s">
+        <v>34</v>
+      </c>
+      <c r="U1" t="s">
+        <v>35</v>
+      </c>
+      <c r="V1" t="s">
+        <v>36</v>
+      </c>
+      <c r="W1" t="s">
         <v>38</v>
       </c>
-      <c r="L1" t="s">
+      <c r="X1" t="s">
         <v>39</v>
       </c>
-      <c r="M1" t="s">
-        <v>40</v>
-      </c>
-      <c r="N1" t="s">
+      <c r="Y1" t="s">
         <v>41</v>
-      </c>
-      <c r="O1" t="s">
-        <v>42</v>
-      </c>
-      <c r="P1" t="s">
-        <v>43</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>44</v>
-      </c>
-      <c r="R1" t="s">
-        <v>45</v>
-      </c>
-      <c r="S1" t="s">
-        <v>46</v>
-      </c>
-      <c r="T1" t="s">
-        <v>47</v>
-      </c>
-      <c r="U1" t="s">
-        <v>48</v>
-      </c>
-      <c r="V1" t="s">
-        <v>50</v>
-      </c>
-      <c r="W1" t="s">
-        <v>51</v>
-      </c>
-      <c r="X1" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="B2">
-        <v>-0.095298105629226179</v>
+        <v>-0.10074103147263815</v>
       </c>
       <c r="C2">
-        <v>0.0010437326266580615</v>
+        <v>0.001043791148499525</v>
       </c>
       <c r="D2">
-        <v>2.2601931473813025e-05</v>
+        <v>1.6498861204195858e-05</v>
       </c>
       <c r="E2">
-        <v>-1.3064620533752677e-07</v>
+        <v>-6.7601626427928528e-08</v>
       </c>
       <c r="F2">
-        <v>6.1521208753834459e-05</v>
+        <v>-2.3124771626424226e-05</v>
       </c>
       <c r="G2">
-        <v>-6.3813940677653644e-05</v>
+        <v>-3.93006395685457e-05</v>
       </c>
       <c r="H2">
-        <v>-3.4384581939129577e-05</v>
+        <v>-3.9874279568030745e-05</v>
       </c>
       <c r="I2">
-        <v>-0.00011305708020917964</v>
+        <v>-8.1063753841659783e-05</v>
       </c>
       <c r="J2">
-        <v>0.00034082808829945401</v>
+        <v>0.00031246276710245654</v>
       </c>
       <c r="K2">
-        <v>8.8915238200703369e-05</v>
+        <v>7.1563341028333955e-07</v>
       </c>
       <c r="L2">
-        <v>2.2518691298354271e-05</v>
+        <v>5.6951370814305671e-05</v>
       </c>
       <c r="M2">
-        <v>-0.00028463225949549085</v>
+        <v>6.163393883347053e-05</v>
       </c>
       <c r="N2">
-        <v>-8.9750651379478879e-05</v>
+        <v>-0.00028430402506798586</v>
       </c>
       <c r="O2">
-        <v>-0.00013847242554323102</v>
+        <v>-3.8920722602061317e-05</v>
       </c>
       <c r="P2">
-        <v>-0.00011221579967702337</v>
+        <v>-0.0001272440148656675</v>
       </c>
       <c r="Q2">
-        <v>-0.00029295302450764812</v>
+        <v>-0.0001258362640066954</v>
       </c>
       <c r="R2">
-        <v>-9.9370182917451902e-05</v>
+        <v>-0.00028059841346779219</v>
       </c>
       <c r="S2">
-        <v>-0.00022817471093144933</v>
+        <v>-8.8746447275772633e-05</v>
       </c>
       <c r="T2">
-        <v>-0.00010821631387866433</v>
+        <v>-0.00021032298716303581</v>
       </c>
       <c r="U2">
-        <v>-6.9321024940633276e-06</v>
+        <v>-8.4927106182090215e-05</v>
       </c>
       <c r="V2">
-        <v>0.00040157041528798257</v>
+        <v>-7.4284829859226058e-06</v>
       </c>
       <c r="W2">
-        <v>5.6577398037686562e-05</v>
+        <v>0.00036498752517602598</v>
       </c>
       <c r="X2">
-        <v>-0.00072011313282233916</v>
+        <v>5.6239799266668124e-05</v>
+      </c>
+      <c r="Y2">
+        <v>-0.00064044979056054299</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="B3">
-        <v>-0.27826422488624331</v>
+        <v>-0.26647018991946842</v>
       </c>
       <c r="C3">
-        <v>2.2601931473813025e-05</v>
+        <v>1.6498861204195858e-05</v>
       </c>
       <c r="D3">
-        <v>6.2391491287775902e-05</v>
+        <v>6.5282062138612862e-05</v>
       </c>
       <c r="E3">
-        <v>-6.778457594025871e-07</v>
+        <v>-6.929025849074784e-07</v>
       </c>
       <c r="F3">
-        <v>-0.00014297425702937405</v>
+        <v>-8.9889594483816564e-05</v>
       </c>
       <c r="G3">
-        <v>-6.6058436388056465e-05</v>
+        <v>-6.9810440789669207e-05</v>
       </c>
       <c r="H3">
-        <v>0.00012530184531136992</v>
+        <v>0.00012210102976128155</v>
       </c>
       <c r="I3">
-        <v>6.5634448482752091e-05</v>
+        <v>9.4876232521119198e-05</v>
       </c>
       <c r="J3">
-        <v>-2.5852937065833168e-05</v>
+        <v>-2.3288574146655997e-05</v>
       </c>
       <c r="K3">
-        <v>5.6815143964197148e-06</v>
+        <v>9.0180261914919149e-06</v>
       </c>
       <c r="L3">
-        <v>7.7808870106821566e-05</v>
+        <v>2.8702559232412559e-06</v>
       </c>
       <c r="M3">
-        <v>2.3600689169367818e-05</v>
+        <v>0.00013151457410522547</v>
       </c>
       <c r="N3">
-        <v>5.4331762009441785e-05</v>
+        <v>8.0832347714027088e-05</v>
       </c>
       <c r="O3">
-        <v>-9.1506885663547154e-05</v>
+        <v>0.00010495530435479061</v>
       </c>
       <c r="P3">
-        <v>-7.981290981518268e-05</v>
+        <v>-9.1215287004425393e-05</v>
       </c>
       <c r="Q3">
-        <v>-0.00014872351794657432</v>
+        <v>-8.1986137076854463e-05</v>
       </c>
       <c r="R3">
-        <v>-9.4522262570792027e-05</v>
+        <v>-0.00015169138433165601</v>
       </c>
       <c r="S3">
-        <v>-9.9054917092345645e-05</v>
+        <v>-8.8691890284921639e-05</v>
       </c>
       <c r="T3">
-        <v>-8.3885481310229805e-05</v>
+        <v>-8.8940442469525861e-05</v>
       </c>
       <c r="U3">
-        <v>7.5202704928168751e-07</v>
+        <v>-7.8505525698549831e-05</v>
       </c>
       <c r="V3">
-        <v>0.00013649220948483475</v>
+        <v>1.8718287569234626e-06</v>
       </c>
       <c r="W3">
-        <v>-5.0547253262777682e-06</v>
+        <v>0.00013893625442215705</v>
       </c>
       <c r="X3">
-        <v>-0.0011345328519525664</v>
+        <v>-7.4758246378438557e-06</v>
+      </c>
+      <c r="Y3">
+        <v>-0.0012660470943110626</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="B4">
-        <v>0.0025651193940754331</v>
+        <v>0.002487791905325045</v>
       </c>
       <c r="C4">
-        <v>-1.3064620533752677e-07</v>
+        <v>-6.7601626427928528e-08</v>
       </c>
       <c r="D4">
-        <v>-6.778457594025871e-07</v>
+        <v>-6.929025849074784e-07</v>
       </c>
       <c r="E4">
-        <v>7.5643136133459055e-09</v>
+        <v>7.6380895579770931e-09</v>
       </c>
       <c r="F4">
-        <v>1.6019173016753625e-06</v>
+        <v>1.1252210522684162e-06</v>
       </c>
       <c r="G4">
-        <v>7.1794860731352265e-07</v>
+        <v>7.2609212950609992e-07</v>
       </c>
       <c r="H4">
-        <v>-1.3701376468002774e-06</v>
+        <v>-1.3360522990434529e-06</v>
       </c>
       <c r="I4">
-        <v>-8.7410745276182499e-07</v>
+        <v>-1.2338079722596618e-06</v>
       </c>
       <c r="J4">
-        <v>4.3759171861429675e-07</v>
+        <v>5.8752020289838951e-07</v>
       </c>
       <c r="K4">
-        <v>-1.0746646030948579e-07</v>
+        <v>5.9277725679184212e-07</v>
       </c>
       <c r="L4">
-        <v>-9.8559503557207274e-07</v>
+        <v>-1.474679746621977e-08</v>
       </c>
       <c r="M4">
-        <v>-3.6016174007484137e-07</v>
+        <v>-1.5665563521198577e-06</v>
       </c>
       <c r="N4">
-        <v>-8.2476281307687229e-07</v>
+        <v>-1.0851384269550113e-06</v>
       </c>
       <c r="O4">
-        <v>1.0633376342336799e-06</v>
+        <v>-1.3472814414901277e-06</v>
       </c>
       <c r="P4">
-        <v>9.8326912203852812e-07</v>
+        <v>9.7506969981564834e-07</v>
       </c>
       <c r="Q4">
-        <v>1.7113118790426884e-06</v>
+        <v>9.2107002652559397e-07</v>
       </c>
       <c r="R4">
-        <v>1.1294189529173196e-06</v>
+        <v>1.6461081322127421e-06</v>
       </c>
       <c r="S4">
-        <v>1.1732345985135603e-06</v>
+        <v>1.0174459094892041e-06</v>
       </c>
       <c r="T4">
-        <v>1.0223614038889259e-06</v>
+        <v>1.0136663447692557e-06</v>
       </c>
       <c r="U4">
-        <v>-8.4777212930309144e-09</v>
+        <v>9.1302955964055782e-07</v>
       </c>
       <c r="V4">
-        <v>-1.4995439368411866e-06</v>
+        <v>-1.9154560661216716e-08</v>
       </c>
       <c r="W4">
-        <v>3.1812329163913154e-09</v>
+        <v>-1.4747777881904504e-06</v>
       </c>
       <c r="X4">
-        <v>1.2160635972344815e-05</v>
+        <v>4.0474610557441579e-08</v>
+      </c>
+      <c r="Y4">
+        <v>1.264992356475351e-05</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="B5">
-        <v>-0.8429623141535505</v>
+        <v>-0.51459734600652374</v>
       </c>
       <c r="C5">
-        <v>6.1521208753834459e-05</v>
+        <v>-2.3124771626424226e-05</v>
       </c>
       <c r="D5">
-        <v>-0.00014297425702937405</v>
+        <v>-8.9889594483816564e-05</v>
       </c>
       <c r="E5">
-        <v>1.6019173016753625e-06</v>
+        <v>1.1252210522684162e-06</v>
       </c>
       <c r="F5">
-        <v>0.0031633790622092686</v>
+        <v>0.0049953821985694496</v>
       </c>
       <c r="G5">
-        <v>5.7240234919485843e-05</v>
+        <v>-1.9506473033149244e-05</v>
       </c>
       <c r="H5">
-        <v>0.00010818109021677519</v>
+        <v>0.00011548955362951864</v>
       </c>
       <c r="I5">
-        <v>-0.00031533583358902238</v>
+        <v>0.00062423123175528764</v>
       </c>
       <c r="J5">
-        <v>-0.00091752691421883345</v>
+        <v>-0.0012771216800244567</v>
       </c>
       <c r="K5">
-        <v>8.293361062148629e-05</v>
+        <v>0.0021473487373343311</v>
       </c>
       <c r="L5">
-        <v>-0.00060934318306670886</v>
+        <v>4.6739158331197919e-05</v>
       </c>
       <c r="M5">
-        <v>-0.00038016221606359624</v>
+        <v>0.00047854327119661004</v>
       </c>
       <c r="N5">
-        <v>-0.00012187286941909301</v>
+        <v>0.00080693434766852909</v>
       </c>
       <c r="O5">
-        <v>0.00033803621963605229</v>
+        <v>0.00078578284075701203</v>
       </c>
       <c r="P5">
-        <v>0.0002719930433817022</v>
+        <v>-3.4310570273278973e-05</v>
       </c>
       <c r="Q5">
-        <v>0.00033106935769794908</v>
+        <v>-8.3773754025549395e-05</v>
       </c>
       <c r="R5">
-        <v>0.00022582791828269387</v>
+        <v>-0.00021048657108744927</v>
       </c>
       <c r="S5">
-        <v>0.00011801533174869087</v>
+        <v>9.5832187450274825e-06</v>
       </c>
       <c r="T5">
-        <v>0.00022810414041111613</v>
+        <v>-0.00021354848745518406</v>
       </c>
       <c r="U5">
-        <v>2.0459051801049969e-05</v>
+        <v>9.9091381182424387e-05</v>
       </c>
       <c r="V5">
-        <v>-0.00027644164177490567</v>
+        <v>2.4506231728311594e-05</v>
       </c>
       <c r="W5">
-        <v>-0.00013432855475457601</v>
+        <v>-3.8005146034112184e-06</v>
       </c>
       <c r="X5">
-        <v>0.0022417792098019958</v>
+        <v>7.2996454601882807e-06</v>
+      </c>
+      <c r="Y5">
+        <v>-0.0016152239097772293</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="B6">
-        <v>-0.0057787576936733989</v>
+        <v>0.0026625266723272378</v>
       </c>
       <c r="C6">
-        <v>-6.3813940677653644e-05</v>
+        <v>-3.93006395685457e-05</v>
       </c>
       <c r="D6">
-        <v>-6.6058436388056465e-05</v>
+        <v>-6.9810440789669207e-05</v>
       </c>
       <c r="E6">
-        <v>7.1794860731352265e-07</v>
+        <v>7.2609212950609992e-07</v>
       </c>
       <c r="F6">
-        <v>5.7240234919485843e-05</v>
+        <v>-1.9506473033149244e-05</v>
       </c>
       <c r="G6">
-        <v>0.0016943233419582564</v>
+        <v>0.0017551173207996293</v>
       </c>
       <c r="H6">
-        <v>0.00066977887716762629</v>
+        <v>0.000680532273525467</v>
       </c>
       <c r="I6">
-        <v>-5.5687918629306125e-05</v>
+        <v>-9.6072639578681924e-05</v>
       </c>
       <c r="J6">
-        <v>-5.752108105342029e-05</v>
+        <v>-7.3118765048290453e-05</v>
       </c>
       <c r="K6">
-        <v>-0.00010808809285006185</v>
+        <v>-0.00015955481976579394</v>
       </c>
       <c r="L6">
-        <v>-5.6462045598308159e-05</v>
+        <v>-5.9336885674704633e-05</v>
       </c>
       <c r="M6">
-        <v>9.5595119520046389e-05</v>
+        <v>-0.00021320012455623206</v>
       </c>
       <c r="N6">
-        <v>-0.0002902814960097272</v>
+        <v>6.4205442760298856e-05</v>
       </c>
       <c r="O6">
-        <v>-3.233330550941226e-05</v>
+        <v>-0.00038931906896025152</v>
       </c>
       <c r="P6">
-        <v>-0.00015333856084332988</v>
+        <v>-4.6567481123565755e-05</v>
       </c>
       <c r="Q6">
-        <v>0.00019725082795417023</v>
+        <v>-0.00020260008679467696</v>
       </c>
       <c r="R6">
-        <v>1.7390659400292393e-05</v>
+        <v>0.00020720516706782349</v>
       </c>
       <c r="S6">
-        <v>8.7714028910309213e-05</v>
+        <v>-1.1949118283552471e-05</v>
       </c>
       <c r="T6">
-        <v>-9.6561788926988624e-06</v>
+        <v>9.2102223806946818e-05</v>
       </c>
       <c r="U6">
-        <v>6.8518628871108378e-06</v>
+        <v>1.6757822339950098e-05</v>
       </c>
       <c r="V6">
-        <v>-0.00033019620567532307</v>
+        <v>6.2149674749857797e-06</v>
       </c>
       <c r="W6">
-        <v>-0.00021823713896273526</v>
+        <v>-0.00034264963633000848</v>
       </c>
       <c r="X6">
-        <v>0.00044527321146397973</v>
+        <v>-0.0002285344336820779</v>
+      </c>
+      <c r="Y6">
+        <v>0.00071567774325853833</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="B7">
-        <v>-0.47476786743986949</v>
+        <v>-0.4749901687863809</v>
       </c>
       <c r="C7">
-        <v>-3.4384581939129577e-05</v>
+        <v>-3.9874279568030745e-05</v>
       </c>
       <c r="D7">
-        <v>0.00012530184531136992</v>
+        <v>0.00012210102976128155</v>
       </c>
       <c r="E7">
-        <v>-1.3701376468002774e-06</v>
+        <v>-1.3360522990434529e-06</v>
       </c>
       <c r="F7">
-        <v>0.00010818109021677519</v>
+        <v>0.00011548955362951864</v>
       </c>
       <c r="G7">
-        <v>0.00066977887716762629</v>
+        <v>0.000680532273525467</v>
       </c>
       <c r="H7">
-        <v>0.00181299809498742</v>
+        <v>0.0017675834595216088</v>
       </c>
       <c r="I7">
-        <v>-0.00026162236527246655</v>
+        <v>-0.00031800149849400556</v>
       </c>
       <c r="J7">
-        <v>-0.00041735847187467827</v>
+        <v>-0.00035730770497057265</v>
       </c>
       <c r="K7">
-        <v>4.305720949670425e-05</v>
+        <v>-7.1299625673885893e-05</v>
       </c>
       <c r="L7">
-        <v>0.00018963489964538875</v>
+        <v>0.00017791546362452398</v>
       </c>
       <c r="M7">
-        <v>0.00011965890061636016</v>
+        <v>0.00017748711483318749</v>
       </c>
       <c r="N7">
-        <v>1.3486121366241329e-06</v>
+        <v>9.2246638850741985e-05</v>
       </c>
       <c r="O7">
-        <v>-0.00059723368872112307</v>
+        <v>-1.0033900881950856e-05</v>
       </c>
       <c r="P7">
-        <v>-0.00062672655019994266</v>
+        <v>-0.00055594811043323798</v>
       </c>
       <c r="Q7">
-        <v>-0.00068159554447576461</v>
+        <v>-0.0005968163365091205</v>
       </c>
       <c r="R7">
-        <v>-0.00076840491580497188</v>
+        <v>-0.00062759782800493819</v>
       </c>
       <c r="S7">
-        <v>-0.00075609783866176184</v>
+        <v>-0.00071367430474530242</v>
       </c>
       <c r="T7">
-        <v>-0.00088185503902758603</v>
+        <v>-0.00068718656734830311</v>
       </c>
       <c r="U7">
-        <v>1.7053546738623702e-05</v>
+        <v>-0.00080606205724166222</v>
       </c>
       <c r="V7">
-        <v>0.00072219725086755595</v>
+        <v>1.7938312877005578e-05</v>
       </c>
       <c r="W7">
-        <v>-5.580709770888607e-05</v>
+        <v>0.000681015709006177</v>
       </c>
       <c r="X7">
-        <v>-0.0025789095078409237</v>
+        <v>-6.6910066608827498e-05</v>
+      </c>
+      <c r="Y7">
+        <v>-0.0024963474378844118</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="B8">
-        <v>0.93750421186777755</v>
+        <v>0.88240068225383161</v>
       </c>
       <c r="C8">
-        <v>-0.00011305708020917964</v>
+        <v>-8.1063753841659783e-05</v>
       </c>
       <c r="D8">
-        <v>6.5634448482752091e-05</v>
+        <v>9.4876232521119198e-05</v>
       </c>
       <c r="E8">
-        <v>-8.7410745276182499e-07</v>
+        <v>-1.2338079722596618e-06</v>
       </c>
       <c r="F8">
-        <v>-0.00031533583358902238</v>
+        <v>0.00062423123175528764</v>
       </c>
       <c r="G8">
-        <v>-5.5687918629306125e-05</v>
+        <v>-9.6072639578681924e-05</v>
       </c>
       <c r="H8">
-        <v>-0.00026162236527246655</v>
+        <v>-0.00031800149849400556</v>
       </c>
       <c r="I8">
-        <v>0.0030176555271030975</v>
+        <v>0.0027853340091008347</v>
       </c>
       <c r="J8">
-        <v>-0.0011360907547083307</v>
+        <v>-0.00094537463233203907</v>
       </c>
       <c r="K8">
-        <v>-0.00033461964570190967</v>
+        <v>-0.00071876140333863067</v>
       </c>
       <c r="L8">
-        <v>0.0015860052655194872</v>
+        <v>-0.00032425428048980798</v>
       </c>
       <c r="M8">
-        <v>0.0022032273785876806</v>
+        <v>0.0016163076863997536</v>
       </c>
       <c r="N8">
-        <v>0.0028372932368571297</v>
+        <v>0.0021330469390605745</v>
       </c>
       <c r="O8">
-        <v>0.00024959660832207971</v>
+        <v>0.0020857649806186426</v>
       </c>
       <c r="P8">
-        <v>9.4972354863021372e-05</v>
+        <v>0.00029339876302770054</v>
       </c>
       <c r="Q8">
-        <v>-9.0052503706154123e-05</v>
+        <v>0.00021783376752924758</v>
       </c>
       <c r="R8">
-        <v>0.00028447059687925673</v>
+        <v>-0.00010402386252439627</v>
       </c>
       <c r="S8">
-        <v>0.0002845578009622058</v>
+        <v>0.00027234897267728242</v>
       </c>
       <c r="T8">
-        <v>0.0003701180278214099</v>
+        <v>0.00032193448589291131</v>
       </c>
       <c r="U8">
-        <v>-8.5035544809324785e-07</v>
+        <v>0.00027991669108765678</v>
       </c>
       <c r="V8">
-        <v>-0.00037172107304085916</v>
+        <v>1.9654224180305869e-06</v>
       </c>
       <c r="W8">
-        <v>0.00037913961581995852</v>
+        <v>-0.00024572290684063457</v>
       </c>
       <c r="X8">
-        <v>-0.0038732700851372235</v>
+        <v>0.0003011311030279391</v>
+      </c>
+      <c r="Y8">
+        <v>-0.003487469223602763</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="B9">
-        <v>0.44489558192862527</v>
+        <v>0.50862489515676512</v>
       </c>
       <c r="C9">
-        <v>0.00034082808829945401</v>
+        <v>0.00031246276710245654</v>
       </c>
       <c r="D9">
-        <v>-2.5852937065833168e-05</v>
+        <v>-2.3288574146655997e-05</v>
       </c>
       <c r="E9">
-        <v>4.3759171861429675e-07</v>
+        <v>5.8752020289838951e-07</v>
       </c>
       <c r="F9">
-        <v>-0.00091752691421883345</v>
+        <v>-0.0012771216800244567</v>
       </c>
       <c r="G9">
-        <v>-5.752108105342029e-05</v>
+        <v>-7.3118765048290453e-05</v>
       </c>
       <c r="H9">
-        <v>-0.00041735847187467827</v>
+        <v>-0.00035730770497057265</v>
       </c>
       <c r="I9">
-        <v>-0.0011360907547083307</v>
+        <v>-0.00094537463233203907</v>
       </c>
       <c r="J9">
-        <v>0.0021071006990368247</v>
+        <v>0.0021306796076095871</v>
       </c>
       <c r="K9">
-        <v>0.00021467655957055202</v>
+        <v>0.0010376431506755417</v>
       </c>
       <c r="L9">
-        <v>-0.00097343630030568315</v>
+        <v>9.2978031368962918e-05</v>
       </c>
       <c r="M9">
-        <v>-0.001267175288682859</v>
+        <v>-0.00090092152075645852</v>
       </c>
       <c r="N9">
-        <v>-0.0016286367406073826</v>
+        <v>-0.0011923852172604319</v>
       </c>
       <c r="O9">
-        <v>0.00029198335029505316</v>
+        <v>-0.0011556430850975974</v>
       </c>
       <c r="P9">
-        <v>0.00049525873916396132</v>
+        <v>0.00019711794185986236</v>
       </c>
       <c r="Q9">
-        <v>0.0003179776587181325</v>
+        <v>0.0003381676734813441</v>
       </c>
       <c r="R9">
-        <v>0.00037859260144083499</v>
+        <v>0.00022810060676861616</v>
       </c>
       <c r="S9">
-        <v>0.00038904607666953844</v>
+        <v>0.00032686164515207978</v>
       </c>
       <c r="T9">
-        <v>0.00020380764841475675</v>
+        <v>0.00030774121592250806</v>
       </c>
       <c r="U9">
-        <v>4.3910361324551279e-06</v>
+        <v>0.00017500382813878619</v>
       </c>
       <c r="V9">
-        <v>-0.00036433122970908391</v>
+        <v>4.5244762591615326e-06</v>
       </c>
       <c r="W9">
-        <v>2.7994241299931422e-05</v>
+        <v>-0.00035887543075653329</v>
       </c>
       <c r="X9">
-        <v>0.00084423847422780772</v>
+        <v>7.9631939084227139e-05</v>
+      </c>
+      <c r="Y9">
+        <v>-0.00041532582422434353</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="B10">
-        <v>0.20644638256596629</v>
+        <v>0.062824125321721921</v>
       </c>
       <c r="C10">
-        <v>8.8915238200703369e-05</v>
+        <v>7.1563341028333955e-07</v>
       </c>
       <c r="D10">
-        <v>5.6815143964197148e-06</v>
+        <v>9.0180261914919149e-06</v>
       </c>
       <c r="E10">
-        <v>-1.0746646030948579e-07</v>
+        <v>5.9277725679184212e-07</v>
       </c>
       <c r="F10">
-        <v>8.293361062148629e-05</v>
+        <v>0.0021473487373343311</v>
       </c>
       <c r="G10">
-        <v>-0.00010808809285006185</v>
+        <v>-0.00015955481976579394</v>
       </c>
       <c r="H10">
-        <v>4.305720949670425e-05</v>
+        <v>-7.1299625673885893e-05</v>
       </c>
       <c r="I10">
-        <v>-0.00033461964570190967</v>
+        <v>-0.00071876140333863067</v>
       </c>
       <c r="J10">
-        <v>0.00021467655957055202</v>
+        <v>0.0010376431506755417</v>
       </c>
       <c r="K10">
-        <v>0.0023118429144961816</v>
+        <v>0.0052155293895569318</v>
       </c>
       <c r="L10">
-        <v>0.00086642935936201513</v>
+        <v>-0.0010435515599043425</v>
       </c>
       <c r="M10">
-        <v>0.00078057163660374376</v>
+        <v>-0.0016852931180749366</v>
       </c>
       <c r="N10">
-        <v>0.00084722437440853319</v>
+        <v>-0.0017858365530969494</v>
       </c>
       <c r="O10">
-        <v>-0.00029185670829086341</v>
+        <v>-0.0018835353579939383</v>
       </c>
       <c r="P10">
-        <v>-0.00032508693657849188</v>
+        <v>-0.00020709024025248983</v>
       </c>
       <c r="Q10">
-        <v>-0.00015643077917438356</v>
+        <v>-6.0307729310336844e-05</v>
       </c>
       <c r="R10">
-        <v>-0.00023469951494034676</v>
+        <v>-0.00023377844551455745</v>
       </c>
       <c r="S10">
-        <v>-0.00019163499080495527</v>
+        <v>-2.1041402402029955e-05</v>
       </c>
       <c r="T10">
-        <v>-0.00017424493903524338</v>
+        <v>-0.00011354907077451646</v>
       </c>
       <c r="U10">
-        <v>1.453275710173959e-05</v>
+        <v>-0.0001052570576502499</v>
       </c>
       <c r="V10">
-        <v>-6.1238467038893723e-05</v>
+        <v>1.2834677817794655e-05</v>
       </c>
       <c r="W10">
-        <v>-4.7476312130766835e-05</v>
+        <v>0.00027463581799472086</v>
       </c>
       <c r="X10">
-        <v>-0.0009377342215026094</v>
+        <v>1.8192177034559529e-05</v>
+      </c>
+      <c r="Y10">
+        <v>-0.0041275485985163719</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="B11">
-        <v>0.53941899967421436</v>
+        <v>0.20507627275525495</v>
       </c>
       <c r="C11">
-        <v>2.2518691298354271e-05</v>
+        <v>5.6951370814305671e-05</v>
       </c>
       <c r="D11">
-        <v>7.7808870106821566e-05</v>
+        <v>2.8702559232412559e-06</v>
       </c>
       <c r="E11">
-        <v>-9.8559503557207274e-07</v>
+        <v>-1.474679746621977e-08</v>
       </c>
       <c r="F11">
-        <v>-0.00060934318306670886</v>
+        <v>4.6739158331197919e-05</v>
       </c>
       <c r="G11">
-        <v>-5.6462045598308159e-05</v>
+        <v>-5.9336885674704633e-05</v>
       </c>
       <c r="H11">
-        <v>0.00018963489964538875</v>
+        <v>0.00017791546362452398</v>
       </c>
       <c r="I11">
-        <v>0.0015860052655194872</v>
+        <v>-0.00032425428048980798</v>
       </c>
       <c r="J11">
-        <v>-0.00097343630030568315</v>
+        <v>9.2978031368962918e-05</v>
       </c>
       <c r="K11">
-        <v>0.00086642935936201513</v>
+        <v>-0.0010435515599043425</v>
       </c>
       <c r="L11">
-        <v>0.0031098541093288407</v>
+        <v>0.0025153386144333534</v>
       </c>
       <c r="M11">
-        <v>0.0024332699258320175</v>
+        <v>0.0010070757911467081</v>
       </c>
       <c r="N11">
-        <v>0.0028959895500655459</v>
+        <v>0.00092403425173872027</v>
       </c>
       <c r="O11">
-        <v>-0.00065870874727564158</v>
+        <v>0.00099814197163227846</v>
       </c>
       <c r="P11">
-        <v>-0.00084032296268217194</v>
+        <v>-0.00016027233155606783</v>
       </c>
       <c r="Q11">
-        <v>-0.00080134447282981193</v>
+        <v>-0.00018868039949890582</v>
       </c>
       <c r="R11">
-        <v>-0.00056009537539158027</v>
+        <v>-0.00013127368460868908</v>
       </c>
       <c r="S11">
-        <v>-0.00058770908704499367</v>
+        <v>-0.00017139461431978727</v>
       </c>
       <c r="T11">
-        <v>-0.00035918477392987485</v>
+        <v>-0.00021630429639756267</v>
       </c>
       <c r="U11">
-        <v>-9.9355374871763541e-06</v>
+        <v>-0.00012771263925984245</v>
       </c>
       <c r="V11">
-        <v>0.00047931725768046946</v>
+        <v>9.5781027227741553e-06</v>
       </c>
       <c r="W11">
-        <v>0.00017878871810228037</v>
+        <v>-9.5631195171544744e-05</v>
       </c>
       <c r="X11">
-        <v>-0.0031997154103937738</v>
+        <v>2.2174538356529191e-06</v>
+      </c>
+      <c r="Y11">
+        <v>-4.6427733482111129e-06</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="B12">
-        <v>0.44037313553150431</v>
+        <v>0.56588094236109443</v>
       </c>
       <c r="C12">
-        <v>-0.00028463225949549085</v>
+        <v>6.163393883347053e-05</v>
       </c>
       <c r="D12">
-        <v>2.3600689169367818e-05</v>
+        <v>0.00013151457410522547</v>
       </c>
       <c r="E12">
-        <v>-3.6016174007484137e-07</v>
+        <v>-1.5665563521198577e-06</v>
       </c>
       <c r="F12">
-        <v>-0.00038016221606359624</v>
+        <v>0.00047854327119661004</v>
       </c>
       <c r="G12">
-        <v>9.5595119520046389e-05</v>
+        <v>-0.00021320012455623206</v>
       </c>
       <c r="H12">
-        <v>0.00011965890061636016</v>
+        <v>0.00017748711483318749</v>
       </c>
       <c r="I12">
-        <v>0.0022032273785876806</v>
+        <v>0.0016163076863997536</v>
       </c>
       <c r="J12">
-        <v>-0.001267175288682859</v>
+        <v>-0.00090092152075645852</v>
       </c>
       <c r="K12">
-        <v>0.00078057163660374376</v>
+        <v>-0.0016852931180749366</v>
       </c>
       <c r="L12">
-        <v>0.0024332699258320175</v>
+        <v>0.0010070757911467081</v>
       </c>
       <c r="M12">
-        <v>0.0039898763579951646</v>
+        <v>0.0035925135373305159</v>
       </c>
       <c r="N12">
-        <v>0.0033631888046579067</v>
+        <v>0.0025195095463350871</v>
       </c>
       <c r="O12">
-        <v>-0.00027149617315768391</v>
+        <v>0.0026022526483639955</v>
       </c>
       <c r="P12">
-        <v>-0.0005273057718902267</v>
+        <v>-0.00055207273872114743</v>
       </c>
       <c r="Q12">
-        <v>-0.00028772734838074503</v>
+        <v>-0.00064604810338496875</v>
       </c>
       <c r="R12">
-        <v>-0.00020113951451158647</v>
+        <v>-0.00084304375843041366</v>
       </c>
       <c r="S12">
-        <v>-0.00015263942728835855</v>
+        <v>-0.00057107519179745215</v>
       </c>
       <c r="T12">
-        <v>-1.202917384056628e-05</v>
+        <v>-0.00058736318493038983</v>
       </c>
       <c r="U12">
-        <v>8.1396332543183519e-06</v>
+        <v>-0.00042980534315882748</v>
       </c>
       <c r="V12">
-        <v>-0.0002246066967197081</v>
+        <v>-1.0400534137344e-05</v>
       </c>
       <c r="W12">
-        <v>0.00011122971900492636</v>
+        <v>0.0006335686073692668</v>
       </c>
       <c r="X12">
-        <v>-0.0033092744992974281</v>
+        <v>0.00016148908529449479</v>
+      </c>
+      <c r="Y12">
+        <v>-0.0026243136545142766</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>41</v>
+        <v>56</v>
       </c>
       <c r="B13">
-        <v>0.57537425577030532</v>
+        <v>0.40372331919932747</v>
       </c>
       <c r="C13">
-        <v>-8.9750651379478879e-05</v>
+        <v>-0.00028430402506798586</v>
       </c>
       <c r="D13">
-        <v>5.4331762009441785e-05</v>
+        <v>8.0832347714027088e-05</v>
       </c>
       <c r="E13">
-        <v>-8.2476281307687229e-07</v>
+        <v>-1.0851384269550113e-06</v>
       </c>
       <c r="F13">
-        <v>-0.00012187286941909301</v>
+        <v>0.00080693434766852909</v>
       </c>
       <c r="G13">
-        <v>-0.0002902814960097272</v>
+        <v>6.4205442760298856e-05</v>
       </c>
       <c r="H13">
-        <v>1.3486121366241329e-06</v>
+        <v>9.2246638850741985e-05</v>
       </c>
       <c r="I13">
-        <v>0.0028372932368571297</v>
+        <v>0.0021330469390605745</v>
       </c>
       <c r="J13">
-        <v>-0.0016286367406073826</v>
+        <v>-0.0011923852172604319</v>
       </c>
       <c r="K13">
-        <v>0.00084722437440853319</v>
+        <v>-0.0017858365530969494</v>
       </c>
       <c r="L13">
-        <v>0.0028959895500655459</v>
+        <v>0.00092403425173872027</v>
       </c>
       <c r="M13">
-        <v>0.0033631888046579067</v>
+        <v>0.0025195095463350871</v>
       </c>
       <c r="N13">
-        <v>0.005664106867557272</v>
+        <v>0.0044388269900471535</v>
       </c>
       <c r="O13">
-        <v>-0.00035623509574636081</v>
+        <v>0.0028932231149928649</v>
       </c>
       <c r="P13">
-        <v>-0.00073096015111432386</v>
+        <v>-6.3751775583421183e-05</v>
       </c>
       <c r="Q13">
-        <v>-0.0007576090463308271</v>
+        <v>-0.00027946823919115186</v>
       </c>
       <c r="R13">
-        <v>-0.00023895471369643788</v>
+        <v>-0.00030097311906708487</v>
       </c>
       <c r="S13">
-        <v>-0.00031958515481583663</v>
+        <v>-0.00010320037531346294</v>
       </c>
       <c r="T13">
-        <v>0.00011544528608480552</v>
+        <v>1.0768937617047807e-05</v>
       </c>
       <c r="U13">
-        <v>6.2240642530676424e-06</v>
+        <v>-1.9326130090205275e-05</v>
       </c>
       <c r="V13">
-        <v>-0.00023805746492108119</v>
+        <v>1.5416006316748464e-05</v>
       </c>
       <c r="W13">
-        <v>0.00038347599303256751</v>
+        <v>-0.00022414732656238294</v>
       </c>
       <c r="X13">
-        <v>-0.0042414041325411619</v>
+        <v>-1.3042622593203122e-05</v>
+      </c>
+      <c r="Y13">
+        <v>-0.0027245869154106902</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>42</v>
+        <v>57</v>
       </c>
       <c r="B14">
-        <v>0.033285856404519601</v>
+        <v>0.52558481720123407</v>
       </c>
       <c r="C14">
-        <v>-0.00013847242554323102</v>
+        <v>-3.8920722602061317e-05</v>
       </c>
       <c r="D14">
-        <v>-9.1506885663547154e-05</v>
+        <v>0.00010495530435479061</v>
       </c>
       <c r="E14">
-        <v>1.0633376342336799e-06</v>
+        <v>-1.3472814414901277e-06</v>
       </c>
       <c r="F14">
-        <v>0.00033803621963605229</v>
+        <v>0.00078578284075701203</v>
       </c>
       <c r="G14">
-        <v>-3.233330550941226e-05</v>
+        <v>-0.00038931906896025152</v>
       </c>
       <c r="H14">
-        <v>-0.00059723368872112307</v>
+        <v>-1.0033900881950856e-05</v>
       </c>
       <c r="I14">
-        <v>0.00024959660832207971</v>
+        <v>0.0020857649806186426</v>
       </c>
       <c r="J14">
-        <v>0.00029198335029505316</v>
+        <v>-0.0011556430850975974</v>
       </c>
       <c r="K14">
-        <v>-0.00029185670829086341</v>
+        <v>-0.0018835353579939383</v>
       </c>
       <c r="L14">
-        <v>-0.00065870874727564158</v>
+        <v>0.00099814197163227846</v>
       </c>
       <c r="M14">
-        <v>-0.00027149617315768391</v>
+        <v>0.0026022526483639955</v>
       </c>
       <c r="N14">
-        <v>-0.00035623509574636081</v>
+        <v>0.0028932231149928649</v>
       </c>
       <c r="O14">
-        <v>0.0073552671818671771</v>
+        <v>0.0046079352816521821</v>
       </c>
       <c r="P14">
-        <v>0.0057566436128687164</v>
+        <v>-9.7391629985936088e-05</v>
       </c>
       <c r="Q14">
-        <v>0.0057718667346482074</v>
+        <v>-0.00038392716413407206</v>
       </c>
       <c r="R14">
-        <v>0.0057541536294530189</v>
+        <v>-0.00065603110943298053</v>
       </c>
       <c r="S14">
-        <v>0.0057560776808683357</v>
+        <v>-0.00011487346041136174</v>
       </c>
       <c r="T14">
-        <v>0.0057331526139639778</v>
+        <v>-0.00021756515072675638</v>
       </c>
       <c r="U14">
-        <v>4.3742425236167177e-07</v>
+        <v>-3.1091163906007491e-05</v>
       </c>
       <c r="V14">
-        <v>-0.0026664312010428294</v>
+        <v>2.9149505368856926e-06</v>
       </c>
       <c r="W14">
-        <v>4.3547638806642683e-05</v>
+        <v>-4.4976876999621536e-05</v>
       </c>
       <c r="X14">
-        <v>-0.0036648491749037078</v>
+        <v>0.00030145806844779854</v>
+      </c>
+      <c r="Y14">
+        <v>-0.0027132550064114126</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="B15">
-        <v>0.017177556497424237</v>
+        <v>0.03599476316905309</v>
       </c>
       <c r="C15">
-        <v>-0.00011221579967702337</v>
+        <v>-0.0001272440148656675</v>
       </c>
       <c r="D15">
-        <v>-7.981290981518268e-05</v>
+        <v>-9.1215287004425393e-05</v>
       </c>
       <c r="E15">
-        <v>9.8326912203852812e-07</v>
+        <v>9.7506969981564834e-07</v>
       </c>
       <c r="F15">
-        <v>0.0002719930433817022</v>
+        <v>-3.4310570273278973e-05</v>
       </c>
       <c r="G15">
-        <v>-0.00015333856084332988</v>
+        <v>-4.6567481123565755e-05</v>
       </c>
       <c r="H15">
-        <v>-0.00062672655019994266</v>
+        <v>-0.00055594811043323798</v>
       </c>
       <c r="I15">
-        <v>9.4972354863021372e-05</v>
+        <v>0.00029339876302770054</v>
       </c>
       <c r="J15">
-        <v>0.00049525873916396132</v>
+        <v>0.00019711794185986236</v>
       </c>
       <c r="K15">
-        <v>-0.00032508693657849188</v>
+        <v>-0.00020709024025248983</v>
       </c>
       <c r="L15">
-        <v>-0.00084032296268217194</v>
+        <v>-0.00016027233155606783</v>
       </c>
       <c r="M15">
-        <v>-0.0005273057718902267</v>
+        <v>-0.00055207273872114743</v>
       </c>
       <c r="N15">
-        <v>-0.00073096015111432386</v>
+        <v>-6.3751775583421183e-05</v>
       </c>
       <c r="O15">
-        <v>0.0057566436128687164</v>
+        <v>-9.7391629985936088e-05</v>
       </c>
       <c r="P15">
-        <v>0.0074014646283387595</v>
+        <v>0.0070426821646098099</v>
       </c>
       <c r="Q15">
-        <v>0.0057848357929516309</v>
+        <v>0.005452479925508992</v>
       </c>
       <c r="R15">
-        <v>0.005768353693555146</v>
+        <v>0.005479399361265104</v>
       </c>
       <c r="S15">
-        <v>0.0057641655154606671</v>
+        <v>0.0054674720206037125</v>
       </c>
       <c r="T15">
-        <v>0.0057171600518556142</v>
+        <v>0.0054602649991082408</v>
       </c>
       <c r="U15">
-        <v>-5.5314161728314652e-08</v>
+        <v>0.005458462947622483</v>
       </c>
       <c r="V15">
-        <v>-0.0026377364984271805</v>
+        <v>1.2549130221555318e-06</v>
       </c>
       <c r="W15">
-        <v>8.0817208774079143e-05</v>
+        <v>-0.0025255690968857447</v>
       </c>
       <c r="X15">
-        <v>-0.0036737343105442094</v>
+        <v>5.1781904114311071e-05</v>
+      </c>
+      <c r="Y15">
+        <v>-0.003321732270885835</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="B16">
-        <v>0.063152380159758201</v>
+        <v>0.044258403960604147</v>
       </c>
       <c r="C16">
-        <v>-0.00029295302450764812</v>
+        <v>-0.0001258362640066954</v>
       </c>
       <c r="D16">
-        <v>-0.00014872351794657432</v>
+        <v>-8.1986137076854463e-05</v>
       </c>
       <c r="E16">
-        <v>1.7113118790426884e-06</v>
+        <v>9.2107002652559397e-07</v>
       </c>
       <c r="F16">
-        <v>0.00033106935769794908</v>
+        <v>-8.3773754025549395e-05</v>
       </c>
       <c r="G16">
-        <v>0.00019725082795417023</v>
+        <v>-0.00020260008679467696</v>
       </c>
       <c r="H16">
-        <v>-0.00068159554447576461</v>
+        <v>-0.0005968163365091205</v>
       </c>
       <c r="I16">
-        <v>-9.0052503706154123e-05</v>
+        <v>0.00021783376752924758</v>
       </c>
       <c r="J16">
-        <v>0.0003179776587181325</v>
+        <v>0.0003381676734813441</v>
       </c>
       <c r="K16">
-        <v>-0.00015643077917438356</v>
+        <v>-6.0307729310336844e-05</v>
       </c>
       <c r="L16">
-        <v>-0.00080134447282981193</v>
+        <v>-0.00018868039949890582</v>
       </c>
       <c r="M16">
-        <v>-0.00028772734838074503</v>
+        <v>-0.00064604810338496875</v>
       </c>
       <c r="N16">
-        <v>-0.0007576090463308271</v>
+        <v>-0.00027946823919115186</v>
       </c>
       <c r="O16">
-        <v>0.0057718667346482074</v>
+        <v>-0.00038392716413407206</v>
       </c>
       <c r="P16">
-        <v>0.0057848357929516309</v>
+        <v>0.005452479925508992</v>
       </c>
       <c r="Q16">
-        <v>0.0076134513863191228</v>
+        <v>0.007107942109433254</v>
       </c>
       <c r="R16">
-        <v>0.0057871303408496564</v>
+        <v>0.0054459425061614041</v>
       </c>
       <c r="S16">
-        <v>0.0057484446472102864</v>
+        <v>0.0054650630779987342</v>
       </c>
       <c r="T16">
-        <v>0.0057692718753511842</v>
+        <v>0.0054416088525621664</v>
       </c>
       <c r="U16">
-        <v>4.5736760741217603e-06</v>
+        <v>0.0054431742454100901</v>
       </c>
       <c r="V16">
-        <v>-0.0028176159796168675</v>
+        <v>1.9150951430091102e-06</v>
       </c>
       <c r="W16">
-        <v>-0.00020145030779158881</v>
+        <v>-0.002494602496549416</v>
       </c>
       <c r="X16">
-        <v>-0.0024157867628509886</v>
+        <v>0.00010252968144034954</v>
+      </c>
+      <c r="Y16">
+        <v>-0.0034873334334948815</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="B17">
-        <v>-0.11173185004290141</v>
+        <v>0.092221804718539482</v>
       </c>
       <c r="C17">
-        <v>-9.9370182917451902e-05</v>
+        <v>-0.00028059841346779219</v>
       </c>
       <c r="D17">
-        <v>-9.4522262570792027e-05</v>
+        <v>-0.00015169138433165601</v>
       </c>
       <c r="E17">
-        <v>1.1294189529173196e-06</v>
+        <v>1.6461081322127421e-06</v>
       </c>
       <c r="F17">
-        <v>0.00022582791828269387</v>
+        <v>-0.00021048657108744927</v>
       </c>
       <c r="G17">
-        <v>1.7390659400292393e-05</v>
+        <v>0.00020720516706782349</v>
       </c>
       <c r="H17">
-        <v>-0.00076840491580497188</v>
+        <v>-0.00062759782800493819</v>
       </c>
       <c r="I17">
-        <v>0.00028447059687925673</v>
+        <v>-0.00010402386252439627</v>
       </c>
       <c r="J17">
-        <v>0.00037859260144083499</v>
+        <v>0.00022810060676861616</v>
       </c>
       <c r="K17">
-        <v>-0.00023469951494034676</v>
+        <v>-0.00023377844551455745</v>
       </c>
       <c r="L17">
-        <v>-0.00056009537539158027</v>
+        <v>-0.00013127368460868908</v>
       </c>
       <c r="M17">
-        <v>-0.00020113951451158647</v>
+        <v>-0.00084304375843041366</v>
       </c>
       <c r="N17">
-        <v>-0.00023895471369643788</v>
+        <v>-0.00030097311906708487</v>
       </c>
       <c r="O17">
-        <v>0.0057541536294530189</v>
+        <v>-0.00065603110943298053</v>
       </c>
       <c r="P17">
-        <v>0.005768353693555146</v>
+        <v>0.005479399361265104</v>
       </c>
       <c r="Q17">
-        <v>0.0057871303408496564</v>
+        <v>0.0054459425061614041</v>
       </c>
       <c r="R17">
-        <v>0.0070466363198167115</v>
+        <v>0.0073673182871146926</v>
       </c>
       <c r="S17">
-        <v>0.0057996176813646157</v>
+        <v>0.0054877605295059629</v>
       </c>
       <c r="T17">
-        <v>0.0058185640541186931</v>
+        <v>0.0054376312522572421</v>
       </c>
       <c r="U17">
-        <v>-6.3104088685286868e-06</v>
+        <v>0.0054883388714956072</v>
       </c>
       <c r="V17">
-        <v>-0.0027234798389865695</v>
+        <v>-4.0996526764122405e-08</v>
       </c>
       <c r="W17">
-        <v>8.8480518575858626e-05</v>
+        <v>-0.00266705419263256</v>
       </c>
       <c r="X17">
-        <v>-0.003623998948298306</v>
+        <v>-0.00016548747466676095</v>
+      </c>
+      <c r="Y17">
+        <v>-0.001760955861341986</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="B18">
-        <v>-0.028060130339037249</v>
+        <v>-0.094789889994195659</v>
       </c>
       <c r="C18">
-        <v>-0.00022817471093144933</v>
+        <v>-8.8746447275772633e-05</v>
       </c>
       <c r="D18">
-        <v>-9.9054917092345645e-05</v>
+        <v>-8.8691890284921639e-05</v>
       </c>
       <c r="E18">
-        <v>1.1732345985135603e-06</v>
+        <v>1.0174459094892041e-06</v>
       </c>
       <c r="F18">
-        <v>0.00011801533174869087</v>
+        <v>9.5832187450274825e-06</v>
       </c>
       <c r="G18">
-        <v>8.7714028910309213e-05</v>
+        <v>-1.1949118283552471e-05</v>
       </c>
       <c r="H18">
-        <v>-0.00075609783866176184</v>
+        <v>-0.00071367430474530242</v>
       </c>
       <c r="I18">
-        <v>0.0002845578009622058</v>
+        <v>0.00027234897267728242</v>
       </c>
       <c r="J18">
-        <v>0.00038904607666953844</v>
+        <v>0.00032686164515207978</v>
       </c>
       <c r="K18">
-        <v>-0.00019163499080495527</v>
+        <v>-2.1041402402029955e-05</v>
       </c>
       <c r="L18">
-        <v>-0.00058770908704499367</v>
+        <v>-0.00017139461431978727</v>
       </c>
       <c r="M18">
-        <v>-0.00015263942728835855</v>
+        <v>-0.00057107519179745215</v>
       </c>
       <c r="N18">
-        <v>-0.00031958515481583663</v>
+        <v>-0.00010320037531346294</v>
       </c>
       <c r="O18">
-        <v>0.0057560776808683357</v>
+        <v>-0.00011487346041136174</v>
       </c>
       <c r="P18">
-        <v>0.0057641655154606671</v>
+        <v>0.0054674720206037125</v>
       </c>
       <c r="Q18">
-        <v>0.0057484446472102864</v>
+        <v>0.0054650630779987342</v>
       </c>
       <c r="R18">
-        <v>0.0057996176813646157</v>
+        <v>0.0054877605295059629</v>
       </c>
       <c r="S18">
-        <v>0.0067756277049650466</v>
+        <v>0.0067547577986824623</v>
       </c>
       <c r="T18">
-        <v>0.0057935992253189969</v>
+        <v>0.0055056274147274459</v>
       </c>
       <c r="U18">
-        <v>7.9648020267373345e-06</v>
+        <v>0.0055311157510140856</v>
       </c>
       <c r="V18">
-        <v>-0.0028540982183731392</v>
+        <v>-5.9274517183892015e-06</v>
       </c>
       <c r="W18">
-        <v>-0.0001234594939325262</v>
+        <v>-0.0025677321170878126</v>
       </c>
       <c r="X18">
-        <v>-0.0037044019217954867</v>
+        <v>9.854709671889856e-05</v>
+      </c>
+      <c r="Y18">
+        <v>-0.003465429394507107</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="B19">
-        <v>-0.099116672791960486</v>
+        <v>-0.0073717591759501792</v>
       </c>
       <c r="C19">
-        <v>-0.00010821631387866433</v>
+        <v>-0.00021032298716303581</v>
       </c>
       <c r="D19">
-        <v>-8.3885481310229805e-05</v>
+        <v>-8.8940442469525861e-05</v>
       </c>
       <c r="E19">
-        <v>1.0223614038889259e-06</v>
+        <v>1.0136663447692557e-06</v>
       </c>
       <c r="F19">
-        <v>0.00022810414041111613</v>
+        <v>-0.00021354848745518406</v>
       </c>
       <c r="G19">
-        <v>-9.6561788926988624e-06</v>
+        <v>9.2102223806946818e-05</v>
       </c>
       <c r="H19">
-        <v>-0.00088185503902758603</v>
+        <v>-0.00068718656734830311</v>
       </c>
       <c r="I19">
-        <v>0.0003701180278214099</v>
+        <v>0.00032193448589291131</v>
       </c>
       <c r="J19">
-        <v>0.00020380764841475675</v>
+        <v>0.00030774121592250806</v>
       </c>
       <c r="K19">
-        <v>-0.00017424493903524338</v>
+        <v>-0.00011354907077451646</v>
       </c>
       <c r="L19">
-        <v>-0.00035918477392987485</v>
+        <v>-0.00021630429639756267</v>
       </c>
       <c r="M19">
-        <v>-1.202917384056628e-05</v>
+        <v>-0.00058736318493038983</v>
       </c>
       <c r="N19">
-        <v>0.00011544528608480552</v>
+        <v>1.0768937617047807e-05</v>
       </c>
       <c r="O19">
-        <v>0.0057331526139639778</v>
+        <v>-0.00021756515072675638</v>
       </c>
       <c r="P19">
-        <v>0.0057171600518556142</v>
+        <v>0.0054602649991082408</v>
       </c>
       <c r="Q19">
-        <v>0.0057692718753511842</v>
+        <v>0.0054416088525621664</v>
       </c>
       <c r="R19">
-        <v>0.0058185640541186931</v>
+        <v>0.0054376312522572421</v>
       </c>
       <c r="S19">
-        <v>0.0057935992253189969</v>
+        <v>0.0055056274147274459</v>
       </c>
       <c r="T19">
-        <v>0.0069149117910419682</v>
+        <v>0.0064996061383945673</v>
       </c>
       <c r="U19">
-        <v>-4.1628717525110849e-06</v>
+        <v>0.0055097964840980949</v>
       </c>
       <c r="V19">
-        <v>-0.0026258835697140297</v>
+        <v>9.1236745013298983e-06</v>
       </c>
       <c r="W19">
-        <v>-6.6630248629776304e-05</v>
+        <v>-0.0027037196405103377</v>
       </c>
       <c r="X19">
-        <v>-0.0039541082576806195</v>
+        <v>-0.0001306247967186318</v>
+      </c>
+      <c r="Y19">
+        <v>-0.0035828098564641051</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="B20">
-        <v>0.0059025714645199994</v>
+        <v>-0.088340340959206676</v>
       </c>
       <c r="C20">
-        <v>-6.9321024940633276e-06</v>
+        <v>-8.4927106182090215e-05</v>
       </c>
       <c r="D20">
-        <v>7.5202704928168751e-07</v>
+        <v>-7.8505525698549831e-05</v>
       </c>
       <c r="E20">
-        <v>-8.4777212930309144e-09</v>
+        <v>9.1302955964055782e-07</v>
       </c>
       <c r="F20">
-        <v>2.0459051801049969e-05</v>
+        <v>9.9091381182424387e-05</v>
       </c>
       <c r="G20">
-        <v>6.8518628871108378e-06</v>
+        <v>1.6757822339950098e-05</v>
       </c>
       <c r="H20">
-        <v>1.7053546738623702e-05</v>
+        <v>-0.00080606205724166222</v>
       </c>
       <c r="I20">
-        <v>-8.5035544809324785e-07</v>
+        <v>0.00027991669108765678</v>
       </c>
       <c r="J20">
-        <v>4.3910361324551279e-06</v>
+        <v>0.00017500382813878619</v>
       </c>
       <c r="K20">
-        <v>1.453275710173959e-05</v>
+        <v>-0.0001052570576502499</v>
       </c>
       <c r="L20">
-        <v>-9.9355374871763541e-06</v>
+        <v>-0.00012771263925984245</v>
       </c>
       <c r="M20">
-        <v>8.1396332543183519e-06</v>
+        <v>-0.00042980534315882748</v>
       </c>
       <c r="N20">
-        <v>6.2240642530676424e-06</v>
+        <v>-1.9326130090205275e-05</v>
       </c>
       <c r="O20">
-        <v>4.3742425236167177e-07</v>
+        <v>-3.1091163906007491e-05</v>
       </c>
       <c r="P20">
-        <v>-5.5314161728314652e-08</v>
+        <v>0.005458462947622483</v>
       </c>
       <c r="Q20">
-        <v>4.5736760741217603e-06</v>
+        <v>0.0054431742454100901</v>
       </c>
       <c r="R20">
-        <v>-6.3104088685286868e-06</v>
+        <v>0.0054883388714956072</v>
       </c>
       <c r="S20">
-        <v>7.9648020267373345e-06</v>
+        <v>0.0055311157510140856</v>
       </c>
       <c r="T20">
-        <v>-4.1628717525110849e-06</v>
+        <v>0.0055097964840980949</v>
       </c>
       <c r="U20">
-        <v>1.4955456692080656e-05</v>
+        <v>0.0066193279181228533</v>
       </c>
       <c r="V20">
-        <v>-6.7605363243405136e-05</v>
+        <v>-4.2244500734245122e-06</v>
       </c>
       <c r="W20">
-        <v>-8.0751454120666689e-05</v>
+        <v>-0.0024581312581667346</v>
       </c>
       <c r="X20">
-        <v>-0.00027202396336519093</v>
+        <v>-6.9574852559287689e-05</v>
+      </c>
+      <c r="Y20">
+        <v>-0.0036288100415798573</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="B21">
-        <v>0.15841378114189855</v>
+        <v>0.0042459895358568948</v>
       </c>
       <c r="C21">
-        <v>0.00040157041528798257</v>
+        <v>-7.4284829859226058e-06</v>
       </c>
       <c r="D21">
-        <v>0.00013649220948483475</v>
+        <v>1.8718287569234626e-06</v>
       </c>
       <c r="E21">
-        <v>-1.4995439368411866e-06</v>
+        <v>-1.9154560661216716e-08</v>
       </c>
       <c r="F21">
-        <v>-0.00027644164177490567</v>
+        <v>2.4506231728311594e-05</v>
       </c>
       <c r="G21">
-        <v>-0.00033019620567532307</v>
+        <v>6.2149674749857797e-06</v>
       </c>
       <c r="H21">
-        <v>0.00072219725086755595</v>
+        <v>1.7938312877005578e-05</v>
       </c>
       <c r="I21">
-        <v>-0.00037172107304085916</v>
+        <v>1.9654224180305869e-06</v>
       </c>
       <c r="J21">
-        <v>-0.00036433122970908391</v>
+        <v>4.5244762591615326e-06</v>
       </c>
       <c r="K21">
-        <v>-6.1238467038893723e-05</v>
+        <v>1.2834677817794655e-05</v>
       </c>
       <c r="L21">
-        <v>0.00047931725768046946</v>
+        <v>9.5781027227741553e-06</v>
       </c>
       <c r="M21">
-        <v>-0.0002246066967197081</v>
+        <v>-1.0400534137344e-05</v>
       </c>
       <c r="N21">
-        <v>-0.00023805746492108119</v>
+        <v>1.5416006316748464e-05</v>
       </c>
       <c r="O21">
-        <v>-0.0026664312010428294</v>
+        <v>2.9149505368856926e-06</v>
       </c>
       <c r="P21">
-        <v>-0.0026377364984271805</v>
+        <v>1.2549130221555318e-06</v>
       </c>
       <c r="Q21">
-        <v>-0.0028176159796168675</v>
+        <v>1.9150951430091102e-06</v>
       </c>
       <c r="R21">
-        <v>-0.0027234798389865695</v>
+        <v>-4.0996526764122405e-08</v>
       </c>
       <c r="S21">
-        <v>-0.0028540982183731392</v>
+        <v>-5.9274517183892015e-06</v>
       </c>
       <c r="T21">
-        <v>-0.0026258835697140297</v>
+        <v>9.1236745013298983e-06</v>
       </c>
       <c r="U21">
-        <v>-6.7605363243405136e-05</v>
+        <v>-4.2244500734245122e-06</v>
       </c>
       <c r="V21">
-        <v>0.0067794907749155536</v>
+        <v>1.5046259140723323e-05</v>
       </c>
       <c r="W21">
-        <v>0.00058562618029462917</v>
+        <v>-6.8053789857073431e-05</v>
       </c>
       <c r="X21">
-        <v>0.00093428246179980514</v>
+        <v>-8.1808312931679484e-05</v>
+      </c>
+      <c r="Y21">
+        <v>-0.00030721928869568917</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="B22">
-        <v>-0.0019375779580146401</v>
+        <v>0.1680229012196536</v>
       </c>
       <c r="C22">
-        <v>5.6577398037686562e-05</v>
+        <v>0.00036498752517602598</v>
       </c>
       <c r="D22">
-        <v>-5.0547253262777682e-06</v>
+        <v>0.00013893625442215705</v>
       </c>
       <c r="E22">
-        <v>3.1812329163913154e-09</v>
+        <v>-1.4747777881904504e-06</v>
       </c>
       <c r="F22">
-        <v>-0.00013432855475457601</v>
+        <v>-3.8005146034112184e-06</v>
       </c>
       <c r="G22">
-        <v>-0.00021823713896273526</v>
+        <v>-0.00034264963633000848</v>
       </c>
       <c r="H22">
-        <v>-5.580709770888607e-05</v>
+        <v>0.000681015709006177</v>
       </c>
       <c r="I22">
-        <v>0.00037913961581995852</v>
+        <v>-0.00024572290684063457</v>
       </c>
       <c r="J22">
-        <v>2.7994241299931422e-05</v>
+        <v>-0.00035887543075653329</v>
       </c>
       <c r="K22">
-        <v>-4.7476312130766835e-05</v>
+        <v>0.00027463581799472086</v>
       </c>
       <c r="L22">
-        <v>0.00017878871810228037</v>
+        <v>-9.5631195171544744e-05</v>
       </c>
       <c r="M22">
-        <v>0.00011122971900492636</v>
+        <v>0.0006335686073692668</v>
       </c>
       <c r="N22">
-        <v>0.00038347599303256751</v>
+        <v>-0.00022414732656238294</v>
       </c>
       <c r="O22">
-        <v>4.3547638806642683e-05</v>
+        <v>-4.4976876999621536e-05</v>
       </c>
       <c r="P22">
-        <v>8.0817208774079143e-05</v>
+        <v>-0.0025255690968857447</v>
       </c>
       <c r="Q22">
-        <v>-0.00020145030779158881</v>
+        <v>-0.002494602496549416</v>
       </c>
       <c r="R22">
-        <v>8.8480518575858626e-05</v>
+        <v>-0.00266705419263256</v>
       </c>
       <c r="S22">
-        <v>-0.0001234594939325262</v>
+        <v>-0.0025677321170878126</v>
       </c>
       <c r="T22">
-        <v>-6.6630248629776304e-05</v>
+        <v>-0.0027037196405103377</v>
       </c>
       <c r="U22">
-        <v>-8.0751454120666689e-05</v>
+        <v>-0.0024581312581667346</v>
       </c>
       <c r="V22">
-        <v>0.00058562618029462917</v>
+        <v>-6.8053789857073431e-05</v>
       </c>
       <c r="W22">
-        <v>0.003445720518748828</v>
+        <v>0.0067216802368352821</v>
       </c>
       <c r="X22">
-        <v>0.00095807992966701842</v>
+        <v>0.00060419941114705849</v>
+      </c>
+      <c r="Y22">
+        <v>0.00038014457003501291</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="B23">
-        <v>3.374888349881024</v>
+        <v>0.0049283868603328951</v>
       </c>
       <c r="C23">
-        <v>-0.00072011313282233916</v>
+        <v>5.6239799266668124e-05</v>
       </c>
       <c r="D23">
-        <v>-0.0011345328519525664</v>
+        <v>-7.4758246378438557e-06</v>
       </c>
       <c r="E23">
-        <v>1.2160635972344815e-05</v>
+        <v>4.0474610557441579e-08</v>
       </c>
       <c r="F23">
-        <v>0.0022417792098019958</v>
+        <v>7.2996454601882807e-06</v>
       </c>
       <c r="G23">
-        <v>0.00044527321146397973</v>
+        <v>-0.0002285344336820779</v>
       </c>
       <c r="H23">
-        <v>-0.0025789095078409237</v>
+        <v>-6.6910066608827498e-05</v>
       </c>
       <c r="I23">
-        <v>-0.0038732700851372235</v>
+        <v>0.0003011311030279391</v>
       </c>
       <c r="J23">
-        <v>0.00084423847422780772</v>
+        <v>7.9631939084227139e-05</v>
       </c>
       <c r="K23">
-        <v>-0.0009377342215026094</v>
+        <v>1.8192177034559529e-05</v>
       </c>
       <c r="L23">
-        <v>-0.0031997154103937738</v>
+        <v>2.2174538356529191e-06</v>
       </c>
       <c r="M23">
-        <v>-0.0033092744992974281</v>
+        <v>0.00016148908529449479</v>
       </c>
       <c r="N23">
-        <v>-0.0042414041325411619</v>
+        <v>-1.3042622593203122e-05</v>
       </c>
       <c r="O23">
-        <v>-0.0036648491749037078</v>
+        <v>0.00030145806844779854</v>
       </c>
       <c r="P23">
-        <v>-0.0036737343105442094</v>
+        <v>5.1781904114311071e-05</v>
       </c>
       <c r="Q23">
-        <v>-0.0024157867628509886</v>
+        <v>0.00010252968144034954</v>
       </c>
       <c r="R23">
-        <v>-0.003623998948298306</v>
+        <v>-0.00016548747466676095</v>
       </c>
       <c r="S23">
-        <v>-0.0037044019217954867</v>
+        <v>9.854709671889856e-05</v>
       </c>
       <c r="T23">
-        <v>-0.0039541082576806195</v>
+        <v>-0.0001306247967186318</v>
       </c>
       <c r="U23">
-        <v>-0.00027202396336519093</v>
+        <v>-6.9574852559287689e-05</v>
       </c>
       <c r="V23">
-        <v>0.00093428246179980514</v>
+        <v>-8.1808312931679484e-05</v>
       </c>
       <c r="W23">
-        <v>0.00095807992966701842</v>
+        <v>0.00060419941114705849</v>
       </c>
       <c r="X23">
-        <v>0.03417419939313867</v>
+        <v>0.0035089251266576227</v>
+      </c>
+      <c r="Y23">
+        <v>0.001055500915242993</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s">
+        <v>41</v>
+      </c>
+      <c r="B24">
+        <v>3.1475096552301176</v>
+      </c>
+      <c r="C24">
+        <v>-0.00064044979056054299</v>
+      </c>
+      <c r="D24">
+        <v>-0.0012660470943110626</v>
+      </c>
+      <c r="E24">
+        <v>1.264992356475351e-05</v>
+      </c>
+      <c r="F24">
+        <v>-0.0016152239097772293</v>
+      </c>
+      <c r="G24">
+        <v>0.00071567774325853833</v>
+      </c>
+      <c r="H24">
+        <v>-0.0024963474378844118</v>
+      </c>
+      <c r="I24">
+        <v>-0.003487469223602763</v>
+      </c>
+      <c r="J24">
+        <v>-0.00041532582422434353</v>
+      </c>
+      <c r="K24">
+        <v>-0.0041275485985163719</v>
+      </c>
+      <c r="L24">
+        <v>-4.6427733482111129e-06</v>
+      </c>
+      <c r="M24">
+        <v>-0.0026243136545142766</v>
+      </c>
+      <c r="N24">
+        <v>-0.0027245869154106902</v>
+      </c>
+      <c r="O24">
+        <v>-0.0027132550064114126</v>
+      </c>
+      <c r="P24">
+        <v>-0.003321732270885835</v>
+      </c>
+      <c r="Q24">
+        <v>-0.0034873334334948815</v>
+      </c>
+      <c r="R24">
+        <v>-0.001760955861341986</v>
+      </c>
+      <c r="S24">
+        <v>-0.003465429394507107</v>
+      </c>
+      <c r="T24">
+        <v>-0.0035828098564641051</v>
+      </c>
+      <c r="U24">
+        <v>-0.0036288100415798573</v>
+      </c>
+      <c r="V24">
+        <v>-0.00030721928869568917</v>
+      </c>
+      <c r="W24">
+        <v>0.00038014457003501291</v>
+      </c>
+      <c r="X24">
+        <v>0.001055500915242993</v>
+      </c>
+      <c r="Y24">
+        <v>0.040411949032238777</v>
       </c>
     </row>
   </sheetData>
@@ -3972,68 +6249,550 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:C43"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="B1" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="C1" s="12" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="B2" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="C2" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="B3" s="17" t="s">
+        <v>62</v>
+      </c>
+      <c r="C3" s="18">
+        <v>-0.35122706167694562</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="19" t="s">
+        <v>59</v>
+      </c>
+      <c r="B4" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4" s="21">
+        <v>0.8937067770233802</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="B5" s="23" t="s">
+        <v>47</v>
+      </c>
+      <c r="C5" s="24">
+        <v>-0.012666405975215914</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="25" t="s">
+        <v>59</v>
+      </c>
+      <c r="B6" s="26" t="s">
+        <v>63</v>
+      </c>
+      <c r="C6" s="27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="28" t="s">
+        <v>59</v>
+      </c>
+      <c r="B7" s="29" t="s">
+        <v>64</v>
+      </c>
+      <c r="C7" s="30">
+        <v>0.29259596485483275</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="31" t="s">
+        <v>59</v>
+      </c>
+      <c r="B8" s="32" t="s">
+        <v>65</v>
+      </c>
+      <c r="C8" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="34" t="s">
+        <v>59</v>
+      </c>
+      <c r="B9" s="35" t="s">
+        <v>66</v>
+      </c>
+      <c r="C9" s="36">
+        <v>0.486102158385816</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="37" t="s">
+        <v>59</v>
+      </c>
+      <c r="B10" s="38" t="s">
+        <v>67</v>
+      </c>
+      <c r="C10" s="39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="40" t="s">
+        <v>59</v>
+      </c>
+      <c r="B11" s="41" t="s">
+        <v>68</v>
+      </c>
+      <c r="C11" s="42">
+        <v>0.40007154815243884</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="43" t="s">
+        <v>59</v>
+      </c>
+      <c r="B12" s="44" t="s">
+        <v>69</v>
+      </c>
+      <c r="C12" s="45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="46" t="s">
+        <v>59</v>
+      </c>
+      <c r="B13" s="47" t="s">
+        <v>70</v>
+      </c>
+      <c r="C13" s="48">
+        <v>0.15550177013700275</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="49" t="s">
+        <v>59</v>
+      </c>
+      <c r="B14" s="50" t="s">
+        <v>71</v>
+      </c>
+      <c r="C14" s="51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="52" t="s">
+        <v>59</v>
+      </c>
+      <c r="B15" s="53" t="s">
+        <v>72</v>
+      </c>
+      <c r="C15" s="54">
+        <v>0.32248867507780776</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="55" t="s">
+        <v>59</v>
+      </c>
+      <c r="B16" s="56" t="s">
+        <v>73</v>
+      </c>
+      <c r="C16" s="57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="58" t="s">
+        <v>59</v>
+      </c>
+      <c r="B17" s="59" t="s">
+        <v>74</v>
+      </c>
+      <c r="C17" s="60">
+        <v>0.045148461696831642</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="61" t="s">
+        <v>59</v>
+      </c>
+      <c r="B18" s="62" t="s">
+        <v>75</v>
+      </c>
+      <c r="C18" s="63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="64" t="s">
+        <v>59</v>
+      </c>
+      <c r="B19" s="65" t="s">
+        <v>76</v>
+      </c>
+      <c r="C19" s="66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="67" t="s">
+        <v>59</v>
+      </c>
+      <c r="B20" s="68" t="s">
+        <v>36</v>
+      </c>
+      <c r="C20" s="69">
+        <v>0.021535792779736385</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="70" t="s">
+        <v>59</v>
+      </c>
+      <c r="B21" s="71" t="s">
+        <v>39</v>
+      </c>
+      <c r="C21" s="72">
+        <v>-0.071367498930058559</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="73" t="s">
+        <v>59</v>
+      </c>
+      <c r="B22" s="74" t="s">
+        <v>77</v>
+      </c>
+      <c r="C22" s="75">
+        <v>-12.604449226554603</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="76" t="s">
+        <v>60</v>
+      </c>
+      <c r="B23" s="77" t="s">
+        <v>61</v>
+      </c>
+      <c r="C23" s="78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="79" t="s">
+        <v>60</v>
+      </c>
+      <c r="B24" s="80" t="s">
+        <v>62</v>
+      </c>
+      <c r="C24" s="81">
+        <v>-0.35122706167694573</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="82" t="s">
+        <v>60</v>
+      </c>
+      <c r="B25" s="83" t="s">
+        <v>21</v>
+      </c>
+      <c r="C25" s="84">
+        <v>0.71544520020009572</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="85" t="s">
+        <v>60</v>
+      </c>
+      <c r="B26" s="86" t="s">
+        <v>47</v>
+      </c>
+      <c r="C26" s="87">
+        <v>-0.010050128997704024</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="88" t="s">
+        <v>60</v>
+      </c>
+      <c r="B27" s="89" t="s">
+        <v>63</v>
+      </c>
+      <c r="C27" s="90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="91" t="s">
+        <v>60</v>
+      </c>
+      <c r="B28" s="92" t="s">
+        <v>64</v>
+      </c>
+      <c r="C28" s="93">
+        <v>0.29259596485483286</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="94" t="s">
+        <v>60</v>
+      </c>
+      <c r="B29" s="95" t="s">
+        <v>65</v>
+      </c>
+      <c r="C29" s="96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="97" t="s">
+        <v>60</v>
+      </c>
+      <c r="B30" s="98" t="s">
+        <v>66</v>
+      </c>
+      <c r="C30" s="99">
+        <v>0.48610215838581611</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="100" t="s">
+        <v>60</v>
+      </c>
+      <c r="B31" s="101" t="s">
+        <v>67</v>
+      </c>
+      <c r="C31" s="102">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="103" t="s">
+        <v>60</v>
+      </c>
+      <c r="B32" s="104" t="s">
+        <v>68</v>
+      </c>
+      <c r="C32" s="105">
+        <v>0.40007154815243895</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="106" t="s">
+        <v>60</v>
+      </c>
+      <c r="B33" s="107" t="s">
+        <v>69</v>
+      </c>
+      <c r="C33" s="108">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="109" t="s">
+        <v>60</v>
+      </c>
+      <c r="B34" s="110" t="s">
+        <v>70</v>
+      </c>
+      <c r="C34" s="111">
+        <v>0.38880775015687302</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="112" t="s">
+        <v>60</v>
+      </c>
+      <c r="B35" s="113" t="s">
+        <v>71</v>
+      </c>
+      <c r="C35" s="114">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="115" t="s">
+        <v>60</v>
+      </c>
+      <c r="B36" s="116" t="s">
+        <v>72</v>
+      </c>
+      <c r="C36" s="117">
+        <v>0.32248867507780787</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="118" t="s">
+        <v>60</v>
+      </c>
+      <c r="B37" s="119" t="s">
+        <v>73</v>
+      </c>
+      <c r="C37" s="120">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="121" t="s">
+        <v>60</v>
+      </c>
+      <c r="B38" s="122" t="s">
+        <v>74</v>
+      </c>
+      <c r="C38" s="123">
+        <v>0.045148461696831656</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="124" t="s">
+        <v>60</v>
+      </c>
+      <c r="B39" s="125" t="s">
+        <v>75</v>
+      </c>
+      <c r="C39" s="126">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="127" t="s">
+        <v>60</v>
+      </c>
+      <c r="B40" s="128" t="s">
+        <v>76</v>
+      </c>
+      <c r="C40" s="129">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="130" t="s">
+        <v>60</v>
+      </c>
+      <c r="B41" s="131" t="s">
+        <v>36</v>
+      </c>
+      <c r="C41" s="132">
+        <v>0.021535792779736392</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="133" t="s">
+        <v>60</v>
+      </c>
+      <c r="B42" s="134" t="s">
+        <v>39</v>
+      </c>
+      <c r="C42" s="135">
+        <v>-0.071367498930058573</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="136" t="s">
+        <v>60</v>
+      </c>
+      <c r="B43" s="137" t="s">
+        <v>77</v>
+      </c>
+      <c r="C43" s="138">
+        <v>-11.711916678161582</v>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:R17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="B1" t="s">
-        <v>54</v>
+        <v>19</v>
       </c>
       <c r="C1" t="s">
-        <v>61</v>
+        <v>80</v>
       </c>
       <c r="D1" t="s">
-        <v>62</v>
+        <v>81</v>
       </c>
       <c r="E1" t="s">
-        <v>63</v>
+        <v>82</v>
       </c>
       <c r="F1" t="s">
-        <v>64</v>
+        <v>83</v>
       </c>
       <c r="G1" t="s">
-        <v>65</v>
+        <v>84</v>
       </c>
       <c r="H1" t="s">
-        <v>66</v>
+        <v>85</v>
       </c>
       <c r="I1" t="s">
-        <v>67</v>
+        <v>86</v>
       </c>
       <c r="J1" t="s">
-        <v>68</v>
+        <v>87</v>
       </c>
       <c r="K1" t="s">
-        <v>69</v>
+        <v>88</v>
       </c>
       <c r="L1" t="s">
-        <v>70</v>
+        <v>89</v>
       </c>
       <c r="M1" t="s">
-        <v>71</v>
+        <v>90</v>
       </c>
       <c r="N1" t="s">
-        <v>72</v>
+        <v>91</v>
       </c>
       <c r="O1" t="s">
-        <v>73</v>
+        <v>92</v>
       </c>
       <c r="P1" t="s">
-        <v>74</v>
+        <v>93</v>
       </c>
       <c r="Q1" t="s">
-        <v>75</v>
+        <v>94</v>
       </c>
       <c r="R1" t="s">
-        <v>76</v>
+        <v>95</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>61</v>
+        <v>80</v>
       </c>
       <c r="B2">
         <v>-0.35122706167694562</v>
@@ -4089,7 +6848,7 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>62</v>
+        <v>81</v>
       </c>
       <c r="B3">
         <v>0.8937067770233802</v>
@@ -4145,7 +6904,7 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>63</v>
+        <v>82</v>
       </c>
       <c r="B4">
         <v>-0.012666405975215914</v>
@@ -4201,7 +6960,7 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>64</v>
+        <v>83</v>
       </c>
       <c r="B5">
         <v>0.29259596485483275</v>
@@ -4257,7 +7016,7 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>65</v>
+        <v>84</v>
       </c>
       <c r="B6">
         <v>0.486102158385816</v>
@@ -4313,7 +7072,7 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>66</v>
+        <v>85</v>
       </c>
       <c r="B7">
         <v>0.40007154815243884</v>
@@ -4369,7 +7128,7 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>67</v>
+        <v>86</v>
       </c>
       <c r="B8">
         <v>0.15550177013700275</v>
@@ -4425,7 +7184,7 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>68</v>
+        <v>87</v>
       </c>
       <c r="B9">
         <v>0.32248867507780776</v>
@@ -4481,7 +7240,7 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>69</v>
+        <v>88</v>
       </c>
       <c r="B10">
         <v>0.045148461696831642</v>
@@ -4537,7 +7296,7 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>70</v>
+        <v>89</v>
       </c>
       <c r="B11">
         <v>0.021535792779736385</v>
@@ -4593,7 +7352,7 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>71</v>
+        <v>90</v>
       </c>
       <c r="B12">
         <v>-0.071367498930058559</v>
@@ -4649,7 +7408,7 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>72</v>
+        <v>91</v>
       </c>
       <c r="B13">
         <v>-12.604449226554603</v>
@@ -4705,7 +7464,7 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>73</v>
+        <v>92</v>
       </c>
       <c r="B14">
         <v>0.71544520020009572</v>
@@ -4761,7 +7520,7 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>74</v>
+        <v>93</v>
       </c>
       <c r="B15">
         <v>-0.010050128997704024</v>
@@ -4817,7 +7576,7 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>75</v>
+        <v>94</v>
       </c>
       <c r="B16">
         <v>0.38880775015687302</v>
@@ -4873,7 +7632,7 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>76</v>
+        <v>95</v>
       </c>
       <c r="B17">
         <v>-11.711916678161582</v>

--- a/input/ES/reg_education.xlsx
+++ b/input/ES/reg_education.xlsx
@@ -10,157 +10,180 @@
     <sheet name="Gof" sheetId="2" r:id="rId4"/>
     <sheet name="E1a" sheetId="3" r:id="rId5"/>
     <sheet name="E1b" sheetId="4" r:id="rId6"/>
-    <sheet name="E2a_raw" sheetId="5" r:id="rId7"/>
-    <sheet name="E2a" sheetId="6" r:id="rId8"/>
+    <sheet name="E2a" sheetId="5" r:id="rId7"/>
   </sheets>
   <calcPr calcId="125725" fullCalcOnLoad="true"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="250" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="167" uniqueCount="82">
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>Authors:</t>
+  </si>
+  <si>
+    <t>Last edit:</t>
+  </si>
+  <si>
+    <t>Process:</t>
+  </si>
+  <si>
+    <t>E1a</t>
+  </si>
+  <si>
+    <t>E1b</t>
+  </si>
+  <si>
+    <t>E2</t>
+  </si>
+  <si>
+    <t>E2a_raw</t>
+  </si>
+  <si>
+    <t>Notes:</t>
+  </si>
+  <si>
+    <t>Modelparametersgoverningproje</t>
+  </si>
+  <si>
+    <t>Ashley Burdett, Aleksandra Kolndrekaj</t>
+  </si>
+  <si>
+    <t>07 Oct. 2026 AK</t>
+  </si>
   <si>
     <t>Description:</t>
   </si>
   <si>
-    <t>Model parameters governing projection of education status</t>
-  </si>
-  <si>
-    <t>Authors:</t>
-  </si>
-  <si>
-    <t>Ashley Burdett, Aleksandra Kolndrekaj</t>
-  </si>
-  <si>
-    <t>Last edit:</t>
-  </si>
-  <si>
-    <t>07 Oct. 2026 AK</t>
-  </si>
-  <si>
-    <t>Process:</t>
-  </si>
-  <si>
-    <t>E1a</t>
-  </si>
-  <si>
     <t>Probit regression estimates of exiting education</t>
   </si>
   <si>
-    <t>E1b</t>
-  </si>
-  <si>
     <t>Probit regression estimates of returning to education</t>
   </si>
   <si>
-    <t>E2</t>
-  </si>
-  <si>
     <t>Generalized ordered logit regression estimates of education attainment - individuals aged 16+ exiting education in t.</t>
   </si>
   <si>
-    <t>E2a_raw</t>
-  </si>
-  <si>
     <t>Raw generalized ordered logit regression estimates of education attainment - individuals aged 16+ exiting education. Useful for the 'Gologit predictor' file.</t>
   </si>
   <si>
-    <t>Notes:</t>
-  </si>
-  <si>
     <t>Regions: ES1 =  Noroeste , ES2 = Noreste , ES3 = Madrid , ES4 =  Centro , ES5 = Este , ES6=  Sur , ES7 = ,  Canarias.</t>
   </si>
   <si>
-    <t>Goodness of fit</t>
+    <t>Goodnessoffit</t>
+  </si>
+  <si>
+    <t>E1a - Remain in education</t>
+  </si>
+  <si>
+    <t>Pseudo R-squared</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>E1b - Return to education</t>
+  </si>
+  <si>
+    <t>E2 - Education attainment</t>
+  </si>
+  <si>
+    <t>B</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>D</t>
+  </si>
+  <si>
+    <t>E</t>
+  </si>
+  <si>
+    <t>Chi^2</t>
+  </si>
+  <si>
+    <t>Log likelihood</t>
+  </si>
+  <si>
+    <t>F</t>
   </si>
   <si>
     <t>REGRESSOR</t>
   </si>
   <si>
+    <t>Dgn</t>
+  </si>
+  <si>
+    <t>Dag</t>
+  </si>
+  <si>
+    <t>Dag16</t>
+  </si>
+  <si>
+    <t>Dag_knot23</t>
+  </si>
+  <si>
+    <t>Dag_knot26</t>
+  </si>
+  <si>
+    <t>Ded_L1</t>
+  </si>
+  <si>
+    <t>Parents_ypnb_Q2_L1</t>
+  </si>
+  <si>
+    <t>Parents_ypnb_Q3_L1</t>
+  </si>
+  <si>
+    <t>Parents_ypnb_Q4_L1</t>
+  </si>
+  <si>
+    <t>Parents_ypnb_Q5_L1</t>
+  </si>
+  <si>
+    <t>ES1</t>
+  </si>
+  <si>
+    <t>ES2</t>
+  </si>
+  <si>
+    <t>ES3</t>
+  </si>
+  <si>
+    <t>ES4</t>
+  </si>
+  <si>
+    <t>ES5</t>
+  </si>
+  <si>
+    <t>ES6</t>
+  </si>
+  <si>
+    <t>Year_transformed</t>
+  </si>
+  <si>
+    <t>Y2020</t>
+  </si>
+  <si>
+    <t>Y2021</t>
+  </si>
+  <si>
+    <t>Y2022</t>
+  </si>
+  <si>
+    <t>Y2023</t>
+  </si>
+  <si>
+    <t>Constant</t>
+  </si>
+  <si>
     <t>COEFFICIENT</t>
   </si>
   <si>
-    <t>Dgn</t>
-  </si>
-  <si>
-    <t>Dag</t>
-  </si>
-  <si>
-    <t>Dag16</t>
-  </si>
-  <si>
-    <t>Dag_knot23</t>
-  </si>
-  <si>
-    <t>Dag_knot26</t>
-  </si>
-  <si>
-    <t>Ded_L1</t>
-  </si>
-  <si>
-    <t>Parents_ypnb_Q2_L1</t>
-  </si>
-  <si>
-    <t>Parents_ypnb_Q3_L1</t>
-  </si>
-  <si>
-    <t>Parents_ypnb_Q4_L1</t>
-  </si>
-  <si>
-    <t>Parents_ypnb_Q5_L1</t>
-  </si>
-  <si>
-    <t>ES1</t>
-  </si>
-  <si>
-    <t>ES2</t>
-  </si>
-  <si>
-    <t>ES3</t>
-  </si>
-  <si>
-    <t>ES4</t>
-  </si>
-  <si>
-    <t>ES5</t>
-  </si>
-  <si>
-    <t>ES6</t>
-  </si>
-  <si>
-    <t>Year_transformed</t>
-  </si>
-  <si>
-    <t>Y2020</t>
-  </si>
-  <si>
-    <t>Y2021</t>
-  </si>
-  <si>
-    <t>Y2022</t>
-  </si>
-  <si>
-    <t>Y2023</t>
-  </si>
-  <si>
-    <t>Constant</t>
-  </si>
-  <si>
-    <t>E1a - Remain in education</t>
-  </si>
-  <si>
-    <t>Pseudo R-squared</t>
-  </si>
-  <si>
-    <t>N</t>
-  </si>
-  <si>
-    <t>Chi^2</t>
-  </si>
-  <si>
-    <t>Log likelihood</t>
-  </si>
-  <si>
     <t>Dag_sq</t>
   </si>
   <si>
@@ -194,72 +217,6 @@
     <t>Parents_known_Ydses_Q5_L1</t>
   </si>
   <si>
-    <t>E1b - Return to education</t>
-  </si>
-  <si>
-    <t>Low</t>
-  </si>
-  <si>
-    <t>Medium</t>
-  </si>
-  <si>
-    <t>0b.Dgn</t>
-  </si>
-  <si>
-    <t>1.Dgn</t>
-  </si>
-  <si>
-    <t>0b.ES1</t>
-  </si>
-  <si>
-    <t>1.ES1</t>
-  </si>
-  <si>
-    <t>0b.ES2</t>
-  </si>
-  <si>
-    <t>1.ES2</t>
-  </si>
-  <si>
-    <t>0b.ES3</t>
-  </si>
-  <si>
-    <t>1.ES3</t>
-  </si>
-  <si>
-    <t>0b.ES4</t>
-  </si>
-  <si>
-    <t>1.ES4</t>
-  </si>
-  <si>
-    <t>0b.ES5</t>
-  </si>
-  <si>
-    <t>1.ES5</t>
-  </si>
-  <si>
-    <t>0b.ES6</t>
-  </si>
-  <si>
-    <t>1.ES6</t>
-  </si>
-  <si>
-    <t>0b.ES7</t>
-  </si>
-  <si>
-    <t>1o.ES7</t>
-  </si>
-  <si>
-    <t>_cons</t>
-  </si>
-  <si>
-    <t>y1</t>
-  </si>
-  <si>
-    <t>CATEGORY</t>
-  </si>
-  <si>
     <t>Dgn_</t>
   </si>
   <si>
@@ -306,625 +263,16 @@
   </si>
   <si>
     <t>Constant_Medium</t>
-  </si>
-  <si>
-    <t>E2 - Education attainment</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <fonts count="150">
+  <fonts count="1">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
     </font>
   </fonts>
   <fills count="2">
@@ -935,7 +283,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="140">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -943,1541 +291,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="140">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="2" fontId="19" fillId="0" borderId="10" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="2" fontId="20" fillId="0" borderId="11" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="2" fontId="21" fillId="0" borderId="12" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="2" fontId="22" fillId="0" borderId="13" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="2" fontId="23" fillId="0" borderId="14" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="2" fontId="24" fillId="0" borderId="15" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="2" fontId="25" fillId="0" borderId="16" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="2" fontId="26" fillId="0" borderId="17" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="2" fontId="27" fillId="0" borderId="18" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="2" fontId="28" fillId="0" borderId="19" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="2" fontId="29" fillId="0" borderId="20" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="2" fontId="30" fillId="0" borderId="21" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="2" fontId="31" fillId="0" borderId="22" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="2" fontId="32" fillId="0" borderId="23" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="2" fontId="33" fillId="0" borderId="24" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="2" fontId="34" fillId="0" borderId="25" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="2" fontId="35" fillId="0" borderId="26" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="2" fontId="36" fillId="0" borderId="27" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="2" fontId="37" fillId="0" borderId="28" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="2" fontId="38" fillId="0" borderId="29" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="2" fontId="39" fillId="0" borderId="30" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="2" fontId="40" fillId="0" borderId="31" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="2" fontId="41" fillId="0" borderId="32" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="2" fontId="42" fillId="0" borderId="33" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="2" fontId="43" fillId="0" borderId="34" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="2" fontId="44" fillId="0" borderId="35" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="2" fontId="45" fillId="0" borderId="36" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="2" fontId="46" fillId="0" borderId="37" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="2" fontId="47" fillId="0" borderId="38" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="2" fontId="48" fillId="0" borderId="39" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="2" fontId="49" fillId="0" borderId="40" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="2" fontId="50" fillId="0" borderId="41" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="2" fontId="51" fillId="0" borderId="42" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="2" fontId="52" fillId="0" borderId="43" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="2" fontId="53" fillId="0" borderId="44" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="2" fontId="54" fillId="0" borderId="45" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="2" fontId="55" fillId="0" borderId="46" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="2" fontId="56" fillId="0" borderId="47" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="2" fontId="57" fillId="0" borderId="48" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="2" fontId="58" fillId="0" borderId="49" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="2" fontId="59" fillId="0" borderId="50" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="2" fontId="60" fillId="0" borderId="51" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="2" fontId="61" fillId="0" borderId="52" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="2" fontId="62" fillId="0" borderId="53" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="2" fontId="63" fillId="0" borderId="54" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="2" fontId="64" fillId="0" borderId="55" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="2" fontId="65" fillId="0" borderId="56" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="2" fontId="66" fillId="0" borderId="57" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="2" fontId="67" fillId="0" borderId="58" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="2" fontId="68" fillId="0" borderId="59" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="2" fontId="69" fillId="0" borderId="60" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="2" fontId="70" fillId="0" borderId="61" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="2" fontId="71" fillId="0" borderId="62" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="2" fontId="72" fillId="0" borderId="63" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="2" fontId="73" fillId="0" borderId="64" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="2" fontId="74" fillId="0" borderId="65" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="2" fontId="75" fillId="0" borderId="66" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="2" fontId="76" fillId="0" borderId="67" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="2" fontId="77" fillId="0" borderId="68" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="2" fontId="78" fillId="0" borderId="69" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="2" fontId="79" fillId="0" borderId="70" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="2" fontId="80" fillId="0" borderId="71" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="2" fontId="81" fillId="0" borderId="72" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="2" fontId="82" fillId="0" borderId="73" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="2" fontId="83" fillId="0" borderId="74" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="2" fontId="84" fillId="0" borderId="75" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="2" fontId="85" fillId="0" borderId="76" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="2" fontId="86" fillId="0" borderId="77" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="2" fontId="87" fillId="0" borderId="78" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="2" fontId="88" fillId="0" borderId="79" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="2" fontId="89" fillId="0" borderId="80" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="2" fontId="90" fillId="0" borderId="81" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="2" fontId="91" fillId="0" borderId="82" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="2" fontId="92" fillId="0" borderId="83" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="2" fontId="93" fillId="0" borderId="84" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="2" fontId="94" fillId="0" borderId="85" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="2" fontId="95" fillId="0" borderId="86" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="2" fontId="96" fillId="0" borderId="87" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="2" fontId="97" fillId="0" borderId="88" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="2" fontId="98" fillId="0" borderId="89" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="2" fontId="99" fillId="0" borderId="90" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="2" fontId="100" fillId="0" borderId="91" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="2" fontId="101" fillId="0" borderId="92" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="2" fontId="102" fillId="0" borderId="93" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="2" fontId="103" fillId="0" borderId="94" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="2" fontId="104" fillId="0" borderId="95" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="2" fontId="105" fillId="0" borderId="96" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="2" fontId="106" fillId="0" borderId="97" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="2" fontId="107" fillId="0" borderId="98" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="2" fontId="108" fillId="0" borderId="99" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="2" fontId="109" fillId="0" borderId="100" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="2" fontId="110" fillId="0" borderId="101" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="2" fontId="111" fillId="0" borderId="102" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="2" fontId="112" fillId="0" borderId="103" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="2" fontId="113" fillId="0" borderId="104" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="2" fontId="114" fillId="0" borderId="105" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="2" fontId="115" fillId="0" borderId="106" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="2" fontId="116" fillId="0" borderId="107" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="2" fontId="117" fillId="0" borderId="108" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="2" fontId="118" fillId="0" borderId="109" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="2" fontId="119" fillId="0" borderId="110" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="2" fontId="120" fillId="0" borderId="111" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="2" fontId="121" fillId="0" borderId="112" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="2" fontId="122" fillId="0" borderId="113" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="2" fontId="123" fillId="0" borderId="114" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="2" fontId="124" fillId="0" borderId="115" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="2" fontId="125" fillId="0" borderId="116" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="2" fontId="126" fillId="0" borderId="117" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="2" fontId="127" fillId="0" borderId="118" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="2" fontId="128" fillId="0" borderId="119" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="2" fontId="129" fillId="0" borderId="120" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="2" fontId="130" fillId="0" borderId="121" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="2" fontId="131" fillId="0" borderId="122" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="2" fontId="132" fillId="0" borderId="123" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="2" fontId="133" fillId="0" borderId="124" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="2" fontId="134" fillId="0" borderId="125" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="2" fontId="135" fillId="0" borderId="126" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="2" fontId="136" fillId="0" borderId="127" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="2" fontId="137" fillId="0" borderId="128" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="2" fontId="138" fillId="0" borderId="129" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="2" fontId="139" fillId="0" borderId="130" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="2" fontId="140" fillId="0" borderId="131" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="2" fontId="141" fillId="0" borderId="132" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="2" fontId="142" fillId="0" borderId="133" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="2" fontId="143" fillId="0" borderId="134" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="2" fontId="144" fillId="0" borderId="135" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="2" fontId="145" fillId="0" borderId="136" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="2" fontId="146" fillId="0" borderId="137" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="2" fontId="147" fillId="0" borderId="138" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="149" fillId="0" borderId="139" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2491,75 +310,75 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="s">
+      <c r="B2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
         <v>2</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>0</v>
+      <c r="B5" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="6" t="s">
-        <v>15</v>
+      <c r="A11" t="s">
+        <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -2572,24 +391,51 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="7" t="s">
-        <v>17</v>
-      </c>
+      <c r="A1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="B2"/>
+      <c r="C2"/>
+      <c r="D2"/>
+      <c r="F2"/>
     </row>
     <row r="3">
-      <c r="A3" s="8" t="s">
-        <v>42</v>
-      </c>
+      <c r="A3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B3"/>
+      <c r="C3"/>
+      <c r="D3"/>
+      <c r="F3"/>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="B4">
         <v>0.12672954670656989</v>
       </c>
+      <c r="C4"/>
+      <c r="D4"/>
       <c r="E4" t="s">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="F4">
         <v>1823.9152379507227</v>
@@ -2597,32 +443,46 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>44</v>
+        <v>21</v>
       </c>
       <c r="B5">
         <v>25554</v>
       </c>
+      <c r="C5"/>
+      <c r="D5"/>
       <c r="E5" t="s">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="F5">
         <v>-15943565.892963625</v>
       </c>
     </row>
+    <row r="6">
+      <c r="B6"/>
+      <c r="C6"/>
+      <c r="D6"/>
+      <c r="F6"/>
+    </row>
     <row r="7">
-      <c r="A7" s="9" t="s">
-        <v>58</v>
-      </c>
+      <c r="A7" t="s">
+        <v>22</v>
+      </c>
+      <c r="B7"/>
+      <c r="C7"/>
+      <c r="D7"/>
+      <c r="F7"/>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="B8">
         <v>0.57222806617156152</v>
       </c>
+      <c r="C8"/>
+      <c r="D8"/>
       <c r="E8" t="s">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="F8">
         <v>4428.8387179836263</v>
@@ -2630,32 +490,46 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>44</v>
+        <v>21</v>
       </c>
       <c r="B9">
         <v>192146</v>
       </c>
+      <c r="C9"/>
+      <c r="D9"/>
       <c r="E9" t="s">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="F9">
         <v>-10735290.422776602</v>
       </c>
     </row>
+    <row r="10">
+      <c r="B10"/>
+      <c r="C10"/>
+      <c r="D10"/>
+      <c r="F10"/>
+    </row>
     <row r="11">
-      <c r="A11" s="139" t="s">
-        <v>96</v>
-      </c>
+      <c r="A11" t="s">
+        <v>23</v>
+      </c>
+      <c r="B11"/>
+      <c r="C11"/>
+      <c r="D11"/>
+      <c r="F11"/>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="B12">
         <v>0.18790239160332234</v>
       </c>
+      <c r="C12"/>
+      <c r="D12"/>
       <c r="E12" t="s">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="F12">
         <v>894.99991527980148</v>
@@ -2663,13 +537,15 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>44</v>
+        <v>21</v>
       </c>
       <c r="B13">
         <v>5852</v>
       </c>
+      <c r="C13"/>
+      <c r="D13"/>
       <c r="E13" t="s">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="F13">
         <v>-5187.4466404954601</v>
@@ -2686,81 +562,81 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="B1" t="s">
-        <v>19</v>
+        <v>54</v>
       </c>
       <c r="C1" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="D1" t="s">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="E1" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="F1" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="G1" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="H1" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="I1" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="J1" t="s">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="K1" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="L1" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="M1" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="N1" t="s">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="O1" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="P1" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="Q1" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="R1" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="S1" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="T1" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="U1" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="V1" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="W1" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="X1" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="B2">
         <v>-0.12402958755245555</v>
@@ -2834,7 +710,7 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="B3">
         <v>-0.17445775137089106</v>
@@ -2908,7 +784,7 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="B4">
         <v>-1.5246444450986871</v>
@@ -2982,7 +858,7 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="B5">
         <v>0.0060212345424837397</v>
@@ -3056,7 +932,7 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="B6">
         <v>0.23211445041900672</v>
@@ -3130,7 +1006,7 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="B7">
         <v>0.16609156248120502</v>
@@ -3204,7 +1080,7 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="B8">
         <v>0.18094009937598848</v>
@@ -3278,7 +1154,7 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="B9">
         <v>0.15079169649961585</v>
@@ -3352,7 +1228,7 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="B10">
         <v>0.25336598800425975</v>
@@ -3426,7 +1302,7 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="B11">
         <v>0.47168682346735069</v>
@@ -3500,7 +1376,7 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="B12">
         <v>-0.064225077405799663</v>
@@ -3574,7 +1450,7 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="B13">
         <v>-0.053450527445847676</v>
@@ -3648,7 +1524,7 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="B14">
         <v>-0.10180304151668637</v>
@@ -3722,7 +1598,7 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="B15">
         <v>-0.083597984689970053</v>
@@ -3796,7 +1672,7 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="B16">
         <v>-0.10969528036612212</v>
@@ -3870,7 +1746,7 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="B17">
         <v>-0.070885848105694038</v>
@@ -3944,7 +1820,7 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="B18">
         <v>0.021044188223740153</v>
@@ -4018,7 +1894,7 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="B19">
         <v>-0.26849540360030261</v>
@@ -4092,7 +1968,7 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="B20">
         <v>0.3375039634777845</v>
@@ -4166,7 +2042,7 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="B21">
         <v>0.41799970214751148</v>
@@ -4240,7 +2116,7 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="B22">
         <v>0.26847735648289772</v>
@@ -4314,7 +2190,7 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="B23">
         <v>3.8752198822121309</v>
@@ -4397,84 +2273,84 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="B1" t="s">
-        <v>19</v>
+        <v>54</v>
       </c>
       <c r="C1" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="D1" t="s">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="E1" t="s">
+        <v>55</v>
+      </c>
+      <c r="F1" t="s">
+        <v>56</v>
+      </c>
+      <c r="G1" t="s">
+        <v>57</v>
+      </c>
+      <c r="H1" t="s">
+        <v>58</v>
+      </c>
+      <c r="I1" t="s">
+        <v>59</v>
+      </c>
+      <c r="J1" t="s">
+        <v>60</v>
+      </c>
+      <c r="K1" t="s">
+        <v>61</v>
+      </c>
+      <c r="L1" t="s">
+        <v>62</v>
+      </c>
+      <c r="M1" t="s">
+        <v>63</v>
+      </c>
+      <c r="N1" t="s">
+        <v>64</v>
+      </c>
+      <c r="O1" t="s">
+        <v>65</v>
+      </c>
+      <c r="P1" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>43</v>
+      </c>
+      <c r="R1" t="s">
+        <v>44</v>
+      </c>
+      <c r="S1" t="s">
+        <v>45</v>
+      </c>
+      <c r="T1" t="s">
+        <v>46</v>
+      </c>
+      <c r="U1" t="s">
         <v>47</v>
       </c>
-      <c r="F1" t="s">
+      <c r="V1" t="s">
         <v>48</v>
       </c>
-      <c r="G1" t="s">
-        <v>49</v>
-      </c>
-      <c r="H1" t="s">
+      <c r="W1" t="s">
         <v>50</v>
       </c>
-      <c r="I1" t="s">
+      <c r="X1" t="s">
         <v>51</v>
       </c>
-      <c r="J1" t="s">
-        <v>52</v>
-      </c>
-      <c r="K1" t="s">
+      <c r="Y1" t="s">
         <v>53</v>
-      </c>
-      <c r="L1" t="s">
-        <v>54</v>
-      </c>
-      <c r="M1" t="s">
-        <v>55</v>
-      </c>
-      <c r="N1" t="s">
-        <v>56</v>
-      </c>
-      <c r="O1" t="s">
-        <v>57</v>
-      </c>
-      <c r="P1" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>31</v>
-      </c>
-      <c r="R1" t="s">
-        <v>32</v>
-      </c>
-      <c r="S1" t="s">
-        <v>33</v>
-      </c>
-      <c r="T1" t="s">
-        <v>34</v>
-      </c>
-      <c r="U1" t="s">
-        <v>35</v>
-      </c>
-      <c r="V1" t="s">
-        <v>36</v>
-      </c>
-      <c r="W1" t="s">
-        <v>38</v>
-      </c>
-      <c r="X1" t="s">
-        <v>39</v>
-      </c>
-      <c r="Y1" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="B2">
         <v>-0.10074103147263815</v>
@@ -4551,7 +2427,7 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="B3">
         <v>-0.26647018991946842</v>
@@ -4628,7 +2504,7 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="B4">
         <v>0.002487791905325045</v>
@@ -4705,7 +2581,7 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="B5">
         <v>-0.51459734600652374</v>
@@ -4782,7 +2658,7 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="B6">
         <v>0.0026625266723272378</v>
@@ -4859,7 +2735,7 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="B7">
         <v>-0.4749901687863809</v>
@@ -4936,7 +2812,7 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="B8">
         <v>0.88240068225383161</v>
@@ -5013,7 +2889,7 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="B9">
         <v>0.50862489515676512</v>
@@ -5090,7 +2966,7 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="B10">
         <v>0.062824125321721921</v>
@@ -5167,7 +3043,7 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="B11">
         <v>0.20507627275525495</v>
@@ -5244,7 +3120,7 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="B12">
         <v>0.56588094236109443</v>
@@ -5321,7 +3197,7 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="B13">
         <v>0.40372331919932747</v>
@@ -5398,7 +3274,7 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="B14">
         <v>0.52558481720123407</v>
@@ -5475,7 +3351,7 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="B15">
         <v>0.03599476316905309</v>
@@ -5552,7 +3428,7 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="B16">
         <v>0.044258403960604147</v>
@@ -5629,7 +3505,7 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="B17">
         <v>0.092221804718539482</v>
@@ -5706,7 +3582,7 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="B18">
         <v>-0.094789889994195659</v>
@@ -5783,7 +3659,7 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="B19">
         <v>-0.0073717591759501792</v>
@@ -5860,7 +3736,7 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="B20">
         <v>-0.088340340959206676</v>
@@ -5937,7 +3813,7 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="B21">
         <v>0.0042459895358568948</v>
@@ -6014,7 +3890,7 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="B22">
         <v>0.1680229012196536</v>
@@ -6091,7 +3967,7 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="B23">
         <v>0.0049283868603328951</v>
@@ -6168,7 +4044,7 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="B24">
         <v>3.1475096552301176</v>
@@ -6249,550 +4125,68 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C43"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="B1" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="C1" s="12" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="13" t="s">
-        <v>59</v>
-      </c>
-      <c r="B2" s="14" t="s">
-        <v>61</v>
-      </c>
-      <c r="C2" s="15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="16" t="s">
-        <v>59</v>
-      </c>
-      <c r="B3" s="17" t="s">
-        <v>62</v>
-      </c>
-      <c r="C3" s="18">
-        <v>-0.35122706167694562</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="19" t="s">
-        <v>59</v>
-      </c>
-      <c r="B4" s="20" t="s">
-        <v>21</v>
-      </c>
-      <c r="C4" s="21">
-        <v>0.8937067770233802</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="22" t="s">
-        <v>59</v>
-      </c>
-      <c r="B5" s="23" t="s">
-        <v>47</v>
-      </c>
-      <c r="C5" s="24">
-        <v>-0.012666405975215914</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="25" t="s">
-        <v>59</v>
-      </c>
-      <c r="B6" s="26" t="s">
-        <v>63</v>
-      </c>
-      <c r="C6" s="27">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="28" t="s">
-        <v>59</v>
-      </c>
-      <c r="B7" s="29" t="s">
-        <v>64</v>
-      </c>
-      <c r="C7" s="30">
-        <v>0.29259596485483275</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="31" t="s">
-        <v>59</v>
-      </c>
-      <c r="B8" s="32" t="s">
-        <v>65</v>
-      </c>
-      <c r="C8" s="33">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="34" t="s">
-        <v>59</v>
-      </c>
-      <c r="B9" s="35" t="s">
-        <v>66</v>
-      </c>
-      <c r="C9" s="36">
-        <v>0.486102158385816</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="37" t="s">
-        <v>59</v>
-      </c>
-      <c r="B10" s="38" t="s">
-        <v>67</v>
-      </c>
-      <c r="C10" s="39">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="40" t="s">
-        <v>59</v>
-      </c>
-      <c r="B11" s="41" t="s">
-        <v>68</v>
-      </c>
-      <c r="C11" s="42">
-        <v>0.40007154815243884</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="43" t="s">
-        <v>59</v>
-      </c>
-      <c r="B12" s="44" t="s">
-        <v>69</v>
-      </c>
-      <c r="C12" s="45">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="46" t="s">
-        <v>59</v>
-      </c>
-      <c r="B13" s="47" t="s">
-        <v>70</v>
-      </c>
-      <c r="C13" s="48">
-        <v>0.15550177013700275</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="49" t="s">
-        <v>59</v>
-      </c>
-      <c r="B14" s="50" t="s">
-        <v>71</v>
-      </c>
-      <c r="C14" s="51">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="52" t="s">
-        <v>59</v>
-      </c>
-      <c r="B15" s="53" t="s">
-        <v>72</v>
-      </c>
-      <c r="C15" s="54">
-        <v>0.32248867507780776</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="55" t="s">
-        <v>59</v>
-      </c>
-      <c r="B16" s="56" t="s">
-        <v>73</v>
-      </c>
-      <c r="C16" s="57">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="58" t="s">
-        <v>59</v>
-      </c>
-      <c r="B17" s="59" t="s">
-        <v>74</v>
-      </c>
-      <c r="C17" s="60">
-        <v>0.045148461696831642</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="61" t="s">
-        <v>59</v>
-      </c>
-      <c r="B18" s="62" t="s">
-        <v>75</v>
-      </c>
-      <c r="C18" s="63">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="64" t="s">
-        <v>59</v>
-      </c>
-      <c r="B19" s="65" t="s">
-        <v>76</v>
-      </c>
-      <c r="C19" s="66">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="67" t="s">
-        <v>59</v>
-      </c>
-      <c r="B20" s="68" t="s">
-        <v>36</v>
-      </c>
-      <c r="C20" s="69">
-        <v>0.021535792779736385</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="70" t="s">
-        <v>59</v>
-      </c>
-      <c r="B21" s="71" t="s">
-        <v>39</v>
-      </c>
-      <c r="C21" s="72">
-        <v>-0.071367498930058559</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="73" t="s">
-        <v>59</v>
-      </c>
-      <c r="B22" s="74" t="s">
-        <v>77</v>
-      </c>
-      <c r="C22" s="75">
-        <v>-12.604449226554603</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="76" t="s">
-        <v>60</v>
-      </c>
-      <c r="B23" s="77" t="s">
-        <v>61</v>
-      </c>
-      <c r="C23" s="78">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="79" t="s">
-        <v>60</v>
-      </c>
-      <c r="B24" s="80" t="s">
-        <v>62</v>
-      </c>
-      <c r="C24" s="81">
-        <v>-0.35122706167694573</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="82" t="s">
-        <v>60</v>
-      </c>
-      <c r="B25" s="83" t="s">
-        <v>21</v>
-      </c>
-      <c r="C25" s="84">
-        <v>0.71544520020009572</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="85" t="s">
-        <v>60</v>
-      </c>
-      <c r="B26" s="86" t="s">
-        <v>47</v>
-      </c>
-      <c r="C26" s="87">
-        <v>-0.010050128997704024</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="88" t="s">
-        <v>60</v>
-      </c>
-      <c r="B27" s="89" t="s">
-        <v>63</v>
-      </c>
-      <c r="C27" s="90">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="91" t="s">
-        <v>60</v>
-      </c>
-      <c r="B28" s="92" t="s">
-        <v>64</v>
-      </c>
-      <c r="C28" s="93">
-        <v>0.29259596485483286</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="94" t="s">
-        <v>60</v>
-      </c>
-      <c r="B29" s="95" t="s">
-        <v>65</v>
-      </c>
-      <c r="C29" s="96">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="97" t="s">
-        <v>60</v>
-      </c>
-      <c r="B30" s="98" t="s">
-        <v>66</v>
-      </c>
-      <c r="C30" s="99">
-        <v>0.48610215838581611</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="100" t="s">
-        <v>60</v>
-      </c>
-      <c r="B31" s="101" t="s">
-        <v>67</v>
-      </c>
-      <c r="C31" s="102">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="103" t="s">
-        <v>60</v>
-      </c>
-      <c r="B32" s="104" t="s">
-        <v>68</v>
-      </c>
-      <c r="C32" s="105">
-        <v>0.40007154815243895</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="106" t="s">
-        <v>60</v>
-      </c>
-      <c r="B33" s="107" t="s">
-        <v>69</v>
-      </c>
-      <c r="C33" s="108">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="109" t="s">
-        <v>60</v>
-      </c>
-      <c r="B34" s="110" t="s">
-        <v>70</v>
-      </c>
-      <c r="C34" s="111">
-        <v>0.38880775015687302</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="112" t="s">
-        <v>60</v>
-      </c>
-      <c r="B35" s="113" t="s">
-        <v>71</v>
-      </c>
-      <c r="C35" s="114">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="115" t="s">
-        <v>60</v>
-      </c>
-      <c r="B36" s="116" t="s">
-        <v>72</v>
-      </c>
-      <c r="C36" s="117">
-        <v>0.32248867507780787</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="118" t="s">
-        <v>60</v>
-      </c>
-      <c r="B37" s="119" t="s">
-        <v>73</v>
-      </c>
-      <c r="C37" s="120">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="121" t="s">
-        <v>60</v>
-      </c>
-      <c r="B38" s="122" t="s">
-        <v>74</v>
-      </c>
-      <c r="C38" s="123">
-        <v>0.045148461696831656</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="124" t="s">
-        <v>60</v>
-      </c>
-      <c r="B39" s="125" t="s">
-        <v>75</v>
-      </c>
-      <c r="C39" s="126">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="127" t="s">
-        <v>60</v>
-      </c>
-      <c r="B40" s="128" t="s">
-        <v>76</v>
-      </c>
-      <c r="C40" s="129">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="130" t="s">
-        <v>60</v>
-      </c>
-      <c r="B41" s="131" t="s">
-        <v>36</v>
-      </c>
-      <c r="C41" s="132">
-        <v>0.021535792779736392</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="133" t="s">
-        <v>60</v>
-      </c>
-      <c r="B42" s="134" t="s">
-        <v>39</v>
-      </c>
-      <c r="C42" s="135">
-        <v>-0.071367498930058573</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="136" t="s">
-        <v>60</v>
-      </c>
-      <c r="B43" s="137" t="s">
-        <v>77</v>
-      </c>
-      <c r="C43" s="138">
-        <v>-11.711916678161582</v>
-      </c>
-    </row>
-  </sheetData>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:R17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="B1" t="s">
-        <v>19</v>
+        <v>54</v>
       </c>
       <c r="C1" t="s">
+        <v>66</v>
+      </c>
+      <c r="D1" t="s">
+        <v>67</v>
+      </c>
+      <c r="E1" t="s">
+        <v>68</v>
+      </c>
+      <c r="F1" t="s">
+        <v>69</v>
+      </c>
+      <c r="G1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H1" t="s">
+        <v>71</v>
+      </c>
+      <c r="I1" t="s">
+        <v>72</v>
+      </c>
+      <c r="J1" t="s">
+        <v>73</v>
+      </c>
+      <c r="K1" t="s">
+        <v>74</v>
+      </c>
+      <c r="L1" t="s">
+        <v>75</v>
+      </c>
+      <c r="M1" t="s">
+        <v>76</v>
+      </c>
+      <c r="N1" t="s">
+        <v>77</v>
+      </c>
+      <c r="O1" t="s">
+        <v>78</v>
+      </c>
+      <c r="P1" t="s">
+        <v>79</v>
+      </c>
+      <c r="Q1" t="s">
         <v>80</v>
       </c>
-      <c r="D1" t="s">
+      <c r="R1" t="s">
         <v>81</v>
-      </c>
-      <c r="E1" t="s">
-        <v>82</v>
-      </c>
-      <c r="F1" t="s">
-        <v>83</v>
-      </c>
-      <c r="G1" t="s">
-        <v>84</v>
-      </c>
-      <c r="H1" t="s">
-        <v>85</v>
-      </c>
-      <c r="I1" t="s">
-        <v>86</v>
-      </c>
-      <c r="J1" t="s">
-        <v>87</v>
-      </c>
-      <c r="K1" t="s">
-        <v>88</v>
-      </c>
-      <c r="L1" t="s">
-        <v>89</v>
-      </c>
-      <c r="M1" t="s">
-        <v>90</v>
-      </c>
-      <c r="N1" t="s">
-        <v>91</v>
-      </c>
-      <c r="O1" t="s">
-        <v>92</v>
-      </c>
-      <c r="P1" t="s">
-        <v>93</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>94</v>
-      </c>
-      <c r="R1" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="B2">
         <v>-0.35122706167694562</v>
@@ -6848,7 +4242,7 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>81</v>
+        <v>67</v>
       </c>
       <c r="B3">
         <v>0.8937067770233802</v>
@@ -6904,7 +4298,7 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="B4">
         <v>-0.012666405975215914</v>
@@ -6960,7 +4354,7 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>83</v>
+        <v>69</v>
       </c>
       <c r="B5">
         <v>0.29259596485483275</v>
@@ -7016,7 +4410,7 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>84</v>
+        <v>70</v>
       </c>
       <c r="B6">
         <v>0.486102158385816</v>
@@ -7072,7 +4466,7 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>85</v>
+        <v>71</v>
       </c>
       <c r="B7">
         <v>0.40007154815243884</v>
@@ -7128,7 +4522,7 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>86</v>
+        <v>72</v>
       </c>
       <c r="B8">
         <v>0.15550177013700275</v>
@@ -7184,7 +4578,7 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>87</v>
+        <v>73</v>
       </c>
       <c r="B9">
         <v>0.32248867507780776</v>
@@ -7240,7 +4634,7 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="B10">
         <v>0.045148461696831642</v>
@@ -7296,7 +4690,7 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="B11">
         <v>0.021535792779736385</v>
@@ -7352,7 +4746,7 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>90</v>
+        <v>76</v>
       </c>
       <c r="B12">
         <v>-0.071367498930058559</v>
@@ -7408,7 +4802,7 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>91</v>
+        <v>77</v>
       </c>
       <c r="B13">
         <v>-12.604449226554603</v>
@@ -7464,7 +4858,7 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>92</v>
+        <v>78</v>
       </c>
       <c r="B14">
         <v>0.71544520020009572</v>
@@ -7520,7 +4914,7 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>93</v>
+        <v>79</v>
       </c>
       <c r="B15">
         <v>-0.010050128997704024</v>
@@ -7576,7 +4970,7 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="B16">
         <v>0.38880775015687302</v>
@@ -7632,7 +5026,7 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="B17">
         <v>-11.711916678161582</v>
